--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\Sauvegarde\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9517918-31DF-44E9-B551-C1569F143B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B5A879-5E2D-45BF-9D40-89A843F7209F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="809">
   <si>
     <t>Artistes / Titres</t>
   </si>
@@ -2466,6 +2466,9 @@
   </si>
   <si>
     <t>https://www.discogs.com/fr/release/1739214-I-Level-Give-Me</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/fr/release/2177186-Surface-Lately/image/SW1hZ2U6OTk4MTU5NTk=</t>
   </si>
 </sst>
 </file>
@@ -2784,7 +2787,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2868,7 +2871,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1"/>
@@ -3251,7 +3253,7 @@
     <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52.140625" style="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="48" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="47" customWidth="1"/>
     <col min="7" max="7" width="2.140625" style="20" customWidth="1"/>
     <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.5703125" style="20" customWidth="1"/>
@@ -3261,31 +3263,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="88" t="s">
+      <c r="B1" s="87" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="86" t="s">
+      <c r="D1" s="85" t="s">
         <v>304</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="82" t="s">
+      <c r="F1" s="81" t="s">
         <v>547</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="76" t="s">
         <v>266</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="I1" s="74"/>
+      <c r="I1" s="73"/>
       <c r="J1" s="8" t="s">
         <v>5</v>
       </c>
@@ -3295,18 +3297,18 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="78"/>
+      <c r="A2" s="80"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="77"/>
       <c r="H2" s="10">
         <f>SUM(G3:G562)</f>
         <v>506</v>
       </c>
-      <c r="I2" s="75"/>
+      <c r="I2" s="74"/>
       <c r="J2" s="11">
         <f>SUM(I3:I562)</f>
         <v>301</v>
@@ -3327,7 +3329,7 @@
         <v>559</v>
       </c>
       <c r="E3" s="31"/>
-      <c r="F3" s="46" t="s">
+      <c r="F3" s="45" t="s">
         <v>558</v>
       </c>
       <c r="G3" s="20">
@@ -3363,7 +3365,7 @@
         <v>422</v>
       </c>
       <c r="E4" s="30"/>
-      <c r="F4" s="44"/>
+      <c r="F4" s="43"/>
       <c r="G4" s="20">
         <f t="shared" ref="G4:G69" si="2">COUNTA(A4)</f>
         <v>1</v>
@@ -3397,7 +3399,7 @@
         <v>467</v>
       </c>
       <c r="E5" s="30"/>
-      <c r="F5" s="44"/>
+      <c r="F5" s="43"/>
       <c r="G5" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3420,18 +3422,18 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="58" t="s">
         <v>521</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="62" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="61" t="s">
         <v>430</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="62">
         <v>22</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="69" t="s">
         <v>548</v>
       </c>
       <c r="G6" s="20">
@@ -3469,7 +3471,7 @@
       <c r="E7" s="30">
         <v>18</v>
       </c>
-      <c r="F7" s="44"/>
+      <c r="F7" s="43"/>
       <c r="G7" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3501,7 +3503,7 @@
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="30"/>
-      <c r="F8" s="44"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3537,7 +3539,7 @@
       <c r="E9" s="30">
         <v>15</v>
       </c>
-      <c r="F9" s="44"/>
+      <c r="F9" s="43"/>
       <c r="G9" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3560,20 +3562,20 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="58" t="s">
         <v>522</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="59" t="s">
         <v>520</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="62" t="s">
+      <c r="C10" s="60"/>
+      <c r="D10" s="61" t="s">
         <v>430</v>
       </c>
-      <c r="E10" s="63">
+      <c r="E10" s="62">
         <v>9</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="69" t="s">
         <v>549</v>
       </c>
       <c r="G10" s="20">
@@ -3599,7 +3601,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="14"/>
       <c r="E11" s="31"/>
-      <c r="F11" s="46" t="s">
+      <c r="F11" s="45" t="s">
         <v>560</v>
       </c>
       <c r="G11" s="20">
@@ -3631,7 +3633,7 @@
       <c r="C12" s="3"/>
       <c r="D12" s="14"/>
       <c r="E12" s="31"/>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="45" t="s">
         <v>561</v>
       </c>
       <c r="G12" s="20">
@@ -3663,7 +3665,7 @@
       <c r="C13" s="3"/>
       <c r="D13" s="14"/>
       <c r="E13" s="31"/>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="45" t="s">
         <v>562</v>
       </c>
       <c r="G13" s="20">
@@ -3697,7 +3699,7 @@
         <v>564</v>
       </c>
       <c r="E14" s="31"/>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="45" t="s">
         <v>563</v>
       </c>
       <c r="G14" s="20">
@@ -3729,7 +3731,7 @@
       <c r="C15" s="3"/>
       <c r="D15" s="14"/>
       <c r="E15" s="31"/>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="45" t="s">
         <v>563</v>
       </c>
       <c r="G15" s="20">
@@ -3753,7 +3755,7 @@
       <c r="C16" s="3"/>
       <c r="D16" s="14"/>
       <c r="E16" s="31"/>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="45" t="s">
         <v>565</v>
       </c>
       <c r="G16" s="20">
@@ -3791,7 +3793,7 @@
       <c r="E17" s="30">
         <v>13.5</v>
       </c>
-      <c r="F17" s="44"/>
+      <c r="F17" s="43"/>
       <c r="G17" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3825,7 +3827,7 @@
         <v>422</v>
       </c>
       <c r="E18" s="30"/>
-      <c r="F18" s="44"/>
+      <c r="F18" s="43"/>
       <c r="G18" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3857,7 +3859,7 @@
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="30"/>
-      <c r="F19" s="44"/>
+      <c r="F19" s="43"/>
       <c r="G19" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3893,7 +3895,7 @@
       <c r="E20" s="30">
         <v>13.5</v>
       </c>
-      <c r="F20" s="44"/>
+      <c r="F20" s="43"/>
       <c r="G20" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3927,7 +3929,7 @@
         <v>422</v>
       </c>
       <c r="E21" s="30"/>
-      <c r="F21" s="44"/>
+      <c r="F21" s="43"/>
       <c r="G21" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3961,7 +3963,7 @@
         <v>566</v>
       </c>
       <c r="E22" s="30"/>
-      <c r="F22" s="44"/>
+      <c r="F22" s="43"/>
       <c r="G22" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -3991,7 +3993,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="14"/>
       <c r="E23" s="31"/>
-      <c r="F23" s="46" t="s">
+      <c r="F23" s="45" t="s">
         <v>567</v>
       </c>
       <c r="G23" s="20">
@@ -4025,7 +4027,7 @@
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="30"/>
-      <c r="F24" s="47"/>
+      <c r="F24" s="46"/>
       <c r="G24" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4059,7 +4061,7 @@
         <v>569</v>
       </c>
       <c r="E25" s="30"/>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="46" t="s">
         <v>568</v>
       </c>
       <c r="G25" s="20">
@@ -4091,7 +4093,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="14"/>
       <c r="E26" s="31"/>
-      <c r="F26" s="46" t="s">
+      <c r="F26" s="45" t="s">
         <v>570</v>
       </c>
       <c r="G26" s="20">
@@ -4125,7 +4127,7 @@
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="30"/>
-      <c r="F27" s="44"/>
+      <c r="F27" s="43"/>
       <c r="G27" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4155,7 +4157,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="14"/>
       <c r="E28" s="31"/>
-      <c r="F28" s="46" t="s">
+      <c r="F28" s="45" t="s">
         <v>571</v>
       </c>
       <c r="G28" s="20">
@@ -4191,7 +4193,7 @@
         <v>422</v>
       </c>
       <c r="E29" s="30"/>
-      <c r="F29" s="44"/>
+      <c r="F29" s="43"/>
       <c r="G29" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4223,7 +4225,7 @@
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="30"/>
-      <c r="F30" s="44"/>
+      <c r="F30" s="43"/>
       <c r="G30" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4253,7 +4255,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="14"/>
       <c r="E31" s="31"/>
-      <c r="F31" s="46" t="s">
+      <c r="F31" s="45" t="s">
         <v>572</v>
       </c>
       <c r="G31" s="20">
@@ -4287,7 +4289,7 @@
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="30"/>
-      <c r="F32" s="44"/>
+      <c r="F32" s="43"/>
       <c r="G32" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4319,7 +4321,7 @@
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="30"/>
-      <c r="F33" s="44"/>
+      <c r="F33" s="43"/>
       <c r="G33" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4353,7 +4355,7 @@
         <v>422</v>
       </c>
       <c r="E34" s="30"/>
-      <c r="F34" s="44"/>
+      <c r="F34" s="43"/>
       <c r="G34" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4385,7 +4387,7 @@
         <v>574</v>
       </c>
       <c r="E35" s="31"/>
-      <c r="F35" s="46" t="s">
+      <c r="F35" s="45" t="s">
         <v>573</v>
       </c>
       <c r="G35" s="20">
@@ -4423,7 +4425,7 @@
       <c r="E36" s="30">
         <v>19</v>
       </c>
-      <c r="F36" s="44"/>
+      <c r="F36" s="43"/>
       <c r="G36" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4457,7 +4459,7 @@
         <v>428</v>
       </c>
       <c r="E37" s="30"/>
-      <c r="F37" s="44"/>
+      <c r="F37" s="43"/>
       <c r="G37" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4491,7 +4493,7 @@
       <c r="E38" s="31">
         <v>8</v>
       </c>
-      <c r="F38" s="46" t="s">
+      <c r="F38" s="45" t="s">
         <v>575</v>
       </c>
       <c r="G38" s="20">
@@ -4525,7 +4527,7 @@
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="30"/>
-      <c r="F39" s="44"/>
+      <c r="F39" s="43"/>
       <c r="G39" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4561,7 +4563,7 @@
       <c r="E40" s="30">
         <v>11</v>
       </c>
-      <c r="F40" s="47" t="s">
+      <c r="F40" s="46" t="s">
         <v>550</v>
       </c>
       <c r="G40" s="20">
@@ -4599,7 +4601,7 @@
       <c r="E41" s="30">
         <v>15</v>
       </c>
-      <c r="F41" s="44"/>
+      <c r="F41" s="43"/>
       <c r="G41" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4629,7 +4631,7 @@
       <c r="C42" s="3"/>
       <c r="D42" s="14"/>
       <c r="E42" s="31"/>
-      <c r="F42" s="46" t="s">
+      <c r="F42" s="45" t="s">
         <v>577</v>
       </c>
       <c r="G42" s="20">
@@ -4663,7 +4665,7 @@
         <v>429</v>
       </c>
       <c r="E43" s="31"/>
-      <c r="F43" s="46" t="s">
+      <c r="F43" s="45" t="s">
         <v>803</v>
       </c>
       <c r="G43" s="20">
@@ -4701,7 +4703,7 @@
       <c r="E44" s="30">
         <v>6.73</v>
       </c>
-      <c r="F44" s="44"/>
+      <c r="F44" s="43"/>
       <c r="G44" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4733,7 +4735,7 @@
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="30"/>
-      <c r="F45" s="47" t="s">
+      <c r="F45" s="46" t="s">
         <v>796</v>
       </c>
       <c r="G45" s="20">
@@ -4759,7 +4761,7 @@
       </c>
       <c r="D46" s="13"/>
       <c r="E46" s="30"/>
-      <c r="F46" s="44"/>
+      <c r="F46" s="43"/>
       <c r="G46" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4789,7 +4791,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="14"/>
       <c r="E47" s="31"/>
-      <c r="F47" s="46" t="s">
+      <c r="F47" s="45" t="s">
         <v>578</v>
       </c>
       <c r="G47" s="20">
@@ -4827,7 +4829,7 @@
       <c r="E48" s="30">
         <v>13.5</v>
       </c>
-      <c r="F48" s="47" t="s">
+      <c r="F48" s="46" t="s">
         <v>551</v>
       </c>
       <c r="G48" s="20">
@@ -4865,7 +4867,7 @@
       <c r="E49" s="30">
         <v>12</v>
       </c>
-      <c r="F49" s="47" t="s">
+      <c r="F49" s="46" t="s">
         <v>553</v>
       </c>
       <c r="G49" s="20">
@@ -4903,7 +4905,7 @@
       <c r="E50" s="30">
         <v>15</v>
       </c>
-      <c r="F50" s="44"/>
+      <c r="F50" s="43"/>
       <c r="G50" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4935,7 +4937,7 @@
       </c>
       <c r="D51" s="13"/>
       <c r="E51" s="30"/>
-      <c r="F51" s="44"/>
+      <c r="F51" s="43"/>
       <c r="G51" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4971,7 +4973,7 @@
       <c r="E52" s="30">
         <v>23</v>
       </c>
-      <c r="F52" s="44"/>
+      <c r="F52" s="43"/>
       <c r="G52" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5001,7 +5003,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="14"/>
       <c r="E53" s="31"/>
-      <c r="F53" s="46" t="s">
+      <c r="F53" s="45" t="s">
         <v>579</v>
       </c>
       <c r="G53" s="20">
@@ -5027,7 +5029,7 @@
         <v>580</v>
       </c>
       <c r="E54" s="31"/>
-      <c r="F54" s="46" t="s">
+      <c r="F54" s="45" t="s">
         <v>582</v>
       </c>
       <c r="G54" s="20">
@@ -5057,7 +5059,7 @@
       <c r="E55" s="30">
         <v>14</v>
       </c>
-      <c r="F55" s="44"/>
+      <c r="F55" s="43"/>
       <c r="G55" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5089,7 +5091,7 @@
       </c>
       <c r="D56" s="13"/>
       <c r="E56" s="30"/>
-      <c r="F56" s="44"/>
+      <c r="F56" s="43"/>
       <c r="G56" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5121,7 +5123,7 @@
       </c>
       <c r="D57" s="13"/>
       <c r="E57" s="30"/>
-      <c r="F57" s="44"/>
+      <c r="F57" s="43"/>
       <c r="G57" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5157,7 +5159,7 @@
       <c r="E58" s="30">
         <v>25</v>
       </c>
-      <c r="F58" s="44"/>
+      <c r="F58" s="43"/>
       <c r="G58" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5189,7 +5191,7 @@
       </c>
       <c r="D59" s="13"/>
       <c r="E59" s="30"/>
-      <c r="F59" s="44"/>
+      <c r="F59" s="43"/>
       <c r="G59" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5219,7 +5221,7 @@
       <c r="C60" s="3"/>
       <c r="D60" s="14"/>
       <c r="E60" s="31"/>
-      <c r="F60" s="46" t="s">
+      <c r="F60" s="45" t="s">
         <v>583</v>
       </c>
       <c r="G60" s="20">
@@ -5253,7 +5255,7 @@
       </c>
       <c r="D61" s="13"/>
       <c r="E61" s="30"/>
-      <c r="F61" s="44"/>
+      <c r="F61" s="43"/>
       <c r="G61" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5287,7 +5289,7 @@
         <v>422</v>
       </c>
       <c r="E62" s="30"/>
-      <c r="F62" s="44"/>
+      <c r="F62" s="43"/>
       <c r="G62" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5317,7 +5319,7 @@
       <c r="C63" s="3"/>
       <c r="D63" s="14"/>
       <c r="E63" s="31"/>
-      <c r="F63" s="46" t="s">
+      <c r="F63" s="45" t="s">
         <v>797</v>
       </c>
       <c r="G63" s="20">
@@ -5355,7 +5357,7 @@
       <c r="E64" s="30">
         <v>37</v>
       </c>
-      <c r="F64" s="44"/>
+      <c r="F64" s="43"/>
       <c r="G64" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5387,7 +5389,7 @@
         <v>800</v>
       </c>
       <c r="E65" s="31"/>
-      <c r="F65" s="46" t="s">
+      <c r="F65" s="45" t="s">
         <v>799</v>
       </c>
       <c r="G65" s="20">
@@ -5421,7 +5423,7 @@
         <v>585</v>
       </c>
       <c r="E66" s="31"/>
-      <c r="F66" s="46" t="s">
+      <c r="F66" s="45" t="s">
         <v>584</v>
       </c>
       <c r="G66" s="20">
@@ -5453,7 +5455,7 @@
       <c r="C67" s="3"/>
       <c r="D67" s="14"/>
       <c r="E67" s="31"/>
-      <c r="F67" s="46" t="s">
+      <c r="F67" s="45" t="s">
         <v>587</v>
       </c>
       <c r="G67" s="20">
@@ -5487,7 +5489,7 @@
       </c>
       <c r="D68" s="13"/>
       <c r="E68" s="30"/>
-      <c r="F68" s="44"/>
+      <c r="F68" s="43"/>
       <c r="G68" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5523,7 +5525,7 @@
       <c r="E69" s="30">
         <v>17.690000000000001</v>
       </c>
-      <c r="F69" s="44"/>
+      <c r="F69" s="43"/>
       <c r="G69" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5547,7 +5549,7 @@
       </c>
       <c r="D70" s="13"/>
       <c r="E70" s="30"/>
-      <c r="F70" s="44"/>
+      <c r="F70" s="43"/>
       <c r="G70" s="20">
         <f t="shared" ref="G70:G134" si="6">COUNTA(A70)</f>
         <v>1</v>
@@ -5579,7 +5581,7 @@
       </c>
       <c r="D71" s="13"/>
       <c r="E71" s="30"/>
-      <c r="F71" s="44"/>
+      <c r="F71" s="43"/>
       <c r="G71" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -5609,7 +5611,7 @@
       <c r="C72" s="3"/>
       <c r="D72" s="14"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="46" t="s">
+      <c r="F72" s="45" t="s">
         <v>588</v>
       </c>
       <c r="G72" s="20">
@@ -5641,7 +5643,7 @@
       <c r="C73" s="3"/>
       <c r="D73" s="14"/>
       <c r="E73" s="31"/>
-      <c r="F73" s="46" t="s">
+      <c r="F73" s="45" t="s">
         <v>590</v>
       </c>
       <c r="G73" s="20">
@@ -5673,7 +5675,7 @@
       <c r="C74" s="3"/>
       <c r="D74" s="14"/>
       <c r="E74" s="31"/>
-      <c r="F74" s="46" t="s">
+      <c r="F74" s="45" t="s">
         <v>591</v>
       </c>
       <c r="G74" s="20">
@@ -5705,7 +5707,7 @@
       <c r="C75" s="3"/>
       <c r="D75" s="14"/>
       <c r="E75" s="31"/>
-      <c r="F75" s="46" t="s">
+      <c r="F75" s="45" t="s">
         <v>592</v>
       </c>
       <c r="G75" s="20">
@@ -5739,7 +5741,7 @@
       </c>
       <c r="D76" s="13"/>
       <c r="E76" s="30"/>
-      <c r="F76" s="44"/>
+      <c r="F76" s="43"/>
       <c r="G76" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -5771,7 +5773,7 @@
       </c>
       <c r="D77" s="13"/>
       <c r="E77" s="30"/>
-      <c r="F77" s="44"/>
+      <c r="F77" s="43"/>
       <c r="G77" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -5807,7 +5809,7 @@
       <c r="E78" s="30">
         <v>13</v>
       </c>
-      <c r="F78" s="44"/>
+      <c r="F78" s="43"/>
       <c r="G78" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -5837,7 +5839,7 @@
       <c r="C79" s="3"/>
       <c r="D79" s="14"/>
       <c r="E79" s="31"/>
-      <c r="F79" s="46" t="s">
+      <c r="F79" s="45" t="s">
         <v>593</v>
       </c>
       <c r="G79" s="20">
@@ -5873,7 +5875,7 @@
         <v>457</v>
       </c>
       <c r="E80" s="30"/>
-      <c r="F80" s="44"/>
+      <c r="F80" s="43"/>
       <c r="G80" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -5907,7 +5909,7 @@
         <v>457</v>
       </c>
       <c r="E81" s="30"/>
-      <c r="F81" s="44"/>
+      <c r="F81" s="43"/>
       <c r="G81" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -5937,7 +5939,7 @@
       <c r="C82" s="3"/>
       <c r="D82" s="14"/>
       <c r="E82" s="31"/>
-      <c r="F82" s="46" t="s">
+      <c r="F82" s="45" t="s">
         <v>594</v>
       </c>
       <c r="G82" s="20">
@@ -5969,7 +5971,7 @@
       <c r="C83" s="3"/>
       <c r="D83" s="14"/>
       <c r="E83" s="31"/>
-      <c r="F83" s="46" t="s">
+      <c r="F83" s="45" t="s">
         <v>595</v>
       </c>
       <c r="G83" s="20">
@@ -6003,7 +6005,7 @@
       </c>
       <c r="D84" s="13"/>
       <c r="E84" s="30"/>
-      <c r="F84" s="44"/>
+      <c r="F84" s="43"/>
       <c r="G84" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6039,7 +6041,7 @@
       <c r="E85" s="30">
         <v>10</v>
       </c>
-      <c r="F85" s="44"/>
+      <c r="F85" s="43"/>
       <c r="G85" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6071,7 +6073,7 @@
       </c>
       <c r="D86" s="13"/>
       <c r="E86" s="30"/>
-      <c r="F86" s="47"/>
+      <c r="F86" s="46"/>
       <c r="G86" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6103,7 +6105,7 @@
         <v>598</v>
       </c>
       <c r="E87" s="31"/>
-      <c r="F87" s="46" t="s">
+      <c r="F87" s="45" t="s">
         <v>599</v>
       </c>
       <c r="G87" s="20">
@@ -6135,7 +6137,7 @@
       <c r="C88" s="3"/>
       <c r="D88" s="14"/>
       <c r="E88" s="31"/>
-      <c r="F88" s="46" t="s">
+      <c r="F88" s="45" t="s">
         <v>596</v>
       </c>
       <c r="G88" s="20">
@@ -6167,7 +6169,7 @@
       <c r="C89" s="3"/>
       <c r="D89" s="14"/>
       <c r="E89" s="31"/>
-      <c r="F89" s="46" t="s">
+      <c r="F89" s="45" t="s">
         <v>600</v>
       </c>
       <c r="G89" s="20">
@@ -6199,7 +6201,7 @@
       <c r="C90" s="3"/>
       <c r="D90" s="14"/>
       <c r="E90" s="31"/>
-      <c r="F90" s="46" t="s">
+      <c r="F90" s="45" t="s">
         <v>601</v>
       </c>
       <c r="G90" s="20">
@@ -6231,7 +6233,7 @@
       <c r="C91" s="3"/>
       <c r="D91" s="14"/>
       <c r="E91" s="31"/>
-      <c r="F91" s="46" t="s">
+      <c r="F91" s="45" t="s">
         <v>602</v>
       </c>
       <c r="G91" s="20">
@@ -6265,7 +6267,7 @@
         <v>603</v>
       </c>
       <c r="E92" s="31"/>
-      <c r="F92" s="46" t="s">
+      <c r="F92" s="45" t="s">
         <v>801</v>
       </c>
       <c r="G92" s="20">
@@ -6303,7 +6305,7 @@
       <c r="E93" s="30">
         <v>35</v>
       </c>
-      <c r="F93" s="47"/>
+      <c r="F93" s="46"/>
       <c r="G93" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6339,7 +6341,7 @@
       <c r="E94" s="30">
         <v>20.74</v>
       </c>
-      <c r="F94" s="44"/>
+      <c r="F94" s="43"/>
       <c r="G94" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6371,7 +6373,7 @@
       </c>
       <c r="D95" s="13"/>
       <c r="E95" s="30"/>
-      <c r="F95" s="44"/>
+      <c r="F95" s="43"/>
       <c r="G95" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6403,7 +6405,7 @@
       </c>
       <c r="D96" s="13"/>
       <c r="E96" s="30"/>
-      <c r="F96" s="44"/>
+      <c r="F96" s="43"/>
       <c r="G96" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6435,7 +6437,7 @@
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="30"/>
-      <c r="F97" s="44"/>
+      <c r="F97" s="43"/>
       <c r="G97" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6467,7 +6469,7 @@
       </c>
       <c r="D98" s="13"/>
       <c r="E98" s="30"/>
-      <c r="F98" s="44"/>
+      <c r="F98" s="43"/>
       <c r="G98" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6503,7 +6505,7 @@
       <c r="E99" s="30">
         <v>18</v>
       </c>
-      <c r="F99" s="44"/>
+      <c r="F99" s="43"/>
       <c r="G99" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6535,7 +6537,7 @@
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="30"/>
-      <c r="F100" s="44"/>
+      <c r="F100" s="43"/>
       <c r="G100" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6558,18 +6560,18 @@
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" s="59" t="s">
+      <c r="A101" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="B101" s="60"/>
-      <c r="C101" s="61"/>
-      <c r="D101" s="62" t="s">
+      <c r="B101" s="59"/>
+      <c r="C101" s="60"/>
+      <c r="D101" s="61" t="s">
         <v>430</v>
       </c>
-      <c r="E101" s="63">
+      <c r="E101" s="62">
         <v>15</v>
       </c>
-      <c r="F101" s="70" t="s">
+      <c r="F101" s="69" t="s">
         <v>554</v>
       </c>
       <c r="G101" s="20">
@@ -6601,7 +6603,7 @@
       <c r="C102" s="35"/>
       <c r="D102" s="36"/>
       <c r="E102" s="37"/>
-      <c r="F102" s="71" t="s">
+      <c r="F102" s="70" t="s">
         <v>604</v>
       </c>
       <c r="G102" s="20">
@@ -6633,7 +6635,7 @@
       <c r="C103" s="3"/>
       <c r="D103" s="14"/>
       <c r="E103" s="31"/>
-      <c r="F103" s="46" t="s">
+      <c r="F103" s="45" t="s">
         <v>605</v>
       </c>
       <c r="G103" s="20">
@@ -6667,7 +6669,7 @@
       </c>
       <c r="D104" s="13"/>
       <c r="E104" s="30"/>
-      <c r="F104" s="44"/>
+      <c r="F104" s="43"/>
       <c r="G104" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6697,7 +6699,7 @@
       <c r="C105" s="3"/>
       <c r="D105" s="14"/>
       <c r="E105" s="31"/>
-      <c r="F105" s="46" t="s">
+      <c r="F105" s="45" t="s">
         <v>606</v>
       </c>
       <c r="G105" s="20">
@@ -6729,7 +6731,7 @@
       <c r="C106" s="3"/>
       <c r="D106" s="14"/>
       <c r="E106" s="31"/>
-      <c r="F106" s="46" t="s">
+      <c r="F106" s="45" t="s">
         <v>607</v>
       </c>
       <c r="G106" s="20">
@@ -6761,7 +6763,7 @@
       <c r="C107" s="3"/>
       <c r="D107" s="14"/>
       <c r="E107" s="31"/>
-      <c r="F107" s="46" t="s">
+      <c r="F107" s="45" t="s">
         <v>608</v>
       </c>
       <c r="G107" s="20">
@@ -6791,7 +6793,7 @@
       <c r="E108" s="30">
         <v>20</v>
       </c>
-      <c r="F108" s="44"/>
+      <c r="F108" s="43"/>
       <c r="G108" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6821,7 +6823,7 @@
       <c r="C109" s="3"/>
       <c r="D109" s="14"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="46" t="s">
+      <c r="F109" s="45" t="s">
         <v>609</v>
       </c>
       <c r="G109" s="20">
@@ -6855,7 +6857,7 @@
       </c>
       <c r="D110" s="13"/>
       <c r="E110" s="30"/>
-      <c r="F110" s="44"/>
+      <c r="F110" s="43"/>
       <c r="G110" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6885,7 +6887,7 @@
       <c r="C111" s="3"/>
       <c r="D111" s="14"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="46" t="s">
+      <c r="F111" s="45" t="s">
         <v>610</v>
       </c>
       <c r="G111" s="20">
@@ -6917,7 +6919,7 @@
       <c r="C112" s="3"/>
       <c r="D112" s="14"/>
       <c r="E112" s="31"/>
-      <c r="F112" s="46" t="s">
+      <c r="F112" s="45" t="s">
         <v>611</v>
       </c>
       <c r="G112" s="20">
@@ -6951,7 +6953,7 @@
       </c>
       <c r="D113" s="13"/>
       <c r="E113" s="30"/>
-      <c r="F113" s="44"/>
+      <c r="F113" s="43"/>
       <c r="G113" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -6987,7 +6989,7 @@
       <c r="E114" s="30">
         <v>15</v>
       </c>
-      <c r="F114" s="44">
+      <c r="F114" s="43">
         <v>23</v>
       </c>
       <c r="G114" s="20">
@@ -7023,7 +7025,7 @@
         <v>425</v>
       </c>
       <c r="E115" s="30"/>
-      <c r="F115" s="44"/>
+      <c r="F115" s="43"/>
       <c r="G115" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7053,7 +7055,7 @@
       <c r="C116" s="3"/>
       <c r="D116" s="14"/>
       <c r="E116" s="31"/>
-      <c r="F116" s="46" t="s">
+      <c r="F116" s="45" t="s">
         <v>613</v>
       </c>
       <c r="G116" s="20">
@@ -7091,7 +7093,7 @@
       <c r="E117" s="30">
         <v>7.63</v>
       </c>
-      <c r="F117" s="44"/>
+      <c r="F117" s="43"/>
       <c r="G117" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7127,7 +7129,7 @@
       <c r="E118" s="30">
         <v>25</v>
       </c>
-      <c r="F118" s="44"/>
+      <c r="F118" s="43"/>
       <c r="G118" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7161,7 +7163,7 @@
         <v>425</v>
       </c>
       <c r="E119" s="30"/>
-      <c r="F119" s="47"/>
+      <c r="F119" s="46"/>
       <c r="G119" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7191,7 +7193,7 @@
       <c r="C120" s="3"/>
       <c r="D120" s="14"/>
       <c r="E120" s="31"/>
-      <c r="F120" s="46" t="s">
+      <c r="F120" s="45" t="s">
         <v>612</v>
       </c>
       <c r="G120" s="20">
@@ -7225,7 +7227,7 @@
       </c>
       <c r="D121" s="13"/>
       <c r="E121" s="30"/>
-      <c r="F121" s="44"/>
+      <c r="F121" s="43"/>
       <c r="G121" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7255,7 +7257,7 @@
       <c r="C122" s="3"/>
       <c r="D122" s="14"/>
       <c r="E122" s="31"/>
-      <c r="F122" s="46" t="s">
+      <c r="F122" s="45" t="s">
         <v>614</v>
       </c>
       <c r="G122" s="20">
@@ -7293,7 +7295,7 @@
       <c r="E123" s="30">
         <v>17.54</v>
       </c>
-      <c r="F123" s="44"/>
+      <c r="F123" s="43"/>
       <c r="G123" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7329,7 +7331,7 @@
       <c r="E124" s="32">
         <v>39</v>
       </c>
-      <c r="F124" s="72" t="s">
+      <c r="F124" s="71" t="s">
         <v>616</v>
       </c>
       <c r="G124" s="20">
@@ -7361,7 +7363,7 @@
       <c r="C125" s="3"/>
       <c r="D125" s="14"/>
       <c r="E125" s="31"/>
-      <c r="F125" s="46" t="s">
+      <c r="F125" s="45" t="s">
         <v>615</v>
       </c>
       <c r="G125" s="20">
@@ -7397,7 +7399,7 @@
         <v>535</v>
       </c>
       <c r="E126" s="32"/>
-      <c r="F126" s="72" t="s">
+      <c r="F126" s="71" t="s">
         <v>617</v>
       </c>
       <c r="G126" s="20">
@@ -7433,7 +7435,7 @@
         <v>480</v>
       </c>
       <c r="E127" s="30"/>
-      <c r="F127" s="44"/>
+      <c r="F127" s="43"/>
       <c r="G127" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7467,7 +7469,7 @@
         <v>422</v>
       </c>
       <c r="E128" s="30"/>
-      <c r="F128" s="44"/>
+      <c r="F128" s="43"/>
       <c r="G128" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7491,7 +7493,7 @@
       </c>
       <c r="D129" s="13"/>
       <c r="E129" s="30"/>
-      <c r="F129" s="44"/>
+      <c r="F129" s="43"/>
       <c r="G129" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7523,7 +7525,7 @@
       </c>
       <c r="D130" s="13"/>
       <c r="E130" s="30"/>
-      <c r="F130" s="44"/>
+      <c r="F130" s="43"/>
       <c r="G130" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7559,7 +7561,7 @@
       <c r="E131" s="30">
         <v>25</v>
       </c>
-      <c r="F131" s="44"/>
+      <c r="F131" s="43"/>
       <c r="G131" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7591,7 +7593,7 @@
       </c>
       <c r="D132" s="13"/>
       <c r="E132" s="30"/>
-      <c r="F132" s="44"/>
+      <c r="F132" s="43"/>
       <c r="G132" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7623,7 +7625,7 @@
       </c>
       <c r="D133" s="13"/>
       <c r="E133" s="30"/>
-      <c r="F133" s="44"/>
+      <c r="F133" s="43"/>
       <c r="G133" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7659,7 +7661,7 @@
       <c r="E134" s="30">
         <v>29</v>
       </c>
-      <c r="F134" s="47" t="s">
+      <c r="F134" s="46" t="s">
         <v>555</v>
       </c>
       <c r="G134" s="20">
@@ -7697,7 +7699,7 @@
       <c r="E135" s="30">
         <v>15</v>
       </c>
-      <c r="F135" s="44"/>
+      <c r="F135" s="43"/>
       <c r="G135" s="20">
         <f t="shared" ref="G135:G199" si="10">COUNTA(A135)</f>
         <v>1</v>
@@ -7733,7 +7735,7 @@
       <c r="E136" s="30">
         <v>34</v>
       </c>
-      <c r="F136" s="44"/>
+      <c r="F136" s="43"/>
       <c r="G136" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -7755,7 +7757,7 @@
       <c r="C137" s="3"/>
       <c r="D137" s="14"/>
       <c r="E137" s="31"/>
-      <c r="F137" s="46" t="s">
+      <c r="F137" s="45" t="s">
         <v>618</v>
       </c>
       <c r="G137" s="20">
@@ -7787,7 +7789,7 @@
       <c r="C138" s="3"/>
       <c r="D138" s="14"/>
       <c r="E138" s="31"/>
-      <c r="F138" s="46" t="s">
+      <c r="F138" s="45" t="s">
         <v>619</v>
       </c>
       <c r="G138" s="20">
@@ -7819,7 +7821,7 @@
       <c r="C139" s="3"/>
       <c r="D139" s="14"/>
       <c r="E139" s="31"/>
-      <c r="F139" s="46" t="s">
+      <c r="F139" s="45" t="s">
         <v>620</v>
       </c>
       <c r="G139" s="20">
@@ -7851,7 +7853,7 @@
       <c r="C140" s="3"/>
       <c r="D140" s="14"/>
       <c r="E140" s="31"/>
-      <c r="F140" s="46" t="s">
+      <c r="F140" s="45" t="s">
         <v>622</v>
       </c>
       <c r="G140" s="20">
@@ -7875,7 +7877,7 @@
       <c r="C141" s="3"/>
       <c r="D141" s="14"/>
       <c r="E141" s="31"/>
-      <c r="F141" s="46" t="s">
+      <c r="F141" s="45" t="s">
         <v>623</v>
       </c>
       <c r="G141" s="20">
@@ -7907,7 +7909,7 @@
       <c r="C142" s="3"/>
       <c r="D142" s="14"/>
       <c r="E142" s="31"/>
-      <c r="F142" s="46" t="s">
+      <c r="F142" s="45" t="s">
         <v>624</v>
       </c>
       <c r="G142" s="20">
@@ -7945,7 +7947,7 @@
       <c r="E143" s="30">
         <v>19</v>
       </c>
-      <c r="F143" s="44"/>
+      <c r="F143" s="43"/>
       <c r="G143" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -7981,7 +7983,7 @@
       <c r="E144" s="30">
         <v>34</v>
       </c>
-      <c r="F144" s="44"/>
+      <c r="F144" s="43"/>
       <c r="G144" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8013,7 +8015,7 @@
       </c>
       <c r="D145" s="13"/>
       <c r="E145" s="30"/>
-      <c r="F145" s="44"/>
+      <c r="F145" s="43"/>
       <c r="G145" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8047,7 +8049,7 @@
         <v>627</v>
       </c>
       <c r="E146" s="30"/>
-      <c r="F146" s="47" t="s">
+      <c r="F146" s="46" t="s">
         <v>626</v>
       </c>
       <c r="G146" s="20">
@@ -8085,7 +8087,7 @@
       <c r="E147" s="30">
         <v>12</v>
       </c>
-      <c r="F147" s="44"/>
+      <c r="F147" s="43"/>
       <c r="G147" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8117,7 +8119,7 @@
         <v>629</v>
       </c>
       <c r="E148" s="31"/>
-      <c r="F148" s="46" t="s">
+      <c r="F148" s="45" t="s">
         <v>628</v>
       </c>
       <c r="G148" s="20">
@@ -8155,7 +8157,7 @@
       <c r="E149" s="30">
         <v>12</v>
       </c>
-      <c r="F149" s="44"/>
+      <c r="F149" s="43"/>
       <c r="G149" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8187,7 +8189,7 @@
       </c>
       <c r="D150" s="13"/>
       <c r="E150" s="30"/>
-      <c r="F150" s="44"/>
+      <c r="F150" s="43"/>
       <c r="G150" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8217,7 +8219,7 @@
       <c r="C151" s="3"/>
       <c r="D151" s="14"/>
       <c r="E151" s="31"/>
-      <c r="F151" s="46" t="s">
+      <c r="F151" s="45" t="s">
         <v>630</v>
       </c>
       <c r="G151" s="20">
@@ -8249,7 +8251,7 @@
       <c r="C152" s="3"/>
       <c r="D152" s="14"/>
       <c r="E152" s="31"/>
-      <c r="F152" s="46" t="s">
+      <c r="F152" s="45" t="s">
         <v>631</v>
       </c>
       <c r="G152" s="20">
@@ -8283,7 +8285,7 @@
       </c>
       <c r="D153" s="13"/>
       <c r="E153" s="30"/>
-      <c r="F153" s="44"/>
+      <c r="F153" s="43"/>
       <c r="G153" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8319,7 +8321,7 @@
       <c r="E154" s="30">
         <v>10.1</v>
       </c>
-      <c r="F154" s="44"/>
+      <c r="F154" s="43"/>
       <c r="G154" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8347,7 +8349,7 @@
       <c r="E155" s="30">
         <v>10</v>
       </c>
-      <c r="F155" s="44">
+      <c r="F155" s="43">
         <v>17</v>
       </c>
       <c r="G155" s="20">
@@ -8385,7 +8387,7 @@
       <c r="E156" s="30">
         <v>7.85</v>
       </c>
-      <c r="F156" s="44"/>
+      <c r="F156" s="43"/>
       <c r="G156" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8415,7 +8417,7 @@
       <c r="C157" s="3"/>
       <c r="D157" s="14"/>
       <c r="E157" s="31"/>
-      <c r="F157" s="46" t="s">
+      <c r="F157" s="45" t="s">
         <v>632</v>
       </c>
       <c r="G157" s="20">
@@ -8449,7 +8451,7 @@
       </c>
       <c r="D158" s="13"/>
       <c r="E158" s="30"/>
-      <c r="F158" s="44"/>
+      <c r="F158" s="43"/>
       <c r="G158" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8485,7 +8487,7 @@
       <c r="E159" s="30">
         <v>12</v>
       </c>
-      <c r="F159" s="44"/>
+      <c r="F159" s="43"/>
       <c r="G159" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8511,7 +8513,7 @@
         <v>430</v>
       </c>
       <c r="E160" s="30"/>
-      <c r="F160" s="44"/>
+      <c r="F160" s="43"/>
       <c r="G160" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8545,7 +8547,7 @@
         <v>470</v>
       </c>
       <c r="E161" s="30"/>
-      <c r="F161" s="44"/>
+      <c r="F161" s="43"/>
       <c r="G161" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8577,7 +8579,7 @@
         <v>633</v>
       </c>
       <c r="E162" s="31"/>
-      <c r="F162" s="46" t="s">
+      <c r="F162" s="45" t="s">
         <v>634</v>
       </c>
       <c r="G162" s="20">
@@ -8609,7 +8611,7 @@
       <c r="C163" s="3"/>
       <c r="D163" s="14"/>
       <c r="E163" s="31"/>
-      <c r="F163" s="46" t="s">
+      <c r="F163" s="45" t="s">
         <v>635</v>
       </c>
       <c r="G163" s="20">
@@ -8641,7 +8643,7 @@
       <c r="C164" s="3"/>
       <c r="D164" s="14"/>
       <c r="E164" s="31"/>
-      <c r="F164" s="46" t="s">
+      <c r="F164" s="45" t="s">
         <v>636</v>
       </c>
       <c r="G164" s="20">
@@ -8679,7 +8681,7 @@
       <c r="E165" s="30">
         <v>15</v>
       </c>
-      <c r="F165" s="44"/>
+      <c r="F165" s="43"/>
       <c r="G165" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8711,7 +8713,7 @@
       </c>
       <c r="D166" s="13"/>
       <c r="E166" s="30"/>
-      <c r="F166" s="44"/>
+      <c r="F166" s="43"/>
       <c r="G166" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8743,7 +8745,7 @@
       </c>
       <c r="D167" s="13"/>
       <c r="E167" s="30"/>
-      <c r="F167" s="44"/>
+      <c r="F167" s="43"/>
       <c r="G167" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8773,7 +8775,7 @@
       <c r="C168" s="3"/>
       <c r="D168" s="14"/>
       <c r="E168" s="31"/>
-      <c r="F168" s="46" t="s">
+      <c r="F168" s="45" t="s">
         <v>637</v>
       </c>
       <c r="G168" s="20">
@@ -8805,7 +8807,7 @@
       <c r="C169" s="3"/>
       <c r="D169" s="14"/>
       <c r="E169" s="31"/>
-      <c r="F169" s="46" t="s">
+      <c r="F169" s="45" t="s">
         <v>639</v>
       </c>
       <c r="G169" s="20">
@@ -8837,7 +8839,7 @@
       <c r="C170" s="3"/>
       <c r="D170" s="14"/>
       <c r="E170" s="31"/>
-      <c r="F170" s="46" t="s">
+      <c r="F170" s="45" t="s">
         <v>640</v>
       </c>
       <c r="G170" s="20">
@@ -8871,7 +8873,7 @@
       </c>
       <c r="D171" s="13"/>
       <c r="E171" s="30"/>
-      <c r="F171" s="44"/>
+      <c r="F171" s="43"/>
       <c r="G171" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8905,7 +8907,7 @@
         <v>422</v>
       </c>
       <c r="E172" s="30"/>
-      <c r="F172" s="44"/>
+      <c r="F172" s="43"/>
       <c r="G172" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8939,7 +8941,7 @@
         <v>524</v>
       </c>
       <c r="E173" s="30"/>
-      <c r="F173" s="44"/>
+      <c r="F173" s="43"/>
       <c r="G173" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8969,7 +8971,7 @@
       <c r="C174" s="3"/>
       <c r="D174" s="14"/>
       <c r="E174" s="31"/>
-      <c r="F174" s="46" t="s">
+      <c r="F174" s="45" t="s">
         <v>641</v>
       </c>
       <c r="G174" s="20">
@@ -9001,7 +9003,7 @@
       <c r="C175" s="3"/>
       <c r="D175" s="14"/>
       <c r="E175" s="31"/>
-      <c r="F175" s="46" t="s">
+      <c r="F175" s="45" t="s">
         <v>642</v>
       </c>
       <c r="G175" s="20">
@@ -9033,7 +9035,7 @@
       <c r="C176" s="3"/>
       <c r="D176" s="14"/>
       <c r="E176" s="31"/>
-      <c r="F176" s="46" t="s">
+      <c r="F176" s="45" t="s">
         <v>643</v>
       </c>
       <c r="G176" s="20">
@@ -9065,7 +9067,7 @@
       <c r="C177" s="3"/>
       <c r="D177" s="14"/>
       <c r="E177" s="31"/>
-      <c r="F177" s="46" t="s">
+      <c r="F177" s="45" t="s">
         <v>644</v>
       </c>
       <c r="G177" s="20">
@@ -9101,7 +9103,7 @@
         <v>422</v>
       </c>
       <c r="E178" s="30"/>
-      <c r="F178" s="44"/>
+      <c r="F178" s="43"/>
       <c r="G178" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9131,7 +9133,7 @@
       <c r="C179" s="3"/>
       <c r="D179" s="14"/>
       <c r="E179" s="31"/>
-      <c r="F179" s="46" t="s">
+      <c r="F179" s="45" t="s">
         <v>645</v>
       </c>
       <c r="G179" s="20">
@@ -9165,7 +9167,7 @@
       </c>
       <c r="D180" s="13"/>
       <c r="E180" s="30"/>
-      <c r="F180" s="44"/>
+      <c r="F180" s="43"/>
       <c r="G180" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9195,7 +9197,7 @@
       <c r="C181" s="3"/>
       <c r="D181" s="14"/>
       <c r="E181" s="31"/>
-      <c r="F181" s="46" t="s">
+      <c r="F181" s="45" t="s">
         <v>646</v>
       </c>
       <c r="G181" s="20">
@@ -9227,7 +9229,7 @@
       <c r="C182" s="3"/>
       <c r="D182" s="14"/>
       <c r="E182" s="31"/>
-      <c r="F182" s="46" t="s">
+      <c r="F182" s="45" t="s">
         <v>647</v>
       </c>
       <c r="G182" s="20">
@@ -9261,7 +9263,7 @@
       </c>
       <c r="D183" s="13"/>
       <c r="E183" s="30"/>
-      <c r="F183" s="44"/>
+      <c r="F183" s="43"/>
       <c r="G183" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9297,7 +9299,7 @@
       <c r="E184" s="30">
         <v>19</v>
       </c>
-      <c r="F184" s="44"/>
+      <c r="F184" s="43"/>
       <c r="G184" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9327,7 +9329,7 @@
       <c r="C185" s="3"/>
       <c r="D185" s="14"/>
       <c r="E185" s="31"/>
-      <c r="F185" s="46" t="s">
+      <c r="F185" s="45" t="s">
         <v>648</v>
       </c>
       <c r="G185" s="20">
@@ -9361,7 +9363,7 @@
       </c>
       <c r="D186" s="13"/>
       <c r="E186" s="30"/>
-      <c r="F186" s="44"/>
+      <c r="F186" s="43"/>
       <c r="G186" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9393,7 +9395,7 @@
         <v>307</v>
       </c>
       <c r="E187" s="31"/>
-      <c r="F187" s="46" t="s">
+      <c r="F187" s="45" t="s">
         <v>649</v>
       </c>
       <c r="G187" s="20">
@@ -9427,7 +9429,7 @@
       </c>
       <c r="D188" s="13"/>
       <c r="E188" s="30"/>
-      <c r="F188" s="44"/>
+      <c r="F188" s="43"/>
       <c r="G188" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9461,7 +9463,7 @@
         <v>489</v>
       </c>
       <c r="E189" s="30"/>
-      <c r="F189" s="44"/>
+      <c r="F189" s="43"/>
       <c r="G189" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9493,7 +9495,7 @@
       </c>
       <c r="D190" s="13"/>
       <c r="E190" s="30"/>
-      <c r="F190" s="44"/>
+      <c r="F190" s="43"/>
       <c r="G190" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9529,7 +9531,7 @@
       <c r="E191" s="30">
         <v>10.1</v>
       </c>
-      <c r="F191" s="47"/>
+      <c r="F191" s="46"/>
       <c r="G191" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9561,7 +9563,7 @@
       </c>
       <c r="D192" s="13"/>
       <c r="E192" s="30"/>
-      <c r="F192" s="44"/>
+      <c r="F192" s="43"/>
       <c r="G192" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9591,7 +9593,7 @@
       <c r="C193" s="3"/>
       <c r="D193" s="14"/>
       <c r="E193" s="31"/>
-      <c r="F193" s="46" t="s">
+      <c r="F193" s="45" t="s">
         <v>650</v>
       </c>
       <c r="G193" s="20">
@@ -9629,7 +9631,7 @@
       <c r="E194" s="30">
         <v>8</v>
       </c>
-      <c r="F194" s="44"/>
+      <c r="F194" s="43"/>
       <c r="G194" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9663,7 +9665,7 @@
         <v>422</v>
       </c>
       <c r="E195" s="30"/>
-      <c r="F195" s="44"/>
+      <c r="F195" s="43"/>
       <c r="G195" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9699,7 +9701,7 @@
       <c r="E196" s="30">
         <v>8</v>
       </c>
-      <c r="F196" s="47"/>
+      <c r="F196" s="46"/>
       <c r="G196" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9731,7 +9733,7 @@
       </c>
       <c r="D197" s="13"/>
       <c r="E197" s="30"/>
-      <c r="F197" s="44"/>
+      <c r="F197" s="43"/>
       <c r="G197" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9763,7 +9765,7 @@
       </c>
       <c r="D198" s="13"/>
       <c r="E198" s="30"/>
-      <c r="F198" s="44"/>
+      <c r="F198" s="43"/>
       <c r="G198" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9795,7 +9797,7 @@
       </c>
       <c r="D199" s="13"/>
       <c r="E199" s="30"/>
-      <c r="F199" s="44"/>
+      <c r="F199" s="43"/>
       <c r="G199" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -9831,7 +9833,7 @@
       <c r="E200" s="30">
         <v>12</v>
       </c>
-      <c r="F200" s="44"/>
+      <c r="F200" s="43"/>
       <c r="G200" s="20">
         <f t="shared" ref="G200:G265" si="15">COUNTA(A200)</f>
         <v>1</v>
@@ -9865,7 +9867,7 @@
         <v>513</v>
       </c>
       <c r="E201" s="30"/>
-      <c r="F201" s="44"/>
+      <c r="F201" s="43"/>
       <c r="G201" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -9899,7 +9901,7 @@
         <v>422</v>
       </c>
       <c r="E202" s="30"/>
-      <c r="F202" s="44"/>
+      <c r="F202" s="43"/>
       <c r="G202" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -9935,7 +9937,7 @@
       <c r="E203" s="30">
         <v>19</v>
       </c>
-      <c r="F203" s="44"/>
+      <c r="F203" s="43"/>
       <c r="G203" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -9967,7 +9969,7 @@
       </c>
       <c r="D204" s="13"/>
       <c r="E204" s="30"/>
-      <c r="F204" s="44"/>
+      <c r="F204" s="43"/>
       <c r="G204" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -9997,7 +9999,7 @@
       <c r="C205" s="3"/>
       <c r="D205" s="14"/>
       <c r="E205" s="31"/>
-      <c r="F205" s="46" t="s">
+      <c r="F205" s="45" t="s">
         <v>652</v>
       </c>
       <c r="G205" s="20">
@@ -10031,7 +10033,7 @@
       </c>
       <c r="D206" s="13"/>
       <c r="E206" s="30"/>
-      <c r="F206" s="44"/>
+      <c r="F206" s="43"/>
       <c r="G206" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10063,7 +10065,7 @@
       </c>
       <c r="D207" s="13"/>
       <c r="E207" s="30"/>
-      <c r="F207" s="44"/>
+      <c r="F207" s="43"/>
       <c r="G207" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10095,7 +10097,7 @@
       </c>
       <c r="D208" s="13"/>
       <c r="E208" s="30"/>
-      <c r="F208" s="47"/>
+      <c r="F208" s="46"/>
       <c r="G208" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10127,7 +10129,7 @@
       </c>
       <c r="D209" s="13"/>
       <c r="E209" s="30"/>
-      <c r="F209" s="44"/>
+      <c r="F209" s="43"/>
       <c r="G209" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10161,7 +10163,7 @@
         <v>544</v>
       </c>
       <c r="E210" s="30"/>
-      <c r="F210" s="44"/>
+      <c r="F210" s="43"/>
       <c r="G210" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10193,7 +10195,7 @@
       </c>
       <c r="D211" s="13"/>
       <c r="E211" s="30"/>
-      <c r="F211" s="44"/>
+      <c r="F211" s="43"/>
       <c r="G211" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10225,7 +10227,7 @@
       </c>
       <c r="D212" s="13"/>
       <c r="E212" s="30"/>
-      <c r="F212" s="44"/>
+      <c r="F212" s="43"/>
       <c r="G212" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10255,7 +10257,7 @@
       <c r="C213" s="3"/>
       <c r="D213" s="14"/>
       <c r="E213" s="31"/>
-      <c r="F213" s="46" t="s">
+      <c r="F213" s="45" t="s">
         <v>653</v>
       </c>
       <c r="G213" s="20">
@@ -10293,7 +10295,7 @@
       <c r="E214" s="30">
         <v>25</v>
       </c>
-      <c r="F214" s="44"/>
+      <c r="F214" s="43"/>
       <c r="G214" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10323,7 +10325,7 @@
       <c r="C215" s="3"/>
       <c r="D215" s="14"/>
       <c r="E215" s="31"/>
-      <c r="F215" s="46" t="s">
+      <c r="F215" s="45" t="s">
         <v>654</v>
       </c>
       <c r="G215" s="20">
@@ -10359,7 +10361,7 @@
         <v>458</v>
       </c>
       <c r="E216" s="30"/>
-      <c r="F216" s="47" t="s">
+      <c r="F216" s="46" t="s">
         <v>655</v>
       </c>
       <c r="G216" s="20">
@@ -10393,7 +10395,7 @@
       </c>
       <c r="D217" s="13"/>
       <c r="E217" s="30"/>
-      <c r="F217" s="44"/>
+      <c r="F217" s="43"/>
       <c r="G217" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10423,7 +10425,7 @@
       <c r="C218" s="3"/>
       <c r="D218" s="14"/>
       <c r="E218" s="31"/>
-      <c r="F218" s="46" t="s">
+      <c r="F218" s="45" t="s">
         <v>656</v>
       </c>
       <c r="G218" s="20">
@@ -10461,7 +10463,7 @@
       <c r="E219" s="30">
         <v>5.68</v>
       </c>
-      <c r="F219" s="44"/>
+      <c r="F219" s="43"/>
       <c r="G219" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10493,7 +10495,7 @@
       </c>
       <c r="D220" s="13"/>
       <c r="E220" s="30"/>
-      <c r="F220" s="44"/>
+      <c r="F220" s="43"/>
       <c r="G220" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10525,7 +10527,7 @@
       </c>
       <c r="D221" s="13"/>
       <c r="E221" s="30"/>
-      <c r="F221" s="44"/>
+      <c r="F221" s="43"/>
       <c r="G221" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10555,7 +10557,7 @@
       <c r="C222" s="3"/>
       <c r="D222" s="14"/>
       <c r="E222" s="31"/>
-      <c r="F222" s="46" t="s">
+      <c r="F222" s="45" t="s">
         <v>660</v>
       </c>
       <c r="G222" s="20">
@@ -10587,7 +10589,7 @@
       <c r="C223" s="3"/>
       <c r="D223" s="14"/>
       <c r="E223" s="31"/>
-      <c r="F223" s="46" t="s">
+      <c r="F223" s="45" t="s">
         <v>658</v>
       </c>
       <c r="G223" s="20">
@@ -10621,7 +10623,7 @@
       </c>
       <c r="D224" s="13"/>
       <c r="E224" s="30"/>
-      <c r="F224" s="44"/>
+      <c r="F224" s="43"/>
       <c r="G224" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10653,7 +10655,7 @@
       </c>
       <c r="D225" s="13"/>
       <c r="E225" s="30"/>
-      <c r="F225" s="44"/>
+      <c r="F225" s="43"/>
       <c r="G225" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10683,7 +10685,7 @@
       <c r="C226" s="3"/>
       <c r="D226" s="14"/>
       <c r="E226" s="31"/>
-      <c r="F226" s="46" t="s">
+      <c r="F226" s="45" t="s">
         <v>661</v>
       </c>
       <c r="G226" s="20">
@@ -10719,7 +10721,7 @@
       <c r="E227" s="31">
         <v>15</v>
       </c>
-      <c r="F227" s="46" t="s">
+      <c r="F227" s="45" t="s">
         <v>662</v>
       </c>
       <c r="G227" s="20">
@@ -10755,7 +10757,7 @@
         <v>310</v>
       </c>
       <c r="E228" s="30"/>
-      <c r="F228" s="44"/>
+      <c r="F228" s="43"/>
       <c r="G228" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10785,7 +10787,7 @@
       <c r="C229" s="3"/>
       <c r="D229" s="14"/>
       <c r="E229" s="31"/>
-      <c r="F229" s="46" t="s">
+      <c r="F229" s="45" t="s">
         <v>663</v>
       </c>
       <c r="G229" s="20">
@@ -10821,7 +10823,7 @@
         <v>425</v>
       </c>
       <c r="E230" s="30"/>
-      <c r="F230" s="44"/>
+      <c r="F230" s="43"/>
       <c r="G230" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10855,7 +10857,7 @@
         <v>310</v>
       </c>
       <c r="E231" s="30"/>
-      <c r="F231" s="44"/>
+      <c r="F231" s="43"/>
       <c r="G231" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10889,7 +10891,7 @@
         <v>426</v>
       </c>
       <c r="E232" s="30"/>
-      <c r="F232" s="44"/>
+      <c r="F232" s="43"/>
       <c r="G232" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10911,7 +10913,7 @@
       <c r="C233" s="3"/>
       <c r="D233" s="14"/>
       <c r="E233" s="31"/>
-      <c r="F233" s="46" t="s">
+      <c r="F233" s="45" t="s">
         <v>664</v>
       </c>
       <c r="G233" s="20">
@@ -10945,7 +10947,7 @@
       </c>
       <c r="D234" s="13"/>
       <c r="E234" s="30"/>
-      <c r="F234" s="44"/>
+      <c r="F234" s="43"/>
       <c r="G234" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10981,7 +10983,7 @@
       <c r="E235" s="30">
         <v>19.48</v>
       </c>
-      <c r="F235" s="44"/>
+      <c r="F235" s="43"/>
       <c r="G235" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11011,7 +11013,7 @@
       <c r="C236" s="35"/>
       <c r="D236" s="36"/>
       <c r="E236" s="37"/>
-      <c r="F236" s="71" t="s">
+      <c r="F236" s="70" t="s">
         <v>805</v>
       </c>
       <c r="G236" s="20">
@@ -11035,7 +11037,7 @@
       <c r="C237" s="35"/>
       <c r="D237" s="36"/>
       <c r="E237" s="37"/>
-      <c r="F237" s="71" t="s">
+      <c r="F237" s="70" t="s">
         <v>807</v>
       </c>
       <c r="G237" s="20">
@@ -11061,7 +11063,7 @@
       </c>
       <c r="D238" s="13"/>
       <c r="E238" s="30"/>
-      <c r="F238" s="44"/>
+      <c r="F238" s="43"/>
       <c r="G238" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11085,7 +11087,7 @@
       </c>
       <c r="D239" s="13"/>
       <c r="E239" s="30"/>
-      <c r="F239" s="44"/>
+      <c r="F239" s="43"/>
       <c r="G239" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11115,7 +11117,7 @@
       <c r="C240" s="3"/>
       <c r="D240" s="14"/>
       <c r="E240" s="31"/>
-      <c r="F240" s="46" t="s">
+      <c r="F240" s="45" t="s">
         <v>665</v>
       </c>
       <c r="G240" s="20">
@@ -11147,7 +11149,7 @@
       <c r="C241" s="3"/>
       <c r="D241" s="14"/>
       <c r="E241" s="31"/>
-      <c r="F241" s="46" t="s">
+      <c r="F241" s="45" t="s">
         <v>666</v>
       </c>
       <c r="G241" s="20">
@@ -11179,7 +11181,7 @@
       <c r="C242" s="3"/>
       <c r="D242" s="14"/>
       <c r="E242" s="31"/>
-      <c r="F242" s="46" t="s">
+      <c r="F242" s="45" t="s">
         <v>667</v>
       </c>
       <c r="G242" s="20">
@@ -11217,7 +11219,7 @@
       <c r="E243" s="30">
         <v>15</v>
       </c>
-      <c r="F243" s="47" t="s">
+      <c r="F243" s="46" t="s">
         <v>556</v>
       </c>
       <c r="G243" s="20">
@@ -11249,7 +11251,7 @@
       <c r="C244" s="3"/>
       <c r="D244" s="14"/>
       <c r="E244" s="31"/>
-      <c r="F244" s="46" t="s">
+      <c r="F244" s="45" t="s">
         <v>668</v>
       </c>
       <c r="G244" s="20">
@@ -11281,7 +11283,7 @@
       <c r="C245" s="3"/>
       <c r="D245" s="14"/>
       <c r="E245" s="31"/>
-      <c r="F245" s="46" t="s">
+      <c r="F245" s="45" t="s">
         <v>669</v>
       </c>
       <c r="G245" s="20">
@@ -11307,7 +11309,7 @@
       </c>
       <c r="D246" s="13"/>
       <c r="E246" s="30"/>
-      <c r="F246" s="44"/>
+      <c r="F246" s="43"/>
       <c r="G246" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11337,7 +11339,7 @@
       <c r="C247" s="3"/>
       <c r="D247" s="14"/>
       <c r="E247" s="31"/>
-      <c r="F247" s="46" t="s">
+      <c r="F247" s="45" t="s">
         <v>671</v>
       </c>
       <c r="G247" s="20">
@@ -11361,7 +11363,7 @@
       <c r="C248" s="3"/>
       <c r="D248" s="14"/>
       <c r="E248" s="31"/>
-      <c r="F248" s="46" t="s">
+      <c r="F248" s="45" t="s">
         <v>672</v>
       </c>
       <c r="G248" s="20">
@@ -11393,7 +11395,7 @@
       <c r="C249" s="3"/>
       <c r="D249" s="14"/>
       <c r="E249" s="31"/>
-      <c r="F249" s="46" t="s">
+      <c r="F249" s="45" t="s">
         <v>673</v>
       </c>
       <c r="G249" s="20">
@@ -11427,7 +11429,7 @@
       </c>
       <c r="D250" s="13"/>
       <c r="E250" s="30"/>
-      <c r="F250" s="44"/>
+      <c r="F250" s="43"/>
       <c r="G250" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11463,7 +11465,7 @@
       <c r="E251" s="30">
         <v>129</v>
       </c>
-      <c r="F251" s="47" t="s">
+      <c r="F251" s="46" t="s">
         <v>557</v>
       </c>
       <c r="G251" s="20">
@@ -11497,7 +11499,7 @@
         <v>675</v>
       </c>
       <c r="E252" s="31"/>
-      <c r="F252" s="46" t="s">
+      <c r="F252" s="45" t="s">
         <v>674</v>
       </c>
       <c r="G252" s="20">
@@ -11531,7 +11533,7 @@
       </c>
       <c r="D253" s="13"/>
       <c r="E253" s="30"/>
-      <c r="F253" s="44"/>
+      <c r="F253" s="43"/>
       <c r="G253" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11563,7 +11565,7 @@
       </c>
       <c r="D254" s="13"/>
       <c r="E254" s="30"/>
-      <c r="F254" s="44"/>
+      <c r="F254" s="43"/>
       <c r="G254" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11595,7 +11597,7 @@
       </c>
       <c r="D255" s="13"/>
       <c r="E255" s="30"/>
-      <c r="F255" s="44"/>
+      <c r="F255" s="43"/>
       <c r="G255" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11627,7 +11629,7 @@
       </c>
       <c r="D256" s="13"/>
       <c r="E256" s="30"/>
-      <c r="F256" s="44"/>
+      <c r="F256" s="43"/>
       <c r="G256" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11657,7 +11659,7 @@
       <c r="C257" s="3"/>
       <c r="D257" s="14"/>
       <c r="E257" s="31"/>
-      <c r="F257" s="46" t="s">
+      <c r="F257" s="45" t="s">
         <v>676</v>
       </c>
       <c r="G257" s="20">
@@ -11691,7 +11693,7 @@
       </c>
       <c r="D258" s="13"/>
       <c r="E258" s="30"/>
-      <c r="F258" s="44"/>
+      <c r="F258" s="43"/>
       <c r="G258" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11723,7 +11725,7 @@
       </c>
       <c r="D259" s="13"/>
       <c r="E259" s="30"/>
-      <c r="F259" s="44"/>
+      <c r="F259" s="43"/>
       <c r="G259" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11753,7 +11755,7 @@
       <c r="C260" s="3"/>
       <c r="D260" s="14"/>
       <c r="E260" s="31"/>
-      <c r="F260" s="46" t="s">
+      <c r="F260" s="45" t="s">
         <v>677</v>
       </c>
       <c r="G260" s="20">
@@ -11787,7 +11789,7 @@
       </c>
       <c r="D261" s="13"/>
       <c r="E261" s="30"/>
-      <c r="F261" s="44"/>
+      <c r="F261" s="43"/>
       <c r="G261" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11819,7 +11821,7 @@
       </c>
       <c r="D262" s="13"/>
       <c r="E262" s="30"/>
-      <c r="F262" s="44"/>
+      <c r="F262" s="43"/>
       <c r="G262" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11851,7 +11853,7 @@
       </c>
       <c r="D263" s="13"/>
       <c r="E263" s="30"/>
-      <c r="F263" s="44"/>
+      <c r="F263" s="43"/>
       <c r="G263" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11881,7 +11883,7 @@
       <c r="C264" s="3"/>
       <c r="D264" s="14"/>
       <c r="E264" s="31"/>
-      <c r="F264" s="46" t="s">
+      <c r="F264" s="45" t="s">
         <v>678</v>
       </c>
       <c r="G264" s="20">
@@ -11913,7 +11915,7 @@
       <c r="C265" s="3"/>
       <c r="D265" s="14"/>
       <c r="E265" s="31"/>
-      <c r="F265" s="46" t="s">
+      <c r="F265" s="45" t="s">
         <v>680</v>
       </c>
       <c r="G265" s="20">
@@ -11945,7 +11947,7 @@
       <c r="C266" s="3"/>
       <c r="D266" s="14"/>
       <c r="E266" s="31"/>
-      <c r="F266" s="46" t="s">
+      <c r="F266" s="45" t="s">
         <v>681</v>
       </c>
       <c r="G266" s="20">
@@ -11977,7 +11979,7 @@
       <c r="C267" s="3"/>
       <c r="D267" s="14"/>
       <c r="E267" s="31"/>
-      <c r="F267" s="46" t="s">
+      <c r="F267" s="45" t="s">
         <v>682</v>
       </c>
       <c r="G267" s="20">
@@ -12009,7 +12011,7 @@
       <c r="C268" s="3"/>
       <c r="D268" s="14"/>
       <c r="E268" s="31"/>
-      <c r="F268" s="46" t="s">
+      <c r="F268" s="45" t="s">
         <v>683</v>
       </c>
       <c r="G268" s="20">
@@ -12041,7 +12043,7 @@
       <c r="C269" s="3"/>
       <c r="D269" s="14"/>
       <c r="E269" s="31"/>
-      <c r="F269" s="46" t="s">
+      <c r="F269" s="45" t="s">
         <v>684</v>
       </c>
       <c r="G269" s="20">
@@ -12075,7 +12077,7 @@
       </c>
       <c r="D270" s="13"/>
       <c r="E270" s="30"/>
-      <c r="F270" s="47"/>
+      <c r="F270" s="46"/>
       <c r="G270" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12107,7 +12109,7 @@
       </c>
       <c r="D271" s="13"/>
       <c r="E271" s="30"/>
-      <c r="F271" s="44"/>
+      <c r="F271" s="43"/>
       <c r="G271" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12143,7 +12145,7 @@
       <c r="E272" s="30">
         <v>19.329999999999998</v>
       </c>
-      <c r="F272" s="47"/>
+      <c r="F272" s="46"/>
       <c r="G272" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12173,7 +12175,7 @@
       <c r="C273" s="3"/>
       <c r="D273" s="14"/>
       <c r="E273" s="31"/>
-      <c r="F273" s="46" t="s">
+      <c r="F273" s="45" t="s">
         <v>685</v>
       </c>
       <c r="G273" s="20">
@@ -12205,7 +12207,7 @@
       <c r="C274" s="3"/>
       <c r="D274" s="14"/>
       <c r="E274" s="31"/>
-      <c r="F274" s="46" t="s">
+      <c r="F274" s="45" t="s">
         <v>686</v>
       </c>
       <c r="G274" s="20">
@@ -12241,7 +12243,7 @@
         <v>422</v>
       </c>
       <c r="E275" s="30"/>
-      <c r="F275" s="44"/>
+      <c r="F275" s="43"/>
       <c r="G275" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12273,7 +12275,7 @@
         <v>688</v>
       </c>
       <c r="E276" s="31"/>
-      <c r="F276" s="46" t="s">
+      <c r="F276" s="45" t="s">
         <v>689</v>
       </c>
       <c r="G276" s="20">
@@ -12305,7 +12307,7 @@
       <c r="C277" s="3"/>
       <c r="D277" s="14"/>
       <c r="E277" s="31"/>
-      <c r="F277" s="46" t="s">
+      <c r="F277" s="45" t="s">
         <v>687</v>
       </c>
       <c r="G277" s="20">
@@ -12337,7 +12339,7 @@
       <c r="C278" s="3"/>
       <c r="D278" s="14"/>
       <c r="E278" s="31"/>
-      <c r="F278" s="46" t="s">
+      <c r="F278" s="45" t="s">
         <v>690</v>
       </c>
       <c r="G278" s="20">
@@ -12373,7 +12375,7 @@
         <v>422</v>
       </c>
       <c r="E279" s="30"/>
-      <c r="F279" s="44"/>
+      <c r="F279" s="43"/>
       <c r="G279" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12403,7 +12405,7 @@
       <c r="C280" s="3"/>
       <c r="D280" s="14"/>
       <c r="E280" s="31"/>
-      <c r="F280" s="46" t="s">
+      <c r="F280" s="45" t="s">
         <v>691</v>
       </c>
       <c r="G280" s="20">
@@ -12439,7 +12441,7 @@
         <v>424</v>
       </c>
       <c r="E281" s="30"/>
-      <c r="F281" s="44"/>
+      <c r="F281" s="43"/>
       <c r="G281" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12473,7 +12475,7 @@
         <v>514</v>
       </c>
       <c r="E282" s="30"/>
-      <c r="F282" s="44"/>
+      <c r="F282" s="43"/>
       <c r="G282" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12509,7 +12511,7 @@
       <c r="E283" s="30">
         <v>15</v>
       </c>
-      <c r="F283" s="44">
+      <c r="F283" s="43">
         <v>12</v>
       </c>
       <c r="G283" s="20">
@@ -12547,7 +12549,7 @@
       <c r="E284" s="30">
         <v>12</v>
       </c>
-      <c r="F284" s="44"/>
+      <c r="F284" s="43"/>
       <c r="G284" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12583,7 +12585,7 @@
       <c r="E285" s="30">
         <v>15</v>
       </c>
-      <c r="F285" s="44">
+      <c r="F285" s="43">
         <v>20</v>
       </c>
       <c r="G285" s="20">
@@ -12615,7 +12617,7 @@
       <c r="C286" s="3"/>
       <c r="D286" s="14"/>
       <c r="E286" s="31"/>
-      <c r="F286" s="46" t="s">
+      <c r="F286" s="45" t="s">
         <v>692</v>
       </c>
       <c r="G286" s="20">
@@ -12651,7 +12653,7 @@
         <v>422</v>
       </c>
       <c r="E287" s="30"/>
-      <c r="F287" s="44"/>
+      <c r="F287" s="43"/>
       <c r="G287" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12683,7 +12685,7 @@
         <v>387</v>
       </c>
       <c r="E288" s="31"/>
-      <c r="F288" s="46" t="s">
+      <c r="F288" s="45" t="s">
         <v>693</v>
       </c>
       <c r="G288" s="20">
@@ -12717,7 +12719,7 @@
         <v>386</v>
       </c>
       <c r="E289" s="31"/>
-      <c r="F289" s="46" t="s">
+      <c r="F289" s="45" t="s">
         <v>694</v>
       </c>
       <c r="G289" s="20">
@@ -12745,7 +12747,7 @@
         <v>422</v>
       </c>
       <c r="E290" s="30"/>
-      <c r="F290" s="44"/>
+      <c r="F290" s="43"/>
       <c r="G290" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12769,7 +12771,7 @@
       </c>
       <c r="D291" s="13"/>
       <c r="E291" s="30"/>
-      <c r="F291" s="44"/>
+      <c r="F291" s="43"/>
       <c r="G291" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -12799,7 +12801,7 @@
       <c r="C292" s="6"/>
       <c r="D292" s="14"/>
       <c r="E292" s="31"/>
-      <c r="F292" s="46" t="s">
+      <c r="F292" s="45" t="s">
         <v>695</v>
       </c>
       <c r="G292" s="20">
@@ -12831,7 +12833,7 @@
       <c r="C293" s="3"/>
       <c r="D293" s="14"/>
       <c r="E293" s="31"/>
-      <c r="F293" s="46" t="s">
+      <c r="F293" s="45" t="s">
         <v>696</v>
       </c>
       <c r="G293" s="20">
@@ -12863,7 +12865,7 @@
       <c r="C294" s="3"/>
       <c r="D294" s="14"/>
       <c r="E294" s="31"/>
-      <c r="F294" s="46" t="s">
+      <c r="F294" s="45" t="s">
         <v>697</v>
       </c>
       <c r="G294" s="20">
@@ -12895,7 +12897,7 @@
       <c r="C295" s="3"/>
       <c r="D295" s="14"/>
       <c r="E295" s="31"/>
-      <c r="F295" s="46" t="s">
+      <c r="F295" s="45" t="s">
         <v>698</v>
       </c>
       <c r="G295" s="20">
@@ -12927,7 +12929,7 @@
       <c r="C296" s="3"/>
       <c r="D296" s="14"/>
       <c r="E296" s="31"/>
-      <c r="F296" s="46" t="s">
+      <c r="F296" s="45" t="s">
         <v>699</v>
       </c>
       <c r="G296" s="20">
@@ -12965,7 +12967,7 @@
       <c r="E297" s="30">
         <v>11.41</v>
       </c>
-      <c r="F297" s="44"/>
+      <c r="F297" s="43"/>
       <c r="G297" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13001,7 +13003,7 @@
         <v>473</v>
       </c>
       <c r="E298" s="30"/>
-      <c r="F298" s="44"/>
+      <c r="F298" s="43"/>
       <c r="G298" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13031,7 +13033,7 @@
       <c r="C299" s="3"/>
       <c r="D299" s="14"/>
       <c r="E299" s="31"/>
-      <c r="F299" s="46" t="s">
+      <c r="F299" s="45" t="s">
         <v>700</v>
       </c>
       <c r="G299" s="20">
@@ -13065,7 +13067,7 @@
       </c>
       <c r="D300" s="13"/>
       <c r="E300" s="30"/>
-      <c r="F300" s="44"/>
+      <c r="F300" s="43"/>
       <c r="G300" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13099,7 +13101,7 @@
         <v>422</v>
       </c>
       <c r="E301" s="30"/>
-      <c r="F301" s="44"/>
+      <c r="F301" s="43"/>
       <c r="G301" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13129,7 +13131,7 @@
       <c r="C302" s="35"/>
       <c r="D302" s="36"/>
       <c r="E302" s="37"/>
-      <c r="F302" s="71" t="s">
+      <c r="F302" s="70" t="s">
         <v>701</v>
       </c>
       <c r="G302" s="20">
@@ -13163,7 +13165,7 @@
         <v>702</v>
       </c>
       <c r="E303" s="31"/>
-      <c r="F303" s="46" t="s">
+      <c r="F303" s="45" t="s">
         <v>703</v>
       </c>
       <c r="G303" s="20">
@@ -13197,7 +13199,7 @@
       </c>
       <c r="D304" s="13"/>
       <c r="E304" s="30"/>
-      <c r="F304" s="44"/>
+      <c r="F304" s="43"/>
       <c r="G304" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13229,7 +13231,7 @@
       </c>
       <c r="D305" s="13"/>
       <c r="E305" s="30"/>
-      <c r="F305" s="44"/>
+      <c r="F305" s="43"/>
       <c r="G305" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13261,7 +13263,7 @@
         <v>702</v>
       </c>
       <c r="E306" s="31"/>
-      <c r="F306" s="46" t="s">
+      <c r="F306" s="45" t="s">
         <v>704</v>
       </c>
       <c r="G306" s="20">
@@ -13293,7 +13295,7 @@
       <c r="C307" s="3"/>
       <c r="D307" s="14"/>
       <c r="E307" s="31"/>
-      <c r="F307" s="46" t="s">
+      <c r="F307" s="45" t="s">
         <v>705</v>
       </c>
       <c r="G307" s="20">
@@ -13325,7 +13327,7 @@
       <c r="C308" s="3"/>
       <c r="D308" s="14"/>
       <c r="E308" s="31"/>
-      <c r="F308" s="46" t="s">
+      <c r="F308" s="45" t="s">
         <v>706</v>
       </c>
       <c r="G308" s="20">
@@ -13357,7 +13359,7 @@
       <c r="C309" s="3"/>
       <c r="D309" s="14"/>
       <c r="E309" s="31"/>
-      <c r="F309" s="46" t="s">
+      <c r="F309" s="45" t="s">
         <v>707</v>
       </c>
       <c r="G309" s="20">
@@ -13391,7 +13393,7 @@
       </c>
       <c r="D310" s="13"/>
       <c r="E310" s="30"/>
-      <c r="F310" s="44"/>
+      <c r="F310" s="43"/>
       <c r="G310" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13423,7 +13425,7 @@
       </c>
       <c r="D311" s="13"/>
       <c r="E311" s="30"/>
-      <c r="F311" s="44"/>
+      <c r="F311" s="43"/>
       <c r="G311" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13453,7 +13455,7 @@
       <c r="C312" s="3"/>
       <c r="D312" s="14"/>
       <c r="E312" s="31"/>
-      <c r="F312" s="46" t="s">
+      <c r="F312" s="45" t="s">
         <v>708</v>
       </c>
       <c r="G312" s="20">
@@ -13485,7 +13487,7 @@
       <c r="C313" s="3"/>
       <c r="D313" s="14"/>
       <c r="E313" s="31"/>
-      <c r="F313" s="46" t="s">
+      <c r="F313" s="45" t="s">
         <v>709</v>
       </c>
       <c r="G313" s="20">
@@ -13517,7 +13519,7 @@
       <c r="C314" s="3"/>
       <c r="D314" s="14"/>
       <c r="E314" s="31"/>
-      <c r="F314" s="46" t="s">
+      <c r="F314" s="45" t="s">
         <v>710</v>
       </c>
       <c r="G314" s="20">
@@ -13549,7 +13551,7 @@
       <c r="C315" s="3"/>
       <c r="D315" s="14"/>
       <c r="E315" s="31"/>
-      <c r="F315" s="46" t="s">
+      <c r="F315" s="45" t="s">
         <v>711</v>
       </c>
       <c r="G315" s="20">
@@ -13581,7 +13583,7 @@
       <c r="C316" s="3"/>
       <c r="D316" s="14"/>
       <c r="E316" s="31"/>
-      <c r="F316" s="46" t="s">
+      <c r="F316" s="45" t="s">
         <v>712</v>
       </c>
       <c r="G316" s="20">
@@ -13619,7 +13621,7 @@
       <c r="E317" s="30">
         <v>15</v>
       </c>
-      <c r="F317" s="44"/>
+      <c r="F317" s="43"/>
       <c r="G317" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13649,7 +13651,7 @@
       <c r="C318" s="3"/>
       <c r="D318" s="14"/>
       <c r="E318" s="31"/>
-      <c r="F318" s="46" t="s">
+      <c r="F318" s="45" t="s">
         <v>713</v>
       </c>
       <c r="G318" s="20">
@@ -13681,7 +13683,7 @@
       <c r="C319" s="3"/>
       <c r="D319" s="14"/>
       <c r="E319" s="31"/>
-      <c r="F319" s="46" t="s">
+      <c r="F319" s="45" t="s">
         <v>714</v>
       </c>
       <c r="G319" s="20">
@@ -13713,7 +13715,7 @@
       <c r="C320" s="3"/>
       <c r="D320" s="14"/>
       <c r="E320" s="31"/>
-      <c r="F320" s="46" t="s">
+      <c r="F320" s="45" t="s">
         <v>715</v>
       </c>
       <c r="G320" s="20">
@@ -13747,7 +13749,7 @@
         <v>465</v>
       </c>
       <c r="E321" s="31"/>
-      <c r="F321" s="46" t="s">
+      <c r="F321" s="45" t="s">
         <v>716</v>
       </c>
       <c r="G321" s="20">
@@ -13779,7 +13781,7 @@
       <c r="C322" s="3"/>
       <c r="D322" s="14"/>
       <c r="E322" s="31"/>
-      <c r="F322" s="46" t="s">
+      <c r="F322" s="45" t="s">
         <v>717</v>
       </c>
       <c r="G322" s="20">
@@ -13817,7 +13819,7 @@
       <c r="E323" s="30">
         <v>15</v>
       </c>
-      <c r="F323" s="44"/>
+      <c r="F323" s="43"/>
       <c r="G323" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13849,7 +13851,7 @@
         <v>719</v>
       </c>
       <c r="E324" s="31"/>
-      <c r="F324" s="46" t="s">
+      <c r="F324" s="45" t="s">
         <v>718</v>
       </c>
       <c r="G324" s="20">
@@ -13873,7 +13875,7 @@
       <c r="C325" s="3"/>
       <c r="D325" s="14"/>
       <c r="E325" s="31"/>
-      <c r="F325" s="46" t="s">
+      <c r="F325" s="45" t="s">
         <v>720</v>
       </c>
       <c r="G325" s="20">
@@ -13907,7 +13909,7 @@
       </c>
       <c r="D326" s="13"/>
       <c r="E326" s="30"/>
-      <c r="F326" s="44"/>
+      <c r="F326" s="43"/>
       <c r="G326" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13939,7 +13941,7 @@
       </c>
       <c r="D327" s="13"/>
       <c r="E327" s="30"/>
-      <c r="F327" s="44"/>
+      <c r="F327" s="43"/>
       <c r="G327" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13975,7 +13977,7 @@
       <c r="E328" s="30">
         <v>12</v>
       </c>
-      <c r="F328" s="44"/>
+      <c r="F328" s="43"/>
       <c r="G328" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -14005,7 +14007,7 @@
       <c r="C329" s="3"/>
       <c r="D329" s="14"/>
       <c r="E329" s="31"/>
-      <c r="F329" s="46" t="s">
+      <c r="F329" s="45" t="s">
         <v>721</v>
       </c>
       <c r="G329" s="20">
@@ -14043,7 +14045,7 @@
       <c r="E330" s="30">
         <v>23</v>
       </c>
-      <c r="F330" s="44"/>
+      <c r="F330" s="43"/>
       <c r="G330" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14073,7 +14075,7 @@
       <c r="C331" s="3"/>
       <c r="D331" s="14"/>
       <c r="E331" s="31"/>
-      <c r="F331" s="46" t="s">
+      <c r="F331" s="45" t="s">
         <v>722</v>
       </c>
       <c r="G331" s="20">
@@ -14111,7 +14113,7 @@
       <c r="E332" s="30">
         <v>25</v>
       </c>
-      <c r="F332" s="44"/>
+      <c r="F332" s="43"/>
       <c r="G332" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14143,7 +14145,7 @@
       </c>
       <c r="D333" s="13"/>
       <c r="E333" s="30"/>
-      <c r="F333" s="44"/>
+      <c r="F333" s="43"/>
       <c r="G333" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14173,7 +14175,7 @@
       <c r="C334" s="3"/>
       <c r="D334" s="14"/>
       <c r="E334" s="31"/>
-      <c r="F334" s="46" t="s">
+      <c r="F334" s="45" t="s">
         <v>723</v>
       </c>
       <c r="G334" s="20">
@@ -14207,7 +14209,7 @@
       </c>
       <c r="D335" s="13"/>
       <c r="E335" s="30"/>
-      <c r="F335" s="44"/>
+      <c r="F335" s="43"/>
       <c r="G335" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14243,7 +14245,7 @@
       <c r="E336" s="30">
         <v>15</v>
       </c>
-      <c r="F336" s="44">
+      <c r="F336" s="43">
         <v>6</v>
       </c>
       <c r="G336" s="20">
@@ -14277,7 +14279,7 @@
       </c>
       <c r="D337" s="13"/>
       <c r="E337" s="30"/>
-      <c r="F337" s="44"/>
+      <c r="F337" s="43"/>
       <c r="G337" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14309,7 +14311,7 @@
       </c>
       <c r="D338" s="13"/>
       <c r="E338" s="30"/>
-      <c r="F338" s="44"/>
+      <c r="F338" s="43"/>
       <c r="G338" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14339,7 +14341,7 @@
       <c r="C339" s="3"/>
       <c r="D339" s="14"/>
       <c r="E339" s="31"/>
-      <c r="F339" s="46" t="s">
+      <c r="F339" s="45" t="s">
         <v>724</v>
       </c>
       <c r="G339" s="20">
@@ -14371,7 +14373,7 @@
       <c r="C340" s="3"/>
       <c r="D340" s="14"/>
       <c r="E340" s="31"/>
-      <c r="F340" s="46" t="s">
+      <c r="F340" s="45" t="s">
         <v>770</v>
       </c>
       <c r="G340" s="20">
@@ -14405,7 +14407,7 @@
       </c>
       <c r="D341" s="13"/>
       <c r="E341" s="30"/>
-      <c r="F341" s="44"/>
+      <c r="F341" s="43"/>
       <c r="G341" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14437,7 +14439,7 @@
       </c>
       <c r="D342" s="13"/>
       <c r="E342" s="30"/>
-      <c r="F342" s="44"/>
+      <c r="F342" s="43"/>
       <c r="G342" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14469,7 +14471,7 @@
       </c>
       <c r="D343" s="13"/>
       <c r="E343" s="30"/>
-      <c r="F343" s="44"/>
+      <c r="F343" s="43"/>
       <c r="G343" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14505,7 +14507,7 @@
       <c r="E344" s="30">
         <v>25</v>
       </c>
-      <c r="F344" s="44"/>
+      <c r="F344" s="43"/>
       <c r="G344" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14539,7 +14541,7 @@
         <v>545</v>
       </c>
       <c r="E345" s="30"/>
-      <c r="F345" s="44"/>
+      <c r="F345" s="43"/>
       <c r="G345" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14573,7 +14575,7 @@
         <v>546</v>
       </c>
       <c r="E346" s="30"/>
-      <c r="F346" s="44"/>
+      <c r="F346" s="43"/>
       <c r="G346" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14605,7 +14607,7 @@
       </c>
       <c r="D347" s="13"/>
       <c r="E347" s="30"/>
-      <c r="F347" s="44"/>
+      <c r="F347" s="43"/>
       <c r="G347" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14639,7 +14641,7 @@
         <v>474</v>
       </c>
       <c r="E348" s="30"/>
-      <c r="F348" s="44"/>
+      <c r="F348" s="43"/>
       <c r="G348" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14669,7 +14671,7 @@
       <c r="C349" s="3"/>
       <c r="D349" s="14"/>
       <c r="E349" s="31"/>
-      <c r="F349" s="46" t="s">
+      <c r="F349" s="45" t="s">
         <v>725</v>
       </c>
       <c r="G349" s="20">
@@ -14703,7 +14705,7 @@
       </c>
       <c r="D350" s="13"/>
       <c r="E350" s="30"/>
-      <c r="F350" s="44"/>
+      <c r="F350" s="43"/>
       <c r="G350" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14733,7 +14735,7 @@
       <c r="C351" s="3"/>
       <c r="D351" s="14"/>
       <c r="E351" s="31"/>
-      <c r="F351" s="46" t="s">
+      <c r="F351" s="45" t="s">
         <v>726</v>
       </c>
       <c r="G351" s="20">
@@ -14767,7 +14769,7 @@
       </c>
       <c r="D352" s="13"/>
       <c r="E352" s="30"/>
-      <c r="F352" s="44"/>
+      <c r="F352" s="43"/>
       <c r="G352" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14799,7 +14801,7 @@
       </c>
       <c r="D353" s="13"/>
       <c r="E353" s="30"/>
-      <c r="F353" s="44"/>
+      <c r="F353" s="43"/>
       <c r="G353" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14831,7 +14833,7 @@
       </c>
       <c r="D354" s="13"/>
       <c r="E354" s="30"/>
-      <c r="F354" s="44"/>
+      <c r="F354" s="43"/>
       <c r="G354" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14861,7 +14863,7 @@
       <c r="C355" s="3"/>
       <c r="D355" s="14"/>
       <c r="E355" s="31"/>
-      <c r="F355" s="46" t="s">
+      <c r="F355" s="45" t="s">
         <v>727</v>
       </c>
       <c r="G355" s="20">
@@ -14895,7 +14897,7 @@
       </c>
       <c r="D356" s="13"/>
       <c r="E356" s="30"/>
-      <c r="F356" s="44"/>
+      <c r="F356" s="43"/>
       <c r="G356" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14927,7 +14929,7 @@
       </c>
       <c r="D357" s="13"/>
       <c r="E357" s="30"/>
-      <c r="F357" s="44"/>
+      <c r="F357" s="43"/>
       <c r="G357" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14959,7 +14961,7 @@
       </c>
       <c r="D358" s="13"/>
       <c r="E358" s="30"/>
-      <c r="F358" s="44"/>
+      <c r="F358" s="43"/>
       <c r="G358" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14991,7 +14993,7 @@
       </c>
       <c r="D359" s="13"/>
       <c r="E359" s="30"/>
-      <c r="F359" s="44"/>
+      <c r="F359" s="43"/>
       <c r="G359" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15025,7 +15027,7 @@
         <v>310</v>
       </c>
       <c r="E360" s="30"/>
-      <c r="F360" s="44"/>
+      <c r="F360" s="43"/>
       <c r="G360" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15057,7 +15059,7 @@
       </c>
       <c r="D361" s="13"/>
       <c r="E361" s="30"/>
-      <c r="F361" s="44"/>
+      <c r="F361" s="43"/>
       <c r="G361" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15087,7 +15089,7 @@
       <c r="C362" s="3"/>
       <c r="D362" s="14"/>
       <c r="E362" s="31"/>
-      <c r="F362" s="46" t="s">
+      <c r="F362" s="45" t="s">
         <v>728</v>
       </c>
       <c r="G362" s="20">
@@ -15123,7 +15125,7 @@
         <v>463</v>
       </c>
       <c r="E363" s="30"/>
-      <c r="F363" s="44"/>
+      <c r="F363" s="43"/>
       <c r="G363" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15155,7 +15157,7 @@
       </c>
       <c r="D364" s="13"/>
       <c r="E364" s="30"/>
-      <c r="F364" s="44"/>
+      <c r="F364" s="43"/>
       <c r="G364" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15187,7 +15189,7 @@
       </c>
       <c r="D365" s="13"/>
       <c r="E365" s="30"/>
-      <c r="F365" s="47"/>
+      <c r="F365" s="46"/>
       <c r="G365" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15217,7 +15219,7 @@
       <c r="C366" s="3"/>
       <c r="D366" s="14"/>
       <c r="E366" s="31"/>
-      <c r="F366" s="46" t="s">
+      <c r="F366" s="45" t="s">
         <v>729</v>
       </c>
       <c r="G366" s="20">
@@ -15249,7 +15251,7 @@
       <c r="C367" s="3"/>
       <c r="D367" s="14"/>
       <c r="E367" s="31"/>
-      <c r="F367" s="46" t="s">
+      <c r="F367" s="45" t="s">
         <v>730</v>
       </c>
       <c r="G367" s="20">
@@ -15283,7 +15285,7 @@
         <v>489</v>
       </c>
       <c r="E368" s="31"/>
-      <c r="F368" s="46" t="s">
+      <c r="F368" s="45" t="s">
         <v>731</v>
       </c>
       <c r="G368" s="20">
@@ -15315,7 +15317,7 @@
       <c r="C369" s="3"/>
       <c r="D369" s="14"/>
       <c r="E369" s="31"/>
-      <c r="F369" s="46" t="s">
+      <c r="F369" s="45" t="s">
         <v>732</v>
       </c>
       <c r="G369" s="20">
@@ -15353,7 +15355,7 @@
       <c r="E370" s="30">
         <v>15.25</v>
       </c>
-      <c r="F370" s="47"/>
+      <c r="F370" s="46"/>
       <c r="G370" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15385,7 +15387,7 @@
       </c>
       <c r="D371" s="13"/>
       <c r="E371" s="30"/>
-      <c r="F371" s="44"/>
+      <c r="F371" s="43"/>
       <c r="G371" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15421,7 +15423,7 @@
       <c r="E372" s="30">
         <v>24</v>
       </c>
-      <c r="F372" s="44"/>
+      <c r="F372" s="43"/>
       <c r="G372" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15453,7 +15455,7 @@
       </c>
       <c r="D373" s="13"/>
       <c r="E373" s="30"/>
-      <c r="F373" s="44"/>
+      <c r="F373" s="43"/>
       <c r="G373" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15483,7 +15485,7 @@
       <c r="C374" s="3"/>
       <c r="D374" s="14"/>
       <c r="E374" s="31"/>
-      <c r="F374" s="46" t="s">
+      <c r="F374" s="45" t="s">
         <v>733</v>
       </c>
       <c r="G374" s="20">
@@ -15517,7 +15519,7 @@
       </c>
       <c r="D375" s="13"/>
       <c r="E375" s="30"/>
-      <c r="F375" s="44"/>
+      <c r="F375" s="43"/>
       <c r="G375" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15547,7 +15549,7 @@
       <c r="C376" s="3"/>
       <c r="D376" s="14"/>
       <c r="E376" s="31"/>
-      <c r="F376" s="46" t="s">
+      <c r="F376" s="45" t="s">
         <v>734</v>
       </c>
       <c r="G376" s="20">
@@ -15585,7 +15587,7 @@
       <c r="E377" s="30">
         <v>17</v>
       </c>
-      <c r="F377" s="44"/>
+      <c r="F377" s="43"/>
       <c r="G377" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15615,7 +15617,7 @@
       <c r="C378" s="3"/>
       <c r="D378" s="14"/>
       <c r="E378" s="31"/>
-      <c r="F378" s="46" t="s">
+      <c r="F378" s="45" t="s">
         <v>735</v>
       </c>
       <c r="G378" s="20">
@@ -15649,7 +15651,7 @@
         <v>736</v>
       </c>
       <c r="E379" s="31"/>
-      <c r="F379" s="46" t="s">
+      <c r="F379" s="45" t="s">
         <v>737</v>
       </c>
       <c r="G379" s="20">
@@ -15681,7 +15683,7 @@
       <c r="C380" s="3"/>
       <c r="D380" s="14"/>
       <c r="E380" s="31"/>
-      <c r="F380" s="46" t="s">
+      <c r="F380" s="45" t="s">
         <v>738</v>
       </c>
       <c r="G380" s="20">
@@ -15715,7 +15717,7 @@
         <v>741</v>
       </c>
       <c r="E381" s="31"/>
-      <c r="F381" s="46" t="s">
+      <c r="F381" s="45" t="s">
         <v>740</v>
       </c>
       <c r="G381" s="20">
@@ -15751,7 +15753,7 @@
       <c r="E382" s="31">
         <v>15</v>
       </c>
-      <c r="F382" s="46" t="s">
+      <c r="F382" s="45" t="s">
         <v>742</v>
       </c>
       <c r="G382" s="20">
@@ -15783,7 +15785,7 @@
       <c r="C383" s="3"/>
       <c r="D383" s="14"/>
       <c r="E383" s="31"/>
-      <c r="F383" s="46" t="s">
+      <c r="F383" s="45" t="s">
         <v>743</v>
       </c>
       <c r="G383" s="20">
@@ -15819,7 +15821,7 @@
         <v>474</v>
       </c>
       <c r="E384" s="30"/>
-      <c r="F384" s="44"/>
+      <c r="F384" s="43"/>
       <c r="G384" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15855,7 +15857,7 @@
       <c r="E385" s="30">
         <v>10</v>
       </c>
-      <c r="F385" s="44"/>
+      <c r="F385" s="43"/>
       <c r="G385" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15887,7 +15889,7 @@
       </c>
       <c r="D386" s="13"/>
       <c r="E386" s="30"/>
-      <c r="F386" s="47"/>
+      <c r="F386" s="46"/>
       <c r="G386" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15919,7 +15921,7 @@
       </c>
       <c r="D387" s="13"/>
       <c r="E387" s="30"/>
-      <c r="F387" s="47"/>
+      <c r="F387" s="46"/>
       <c r="G387" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15955,7 +15957,7 @@
       <c r="E388" s="30">
         <v>11</v>
       </c>
-      <c r="F388" s="44"/>
+      <c r="F388" s="43"/>
       <c r="G388" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15985,7 +15987,7 @@
       <c r="C389" s="3"/>
       <c r="D389" s="14"/>
       <c r="E389" s="31"/>
-      <c r="F389" s="46" t="s">
+      <c r="F389" s="45" t="s">
         <v>744</v>
       </c>
       <c r="G389" s="20">
@@ -16017,7 +16019,7 @@
       <c r="C390" s="3"/>
       <c r="D390" s="14"/>
       <c r="E390" s="31"/>
-      <c r="F390" s="46" t="s">
+      <c r="F390" s="45" t="s">
         <v>745</v>
       </c>
       <c r="G390" s="20">
@@ -16051,7 +16053,7 @@
       </c>
       <c r="D391" s="13"/>
       <c r="E391" s="30"/>
-      <c r="F391" s="44"/>
+      <c r="F391" s="43"/>
       <c r="G391" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -16081,7 +16083,7 @@
       <c r="C392" s="3"/>
       <c r="D392" s="14"/>
       <c r="E392" s="31"/>
-      <c r="F392" s="46" t="s">
+      <c r="F392" s="45" t="s">
         <v>746</v>
       </c>
       <c r="G392" s="20">
@@ -16115,7 +16117,7 @@
       </c>
       <c r="D393" s="13"/>
       <c r="E393" s="30"/>
-      <c r="F393" s="44"/>
+      <c r="F393" s="43"/>
       <c r="G393" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16147,7 +16149,7 @@
       </c>
       <c r="D394" s="13"/>
       <c r="E394" s="30"/>
-      <c r="F394" s="44"/>
+      <c r="F394" s="43"/>
       <c r="G394" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16183,7 +16185,7 @@
       <c r="E395" s="30">
         <v>18</v>
       </c>
-      <c r="F395" s="44"/>
+      <c r="F395" s="43"/>
       <c r="G395" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16213,7 +16215,7 @@
       <c r="C396" s="3"/>
       <c r="D396" s="14"/>
       <c r="E396" s="31"/>
-      <c r="F396" s="46" t="s">
+      <c r="F396" s="45" t="s">
         <v>747</v>
       </c>
       <c r="G396" s="20">
@@ -16245,7 +16247,7 @@
       <c r="C397" s="3"/>
       <c r="D397" s="14"/>
       <c r="E397" s="31"/>
-      <c r="F397" s="46" t="s">
+      <c r="F397" s="45" t="s">
         <v>748</v>
       </c>
       <c r="G397" s="20">
@@ -16277,7 +16279,7 @@
       <c r="C398" s="3"/>
       <c r="D398" s="14"/>
       <c r="E398" s="31"/>
-      <c r="F398" s="46" t="s">
+      <c r="F398" s="45" t="s">
         <v>749</v>
       </c>
       <c r="G398" s="20">
@@ -16315,7 +16317,7 @@
       <c r="E399" s="30">
         <v>10</v>
       </c>
-      <c r="F399" s="44"/>
+      <c r="F399" s="43"/>
       <c r="G399" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16339,7 +16341,7 @@
       </c>
       <c r="D400" s="13"/>
       <c r="E400" s="30"/>
-      <c r="F400" s="44"/>
+      <c r="F400" s="43"/>
       <c r="G400" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16371,7 +16373,7 @@
       </c>
       <c r="D401" s="13"/>
       <c r="E401" s="30"/>
-      <c r="F401" s="44"/>
+      <c r="F401" s="43"/>
       <c r="G401" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16405,7 +16407,7 @@
       <c r="E402" s="31">
         <v>19</v>
       </c>
-      <c r="F402" s="46" t="s">
+      <c r="F402" s="45" t="s">
         <v>750</v>
       </c>
       <c r="G402" s="20">
@@ -16437,7 +16439,7 @@
       <c r="C403" s="3"/>
       <c r="D403" s="14"/>
       <c r="E403" s="31"/>
-      <c r="F403" s="46" t="s">
+      <c r="F403" s="45" t="s">
         <v>751</v>
       </c>
       <c r="G403" s="20">
@@ -16469,7 +16471,7 @@
       <c r="C404" s="3"/>
       <c r="D404" s="14"/>
       <c r="E404" s="31"/>
-      <c r="F404" s="46" t="s">
+      <c r="F404" s="45" t="s">
         <v>752</v>
       </c>
       <c r="G404" s="20">
@@ -16507,7 +16509,7 @@
       <c r="E405" s="32">
         <v>24</v>
       </c>
-      <c r="F405" s="72" t="s">
+      <c r="F405" s="71" t="s">
         <v>753</v>
       </c>
       <c r="G405" s="20">
@@ -16539,7 +16541,7 @@
       <c r="C406" s="3"/>
       <c r="D406" s="14"/>
       <c r="E406" s="31"/>
-      <c r="F406" s="46" t="s">
+      <c r="F406" s="45" t="s">
         <v>754</v>
       </c>
       <c r="G406" s="20">
@@ -16571,7 +16573,7 @@
       <c r="C407" s="3"/>
       <c r="D407" s="14"/>
       <c r="E407" s="31"/>
-      <c r="F407" s="46" t="s">
+      <c r="F407" s="45" t="s">
         <v>754</v>
       </c>
       <c r="G407" s="20">
@@ -16605,7 +16607,7 @@
       </c>
       <c r="D408" s="13"/>
       <c r="E408" s="30"/>
-      <c r="F408" s="44"/>
+      <c r="F408" s="43"/>
       <c r="G408" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16641,7 +16643,7 @@
       <c r="E409" s="30">
         <v>12</v>
       </c>
-      <c r="F409" s="44"/>
+      <c r="F409" s="43"/>
       <c r="G409" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16671,7 +16673,7 @@
       <c r="C410" s="3"/>
       <c r="D410" s="14"/>
       <c r="E410" s="31"/>
-      <c r="F410" s="46" t="s">
+      <c r="F410" s="45" t="s">
         <v>755</v>
       </c>
       <c r="G410" s="20">
@@ -16707,7 +16709,7 @@
         <v>465</v>
       </c>
       <c r="E411" s="30"/>
-      <c r="F411" s="44"/>
+      <c r="F411" s="43"/>
       <c r="G411" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16739,7 +16741,7 @@
       </c>
       <c r="D412" s="13"/>
       <c r="E412" s="30"/>
-      <c r="F412" s="44"/>
+      <c r="F412" s="43"/>
       <c r="G412" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16771,7 +16773,7 @@
       </c>
       <c r="D413" s="13"/>
       <c r="E413" s="30"/>
-      <c r="F413" s="44"/>
+      <c r="F413" s="43"/>
       <c r="G413" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16807,7 +16809,7 @@
       <c r="E414" s="30">
         <v>17.190000000000001</v>
       </c>
-      <c r="F414" s="44"/>
+      <c r="F414" s="43"/>
       <c r="G414" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16839,7 +16841,7 @@
         <v>558</v>
       </c>
       <c r="E415" s="31"/>
-      <c r="F415" s="46" t="s">
+      <c r="F415" s="45" t="s">
         <v>756</v>
       </c>
       <c r="G415" s="20">
@@ -16863,7 +16865,7 @@
       <c r="C416" s="3"/>
       <c r="D416" s="14"/>
       <c r="E416" s="31"/>
-      <c r="F416" s="46" t="s">
+      <c r="F416" s="45" t="s">
         <v>757</v>
       </c>
       <c r="G416" s="20">
@@ -16897,7 +16899,7 @@
       </c>
       <c r="D417" s="13"/>
       <c r="E417" s="30"/>
-      <c r="F417" s="44"/>
+      <c r="F417" s="43"/>
       <c r="G417" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16933,7 +16935,7 @@
       <c r="E418" s="30">
         <v>23</v>
       </c>
-      <c r="F418" s="44"/>
+      <c r="F418" s="43"/>
       <c r="G418" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16965,7 +16967,7 @@
       </c>
       <c r="D419" s="13"/>
       <c r="E419" s="30"/>
-      <c r="F419" s="44"/>
+      <c r="F419" s="43"/>
       <c r="G419" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16999,7 +17001,7 @@
         <v>8</v>
       </c>
       <c r="E420" s="30"/>
-      <c r="F420" s="44"/>
+      <c r="F420" s="43"/>
       <c r="G420" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17033,7 +17035,7 @@
         <v>422</v>
       </c>
       <c r="E421" s="30"/>
-      <c r="F421" s="44"/>
+      <c r="F421" s="43"/>
       <c r="G421" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17063,7 +17065,7 @@
       <c r="C422" s="3"/>
       <c r="D422" s="14"/>
       <c r="E422" s="31"/>
-      <c r="F422" s="46" t="s">
+      <c r="F422" s="45" t="s">
         <v>758</v>
       </c>
       <c r="G422" s="20">
@@ -17095,7 +17097,7 @@
       <c r="C423" s="3"/>
       <c r="D423" s="14"/>
       <c r="E423" s="31"/>
-      <c r="F423" s="46" t="s">
+      <c r="F423" s="45" t="s">
         <v>759</v>
       </c>
       <c r="G423" s="20">
@@ -17133,7 +17135,7 @@
       <c r="E424" s="30">
         <v>12</v>
       </c>
-      <c r="F424" s="44"/>
+      <c r="F424" s="43"/>
       <c r="G424" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17165,7 +17167,7 @@
       </c>
       <c r="D425" s="13"/>
       <c r="E425" s="30"/>
-      <c r="F425" s="44"/>
+      <c r="F425" s="43"/>
       <c r="G425" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17197,7 +17199,7 @@
       </c>
       <c r="D426" s="13"/>
       <c r="E426" s="30"/>
-      <c r="F426" s="44"/>
+      <c r="F426" s="43"/>
       <c r="G426" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17233,7 +17235,7 @@
       <c r="E427" s="30">
         <v>8.8800000000000008</v>
       </c>
-      <c r="F427" s="44"/>
+      <c r="F427" s="43"/>
       <c r="G427" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17265,7 +17267,7 @@
         <v>761</v>
       </c>
       <c r="E428" s="31"/>
-      <c r="F428" s="46" t="s">
+      <c r="F428" s="45" t="s">
         <v>760</v>
       </c>
       <c r="G428" s="20">
@@ -17291,7 +17293,7 @@
       </c>
       <c r="D429" s="13"/>
       <c r="E429" s="30"/>
-      <c r="F429" s="44"/>
+      <c r="F429" s="43"/>
       <c r="G429" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17323,7 +17325,9 @@
         <v>763</v>
       </c>
       <c r="E430" s="31"/>
-      <c r="F430" s="43"/>
+      <c r="F430" s="45" t="s">
+        <v>808</v>
+      </c>
       <c r="G430" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17353,7 +17357,7 @@
       <c r="C431" s="3"/>
       <c r="D431" s="14"/>
       <c r="E431" s="31"/>
-      <c r="F431" s="46" t="s">
+      <c r="F431" s="45" t="s">
         <v>762</v>
       </c>
       <c r="G431" s="20">
@@ -17387,7 +17391,7 @@
       </c>
       <c r="D432" s="13"/>
       <c r="E432" s="30"/>
-      <c r="F432" s="44"/>
+      <c r="F432" s="43"/>
       <c r="G432" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17419,7 +17423,7 @@
       </c>
       <c r="D433" s="13"/>
       <c r="E433" s="30"/>
-      <c r="F433" s="44"/>
+      <c r="F433" s="43"/>
       <c r="G433" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17451,7 +17455,7 @@
       </c>
       <c r="D434" s="13"/>
       <c r="E434" s="30"/>
-      <c r="F434" s="44"/>
+      <c r="F434" s="43"/>
       <c r="G434" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17481,7 +17485,7 @@
       <c r="C435" s="3"/>
       <c r="D435" s="14"/>
       <c r="E435" s="31"/>
-      <c r="F435" s="46" t="s">
+      <c r="F435" s="45" t="s">
         <v>764</v>
       </c>
       <c r="G435" s="20">
@@ -17517,7 +17521,7 @@
         <v>422</v>
       </c>
       <c r="E436" s="30"/>
-      <c r="F436" s="44"/>
+      <c r="F436" s="43"/>
       <c r="G436" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17549,7 +17553,7 @@
       </c>
       <c r="D437" s="13"/>
       <c r="E437" s="30"/>
-      <c r="F437" s="44"/>
+      <c r="F437" s="43"/>
       <c r="G437" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17579,7 +17583,7 @@
       <c r="C438" s="3"/>
       <c r="D438" s="14"/>
       <c r="E438" s="31"/>
-      <c r="F438" s="46" t="s">
+      <c r="F438" s="45" t="s">
         <v>765</v>
       </c>
       <c r="G438" s="20">
@@ -17615,7 +17619,7 @@
         <v>446</v>
       </c>
       <c r="E439" s="30"/>
-      <c r="F439" s="44"/>
+      <c r="F439" s="43"/>
       <c r="G439" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17641,7 +17645,7 @@
         <v>422</v>
       </c>
       <c r="E440" s="30"/>
-      <c r="F440" s="44"/>
+      <c r="F440" s="43"/>
       <c r="G440" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17673,7 +17677,7 @@
         <v>761</v>
       </c>
       <c r="E441" s="31"/>
-      <c r="F441" s="46" t="s">
+      <c r="F441" s="45" t="s">
         <v>767</v>
       </c>
       <c r="G441" s="20">
@@ -17707,7 +17711,7 @@
       </c>
       <c r="D442" s="13"/>
       <c r="E442" s="30"/>
-      <c r="F442" s="44"/>
+      <c r="F442" s="43"/>
       <c r="G442" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17739,7 +17743,7 @@
       </c>
       <c r="D443" s="13"/>
       <c r="E443" s="30"/>
-      <c r="F443" s="44"/>
+      <c r="F443" s="43"/>
       <c r="G443" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17773,7 +17777,7 @@
         <v>422</v>
       </c>
       <c r="E444" s="30"/>
-      <c r="F444" s="44"/>
+      <c r="F444" s="43"/>
       <c r="G444" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17809,7 +17813,7 @@
       <c r="E445" s="30">
         <v>16.579999999999998</v>
       </c>
-      <c r="F445" s="47"/>
+      <c r="F445" s="46"/>
       <c r="G445" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17845,7 +17849,7 @@
       <c r="E446" s="30">
         <v>11</v>
       </c>
-      <c r="F446" s="44"/>
+      <c r="F446" s="43"/>
       <c r="G446" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17879,7 +17883,7 @@
         <v>471</v>
       </c>
       <c r="E447" s="30"/>
-      <c r="F447" s="44"/>
+      <c r="F447" s="43"/>
       <c r="G447" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17911,7 +17915,7 @@
         <v>489</v>
       </c>
       <c r="E448" s="31"/>
-      <c r="F448" s="46" t="s">
+      <c r="F448" s="45" t="s">
         <v>768</v>
       </c>
       <c r="G448" s="20">
@@ -17945,7 +17949,7 @@
       </c>
       <c r="D449" s="13"/>
       <c r="E449" s="30"/>
-      <c r="F449" s="44"/>
+      <c r="F449" s="43"/>
       <c r="G449" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17981,7 +17985,7 @@
       <c r="E450" s="30">
         <v>9</v>
       </c>
-      <c r="F450" s="47" t="s">
+      <c r="F450" s="46" t="s">
         <v>795</v>
       </c>
       <c r="G450" s="20">
@@ -18017,7 +18021,7 @@
       <c r="E451" s="30">
         <v>10</v>
       </c>
-      <c r="F451" s="44"/>
+      <c r="F451" s="43"/>
       <c r="G451" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -18049,7 +18053,7 @@
       </c>
       <c r="D452" s="13"/>
       <c r="E452" s="30"/>
-      <c r="F452" s="44"/>
+      <c r="F452" s="43"/>
       <c r="G452" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -18085,7 +18089,7 @@
       <c r="E453" s="30">
         <v>8.83</v>
       </c>
-      <c r="F453" s="44"/>
+      <c r="F453" s="43"/>
       <c r="G453" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -18121,7 +18125,7 @@
       <c r="E454" s="30">
         <v>20</v>
       </c>
-      <c r="F454" s="44">
+      <c r="F454" s="43">
         <v>15</v>
       </c>
       <c r="G454" s="20">
@@ -18153,7 +18157,7 @@
       <c r="C455" s="3"/>
       <c r="D455" s="14"/>
       <c r="E455" s="31"/>
-      <c r="F455" s="46" t="s">
+      <c r="F455" s="45" t="s">
         <v>769</v>
       </c>
       <c r="G455" s="20">
@@ -18178,20 +18182,20 @@
       </c>
     </row>
     <row r="456" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A456" s="64" t="s">
+      <c r="A456" s="63" t="s">
         <v>469</v>
       </c>
-      <c r="B456" s="65"/>
-      <c r="C456" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="D456" s="67" t="s">
+      <c r="B456" s="64"/>
+      <c r="C456" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D456" s="66" t="s">
         <v>456</v>
       </c>
-      <c r="E456" s="68">
+      <c r="E456" s="67">
         <v>8</v>
       </c>
-      <c r="F456" s="69"/>
+      <c r="F456" s="68"/>
       <c r="G456" s="20">
         <f t="shared" ref="G456:G512" si="33">COUNTA(A456)</f>
         <v>1</v>
@@ -18223,7 +18227,7 @@
       </c>
       <c r="D457" s="13"/>
       <c r="E457" s="30"/>
-      <c r="F457" s="44"/>
+      <c r="F457" s="43"/>
       <c r="G457" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18246,20 +18250,20 @@
       </c>
     </row>
     <row r="458" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A458" s="64" t="s">
+      <c r="A458" s="63" t="s">
         <v>157</v>
       </c>
-      <c r="B458" s="65"/>
-      <c r="C458" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="D458" s="67" t="s">
+      <c r="B458" s="64"/>
+      <c r="C458" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D458" s="66" t="s">
         <v>430</v>
       </c>
-      <c r="E458" s="68">
+      <c r="E458" s="67">
         <v>14</v>
       </c>
-      <c r="F458" s="69"/>
+      <c r="F458" s="68"/>
       <c r="G458" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18289,7 +18293,7 @@
       <c r="C459" s="40"/>
       <c r="D459" s="41"/>
       <c r="E459" s="42"/>
-      <c r="F459" s="73" t="s">
+      <c r="F459" s="72" t="s">
         <v>725</v>
       </c>
       <c r="G459" s="20">
@@ -18323,7 +18327,7 @@
       </c>
       <c r="D460" s="13"/>
       <c r="E460" s="30"/>
-      <c r="F460" s="44"/>
+      <c r="F460" s="43"/>
       <c r="G460" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18355,7 +18359,7 @@
       </c>
       <c r="D461" s="13"/>
       <c r="E461" s="30"/>
-      <c r="F461" s="44"/>
+      <c r="F461" s="43"/>
       <c r="G461" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18385,7 +18389,7 @@
       <c r="C462" s="3"/>
       <c r="D462" s="14"/>
       <c r="E462" s="31"/>
-      <c r="F462" s="46" t="s">
+      <c r="F462" s="45" t="s">
         <v>772</v>
       </c>
       <c r="G462" s="20">
@@ -18417,7 +18421,7 @@
       <c r="C463" s="3"/>
       <c r="D463" s="14"/>
       <c r="E463" s="31"/>
-      <c r="F463" s="46" t="s">
+      <c r="F463" s="45" t="s">
         <v>773</v>
       </c>
       <c r="G463" s="20">
@@ -18451,7 +18455,7 @@
         <v>774</v>
       </c>
       <c r="E464" s="31"/>
-      <c r="F464" s="46" t="s">
+      <c r="F464" s="45" t="s">
         <v>775</v>
       </c>
       <c r="G464" s="20">
@@ -18485,7 +18489,7 @@
       </c>
       <c r="D465" s="13"/>
       <c r="E465" s="30"/>
-      <c r="F465" s="44"/>
+      <c r="F465" s="43"/>
       <c r="G465" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18509,7 +18513,7 @@
       </c>
       <c r="D466" s="13"/>
       <c r="E466" s="30"/>
-      <c r="F466" s="44"/>
+      <c r="F466" s="43"/>
       <c r="G466" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18539,7 +18543,7 @@
       <c r="C467" s="3"/>
       <c r="D467" s="14"/>
       <c r="E467" s="31"/>
-      <c r="F467" s="46" t="s">
+      <c r="F467" s="45" t="s">
         <v>776</v>
       </c>
       <c r="G467" s="20">
@@ -18575,7 +18579,7 @@
         <v>430</v>
       </c>
       <c r="E468" s="30"/>
-      <c r="F468" s="44"/>
+      <c r="F468" s="43"/>
       <c r="G468" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18607,7 +18611,7 @@
       </c>
       <c r="D469" s="13"/>
       <c r="E469" s="30"/>
-      <c r="F469" s="44"/>
+      <c r="F469" s="43"/>
       <c r="G469" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18639,7 +18643,7 @@
         <v>778</v>
       </c>
       <c r="E470" s="31"/>
-      <c r="F470" s="46" t="s">
+      <c r="F470" s="45" t="s">
         <v>777</v>
       </c>
       <c r="G470" s="20">
@@ -18677,7 +18681,7 @@
       <c r="E471" s="30">
         <v>28</v>
       </c>
-      <c r="F471" s="44"/>
+      <c r="F471" s="43"/>
       <c r="G471" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18707,7 +18711,7 @@
       <c r="C472" s="3"/>
       <c r="D472" s="14"/>
       <c r="E472" s="31"/>
-      <c r="F472" s="46" t="s">
+      <c r="F472" s="45" t="s">
         <v>779</v>
       </c>
       <c r="G472" s="20">
@@ -18743,7 +18747,7 @@
         <v>430</v>
       </c>
       <c r="E473" s="30"/>
-      <c r="F473" s="44"/>
+      <c r="F473" s="43"/>
       <c r="G473" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18773,7 +18777,7 @@
       <c r="C474" s="3"/>
       <c r="D474" s="14"/>
       <c r="E474" s="31"/>
-      <c r="F474" s="46" t="s">
+      <c r="F474" s="45" t="s">
         <v>780</v>
       </c>
       <c r="G474" s="20">
@@ -18805,7 +18809,7 @@
       <c r="C475" s="3"/>
       <c r="D475" s="14"/>
       <c r="E475" s="31"/>
-      <c r="F475" s="46" t="s">
+      <c r="F475" s="45" t="s">
         <v>782</v>
       </c>
       <c r="G475" s="20">
@@ -18839,7 +18843,7 @@
       </c>
       <c r="D476" s="13"/>
       <c r="E476" s="30"/>
-      <c r="F476" s="44"/>
+      <c r="F476" s="43"/>
       <c r="G476" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18871,7 +18875,7 @@
       </c>
       <c r="D477" s="13"/>
       <c r="E477" s="30"/>
-      <c r="F477" s="44"/>
+      <c r="F477" s="43"/>
       <c r="G477" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18907,7 +18911,7 @@
       <c r="E478" s="30">
         <v>13.43</v>
       </c>
-      <c r="F478" s="44"/>
+      <c r="F478" s="43"/>
       <c r="G478" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18939,7 +18943,7 @@
       </c>
       <c r="D479" s="13"/>
       <c r="E479" s="30"/>
-      <c r="F479" s="44"/>
+      <c r="F479" s="43"/>
       <c r="G479" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18969,7 +18973,7 @@
       <c r="C480" s="3"/>
       <c r="D480" s="14"/>
       <c r="E480" s="31"/>
-      <c r="F480" s="46" t="s">
+      <c r="F480" s="45" t="s">
         <v>783</v>
       </c>
       <c r="G480" s="20">
@@ -19007,7 +19011,7 @@
       <c r="E481" s="30">
         <v>29</v>
       </c>
-      <c r="F481" s="44"/>
+      <c r="F481" s="43"/>
       <c r="G481" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19033,7 +19037,7 @@
         <v>784</v>
       </c>
       <c r="E482" s="30"/>
-      <c r="F482" s="44"/>
+      <c r="F482" s="43"/>
       <c r="G482" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19069,7 +19073,7 @@
       <c r="E483" s="30">
         <v>15</v>
       </c>
-      <c r="F483" s="44">
+      <c r="F483" s="43">
         <v>40</v>
       </c>
       <c r="G483" s="20">
@@ -19103,7 +19107,7 @@
         <v>786</v>
       </c>
       <c r="E484" s="31"/>
-      <c r="F484" s="46" t="s">
+      <c r="F484" s="45" t="s">
         <v>785</v>
       </c>
       <c r="G484" s="20">
@@ -19135,7 +19139,7 @@
       <c r="C485" s="3"/>
       <c r="D485" s="14"/>
       <c r="E485" s="31"/>
-      <c r="F485" s="46" t="s">
+      <c r="F485" s="45" t="s">
         <v>787</v>
       </c>
       <c r="G485" s="20">
@@ -19169,7 +19173,7 @@
       </c>
       <c r="D486" s="13"/>
       <c r="E486" s="30"/>
-      <c r="F486" s="44"/>
+      <c r="F486" s="43"/>
       <c r="G486" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19193,7 +19197,7 @@
       </c>
       <c r="D487" s="13"/>
       <c r="E487" s="30"/>
-      <c r="F487" s="44"/>
+      <c r="F487" s="43"/>
       <c r="G487" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19225,7 +19229,7 @@
       </c>
       <c r="D488" s="13"/>
       <c r="E488" s="30"/>
-      <c r="F488" s="47"/>
+      <c r="F488" s="46"/>
       <c r="G488" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19259,7 +19263,7 @@
         <v>422</v>
       </c>
       <c r="E489" s="30"/>
-      <c r="F489" s="44"/>
+      <c r="F489" s="43"/>
       <c r="G489" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19293,7 +19297,7 @@
         <v>422</v>
       </c>
       <c r="E490" s="30"/>
-      <c r="F490" s="44"/>
+      <c r="F490" s="43"/>
       <c r="G490" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19323,7 +19327,7 @@
       <c r="C491" s="3"/>
       <c r="D491" s="14"/>
       <c r="E491" s="31"/>
-      <c r="F491" s="46" t="s">
+      <c r="F491" s="45" t="s">
         <v>788</v>
       </c>
       <c r="G491" s="20">
@@ -19357,7 +19361,7 @@
       </c>
       <c r="D492" s="13"/>
       <c r="E492" s="30"/>
-      <c r="F492" s="44"/>
+      <c r="F492" s="43"/>
       <c r="G492" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19389,7 +19393,7 @@
       </c>
       <c r="D493" s="13"/>
       <c r="E493" s="30"/>
-      <c r="F493" s="44"/>
+      <c r="F493" s="43"/>
       <c r="G493" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19421,7 +19425,7 @@
       </c>
       <c r="D494" s="13"/>
       <c r="E494" s="30"/>
-      <c r="F494" s="44"/>
+      <c r="F494" s="43"/>
       <c r="G494" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19453,7 +19457,7 @@
       </c>
       <c r="D495" s="13"/>
       <c r="E495" s="30"/>
-      <c r="F495" s="44"/>
+      <c r="F495" s="43"/>
       <c r="G495" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19487,7 +19491,7 @@
         <v>401</v>
       </c>
       <c r="E496" s="30"/>
-      <c r="F496" s="44"/>
+      <c r="F496" s="43"/>
       <c r="G496" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19523,7 +19527,7 @@
       <c r="E497" s="30">
         <v>10</v>
       </c>
-      <c r="F497" s="44"/>
+      <c r="F497" s="43"/>
       <c r="G497" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19555,7 +19559,7 @@
       </c>
       <c r="D498" s="13"/>
       <c r="E498" s="30"/>
-      <c r="F498" s="44"/>
+      <c r="F498" s="43"/>
       <c r="G498" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19585,7 +19589,7 @@
       <c r="C499" s="3"/>
       <c r="D499" s="14"/>
       <c r="E499" s="31"/>
-      <c r="F499" s="46" t="s">
+      <c r="F499" s="45" t="s">
         <v>789</v>
       </c>
       <c r="G499" s="20">
@@ -19623,7 +19627,7 @@
       <c r="E500" s="30">
         <v>19</v>
       </c>
-      <c r="F500" s="44"/>
+      <c r="F500" s="43"/>
       <c r="G500" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19655,7 +19659,7 @@
       </c>
       <c r="D501" s="13"/>
       <c r="E501" s="30"/>
-      <c r="F501" s="44"/>
+      <c r="F501" s="43"/>
       <c r="G501" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19685,7 +19689,7 @@
       <c r="C502" s="3"/>
       <c r="D502" s="14"/>
       <c r="E502" s="31"/>
-      <c r="F502" s="46" t="s">
+      <c r="F502" s="45" t="s">
         <v>790</v>
       </c>
       <c r="G502" s="20">
@@ -19719,7 +19723,7 @@
       </c>
       <c r="D503" s="13"/>
       <c r="E503" s="30"/>
-      <c r="F503" s="44"/>
+      <c r="F503" s="43"/>
       <c r="G503" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19751,7 +19755,7 @@
       </c>
       <c r="D504" s="13"/>
       <c r="E504" s="30"/>
-      <c r="F504" s="44"/>
+      <c r="F504" s="43"/>
       <c r="G504" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19785,7 +19789,7 @@
         <v>422</v>
       </c>
       <c r="E505" s="30"/>
-      <c r="F505" s="44"/>
+      <c r="F505" s="43"/>
       <c r="G505" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19815,7 +19819,7 @@
       <c r="C506" s="3"/>
       <c r="D506" s="14"/>
       <c r="E506" s="31"/>
-      <c r="F506" s="46" t="s">
+      <c r="F506" s="45" t="s">
         <v>791</v>
       </c>
       <c r="G506" s="20">
@@ -19847,7 +19851,7 @@
       <c r="C507" s="3"/>
       <c r="D507" s="14"/>
       <c r="E507" s="31"/>
-      <c r="F507" s="46" t="s">
+      <c r="F507" s="45" t="s">
         <v>792</v>
       </c>
       <c r="G507" s="20">
@@ -19881,7 +19885,7 @@
         <v>794</v>
       </c>
       <c r="E508" s="31"/>
-      <c r="F508" s="46" t="s">
+      <c r="F508" s="45" t="s">
         <v>793</v>
       </c>
       <c r="G508" s="20">
@@ -19911,7 +19915,7 @@
       <c r="C509" s="35"/>
       <c r="D509" s="36"/>
       <c r="E509" s="37"/>
-      <c r="F509" s="45"/>
+      <c r="F509" s="44"/>
       <c r="G509" s="20">
         <f t="shared" si="33"/>
         <v>0</v>
@@ -19939,7 +19943,7 @@
       <c r="C510" s="35"/>
       <c r="D510" s="36"/>
       <c r="E510" s="37"/>
-      <c r="F510" s="45"/>
+      <c r="F510" s="44"/>
       <c r="G510" s="20">
         <f t="shared" si="33"/>
         <v>0</v>
@@ -19967,7 +19971,7 @@
       <c r="C511" s="35"/>
       <c r="D511" s="36"/>
       <c r="E511" s="37"/>
-      <c r="F511" s="45"/>
+      <c r="F511" s="44"/>
       <c r="G511" s="20">
         <f t="shared" si="33"/>
         <v>0</v>
@@ -19995,7 +19999,7 @@
       <c r="C512" s="35"/>
       <c r="D512" s="36"/>
       <c r="E512" s="37"/>
-      <c r="F512" s="45"/>
+      <c r="F512" s="44"/>
       <c r="G512" s="20">
         <f t="shared" si="33"/>
         <v>0</v>
@@ -20018,2009 +20022,2009 @@
       </c>
     </row>
     <row r="513" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A513" s="49"/>
-      <c r="B513" s="51"/>
-      <c r="C513" s="49"/>
-      <c r="D513" s="53"/>
-      <c r="E513" s="55"/>
-      <c r="F513" s="58"/>
-      <c r="G513" s="79"/>
+      <c r="A513" s="48"/>
+      <c r="B513" s="50"/>
+      <c r="C513" s="48"/>
+      <c r="D513" s="52"/>
+      <c r="E513" s="54"/>
+      <c r="F513" s="57"/>
+      <c r="G513" s="78"/>
       <c r="H513" s="24"/>
-      <c r="I513" s="76"/>
+      <c r="I513" s="75"/>
       <c r="J513" s="24"/>
       <c r="K513" s="24"/>
       <c r="L513" s="24"/>
       <c r="M513" s="23"/>
     </row>
     <row r="514" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A514" s="49"/>
-      <c r="B514" s="50"/>
-      <c r="C514" s="49"/>
-      <c r="D514" s="53"/>
-      <c r="E514" s="54"/>
-      <c r="F514" s="57"/>
+      <c r="A514" s="48"/>
+      <c r="B514" s="49"/>
+      <c r="C514" s="48"/>
+      <c r="D514" s="52"/>
+      <c r="E514" s="53"/>
+      <c r="F514" s="56"/>
       <c r="I514" s="19"/>
     </row>
     <row r="515" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A515" s="49"/>
-      <c r="B515" s="50"/>
-      <c r="C515" s="49"/>
-      <c r="D515" s="53"/>
-      <c r="E515" s="54"/>
-      <c r="F515" s="57"/>
+      <c r="A515" s="48"/>
+      <c r="B515" s="49"/>
+      <c r="C515" s="48"/>
+      <c r="D515" s="52"/>
+      <c r="E515" s="53"/>
+      <c r="F515" s="56"/>
       <c r="I515" s="19"/>
     </row>
     <row r="516" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A516" s="49"/>
-      <c r="B516" s="50"/>
-      <c r="C516" s="49"/>
-      <c r="D516" s="53"/>
-      <c r="E516" s="54"/>
-      <c r="F516" s="57"/>
+      <c r="A516" s="48"/>
+      <c r="B516" s="49"/>
+      <c r="C516" s="48"/>
+      <c r="D516" s="52"/>
+      <c r="E516" s="53"/>
+      <c r="F516" s="56"/>
       <c r="I516" s="19"/>
     </row>
     <row r="517" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A517" s="49"/>
-      <c r="B517" s="50"/>
-      <c r="C517" s="49"/>
-      <c r="D517" s="53"/>
-      <c r="E517" s="54"/>
-      <c r="F517" s="57"/>
+      <c r="A517" s="48"/>
+      <c r="B517" s="49"/>
+      <c r="C517" s="48"/>
+      <c r="D517" s="52"/>
+      <c r="E517" s="53"/>
+      <c r="F517" s="56"/>
       <c r="I517" s="19"/>
     </row>
     <row r="518" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A518" s="49"/>
-      <c r="B518" s="50"/>
-      <c r="C518" s="49"/>
-      <c r="D518" s="53"/>
-      <c r="E518" s="54"/>
-      <c r="F518" s="57"/>
+      <c r="A518" s="48"/>
+      <c r="B518" s="49"/>
+      <c r="C518" s="48"/>
+      <c r="D518" s="52"/>
+      <c r="E518" s="53"/>
+      <c r="F518" s="56"/>
       <c r="I518" s="19"/>
     </row>
     <row r="519" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A519" s="49"/>
-      <c r="B519" s="50"/>
-      <c r="C519" s="49"/>
-      <c r="D519" s="53"/>
-      <c r="E519" s="54"/>
-      <c r="F519" s="57"/>
+      <c r="A519" s="48"/>
+      <c r="B519" s="49"/>
+      <c r="C519" s="48"/>
+      <c r="D519" s="52"/>
+      <c r="E519" s="53"/>
+      <c r="F519" s="56"/>
       <c r="I519" s="19"/>
     </row>
     <row r="520" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A520" s="49"/>
-      <c r="B520" s="50"/>
-      <c r="C520" s="49"/>
-      <c r="D520" s="53"/>
-      <c r="E520" s="54"/>
-      <c r="F520" s="57"/>
+      <c r="A520" s="48"/>
+      <c r="B520" s="49"/>
+      <c r="C520" s="48"/>
+      <c r="D520" s="52"/>
+      <c r="E520" s="53"/>
+      <c r="F520" s="56"/>
       <c r="I520" s="19"/>
     </row>
     <row r="521" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A521" s="49"/>
-      <c r="B521" s="50"/>
-      <c r="C521" s="49"/>
-      <c r="D521" s="53"/>
-      <c r="E521" s="54"/>
-      <c r="F521" s="57"/>
+      <c r="A521" s="48"/>
+      <c r="B521" s="49"/>
+      <c r="C521" s="48"/>
+      <c r="D521" s="52"/>
+      <c r="E521" s="53"/>
+      <c r="F521" s="56"/>
       <c r="I521" s="19"/>
     </row>
     <row r="522" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A522" s="49"/>
-      <c r="B522" s="50"/>
-      <c r="C522" s="49"/>
-      <c r="D522" s="53"/>
-      <c r="E522" s="54"/>
-      <c r="F522" s="57"/>
+      <c r="A522" s="48"/>
+      <c r="B522" s="49"/>
+      <c r="C522" s="48"/>
+      <c r="D522" s="52"/>
+      <c r="E522" s="53"/>
+      <c r="F522" s="56"/>
       <c r="I522" s="19"/>
     </row>
     <row r="523" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A523" s="49"/>
-      <c r="B523" s="50"/>
-      <c r="C523" s="49"/>
-      <c r="D523" s="53"/>
-      <c r="E523" s="54"/>
-      <c r="F523" s="57"/>
+      <c r="A523" s="48"/>
+      <c r="B523" s="49"/>
+      <c r="C523" s="48"/>
+      <c r="D523" s="52"/>
+      <c r="E523" s="53"/>
+      <c r="F523" s="56"/>
       <c r="I523" s="19"/>
     </row>
     <row r="524" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A524" s="49"/>
-      <c r="B524" s="50"/>
-      <c r="C524" s="49"/>
-      <c r="D524" s="53"/>
-      <c r="E524" s="54"/>
-      <c r="F524" s="57"/>
+      <c r="A524" s="48"/>
+      <c r="B524" s="49"/>
+      <c r="C524" s="48"/>
+      <c r="D524" s="52"/>
+      <c r="E524" s="53"/>
+      <c r="F524" s="56"/>
       <c r="I524" s="19"/>
     </row>
     <row r="525" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A525" s="49"/>
-      <c r="B525" s="50"/>
-      <c r="C525" s="49"/>
-      <c r="D525" s="53"/>
-      <c r="E525" s="54"/>
-      <c r="F525" s="57"/>
+      <c r="A525" s="48"/>
+      <c r="B525" s="49"/>
+      <c r="C525" s="48"/>
+      <c r="D525" s="52"/>
+      <c r="E525" s="53"/>
+      <c r="F525" s="56"/>
       <c r="I525" s="19"/>
     </row>
     <row r="526" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A526" s="49"/>
-      <c r="B526" s="50"/>
-      <c r="C526" s="49"/>
-      <c r="D526" s="53"/>
-      <c r="E526" s="54"/>
-      <c r="F526" s="57"/>
+      <c r="A526" s="48"/>
+      <c r="B526" s="49"/>
+      <c r="C526" s="48"/>
+      <c r="D526" s="52"/>
+      <c r="E526" s="53"/>
+      <c r="F526" s="56"/>
       <c r="I526" s="19"/>
     </row>
     <row r="527" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A527" s="49"/>
-      <c r="B527" s="50"/>
-      <c r="C527" s="49"/>
-      <c r="D527" s="53"/>
-      <c r="E527" s="54"/>
-      <c r="F527" s="57"/>
+      <c r="A527" s="48"/>
+      <c r="B527" s="49"/>
+      <c r="C527" s="48"/>
+      <c r="D527" s="52"/>
+      <c r="E527" s="53"/>
+      <c r="F527" s="56"/>
       <c r="I527" s="19"/>
     </row>
     <row r="528" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A528" s="49"/>
-      <c r="B528" s="50"/>
-      <c r="C528" s="49"/>
-      <c r="D528" s="53"/>
-      <c r="E528" s="54"/>
-      <c r="F528" s="57"/>
+      <c r="A528" s="48"/>
+      <c r="B528" s="49"/>
+      <c r="C528" s="48"/>
+      <c r="D528" s="52"/>
+      <c r="E528" s="53"/>
+      <c r="F528" s="56"/>
       <c r="I528" s="19"/>
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A529" s="49"/>
-      <c r="B529" s="50"/>
-      <c r="C529" s="49"/>
-      <c r="D529" s="53"/>
-      <c r="E529" s="54"/>
-      <c r="F529" s="57"/>
+      <c r="A529" s="48"/>
+      <c r="B529" s="49"/>
+      <c r="C529" s="48"/>
+      <c r="D529" s="52"/>
+      <c r="E529" s="53"/>
+      <c r="F529" s="56"/>
       <c r="I529" s="19"/>
     </row>
     <row r="530" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A530" s="49"/>
-      <c r="B530" s="50"/>
-      <c r="C530" s="49"/>
-      <c r="D530" s="53"/>
-      <c r="E530" s="54"/>
-      <c r="F530" s="57"/>
+      <c r="A530" s="48"/>
+      <c r="B530" s="49"/>
+      <c r="C530" s="48"/>
+      <c r="D530" s="52"/>
+      <c r="E530" s="53"/>
+      <c r="F530" s="56"/>
       <c r="I530" s="19"/>
     </row>
     <row r="531" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A531" s="49"/>
-      <c r="B531" s="50"/>
-      <c r="C531" s="49"/>
-      <c r="D531" s="53"/>
-      <c r="E531" s="54"/>
-      <c r="F531" s="57"/>
+      <c r="A531" s="48"/>
+      <c r="B531" s="49"/>
+      <c r="C531" s="48"/>
+      <c r="D531" s="52"/>
+      <c r="E531" s="53"/>
+      <c r="F531" s="56"/>
       <c r="I531" s="19"/>
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A532" s="49"/>
-      <c r="B532" s="50"/>
-      <c r="C532" s="49"/>
-      <c r="D532" s="53"/>
-      <c r="E532" s="54"/>
-      <c r="F532" s="57"/>
+      <c r="A532" s="48"/>
+      <c r="B532" s="49"/>
+      <c r="C532" s="48"/>
+      <c r="D532" s="52"/>
+      <c r="E532" s="53"/>
+      <c r="F532" s="56"/>
       <c r="I532" s="19"/>
     </row>
     <row r="533" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A533" s="49"/>
-      <c r="B533" s="50"/>
-      <c r="C533" s="49"/>
-      <c r="D533" s="53"/>
-      <c r="E533" s="54"/>
-      <c r="F533" s="57"/>
+      <c r="A533" s="48"/>
+      <c r="B533" s="49"/>
+      <c r="C533" s="48"/>
+      <c r="D533" s="52"/>
+      <c r="E533" s="53"/>
+      <c r="F533" s="56"/>
       <c r="I533" s="19"/>
     </row>
     <row r="534" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A534" s="49"/>
-      <c r="B534" s="50"/>
-      <c r="C534" s="49"/>
-      <c r="D534" s="53"/>
-      <c r="E534" s="54"/>
-      <c r="F534" s="57"/>
+      <c r="A534" s="48"/>
+      <c r="B534" s="49"/>
+      <c r="C534" s="48"/>
+      <c r="D534" s="52"/>
+      <c r="E534" s="53"/>
+      <c r="F534" s="56"/>
       <c r="I534" s="19"/>
     </row>
     <row r="535" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A535" s="49"/>
-      <c r="B535" s="50"/>
-      <c r="C535" s="49"/>
-      <c r="D535" s="53"/>
-      <c r="E535" s="54"/>
-      <c r="F535" s="57"/>
+      <c r="A535" s="48"/>
+      <c r="B535" s="49"/>
+      <c r="C535" s="48"/>
+      <c r="D535" s="52"/>
+      <c r="E535" s="53"/>
+      <c r="F535" s="56"/>
       <c r="I535" s="19"/>
     </row>
     <row r="536" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A536" s="49"/>
-      <c r="B536" s="50"/>
-      <c r="C536" s="49"/>
-      <c r="D536" s="53"/>
-      <c r="E536" s="54"/>
-      <c r="F536" s="57"/>
+      <c r="A536" s="48"/>
+      <c r="B536" s="49"/>
+      <c r="C536" s="48"/>
+      <c r="D536" s="52"/>
+      <c r="E536" s="53"/>
+      <c r="F536" s="56"/>
       <c r="I536" s="19"/>
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A537" s="49"/>
-      <c r="B537" s="50"/>
-      <c r="C537" s="49"/>
-      <c r="D537" s="53"/>
-      <c r="E537" s="54"/>
-      <c r="F537" s="57"/>
+      <c r="A537" s="48"/>
+      <c r="B537" s="49"/>
+      <c r="C537" s="48"/>
+      <c r="D537" s="52"/>
+      <c r="E537" s="53"/>
+      <c r="F537" s="56"/>
       <c r="I537" s="19"/>
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A538" s="49"/>
-      <c r="B538" s="50"/>
-      <c r="C538" s="49"/>
-      <c r="D538" s="53"/>
-      <c r="E538" s="54"/>
-      <c r="F538" s="57"/>
+      <c r="A538" s="48"/>
+      <c r="B538" s="49"/>
+      <c r="C538" s="48"/>
+      <c r="D538" s="52"/>
+      <c r="E538" s="53"/>
+      <c r="F538" s="56"/>
       <c r="I538" s="19"/>
     </row>
     <row r="539" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A539" s="49"/>
-      <c r="B539" s="50"/>
-      <c r="C539" s="49"/>
-      <c r="D539" s="53"/>
-      <c r="E539" s="54"/>
-      <c r="F539" s="57"/>
+      <c r="A539" s="48"/>
+      <c r="B539" s="49"/>
+      <c r="C539" s="48"/>
+      <c r="D539" s="52"/>
+      <c r="E539" s="53"/>
+      <c r="F539" s="56"/>
       <c r="I539" s="19"/>
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A540" s="49"/>
-      <c r="B540" s="50"/>
-      <c r="C540" s="49"/>
-      <c r="D540" s="53"/>
-      <c r="E540" s="54"/>
-      <c r="F540" s="57"/>
+      <c r="A540" s="48"/>
+      <c r="B540" s="49"/>
+      <c r="C540" s="48"/>
+      <c r="D540" s="52"/>
+      <c r="E540" s="53"/>
+      <c r="F540" s="56"/>
       <c r="I540" s="19"/>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A541" s="49"/>
-      <c r="B541" s="50"/>
-      <c r="C541" s="49"/>
-      <c r="D541" s="53"/>
-      <c r="E541" s="54"/>
-      <c r="F541" s="57"/>
+      <c r="A541" s="48"/>
+      <c r="B541" s="49"/>
+      <c r="C541" s="48"/>
+      <c r="D541" s="52"/>
+      <c r="E541" s="53"/>
+      <c r="F541" s="56"/>
       <c r="I541" s="19"/>
     </row>
     <row r="542" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A542" s="49"/>
-      <c r="B542" s="50"/>
-      <c r="C542" s="49"/>
-      <c r="D542" s="53"/>
-      <c r="E542" s="54"/>
-      <c r="F542" s="57"/>
+      <c r="A542" s="48"/>
+      <c r="B542" s="49"/>
+      <c r="C542" s="48"/>
+      <c r="D542" s="52"/>
+      <c r="E542" s="53"/>
+      <c r="F542" s="56"/>
       <c r="I542" s="19"/>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A543" s="49"/>
-      <c r="B543" s="50"/>
-      <c r="C543" s="49"/>
-      <c r="D543" s="53"/>
-      <c r="E543" s="54"/>
-      <c r="F543" s="57"/>
+      <c r="A543" s="48"/>
+      <c r="B543" s="49"/>
+      <c r="C543" s="48"/>
+      <c r="D543" s="52"/>
+      <c r="E543" s="53"/>
+      <c r="F543" s="56"/>
       <c r="I543" s="19"/>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A544" s="49"/>
-      <c r="B544" s="50"/>
-      <c r="C544" s="49"/>
-      <c r="D544" s="53"/>
-      <c r="E544" s="54"/>
-      <c r="F544" s="57"/>
+      <c r="A544" s="48"/>
+      <c r="B544" s="49"/>
+      <c r="C544" s="48"/>
+      <c r="D544" s="52"/>
+      <c r="E544" s="53"/>
+      <c r="F544" s="56"/>
       <c r="I544" s="19"/>
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A545" s="49"/>
-      <c r="B545" s="50"/>
-      <c r="C545" s="49"/>
-      <c r="D545" s="53"/>
-      <c r="E545" s="54"/>
-      <c r="F545" s="57"/>
+      <c r="A545" s="48"/>
+      <c r="B545" s="49"/>
+      <c r="C545" s="48"/>
+      <c r="D545" s="52"/>
+      <c r="E545" s="53"/>
+      <c r="F545" s="56"/>
       <c r="I545" s="19"/>
     </row>
     <row r="546" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A546" s="49"/>
-      <c r="B546" s="50"/>
-      <c r="C546" s="49"/>
-      <c r="D546" s="53"/>
-      <c r="E546" s="54"/>
-      <c r="F546" s="57"/>
+      <c r="A546" s="48"/>
+      <c r="B546" s="49"/>
+      <c r="C546" s="48"/>
+      <c r="D546" s="52"/>
+      <c r="E546" s="53"/>
+      <c r="F546" s="56"/>
       <c r="I546" s="19"/>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A547" s="49"/>
-      <c r="B547" s="50"/>
-      <c r="C547" s="49"/>
-      <c r="D547" s="53"/>
-      <c r="E547" s="54"/>
-      <c r="F547" s="57"/>
+      <c r="A547" s="48"/>
+      <c r="B547" s="49"/>
+      <c r="C547" s="48"/>
+      <c r="D547" s="52"/>
+      <c r="E547" s="53"/>
+      <c r="F547" s="56"/>
       <c r="I547" s="19"/>
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A548" s="49"/>
-      <c r="B548" s="50"/>
-      <c r="C548" s="49"/>
-      <c r="D548" s="53"/>
-      <c r="E548" s="54"/>
-      <c r="F548" s="57"/>
+      <c r="A548" s="48"/>
+      <c r="B548" s="49"/>
+      <c r="C548" s="48"/>
+      <c r="D548" s="52"/>
+      <c r="E548" s="53"/>
+      <c r="F548" s="56"/>
       <c r="I548" s="19"/>
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A549" s="49"/>
-      <c r="B549" s="50"/>
-      <c r="C549" s="49"/>
-      <c r="D549" s="53"/>
-      <c r="E549" s="54"/>
-      <c r="F549" s="57"/>
+      <c r="A549" s="48"/>
+      <c r="B549" s="49"/>
+      <c r="C549" s="48"/>
+      <c r="D549" s="52"/>
+      <c r="E549" s="53"/>
+      <c r="F549" s="56"/>
       <c r="I549" s="19"/>
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A550" s="49"/>
-      <c r="B550" s="50"/>
-      <c r="C550" s="49"/>
-      <c r="D550" s="53"/>
-      <c r="E550" s="54"/>
-      <c r="F550" s="57"/>
+      <c r="A550" s="48"/>
+      <c r="B550" s="49"/>
+      <c r="C550" s="48"/>
+      <c r="D550" s="52"/>
+      <c r="E550" s="53"/>
+      <c r="F550" s="56"/>
       <c r="I550" s="19"/>
     </row>
     <row r="551" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A551" s="49"/>
-      <c r="B551" s="50"/>
-      <c r="C551" s="49"/>
-      <c r="D551" s="53"/>
-      <c r="E551" s="54"/>
-      <c r="F551" s="57"/>
+      <c r="A551" s="48"/>
+      <c r="B551" s="49"/>
+      <c r="C551" s="48"/>
+      <c r="D551" s="52"/>
+      <c r="E551" s="53"/>
+      <c r="F551" s="56"/>
       <c r="I551" s="19"/>
     </row>
     <row r="552" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A552" s="49"/>
-      <c r="B552" s="50"/>
-      <c r="C552" s="49"/>
-      <c r="D552" s="53"/>
-      <c r="E552" s="54"/>
-      <c r="F552" s="57"/>
+      <c r="A552" s="48"/>
+      <c r="B552" s="49"/>
+      <c r="C552" s="48"/>
+      <c r="D552" s="52"/>
+      <c r="E552" s="53"/>
+      <c r="F552" s="56"/>
       <c r="I552" s="19"/>
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A553" s="49"/>
-      <c r="B553" s="50"/>
-      <c r="C553" s="49"/>
-      <c r="D553" s="53"/>
-      <c r="E553" s="54"/>
-      <c r="F553" s="57"/>
+      <c r="A553" s="48"/>
+      <c r="B553" s="49"/>
+      <c r="C553" s="48"/>
+      <c r="D553" s="52"/>
+      <c r="E553" s="53"/>
+      <c r="F553" s="56"/>
       <c r="I553" s="19"/>
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A554" s="49"/>
-      <c r="B554" s="50"/>
-      <c r="C554" s="49"/>
-      <c r="D554" s="53"/>
-      <c r="E554" s="54"/>
-      <c r="F554" s="57"/>
+      <c r="A554" s="48"/>
+      <c r="B554" s="49"/>
+      <c r="C554" s="48"/>
+      <c r="D554" s="52"/>
+      <c r="E554" s="53"/>
+      <c r="F554" s="56"/>
       <c r="I554" s="19"/>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A555" s="49"/>
-      <c r="B555" s="50"/>
-      <c r="C555" s="49"/>
-      <c r="D555" s="53"/>
-      <c r="E555" s="54"/>
-      <c r="F555" s="57"/>
+      <c r="A555" s="48"/>
+      <c r="B555" s="49"/>
+      <c r="C555" s="48"/>
+      <c r="D555" s="52"/>
+      <c r="E555" s="53"/>
+      <c r="F555" s="56"/>
       <c r="I555" s="19"/>
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A556" s="49"/>
-      <c r="B556" s="50"/>
-      <c r="C556" s="49"/>
-      <c r="D556" s="53"/>
-      <c r="E556" s="54"/>
-      <c r="F556" s="57"/>
+      <c r="A556" s="48"/>
+      <c r="B556" s="49"/>
+      <c r="C556" s="48"/>
+      <c r="D556" s="52"/>
+      <c r="E556" s="53"/>
+      <c r="F556" s="56"/>
       <c r="I556" s="19"/>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A557" s="49"/>
-      <c r="B557" s="50"/>
-      <c r="C557" s="49"/>
-      <c r="D557" s="53"/>
-      <c r="E557" s="54"/>
-      <c r="F557" s="57"/>
+      <c r="A557" s="48"/>
+      <c r="B557" s="49"/>
+      <c r="C557" s="48"/>
+      <c r="D557" s="52"/>
+      <c r="E557" s="53"/>
+      <c r="F557" s="56"/>
       <c r="I557" s="19"/>
     </row>
     <row r="558" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A558" s="49"/>
-      <c r="B558" s="50"/>
-      <c r="C558" s="49"/>
-      <c r="D558" s="53"/>
-      <c r="E558" s="54"/>
-      <c r="F558" s="57"/>
+      <c r="A558" s="48"/>
+      <c r="B558" s="49"/>
+      <c r="C558" s="48"/>
+      <c r="D558" s="52"/>
+      <c r="E558" s="53"/>
+      <c r="F558" s="56"/>
       <c r="I558" s="19"/>
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A559" s="49"/>
-      <c r="B559" s="50"/>
-      <c r="C559" s="49"/>
-      <c r="D559" s="53"/>
-      <c r="E559" s="54"/>
-      <c r="F559" s="57"/>
+      <c r="A559" s="48"/>
+      <c r="B559" s="49"/>
+      <c r="C559" s="48"/>
+      <c r="D559" s="52"/>
+      <c r="E559" s="53"/>
+      <c r="F559" s="56"/>
       <c r="I559" s="19"/>
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A560" s="49"/>
-      <c r="B560" s="50"/>
-      <c r="C560" s="49"/>
-      <c r="D560" s="53"/>
-      <c r="E560" s="54"/>
-      <c r="F560" s="57"/>
+      <c r="A560" s="48"/>
+      <c r="B560" s="49"/>
+      <c r="C560" s="48"/>
+      <c r="D560" s="52"/>
+      <c r="E560" s="53"/>
+      <c r="F560" s="56"/>
       <c r="I560" s="19"/>
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A561" s="49"/>
-      <c r="B561" s="50"/>
-      <c r="C561" s="49"/>
-      <c r="D561" s="53"/>
-      <c r="E561" s="54"/>
-      <c r="F561" s="57"/>
+      <c r="A561" s="48"/>
+      <c r="B561" s="49"/>
+      <c r="C561" s="48"/>
+      <c r="D561" s="52"/>
+      <c r="E561" s="53"/>
+      <c r="F561" s="56"/>
       <c r="I561" s="19"/>
     </row>
     <row r="562" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A562" s="49"/>
-      <c r="B562" s="50"/>
-      <c r="C562" s="49"/>
-      <c r="D562" s="53"/>
-      <c r="E562" s="54"/>
-      <c r="F562" s="57"/>
+      <c r="A562" s="48"/>
+      <c r="B562" s="49"/>
+      <c r="C562" s="48"/>
+      <c r="D562" s="52"/>
+      <c r="E562" s="53"/>
+      <c r="F562" s="56"/>
       <c r="I562" s="19"/>
     </row>
     <row r="563" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A563" s="49"/>
-      <c r="B563" s="50"/>
-      <c r="C563" s="49"/>
-      <c r="D563" s="53"/>
-      <c r="E563" s="54"/>
-      <c r="F563" s="57"/>
+      <c r="A563" s="48"/>
+      <c r="B563" s="49"/>
+      <c r="C563" s="48"/>
+      <c r="D563" s="52"/>
+      <c r="E563" s="53"/>
+      <c r="F563" s="56"/>
       <c r="I563" s="19"/>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A564" s="49"/>
-      <c r="B564" s="50"/>
-      <c r="C564" s="49"/>
-      <c r="D564" s="53"/>
-      <c r="E564" s="54"/>
-      <c r="F564" s="57"/>
+      <c r="A564" s="48"/>
+      <c r="B564" s="49"/>
+      <c r="C564" s="48"/>
+      <c r="D564" s="52"/>
+      <c r="E564" s="53"/>
+      <c r="F564" s="56"/>
       <c r="I564" s="19"/>
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A565" s="49"/>
-      <c r="B565" s="50"/>
-      <c r="C565" s="49"/>
-      <c r="D565" s="53"/>
-      <c r="E565" s="54"/>
-      <c r="F565" s="57"/>
+      <c r="A565" s="48"/>
+      <c r="B565" s="49"/>
+      <c r="C565" s="48"/>
+      <c r="D565" s="52"/>
+      <c r="E565" s="53"/>
+      <c r="F565" s="56"/>
       <c r="I565" s="19"/>
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A566" s="49"/>
-      <c r="B566" s="50"/>
-      <c r="C566" s="49"/>
-      <c r="D566" s="53"/>
-      <c r="E566" s="54"/>
-      <c r="F566" s="57"/>
+      <c r="A566" s="48"/>
+      <c r="B566" s="49"/>
+      <c r="C566" s="48"/>
+      <c r="D566" s="52"/>
+      <c r="E566" s="53"/>
+      <c r="F566" s="56"/>
       <c r="I566" s="19"/>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A567" s="49"/>
-      <c r="B567" s="50"/>
-      <c r="C567" s="49"/>
-      <c r="D567" s="53"/>
-      <c r="E567" s="54"/>
-      <c r="F567" s="57"/>
+      <c r="A567" s="48"/>
+      <c r="B567" s="49"/>
+      <c r="C567" s="48"/>
+      <c r="D567" s="52"/>
+      <c r="E567" s="53"/>
+      <c r="F567" s="56"/>
       <c r="I567" s="19"/>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A568" s="49"/>
-      <c r="B568" s="50"/>
-      <c r="C568" s="49"/>
-      <c r="D568" s="53"/>
-      <c r="E568" s="54"/>
-      <c r="F568" s="57"/>
+      <c r="A568" s="48"/>
+      <c r="B568" s="49"/>
+      <c r="C568" s="48"/>
+      <c r="D568" s="52"/>
+      <c r="E568" s="53"/>
+      <c r="F568" s="56"/>
       <c r="I568" s="19"/>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A569" s="49"/>
-      <c r="B569" s="50"/>
-      <c r="C569" s="49"/>
-      <c r="D569" s="53"/>
-      <c r="E569" s="54"/>
-      <c r="F569" s="57"/>
+      <c r="A569" s="48"/>
+      <c r="B569" s="49"/>
+      <c r="C569" s="48"/>
+      <c r="D569" s="52"/>
+      <c r="E569" s="53"/>
+      <c r="F569" s="56"/>
       <c r="I569" s="19"/>
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A570" s="49"/>
-      <c r="B570" s="50"/>
-      <c r="C570" s="49"/>
-      <c r="D570" s="53"/>
-      <c r="E570" s="54"/>
-      <c r="F570" s="57"/>
+      <c r="A570" s="48"/>
+      <c r="B570" s="49"/>
+      <c r="C570" s="48"/>
+      <c r="D570" s="52"/>
+      <c r="E570" s="53"/>
+      <c r="F570" s="56"/>
       <c r="I570" s="19"/>
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A571" s="49"/>
-      <c r="B571" s="50"/>
-      <c r="C571" s="49"/>
-      <c r="D571" s="53"/>
-      <c r="E571" s="54"/>
-      <c r="F571" s="57"/>
+      <c r="A571" s="48"/>
+      <c r="B571" s="49"/>
+      <c r="C571" s="48"/>
+      <c r="D571" s="52"/>
+      <c r="E571" s="53"/>
+      <c r="F571" s="56"/>
       <c r="I571" s="19"/>
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A572" s="49"/>
-      <c r="B572" s="50"/>
-      <c r="C572" s="49"/>
-      <c r="D572" s="53"/>
-      <c r="E572" s="54"/>
-      <c r="F572" s="57"/>
+      <c r="A572" s="48"/>
+      <c r="B572" s="49"/>
+      <c r="C572" s="48"/>
+      <c r="D572" s="52"/>
+      <c r="E572" s="53"/>
+      <c r="F572" s="56"/>
       <c r="I572" s="19"/>
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A573" s="49"/>
-      <c r="B573" s="50"/>
-      <c r="C573" s="49"/>
-      <c r="D573" s="53"/>
-      <c r="E573" s="54"/>
-      <c r="F573" s="57"/>
+      <c r="A573" s="48"/>
+      <c r="B573" s="49"/>
+      <c r="C573" s="48"/>
+      <c r="D573" s="52"/>
+      <c r="E573" s="53"/>
+      <c r="F573" s="56"/>
       <c r="I573" s="19"/>
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A574" s="49"/>
-      <c r="B574" s="50"/>
-      <c r="C574" s="49"/>
-      <c r="D574" s="53"/>
-      <c r="E574" s="54"/>
-      <c r="F574" s="57"/>
+      <c r="A574" s="48"/>
+      <c r="B574" s="49"/>
+      <c r="C574" s="48"/>
+      <c r="D574" s="52"/>
+      <c r="E574" s="53"/>
+      <c r="F574" s="56"/>
       <c r="I574" s="19"/>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A575" s="49"/>
-      <c r="B575" s="50"/>
-      <c r="C575" s="49"/>
-      <c r="D575" s="53"/>
-      <c r="E575" s="54"/>
-      <c r="F575" s="57"/>
+      <c r="A575" s="48"/>
+      <c r="B575" s="49"/>
+      <c r="C575" s="48"/>
+      <c r="D575" s="52"/>
+      <c r="E575" s="53"/>
+      <c r="F575" s="56"/>
       <c r="I575" s="19"/>
     </row>
     <row r="576" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A576" s="49"/>
-      <c r="B576" s="50"/>
-      <c r="C576" s="49"/>
-      <c r="D576" s="53"/>
-      <c r="E576" s="54"/>
-      <c r="F576" s="57"/>
+      <c r="A576" s="48"/>
+      <c r="B576" s="49"/>
+      <c r="C576" s="48"/>
+      <c r="D576" s="52"/>
+      <c r="E576" s="53"/>
+      <c r="F576" s="56"/>
       <c r="I576" s="19"/>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A577" s="49"/>
-      <c r="B577" s="50"/>
-      <c r="C577" s="49"/>
-      <c r="D577" s="53"/>
-      <c r="E577" s="54"/>
-      <c r="F577" s="57"/>
+      <c r="A577" s="48"/>
+      <c r="B577" s="49"/>
+      <c r="C577" s="48"/>
+      <c r="D577" s="52"/>
+      <c r="E577" s="53"/>
+      <c r="F577" s="56"/>
       <c r="I577" s="19"/>
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A578" s="49"/>
-      <c r="B578" s="50"/>
-      <c r="C578" s="49"/>
-      <c r="D578" s="53"/>
-      <c r="E578" s="54"/>
-      <c r="F578" s="57"/>
+      <c r="A578" s="48"/>
+      <c r="B578" s="49"/>
+      <c r="C578" s="48"/>
+      <c r="D578" s="52"/>
+      <c r="E578" s="53"/>
+      <c r="F578" s="56"/>
       <c r="I578" s="19"/>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A579" s="49"/>
-      <c r="B579" s="50"/>
-      <c r="C579" s="49"/>
-      <c r="D579" s="53"/>
-      <c r="E579" s="54"/>
-      <c r="F579" s="57"/>
+      <c r="A579" s="48"/>
+      <c r="B579" s="49"/>
+      <c r="C579" s="48"/>
+      <c r="D579" s="52"/>
+      <c r="E579" s="53"/>
+      <c r="F579" s="56"/>
       <c r="I579" s="19"/>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A580" s="49"/>
-      <c r="B580" s="50"/>
-      <c r="C580" s="49"/>
-      <c r="D580" s="53"/>
-      <c r="E580" s="54"/>
-      <c r="F580" s="57"/>
+      <c r="A580" s="48"/>
+      <c r="B580" s="49"/>
+      <c r="C580" s="48"/>
+      <c r="D580" s="52"/>
+      <c r="E580" s="53"/>
+      <c r="F580" s="56"/>
       <c r="I580" s="19"/>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A581" s="49"/>
-      <c r="B581" s="50"/>
-      <c r="C581" s="49"/>
-      <c r="D581" s="53"/>
-      <c r="E581" s="54"/>
-      <c r="F581" s="57"/>
+      <c r="A581" s="48"/>
+      <c r="B581" s="49"/>
+      <c r="C581" s="48"/>
+      <c r="D581" s="52"/>
+      <c r="E581" s="53"/>
+      <c r="F581" s="56"/>
       <c r="I581" s="19"/>
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A582" s="49"/>
-      <c r="B582" s="50"/>
-      <c r="C582" s="49"/>
-      <c r="D582" s="53"/>
-      <c r="E582" s="54"/>
-      <c r="F582" s="57"/>
+      <c r="A582" s="48"/>
+      <c r="B582" s="49"/>
+      <c r="C582" s="48"/>
+      <c r="D582" s="52"/>
+      <c r="E582" s="53"/>
+      <c r="F582" s="56"/>
       <c r="I582" s="19"/>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A583" s="49"/>
-      <c r="B583" s="50"/>
-      <c r="C583" s="49"/>
-      <c r="D583" s="53"/>
-      <c r="E583" s="54"/>
-      <c r="F583" s="57"/>
+      <c r="A583" s="48"/>
+      <c r="B583" s="49"/>
+      <c r="C583" s="48"/>
+      <c r="D583" s="52"/>
+      <c r="E583" s="53"/>
+      <c r="F583" s="56"/>
       <c r="I583" s="19"/>
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A584" s="49"/>
-      <c r="B584" s="50"/>
-      <c r="C584" s="49"/>
-      <c r="D584" s="53"/>
-      <c r="E584" s="54"/>
-      <c r="F584" s="57"/>
+      <c r="A584" s="48"/>
+      <c r="B584" s="49"/>
+      <c r="C584" s="48"/>
+      <c r="D584" s="52"/>
+      <c r="E584" s="53"/>
+      <c r="F584" s="56"/>
       <c r="I584" s="19"/>
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A585" s="49"/>
-      <c r="B585" s="50"/>
-      <c r="C585" s="49"/>
-      <c r="D585" s="53"/>
-      <c r="E585" s="54"/>
-      <c r="F585" s="57"/>
+      <c r="A585" s="48"/>
+      <c r="B585" s="49"/>
+      <c r="C585" s="48"/>
+      <c r="D585" s="52"/>
+      <c r="E585" s="53"/>
+      <c r="F585" s="56"/>
       <c r="I585" s="19"/>
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A586" s="49"/>
-      <c r="B586" s="50"/>
-      <c r="C586" s="49"/>
-      <c r="D586" s="53"/>
-      <c r="E586" s="54"/>
-      <c r="F586" s="57"/>
+      <c r="A586" s="48"/>
+      <c r="B586" s="49"/>
+      <c r="C586" s="48"/>
+      <c r="D586" s="52"/>
+      <c r="E586" s="53"/>
+      <c r="F586" s="56"/>
       <c r="I586" s="19"/>
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A587" s="49"/>
-      <c r="B587" s="50"/>
-      <c r="C587" s="49"/>
-      <c r="D587" s="53"/>
-      <c r="E587" s="54"/>
-      <c r="F587" s="57"/>
+      <c r="A587" s="48"/>
+      <c r="B587" s="49"/>
+      <c r="C587" s="48"/>
+      <c r="D587" s="52"/>
+      <c r="E587" s="53"/>
+      <c r="F587" s="56"/>
       <c r="I587" s="19"/>
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A588" s="49"/>
-      <c r="B588" s="50"/>
-      <c r="C588" s="49"/>
-      <c r="D588" s="53"/>
-      <c r="E588" s="54"/>
-      <c r="F588" s="57"/>
+      <c r="A588" s="48"/>
+      <c r="B588" s="49"/>
+      <c r="C588" s="48"/>
+      <c r="D588" s="52"/>
+      <c r="E588" s="53"/>
+      <c r="F588" s="56"/>
       <c r="I588" s="19"/>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A589" s="49"/>
-      <c r="B589" s="50"/>
-      <c r="C589" s="49"/>
-      <c r="D589" s="53"/>
-      <c r="E589" s="54"/>
-      <c r="F589" s="57"/>
+      <c r="A589" s="48"/>
+      <c r="B589" s="49"/>
+      <c r="C589" s="48"/>
+      <c r="D589" s="52"/>
+      <c r="E589" s="53"/>
+      <c r="F589" s="56"/>
       <c r="I589" s="19"/>
     </row>
     <row r="590" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A590" s="49"/>
-      <c r="B590" s="50"/>
-      <c r="C590" s="49"/>
-      <c r="D590" s="53"/>
-      <c r="E590" s="54"/>
-      <c r="F590" s="57"/>
+      <c r="A590" s="48"/>
+      <c r="B590" s="49"/>
+      <c r="C590" s="48"/>
+      <c r="D590" s="52"/>
+      <c r="E590" s="53"/>
+      <c r="F590" s="56"/>
       <c r="I590" s="19"/>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A591" s="49"/>
-      <c r="B591" s="50"/>
-      <c r="C591" s="49"/>
-      <c r="D591" s="53"/>
-      <c r="E591" s="54"/>
-      <c r="F591" s="57"/>
+      <c r="A591" s="48"/>
+      <c r="B591" s="49"/>
+      <c r="C591" s="48"/>
+      <c r="D591" s="52"/>
+      <c r="E591" s="53"/>
+      <c r="F591" s="56"/>
       <c r="I591" s="19"/>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A592" s="49"/>
-      <c r="B592" s="50"/>
-      <c r="C592" s="49"/>
-      <c r="D592" s="53"/>
-      <c r="E592" s="54"/>
-      <c r="F592" s="57"/>
+      <c r="A592" s="48"/>
+      <c r="B592" s="49"/>
+      <c r="C592" s="48"/>
+      <c r="D592" s="52"/>
+      <c r="E592" s="53"/>
+      <c r="F592" s="56"/>
       <c r="I592" s="19"/>
     </row>
     <row r="593" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A593" s="49"/>
-      <c r="B593" s="50"/>
-      <c r="C593" s="49"/>
-      <c r="D593" s="53"/>
-      <c r="E593" s="54"/>
-      <c r="F593" s="57"/>
+      <c r="A593" s="48"/>
+      <c r="B593" s="49"/>
+      <c r="C593" s="48"/>
+      <c r="D593" s="52"/>
+      <c r="E593" s="53"/>
+      <c r="F593" s="56"/>
       <c r="I593" s="19"/>
     </row>
     <row r="594" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A594" s="49"/>
-      <c r="B594" s="50"/>
-      <c r="C594" s="49"/>
-      <c r="D594" s="53"/>
-      <c r="E594" s="54"/>
-      <c r="F594" s="57"/>
+      <c r="A594" s="48"/>
+      <c r="B594" s="49"/>
+      <c r="C594" s="48"/>
+      <c r="D594" s="52"/>
+      <c r="E594" s="53"/>
+      <c r="F594" s="56"/>
       <c r="I594" s="19"/>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A595" s="49"/>
-      <c r="B595" s="50"/>
-      <c r="C595" s="49"/>
-      <c r="D595" s="53"/>
-      <c r="E595" s="54"/>
-      <c r="F595" s="57"/>
+      <c r="A595" s="48"/>
+      <c r="B595" s="49"/>
+      <c r="C595" s="48"/>
+      <c r="D595" s="52"/>
+      <c r="E595" s="53"/>
+      <c r="F595" s="56"/>
       <c r="I595" s="19"/>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A596" s="49"/>
-      <c r="B596" s="50"/>
-      <c r="C596" s="49"/>
-      <c r="D596" s="53"/>
-      <c r="E596" s="54"/>
-      <c r="F596" s="57"/>
+      <c r="A596" s="48"/>
+      <c r="B596" s="49"/>
+      <c r="C596" s="48"/>
+      <c r="D596" s="52"/>
+      <c r="E596" s="53"/>
+      <c r="F596" s="56"/>
       <c r="I596" s="19"/>
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A597" s="49"/>
-      <c r="B597" s="50"/>
-      <c r="C597" s="49"/>
-      <c r="D597" s="53"/>
-      <c r="E597" s="54"/>
-      <c r="F597" s="57"/>
+      <c r="A597" s="48"/>
+      <c r="B597" s="49"/>
+      <c r="C597" s="48"/>
+      <c r="D597" s="52"/>
+      <c r="E597" s="53"/>
+      <c r="F597" s="56"/>
       <c r="I597" s="19"/>
     </row>
     <row r="598" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A598" s="49"/>
-      <c r="B598" s="50"/>
-      <c r="C598" s="49"/>
-      <c r="D598" s="53"/>
-      <c r="E598" s="54"/>
-      <c r="F598" s="57"/>
+      <c r="A598" s="48"/>
+      <c r="B598" s="49"/>
+      <c r="C598" s="48"/>
+      <c r="D598" s="52"/>
+      <c r="E598" s="53"/>
+      <c r="F598" s="56"/>
       <c r="I598" s="19"/>
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A599" s="49"/>
-      <c r="B599" s="50"/>
-      <c r="C599" s="49"/>
-      <c r="D599" s="53"/>
-      <c r="E599" s="54"/>
-      <c r="F599" s="57"/>
+      <c r="A599" s="48"/>
+      <c r="B599" s="49"/>
+      <c r="C599" s="48"/>
+      <c r="D599" s="52"/>
+      <c r="E599" s="53"/>
+      <c r="F599" s="56"/>
       <c r="I599" s="19"/>
     </row>
     <row r="600" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A600" s="49"/>
-      <c r="B600" s="50"/>
-      <c r="C600" s="49"/>
-      <c r="D600" s="53"/>
-      <c r="E600" s="54"/>
-      <c r="F600" s="57"/>
+      <c r="A600" s="48"/>
+      <c r="B600" s="49"/>
+      <c r="C600" s="48"/>
+      <c r="D600" s="52"/>
+      <c r="E600" s="53"/>
+      <c r="F600" s="56"/>
       <c r="I600" s="19"/>
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A601" s="49"/>
-      <c r="B601" s="50"/>
-      <c r="C601" s="49"/>
-      <c r="D601" s="53"/>
-      <c r="E601" s="54"/>
-      <c r="F601" s="57"/>
+      <c r="A601" s="48"/>
+      <c r="B601" s="49"/>
+      <c r="C601" s="48"/>
+      <c r="D601" s="52"/>
+      <c r="E601" s="53"/>
+      <c r="F601" s="56"/>
       <c r="I601" s="19"/>
     </row>
     <row r="602" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A602" s="49"/>
-      <c r="B602" s="50"/>
-      <c r="C602" s="49"/>
-      <c r="D602" s="53"/>
-      <c r="E602" s="54"/>
-      <c r="F602" s="57"/>
+      <c r="A602" s="48"/>
+      <c r="B602" s="49"/>
+      <c r="C602" s="48"/>
+      <c r="D602" s="52"/>
+      <c r="E602" s="53"/>
+      <c r="F602" s="56"/>
       <c r="I602" s="19"/>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A603" s="49"/>
-      <c r="B603" s="50"/>
-      <c r="C603" s="49"/>
-      <c r="D603" s="53"/>
-      <c r="E603" s="54"/>
-      <c r="F603" s="57"/>
+      <c r="A603" s="48"/>
+      <c r="B603" s="49"/>
+      <c r="C603" s="48"/>
+      <c r="D603" s="52"/>
+      <c r="E603" s="53"/>
+      <c r="F603" s="56"/>
       <c r="I603" s="19"/>
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A604" s="49"/>
-      <c r="B604" s="50"/>
-      <c r="C604" s="49"/>
-      <c r="D604" s="53"/>
-      <c r="E604" s="54"/>
-      <c r="F604" s="57"/>
+      <c r="A604" s="48"/>
+      <c r="B604" s="49"/>
+      <c r="C604" s="48"/>
+      <c r="D604" s="52"/>
+      <c r="E604" s="53"/>
+      <c r="F604" s="56"/>
       <c r="I604" s="19"/>
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A605" s="49"/>
-      <c r="B605" s="50"/>
-      <c r="C605" s="49"/>
-      <c r="D605" s="53"/>
-      <c r="E605" s="54"/>
-      <c r="F605" s="57"/>
+      <c r="A605" s="48"/>
+      <c r="B605" s="49"/>
+      <c r="C605" s="48"/>
+      <c r="D605" s="52"/>
+      <c r="E605" s="53"/>
+      <c r="F605" s="56"/>
       <c r="I605" s="19"/>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A606" s="49"/>
-      <c r="B606" s="50"/>
-      <c r="C606" s="49"/>
-      <c r="D606" s="53"/>
-      <c r="E606" s="54"/>
-      <c r="F606" s="57"/>
+      <c r="A606" s="48"/>
+      <c r="B606" s="49"/>
+      <c r="C606" s="48"/>
+      <c r="D606" s="52"/>
+      <c r="E606" s="53"/>
+      <c r="F606" s="56"/>
       <c r="I606" s="19"/>
     </row>
     <row r="607" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A607" s="49"/>
-      <c r="B607" s="50"/>
-      <c r="C607" s="49"/>
-      <c r="D607" s="53"/>
-      <c r="E607" s="54"/>
-      <c r="F607" s="57"/>
+      <c r="A607" s="48"/>
+      <c r="B607" s="49"/>
+      <c r="C607" s="48"/>
+      <c r="D607" s="52"/>
+      <c r="E607" s="53"/>
+      <c r="F607" s="56"/>
       <c r="I607" s="19"/>
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A608" s="49"/>
-      <c r="B608" s="50"/>
-      <c r="C608" s="49"/>
-      <c r="D608" s="53"/>
-      <c r="E608" s="54"/>
-      <c r="F608" s="57"/>
+      <c r="A608" s="48"/>
+      <c r="B608" s="49"/>
+      <c r="C608" s="48"/>
+      <c r="D608" s="52"/>
+      <c r="E608" s="53"/>
+      <c r="F608" s="56"/>
       <c r="I608" s="19"/>
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A609" s="49"/>
-      <c r="B609" s="50"/>
-      <c r="C609" s="49"/>
-      <c r="D609" s="53"/>
-      <c r="E609" s="54"/>
-      <c r="F609" s="57"/>
+      <c r="A609" s="48"/>
+      <c r="B609" s="49"/>
+      <c r="C609" s="48"/>
+      <c r="D609" s="52"/>
+      <c r="E609" s="53"/>
+      <c r="F609" s="56"/>
       <c r="I609" s="19"/>
     </row>
     <row r="610" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A610" s="49"/>
-      <c r="B610" s="50"/>
-      <c r="C610" s="49"/>
-      <c r="D610" s="53"/>
-      <c r="E610" s="54"/>
-      <c r="F610" s="57"/>
+      <c r="A610" s="48"/>
+      <c r="B610" s="49"/>
+      <c r="C610" s="48"/>
+      <c r="D610" s="52"/>
+      <c r="E610" s="53"/>
+      <c r="F610" s="56"/>
       <c r="I610" s="19"/>
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A611" s="49"/>
-      <c r="B611" s="50"/>
-      <c r="C611" s="49"/>
-      <c r="D611" s="53"/>
-      <c r="E611" s="54"/>
-      <c r="F611" s="57"/>
+      <c r="A611" s="48"/>
+      <c r="B611" s="49"/>
+      <c r="C611" s="48"/>
+      <c r="D611" s="52"/>
+      <c r="E611" s="53"/>
+      <c r="F611" s="56"/>
       <c r="I611" s="19"/>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A612" s="49"/>
-      <c r="B612" s="50"/>
-      <c r="C612" s="49"/>
-      <c r="D612" s="53"/>
-      <c r="E612" s="54"/>
-      <c r="F612" s="57"/>
+      <c r="A612" s="48"/>
+      <c r="B612" s="49"/>
+      <c r="C612" s="48"/>
+      <c r="D612" s="52"/>
+      <c r="E612" s="53"/>
+      <c r="F612" s="56"/>
       <c r="I612" s="19"/>
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A613" s="49"/>
-      <c r="B613" s="50"/>
-      <c r="C613" s="49"/>
-      <c r="D613" s="53"/>
-      <c r="E613" s="54"/>
-      <c r="F613" s="57"/>
+      <c r="A613" s="48"/>
+      <c r="B613" s="49"/>
+      <c r="C613" s="48"/>
+      <c r="D613" s="52"/>
+      <c r="E613" s="53"/>
+      <c r="F613" s="56"/>
       <c r="I613" s="19"/>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A614" s="49"/>
-      <c r="B614" s="50"/>
-      <c r="C614" s="49"/>
-      <c r="D614" s="53"/>
-      <c r="E614" s="54"/>
-      <c r="F614" s="57"/>
+      <c r="A614" s="48"/>
+      <c r="B614" s="49"/>
+      <c r="C614" s="48"/>
+      <c r="D614" s="52"/>
+      <c r="E614" s="53"/>
+      <c r="F614" s="56"/>
       <c r="I614" s="19"/>
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A615" s="49"/>
-      <c r="B615" s="50"/>
-      <c r="C615" s="49"/>
-      <c r="D615" s="53"/>
-      <c r="E615" s="54"/>
-      <c r="F615" s="57"/>
+      <c r="A615" s="48"/>
+      <c r="B615" s="49"/>
+      <c r="C615" s="48"/>
+      <c r="D615" s="52"/>
+      <c r="E615" s="53"/>
+      <c r="F615" s="56"/>
       <c r="I615" s="19"/>
     </row>
     <row r="616" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A616" s="49"/>
-      <c r="B616" s="50"/>
-      <c r="C616" s="49"/>
-      <c r="D616" s="53"/>
-      <c r="E616" s="54"/>
-      <c r="F616" s="57"/>
+      <c r="A616" s="48"/>
+      <c r="B616" s="49"/>
+      <c r="C616" s="48"/>
+      <c r="D616" s="52"/>
+      <c r="E616" s="53"/>
+      <c r="F616" s="56"/>
       <c r="I616" s="19"/>
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A617" s="49"/>
-      <c r="B617" s="50"/>
-      <c r="C617" s="49"/>
-      <c r="D617" s="53"/>
-      <c r="E617" s="54"/>
-      <c r="F617" s="57"/>
+      <c r="A617" s="48"/>
+      <c r="B617" s="49"/>
+      <c r="C617" s="48"/>
+      <c r="D617" s="52"/>
+      <c r="E617" s="53"/>
+      <c r="F617" s="56"/>
       <c r="I617" s="19"/>
     </row>
     <row r="618" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A618" s="49"/>
-      <c r="B618" s="50"/>
-      <c r="C618" s="49"/>
-      <c r="D618" s="53"/>
-      <c r="E618" s="54"/>
-      <c r="F618" s="57"/>
+      <c r="A618" s="48"/>
+      <c r="B618" s="49"/>
+      <c r="C618" s="48"/>
+      <c r="D618" s="52"/>
+      <c r="E618" s="53"/>
+      <c r="F618" s="56"/>
       <c r="I618" s="19"/>
     </row>
     <row r="619" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A619" s="49"/>
-      <c r="B619" s="50"/>
-      <c r="C619" s="49"/>
-      <c r="D619" s="53"/>
-      <c r="E619" s="54"/>
-      <c r="F619" s="57"/>
+      <c r="A619" s="48"/>
+      <c r="B619" s="49"/>
+      <c r="C619" s="48"/>
+      <c r="D619" s="52"/>
+      <c r="E619" s="53"/>
+      <c r="F619" s="56"/>
       <c r="I619" s="19"/>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A620" s="49"/>
-      <c r="B620" s="50"/>
-      <c r="C620" s="49"/>
-      <c r="D620" s="53"/>
-      <c r="E620" s="54"/>
-      <c r="F620" s="57"/>
+      <c r="A620" s="48"/>
+      <c r="B620" s="49"/>
+      <c r="C620" s="48"/>
+      <c r="D620" s="52"/>
+      <c r="E620" s="53"/>
+      <c r="F620" s="56"/>
       <c r="I620" s="19"/>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A621" s="49"/>
-      <c r="B621" s="50"/>
-      <c r="C621" s="49"/>
-      <c r="D621" s="53"/>
-      <c r="E621" s="54"/>
-      <c r="F621" s="57"/>
+      <c r="A621" s="48"/>
+      <c r="B621" s="49"/>
+      <c r="C621" s="48"/>
+      <c r="D621" s="52"/>
+      <c r="E621" s="53"/>
+      <c r="F621" s="56"/>
       <c r="I621" s="19"/>
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A622" s="49"/>
-      <c r="B622" s="50"/>
-      <c r="C622" s="49"/>
-      <c r="D622" s="53"/>
-      <c r="E622" s="54"/>
-      <c r="F622" s="57"/>
+      <c r="A622" s="48"/>
+      <c r="B622" s="49"/>
+      <c r="C622" s="48"/>
+      <c r="D622" s="52"/>
+      <c r="E622" s="53"/>
+      <c r="F622" s="56"/>
       <c r="I622" s="19"/>
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A623" s="49"/>
-      <c r="B623" s="50"/>
-      <c r="C623" s="49"/>
-      <c r="D623" s="53"/>
-      <c r="E623" s="54"/>
-      <c r="F623" s="57"/>
+      <c r="A623" s="48"/>
+      <c r="B623" s="49"/>
+      <c r="C623" s="48"/>
+      <c r="D623" s="52"/>
+      <c r="E623" s="53"/>
+      <c r="F623" s="56"/>
       <c r="I623" s="19"/>
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A624" s="49"/>
-      <c r="B624" s="50"/>
-      <c r="C624" s="49"/>
-      <c r="D624" s="53"/>
-      <c r="E624" s="54"/>
-      <c r="F624" s="57"/>
+      <c r="A624" s="48"/>
+      <c r="B624" s="49"/>
+      <c r="C624" s="48"/>
+      <c r="D624" s="52"/>
+      <c r="E624" s="53"/>
+      <c r="F624" s="56"/>
       <c r="I624" s="19"/>
     </row>
     <row r="625" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A625" s="49"/>
-      <c r="B625" s="50"/>
-      <c r="C625" s="49"/>
-      <c r="D625" s="53"/>
-      <c r="E625" s="54"/>
-      <c r="F625" s="57"/>
+      <c r="A625" s="48"/>
+      <c r="B625" s="49"/>
+      <c r="C625" s="48"/>
+      <c r="D625" s="52"/>
+      <c r="E625" s="53"/>
+      <c r="F625" s="56"/>
       <c r="I625" s="19"/>
     </row>
     <row r="626" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A626" s="49"/>
-      <c r="B626" s="50"/>
-      <c r="C626" s="49"/>
-      <c r="D626" s="53"/>
-      <c r="E626" s="54"/>
-      <c r="F626" s="57"/>
+      <c r="A626" s="48"/>
+      <c r="B626" s="49"/>
+      <c r="C626" s="48"/>
+      <c r="D626" s="52"/>
+      <c r="E626" s="53"/>
+      <c r="F626" s="56"/>
       <c r="I626" s="19"/>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A627" s="49"/>
-      <c r="B627" s="50"/>
-      <c r="C627" s="49"/>
-      <c r="D627" s="53"/>
-      <c r="E627" s="54"/>
-      <c r="F627" s="57"/>
+      <c r="A627" s="48"/>
+      <c r="B627" s="49"/>
+      <c r="C627" s="48"/>
+      <c r="D627" s="52"/>
+      <c r="E627" s="53"/>
+      <c r="F627" s="56"/>
       <c r="I627" s="19"/>
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A628" s="49"/>
-      <c r="B628" s="50"/>
-      <c r="C628" s="49"/>
-      <c r="D628" s="53"/>
-      <c r="E628" s="54"/>
-      <c r="F628" s="57"/>
+      <c r="A628" s="48"/>
+      <c r="B628" s="49"/>
+      <c r="C628" s="48"/>
+      <c r="D628" s="52"/>
+      <c r="E628" s="53"/>
+      <c r="F628" s="56"/>
       <c r="I628" s="19"/>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A629" s="49"/>
-      <c r="B629" s="50"/>
-      <c r="C629" s="49"/>
-      <c r="D629" s="53"/>
-      <c r="E629" s="54"/>
-      <c r="F629" s="57"/>
+      <c r="A629" s="48"/>
+      <c r="B629" s="49"/>
+      <c r="C629" s="48"/>
+      <c r="D629" s="52"/>
+      <c r="E629" s="53"/>
+      <c r="F629" s="56"/>
       <c r="I629" s="19"/>
     </row>
     <row r="630" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A630" s="49"/>
-      <c r="B630" s="50"/>
-      <c r="C630" s="49"/>
-      <c r="D630" s="53"/>
-      <c r="E630" s="54"/>
-      <c r="F630" s="57"/>
+      <c r="A630" s="48"/>
+      <c r="B630" s="49"/>
+      <c r="C630" s="48"/>
+      <c r="D630" s="52"/>
+      <c r="E630" s="53"/>
+      <c r="F630" s="56"/>
       <c r="I630" s="19"/>
     </row>
     <row r="631" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A631" s="49"/>
-      <c r="B631" s="50"/>
-      <c r="C631" s="49"/>
-      <c r="D631" s="53"/>
-      <c r="E631" s="54"/>
-      <c r="F631" s="57"/>
+      <c r="A631" s="48"/>
+      <c r="B631" s="49"/>
+      <c r="C631" s="48"/>
+      <c r="D631" s="52"/>
+      <c r="E631" s="53"/>
+      <c r="F631" s="56"/>
       <c r="I631" s="19"/>
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A632" s="49"/>
-      <c r="B632" s="50"/>
-      <c r="C632" s="49"/>
-      <c r="D632" s="53"/>
-      <c r="E632" s="54"/>
-      <c r="F632" s="57"/>
+      <c r="A632" s="48"/>
+      <c r="B632" s="49"/>
+      <c r="C632" s="48"/>
+      <c r="D632" s="52"/>
+      <c r="E632" s="53"/>
+      <c r="F632" s="56"/>
       <c r="I632" s="19"/>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A633" s="49"/>
-      <c r="B633" s="50"/>
-      <c r="C633" s="49"/>
-      <c r="D633" s="53"/>
-      <c r="E633" s="54"/>
-      <c r="F633" s="57"/>
+      <c r="A633" s="48"/>
+      <c r="B633" s="49"/>
+      <c r="C633" s="48"/>
+      <c r="D633" s="52"/>
+      <c r="E633" s="53"/>
+      <c r="F633" s="56"/>
       <c r="I633" s="19"/>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A634" s="49"/>
-      <c r="B634" s="50"/>
-      <c r="C634" s="49"/>
-      <c r="D634" s="53"/>
-      <c r="E634" s="54"/>
-      <c r="F634" s="57"/>
+      <c r="A634" s="48"/>
+      <c r="B634" s="49"/>
+      <c r="C634" s="48"/>
+      <c r="D634" s="52"/>
+      <c r="E634" s="53"/>
+      <c r="F634" s="56"/>
       <c r="I634" s="19"/>
     </row>
     <row r="635" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A635" s="49"/>
-      <c r="B635" s="50"/>
-      <c r="C635" s="49"/>
-      <c r="D635" s="53"/>
-      <c r="E635" s="54"/>
-      <c r="F635" s="57"/>
+      <c r="A635" s="48"/>
+      <c r="B635" s="49"/>
+      <c r="C635" s="48"/>
+      <c r="D635" s="52"/>
+      <c r="E635" s="53"/>
+      <c r="F635" s="56"/>
       <c r="I635" s="19"/>
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A636" s="49"/>
-      <c r="B636" s="50"/>
-      <c r="C636" s="49"/>
-      <c r="D636" s="53"/>
-      <c r="E636" s="54"/>
-      <c r="F636" s="57"/>
+      <c r="A636" s="48"/>
+      <c r="B636" s="49"/>
+      <c r="C636" s="48"/>
+      <c r="D636" s="52"/>
+      <c r="E636" s="53"/>
+      <c r="F636" s="56"/>
       <c r="I636" s="19"/>
     </row>
     <row r="637" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A637" s="49"/>
-      <c r="B637" s="50"/>
-      <c r="C637" s="49"/>
-      <c r="D637" s="53"/>
-      <c r="E637" s="54"/>
-      <c r="F637" s="57"/>
+      <c r="A637" s="48"/>
+      <c r="B637" s="49"/>
+      <c r="C637" s="48"/>
+      <c r="D637" s="52"/>
+      <c r="E637" s="53"/>
+      <c r="F637" s="56"/>
       <c r="I637" s="19"/>
     </row>
     <row r="638" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A638" s="49"/>
-      <c r="B638" s="50"/>
-      <c r="C638" s="49"/>
-      <c r="D638" s="53"/>
-      <c r="E638" s="54"/>
-      <c r="F638" s="57"/>
+      <c r="A638" s="48"/>
+      <c r="B638" s="49"/>
+      <c r="C638" s="48"/>
+      <c r="D638" s="52"/>
+      <c r="E638" s="53"/>
+      <c r="F638" s="56"/>
       <c r="I638" s="19"/>
     </row>
     <row r="639" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A639" s="49"/>
-      <c r="B639" s="50"/>
-      <c r="C639" s="49"/>
-      <c r="D639" s="53"/>
-      <c r="E639" s="54"/>
-      <c r="F639" s="57"/>
+      <c r="A639" s="48"/>
+      <c r="B639" s="49"/>
+      <c r="C639" s="48"/>
+      <c r="D639" s="52"/>
+      <c r="E639" s="53"/>
+      <c r="F639" s="56"/>
       <c r="I639" s="19"/>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A640" s="49"/>
-      <c r="B640" s="50"/>
-      <c r="C640" s="49"/>
-      <c r="D640" s="53"/>
-      <c r="E640" s="54"/>
-      <c r="F640" s="57"/>
+      <c r="A640" s="48"/>
+      <c r="B640" s="49"/>
+      <c r="C640" s="48"/>
+      <c r="D640" s="52"/>
+      <c r="E640" s="53"/>
+      <c r="F640" s="56"/>
       <c r="I640" s="19"/>
     </row>
     <row r="641" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A641" s="49"/>
-      <c r="B641" s="50"/>
-      <c r="C641" s="49"/>
-      <c r="D641" s="53"/>
-      <c r="E641" s="54"/>
-      <c r="F641" s="57"/>
+      <c r="A641" s="48"/>
+      <c r="B641" s="49"/>
+      <c r="C641" s="48"/>
+      <c r="D641" s="52"/>
+      <c r="E641" s="53"/>
+      <c r="F641" s="56"/>
       <c r="I641" s="19"/>
     </row>
     <row r="642" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A642" s="49"/>
-      <c r="B642" s="50"/>
-      <c r="C642" s="49"/>
-      <c r="D642" s="53"/>
-      <c r="E642" s="54"/>
-      <c r="F642" s="57"/>
+      <c r="A642" s="48"/>
+      <c r="B642" s="49"/>
+      <c r="C642" s="48"/>
+      <c r="D642" s="52"/>
+      <c r="E642" s="53"/>
+      <c r="F642" s="56"/>
       <c r="I642" s="19"/>
     </row>
     <row r="643" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A643" s="49"/>
-      <c r="B643" s="50"/>
-      <c r="C643" s="49"/>
-      <c r="D643" s="53"/>
-      <c r="E643" s="54"/>
-      <c r="F643" s="57"/>
+      <c r="A643" s="48"/>
+      <c r="B643" s="49"/>
+      <c r="C643" s="48"/>
+      <c r="D643" s="52"/>
+      <c r="E643" s="53"/>
+      <c r="F643" s="56"/>
       <c r="I643" s="19"/>
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A644" s="49"/>
-      <c r="B644" s="50"/>
-      <c r="C644" s="49"/>
-      <c r="D644" s="53"/>
-      <c r="E644" s="54"/>
-      <c r="F644" s="57"/>
+      <c r="A644" s="48"/>
+      <c r="B644" s="49"/>
+      <c r="C644" s="48"/>
+      <c r="D644" s="52"/>
+      <c r="E644" s="53"/>
+      <c r="F644" s="56"/>
       <c r="I644" s="19"/>
     </row>
     <row r="645" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A645" s="49"/>
-      <c r="B645" s="50"/>
-      <c r="C645" s="49"/>
-      <c r="D645" s="53"/>
-      <c r="E645" s="54"/>
-      <c r="F645" s="57"/>
+      <c r="A645" s="48"/>
+      <c r="B645" s="49"/>
+      <c r="C645" s="48"/>
+      <c r="D645" s="52"/>
+      <c r="E645" s="53"/>
+      <c r="F645" s="56"/>
       <c r="I645" s="19"/>
     </row>
     <row r="646" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A646" s="49"/>
-      <c r="B646" s="50"/>
-      <c r="C646" s="49"/>
-      <c r="D646" s="53"/>
-      <c r="E646" s="54"/>
-      <c r="F646" s="57"/>
+      <c r="A646" s="48"/>
+      <c r="B646" s="49"/>
+      <c r="C646" s="48"/>
+      <c r="D646" s="52"/>
+      <c r="E646" s="53"/>
+      <c r="F646" s="56"/>
       <c r="I646" s="19"/>
     </row>
     <row r="647" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A647" s="49"/>
-      <c r="B647" s="50"/>
-      <c r="C647" s="49"/>
-      <c r="D647" s="53"/>
-      <c r="E647" s="54"/>
-      <c r="F647" s="57"/>
+      <c r="A647" s="48"/>
+      <c r="B647" s="49"/>
+      <c r="C647" s="48"/>
+      <c r="D647" s="52"/>
+      <c r="E647" s="53"/>
+      <c r="F647" s="56"/>
       <c r="I647" s="19"/>
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A648" s="49"/>
-      <c r="B648" s="50"/>
-      <c r="C648" s="49"/>
-      <c r="D648" s="53"/>
-      <c r="E648" s="54"/>
-      <c r="F648" s="57"/>
+      <c r="A648" s="48"/>
+      <c r="B648" s="49"/>
+      <c r="C648" s="48"/>
+      <c r="D648" s="52"/>
+      <c r="E648" s="53"/>
+      <c r="F648" s="56"/>
       <c r="I648" s="19"/>
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A649" s="49"/>
-      <c r="B649" s="50"/>
-      <c r="C649" s="49"/>
-      <c r="D649" s="53"/>
-      <c r="E649" s="54"/>
-      <c r="F649" s="57"/>
+      <c r="A649" s="48"/>
+      <c r="B649" s="49"/>
+      <c r="C649" s="48"/>
+      <c r="D649" s="52"/>
+      <c r="E649" s="53"/>
+      <c r="F649" s="56"/>
       <c r="I649" s="19"/>
     </row>
     <row r="650" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A650" s="49"/>
-      <c r="B650" s="50"/>
-      <c r="C650" s="49"/>
-      <c r="D650" s="53"/>
-      <c r="E650" s="54"/>
-      <c r="F650" s="57"/>
+      <c r="A650" s="48"/>
+      <c r="B650" s="49"/>
+      <c r="C650" s="48"/>
+      <c r="D650" s="52"/>
+      <c r="E650" s="53"/>
+      <c r="F650" s="56"/>
       <c r="I650" s="19"/>
     </row>
     <row r="651" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A651" s="49"/>
-      <c r="B651" s="50"/>
-      <c r="C651" s="49"/>
-      <c r="D651" s="53"/>
-      <c r="E651" s="54"/>
-      <c r="F651" s="57"/>
+      <c r="A651" s="48"/>
+      <c r="B651" s="49"/>
+      <c r="C651" s="48"/>
+      <c r="D651" s="52"/>
+      <c r="E651" s="53"/>
+      <c r="F651" s="56"/>
       <c r="I651" s="19"/>
     </row>
     <row r="652" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A652" s="49"/>
-      <c r="B652" s="50"/>
-      <c r="C652" s="49"/>
-      <c r="D652" s="53"/>
-      <c r="E652" s="54"/>
-      <c r="F652" s="57"/>
+      <c r="A652" s="48"/>
+      <c r="B652" s="49"/>
+      <c r="C652" s="48"/>
+      <c r="D652" s="52"/>
+      <c r="E652" s="53"/>
+      <c r="F652" s="56"/>
       <c r="I652" s="19"/>
     </row>
     <row r="653" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A653" s="49"/>
-      <c r="B653" s="50"/>
-      <c r="C653" s="49"/>
-      <c r="D653" s="53"/>
-      <c r="E653" s="54"/>
-      <c r="F653" s="57"/>
+      <c r="A653" s="48"/>
+      <c r="B653" s="49"/>
+      <c r="C653" s="48"/>
+      <c r="D653" s="52"/>
+      <c r="E653" s="53"/>
+      <c r="F653" s="56"/>
       <c r="I653" s="19"/>
     </row>
     <row r="654" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A654" s="49"/>
-      <c r="B654" s="50"/>
-      <c r="C654" s="49"/>
-      <c r="D654" s="53"/>
-      <c r="E654" s="54"/>
-      <c r="F654" s="57"/>
+      <c r="A654" s="48"/>
+      <c r="B654" s="49"/>
+      <c r="C654" s="48"/>
+      <c r="D654" s="52"/>
+      <c r="E654" s="53"/>
+      <c r="F654" s="56"/>
       <c r="I654" s="19"/>
     </row>
     <row r="655" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A655" s="49"/>
-      <c r="B655" s="50"/>
-      <c r="C655" s="49"/>
-      <c r="D655" s="53"/>
-      <c r="E655" s="54"/>
-      <c r="F655" s="57"/>
+      <c r="A655" s="48"/>
+      <c r="B655" s="49"/>
+      <c r="C655" s="48"/>
+      <c r="D655" s="52"/>
+      <c r="E655" s="53"/>
+      <c r="F655" s="56"/>
       <c r="I655" s="19"/>
     </row>
     <row r="656" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A656" s="49"/>
-      <c r="B656" s="50"/>
-      <c r="C656" s="49"/>
-      <c r="D656" s="53"/>
-      <c r="E656" s="54"/>
-      <c r="F656" s="57"/>
+      <c r="A656" s="48"/>
+      <c r="B656" s="49"/>
+      <c r="C656" s="48"/>
+      <c r="D656" s="52"/>
+      <c r="E656" s="53"/>
+      <c r="F656" s="56"/>
       <c r="I656" s="19"/>
     </row>
     <row r="657" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A657" s="49"/>
-      <c r="B657" s="50"/>
-      <c r="C657" s="49"/>
-      <c r="D657" s="53"/>
-      <c r="E657" s="54"/>
-      <c r="F657" s="57"/>
+      <c r="A657" s="48"/>
+      <c r="B657" s="49"/>
+      <c r="C657" s="48"/>
+      <c r="D657" s="52"/>
+      <c r="E657" s="53"/>
+      <c r="F657" s="56"/>
       <c r="I657" s="19"/>
     </row>
     <row r="658" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A658" s="49"/>
-      <c r="B658" s="50"/>
-      <c r="C658" s="49"/>
-      <c r="D658" s="53"/>
-      <c r="E658" s="54"/>
-      <c r="F658" s="57"/>
+      <c r="A658" s="48"/>
+      <c r="B658" s="49"/>
+      <c r="C658" s="48"/>
+      <c r="D658" s="52"/>
+      <c r="E658" s="53"/>
+      <c r="F658" s="56"/>
       <c r="I658" s="19"/>
     </row>
     <row r="659" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A659" s="49"/>
-      <c r="B659" s="50"/>
-      <c r="C659" s="49"/>
-      <c r="D659" s="53"/>
-      <c r="E659" s="54"/>
-      <c r="F659" s="57"/>
+      <c r="A659" s="48"/>
+      <c r="B659" s="49"/>
+      <c r="C659" s="48"/>
+      <c r="D659" s="52"/>
+      <c r="E659" s="53"/>
+      <c r="F659" s="56"/>
       <c r="I659" s="19"/>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A660" s="49"/>
-      <c r="B660" s="50"/>
-      <c r="C660" s="49"/>
-      <c r="D660" s="53"/>
-      <c r="E660" s="54"/>
-      <c r="F660" s="57"/>
+      <c r="A660" s="48"/>
+      <c r="B660" s="49"/>
+      <c r="C660" s="48"/>
+      <c r="D660" s="52"/>
+      <c r="E660" s="53"/>
+      <c r="F660" s="56"/>
       <c r="I660" s="19"/>
     </row>
     <row r="661" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A661" s="49"/>
-      <c r="B661" s="50"/>
-      <c r="C661" s="49"/>
-      <c r="D661" s="53"/>
-      <c r="E661" s="54"/>
-      <c r="F661" s="57"/>
+      <c r="A661" s="48"/>
+      <c r="B661" s="49"/>
+      <c r="C661" s="48"/>
+      <c r="D661" s="52"/>
+      <c r="E661" s="53"/>
+      <c r="F661" s="56"/>
       <c r="I661" s="19"/>
     </row>
     <row r="662" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A662" s="49"/>
-      <c r="B662" s="50"/>
-      <c r="C662" s="49"/>
-      <c r="D662" s="53"/>
-      <c r="E662" s="54"/>
-      <c r="F662" s="57"/>
+      <c r="A662" s="48"/>
+      <c r="B662" s="49"/>
+      <c r="C662" s="48"/>
+      <c r="D662" s="52"/>
+      <c r="E662" s="53"/>
+      <c r="F662" s="56"/>
       <c r="I662" s="19"/>
     </row>
     <row r="663" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A663" s="49"/>
-      <c r="B663" s="50"/>
-      <c r="C663" s="49"/>
-      <c r="D663" s="53"/>
-      <c r="E663" s="54"/>
-      <c r="F663" s="57"/>
+      <c r="A663" s="48"/>
+      <c r="B663" s="49"/>
+      <c r="C663" s="48"/>
+      <c r="D663" s="52"/>
+      <c r="E663" s="53"/>
+      <c r="F663" s="56"/>
       <c r="I663" s="19"/>
     </row>
     <row r="664" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A664" s="49"/>
-      <c r="B664" s="50"/>
-      <c r="C664" s="49"/>
-      <c r="D664" s="53"/>
-      <c r="E664" s="54"/>
-      <c r="F664" s="57"/>
+      <c r="A664" s="48"/>
+      <c r="B664" s="49"/>
+      <c r="C664" s="48"/>
+      <c r="D664" s="52"/>
+      <c r="E664" s="53"/>
+      <c r="F664" s="56"/>
       <c r="I664" s="19"/>
     </row>
     <row r="665" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A665" s="49"/>
-      <c r="B665" s="50"/>
-      <c r="C665" s="49"/>
-      <c r="D665" s="53"/>
-      <c r="E665" s="54"/>
-      <c r="F665" s="57"/>
+      <c r="A665" s="48"/>
+      <c r="B665" s="49"/>
+      <c r="C665" s="48"/>
+      <c r="D665" s="52"/>
+      <c r="E665" s="53"/>
+      <c r="F665" s="56"/>
       <c r="I665" s="19"/>
     </row>
     <row r="666" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A666" s="49"/>
-      <c r="B666" s="50"/>
-      <c r="C666" s="49"/>
-      <c r="D666" s="53"/>
-      <c r="E666" s="54"/>
-      <c r="F666" s="57"/>
+      <c r="A666" s="48"/>
+      <c r="B666" s="49"/>
+      <c r="C666" s="48"/>
+      <c r="D666" s="52"/>
+      <c r="E666" s="53"/>
+      <c r="F666" s="56"/>
       <c r="I666" s="19"/>
     </row>
     <row r="667" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A667" s="49"/>
-      <c r="B667" s="50"/>
-      <c r="C667" s="49"/>
-      <c r="D667" s="53"/>
-      <c r="E667" s="54"/>
-      <c r="F667" s="57"/>
+      <c r="A667" s="48"/>
+      <c r="B667" s="49"/>
+      <c r="C667" s="48"/>
+      <c r="D667" s="52"/>
+      <c r="E667" s="53"/>
+      <c r="F667" s="56"/>
       <c r="I667" s="19"/>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A668" s="49"/>
-      <c r="B668" s="50"/>
-      <c r="C668" s="49"/>
-      <c r="D668" s="53"/>
-      <c r="E668" s="54"/>
-      <c r="F668" s="57"/>
+      <c r="A668" s="48"/>
+      <c r="B668" s="49"/>
+      <c r="C668" s="48"/>
+      <c r="D668" s="52"/>
+      <c r="E668" s="53"/>
+      <c r="F668" s="56"/>
       <c r="I668" s="19"/>
     </row>
     <row r="669" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A669" s="49"/>
-      <c r="B669" s="50"/>
-      <c r="C669" s="49"/>
-      <c r="D669" s="53"/>
-      <c r="E669" s="54"/>
-      <c r="F669" s="57"/>
+      <c r="A669" s="48"/>
+      <c r="B669" s="49"/>
+      <c r="C669" s="48"/>
+      <c r="D669" s="52"/>
+      <c r="E669" s="53"/>
+      <c r="F669" s="56"/>
       <c r="I669" s="19"/>
     </row>
     <row r="670" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A670" s="49"/>
-      <c r="B670" s="50"/>
-      <c r="C670" s="49"/>
-      <c r="D670" s="53"/>
-      <c r="E670" s="54"/>
-      <c r="F670" s="57"/>
+      <c r="A670" s="48"/>
+      <c r="B670" s="49"/>
+      <c r="C670" s="48"/>
+      <c r="D670" s="52"/>
+      <c r="E670" s="53"/>
+      <c r="F670" s="56"/>
       <c r="I670" s="19"/>
     </row>
     <row r="671" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A671" s="49"/>
-      <c r="B671" s="50"/>
-      <c r="C671" s="49"/>
-      <c r="D671" s="53"/>
-      <c r="E671" s="54"/>
-      <c r="F671" s="57"/>
+      <c r="A671" s="48"/>
+      <c r="B671" s="49"/>
+      <c r="C671" s="48"/>
+      <c r="D671" s="52"/>
+      <c r="E671" s="53"/>
+      <c r="F671" s="56"/>
       <c r="I671" s="19"/>
     </row>
     <row r="672" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A672" s="49"/>
-      <c r="B672" s="50"/>
-      <c r="C672" s="49"/>
-      <c r="D672" s="53"/>
-      <c r="E672" s="54"/>
-      <c r="F672" s="57"/>
+      <c r="A672" s="48"/>
+      <c r="B672" s="49"/>
+      <c r="C672" s="48"/>
+      <c r="D672" s="52"/>
+      <c r="E672" s="53"/>
+      <c r="F672" s="56"/>
       <c r="I672" s="19"/>
     </row>
     <row r="673" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A673" s="49"/>
-      <c r="B673" s="50"/>
-      <c r="C673" s="49"/>
-      <c r="D673" s="53"/>
-      <c r="E673" s="54"/>
-      <c r="F673" s="57"/>
+      <c r="A673" s="48"/>
+      <c r="B673" s="49"/>
+      <c r="C673" s="48"/>
+      <c r="D673" s="52"/>
+      <c r="E673" s="53"/>
+      <c r="F673" s="56"/>
       <c r="I673" s="19"/>
     </row>
     <row r="674" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A674" s="49"/>
-      <c r="B674" s="50"/>
-      <c r="C674" s="49"/>
-      <c r="D674" s="53"/>
-      <c r="E674" s="54"/>
-      <c r="F674" s="57"/>
+      <c r="A674" s="48"/>
+      <c r="B674" s="49"/>
+      <c r="C674" s="48"/>
+      <c r="D674" s="52"/>
+      <c r="E674" s="53"/>
+      <c r="F674" s="56"/>
       <c r="I674" s="19"/>
     </row>
     <row r="675" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A675" s="49"/>
-      <c r="B675" s="50"/>
-      <c r="C675" s="49"/>
-      <c r="D675" s="53"/>
-      <c r="E675" s="54"/>
-      <c r="F675" s="57"/>
+      <c r="A675" s="48"/>
+      <c r="B675" s="49"/>
+      <c r="C675" s="48"/>
+      <c r="D675" s="52"/>
+      <c r="E675" s="53"/>
+      <c r="F675" s="56"/>
       <c r="I675" s="19"/>
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A676" s="49"/>
-      <c r="B676" s="50"/>
-      <c r="C676" s="49"/>
-      <c r="D676" s="53"/>
-      <c r="E676" s="54"/>
-      <c r="F676" s="57"/>
+      <c r="A676" s="48"/>
+      <c r="B676" s="49"/>
+      <c r="C676" s="48"/>
+      <c r="D676" s="52"/>
+      <c r="E676" s="53"/>
+      <c r="F676" s="56"/>
       <c r="I676" s="19"/>
     </row>
     <row r="677" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A677" s="49"/>
-      <c r="B677" s="50"/>
-      <c r="C677" s="49"/>
-      <c r="D677" s="53"/>
-      <c r="E677" s="54"/>
-      <c r="F677" s="57"/>
+      <c r="A677" s="48"/>
+      <c r="B677" s="49"/>
+      <c r="C677" s="48"/>
+      <c r="D677" s="52"/>
+      <c r="E677" s="53"/>
+      <c r="F677" s="56"/>
       <c r="I677" s="19"/>
     </row>
     <row r="678" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A678" s="49"/>
-      <c r="B678" s="50"/>
-      <c r="C678" s="49"/>
-      <c r="D678" s="53"/>
-      <c r="E678" s="54"/>
-      <c r="F678" s="57"/>
+      <c r="A678" s="48"/>
+      <c r="B678" s="49"/>
+      <c r="C678" s="48"/>
+      <c r="D678" s="52"/>
+      <c r="E678" s="53"/>
+      <c r="F678" s="56"/>
       <c r="I678" s="19"/>
     </row>
     <row r="679" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A679" s="49"/>
-      <c r="B679" s="50"/>
-      <c r="C679" s="49"/>
-      <c r="D679" s="53"/>
-      <c r="E679" s="54"/>
-      <c r="F679" s="57"/>
+      <c r="A679" s="48"/>
+      <c r="B679" s="49"/>
+      <c r="C679" s="48"/>
+      <c r="D679" s="52"/>
+      <c r="E679" s="53"/>
+      <c r="F679" s="56"/>
       <c r="I679" s="19"/>
     </row>
     <row r="680" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A680" s="49"/>
-      <c r="B680" s="50"/>
-      <c r="C680" s="49"/>
-      <c r="D680" s="53"/>
-      <c r="E680" s="54"/>
-      <c r="F680" s="57"/>
+      <c r="A680" s="48"/>
+      <c r="B680" s="49"/>
+      <c r="C680" s="48"/>
+      <c r="D680" s="52"/>
+      <c r="E680" s="53"/>
+      <c r="F680" s="56"/>
       <c r="I680" s="19"/>
     </row>
     <row r="681" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A681" s="49"/>
-      <c r="B681" s="50"/>
-      <c r="C681" s="49"/>
-      <c r="D681" s="53"/>
-      <c r="E681" s="54"/>
-      <c r="F681" s="57"/>
+      <c r="A681" s="48"/>
+      <c r="B681" s="49"/>
+      <c r="C681" s="48"/>
+      <c r="D681" s="52"/>
+      <c r="E681" s="53"/>
+      <c r="F681" s="56"/>
       <c r="I681" s="19"/>
     </row>
     <row r="682" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A682" s="49"/>
-      <c r="B682" s="50"/>
-      <c r="C682" s="49"/>
-      <c r="D682" s="53"/>
-      <c r="E682" s="54"/>
-      <c r="F682" s="57"/>
+      <c r="A682" s="48"/>
+      <c r="B682" s="49"/>
+      <c r="C682" s="48"/>
+      <c r="D682" s="52"/>
+      <c r="E682" s="53"/>
+      <c r="F682" s="56"/>
       <c r="I682" s="19"/>
     </row>
     <row r="683" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A683" s="49"/>
-      <c r="B683" s="50"/>
-      <c r="C683" s="49"/>
-      <c r="D683" s="53"/>
-      <c r="E683" s="54"/>
-      <c r="F683" s="57"/>
+      <c r="A683" s="48"/>
+      <c r="B683" s="49"/>
+      <c r="C683" s="48"/>
+      <c r="D683" s="52"/>
+      <c r="E683" s="53"/>
+      <c r="F683" s="56"/>
       <c r="I683" s="19"/>
     </row>
     <row r="684" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A684" s="49"/>
-      <c r="B684" s="50"/>
-      <c r="C684" s="49"/>
-      <c r="D684" s="53"/>
-      <c r="E684" s="54"/>
-      <c r="F684" s="57"/>
+      <c r="A684" s="48"/>
+      <c r="B684" s="49"/>
+      <c r="C684" s="48"/>
+      <c r="D684" s="52"/>
+      <c r="E684" s="53"/>
+      <c r="F684" s="56"/>
       <c r="I684" s="19"/>
     </row>
     <row r="685" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A685" s="49"/>
-      <c r="B685" s="50"/>
-      <c r="C685" s="49"/>
-      <c r="D685" s="53"/>
-      <c r="E685" s="54"/>
-      <c r="F685" s="57"/>
+      <c r="A685" s="48"/>
+      <c r="B685" s="49"/>
+      <c r="C685" s="48"/>
+      <c r="D685" s="52"/>
+      <c r="E685" s="53"/>
+      <c r="F685" s="56"/>
       <c r="I685" s="19"/>
     </row>
     <row r="686" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A686" s="49"/>
-      <c r="B686" s="50"/>
-      <c r="C686" s="49"/>
-      <c r="D686" s="53"/>
-      <c r="E686" s="54"/>
-      <c r="F686" s="57"/>
+      <c r="A686" s="48"/>
+      <c r="B686" s="49"/>
+      <c r="C686" s="48"/>
+      <c r="D686" s="52"/>
+      <c r="E686" s="53"/>
+      <c r="F686" s="56"/>
       <c r="I686" s="19"/>
     </row>
     <row r="687" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A687" s="49"/>
-      <c r="B687" s="50"/>
-      <c r="C687" s="49"/>
-      <c r="D687" s="53"/>
-      <c r="E687" s="54"/>
-      <c r="F687" s="57"/>
+      <c r="A687" s="48"/>
+      <c r="B687" s="49"/>
+      <c r="C687" s="48"/>
+      <c r="D687" s="52"/>
+      <c r="E687" s="53"/>
+      <c r="F687" s="56"/>
       <c r="I687" s="19"/>
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A688" s="49"/>
-      <c r="B688" s="50"/>
-      <c r="C688" s="49"/>
-      <c r="D688" s="53"/>
-      <c r="E688" s="54"/>
-      <c r="F688" s="57"/>
+      <c r="A688" s="48"/>
+      <c r="B688" s="49"/>
+      <c r="C688" s="48"/>
+      <c r="D688" s="52"/>
+      <c r="E688" s="53"/>
+      <c r="F688" s="56"/>
       <c r="I688" s="19"/>
     </row>
     <row r="689" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A689" s="49"/>
-      <c r="B689" s="50"/>
-      <c r="C689" s="49"/>
-      <c r="D689" s="53"/>
-      <c r="E689" s="54"/>
-      <c r="F689" s="57"/>
+      <c r="A689" s="48"/>
+      <c r="B689" s="49"/>
+      <c r="C689" s="48"/>
+      <c r="D689" s="52"/>
+      <c r="E689" s="53"/>
+      <c r="F689" s="56"/>
       <c r="I689" s="19"/>
     </row>
     <row r="690" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A690" s="49"/>
-      <c r="B690" s="50"/>
-      <c r="C690" s="49"/>
-      <c r="D690" s="53"/>
-      <c r="E690" s="54"/>
-      <c r="F690" s="57"/>
+      <c r="A690" s="48"/>
+      <c r="B690" s="49"/>
+      <c r="C690" s="48"/>
+      <c r="D690" s="52"/>
+      <c r="E690" s="53"/>
+      <c r="F690" s="56"/>
       <c r="I690" s="19"/>
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A691" s="49"/>
-      <c r="B691" s="50"/>
-      <c r="C691" s="49"/>
-      <c r="D691" s="53"/>
-      <c r="E691" s="54"/>
-      <c r="F691" s="57"/>
+      <c r="A691" s="48"/>
+      <c r="B691" s="49"/>
+      <c r="C691" s="48"/>
+      <c r="D691" s="52"/>
+      <c r="E691" s="53"/>
+      <c r="F691" s="56"/>
       <c r="I691" s="19"/>
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A692" s="49"/>
-      <c r="B692" s="50"/>
-      <c r="C692" s="49"/>
-      <c r="D692" s="53"/>
-      <c r="E692" s="54"/>
-      <c r="F692" s="57"/>
+      <c r="A692" s="48"/>
+      <c r="B692" s="49"/>
+      <c r="C692" s="48"/>
+      <c r="D692" s="52"/>
+      <c r="E692" s="53"/>
+      <c r="F692" s="56"/>
       <c r="I692" s="19"/>
     </row>
     <row r="693" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A693" s="49"/>
-      <c r="B693" s="50"/>
-      <c r="C693" s="49"/>
-      <c r="D693" s="53"/>
-      <c r="E693" s="54"/>
-      <c r="F693" s="57"/>
+      <c r="A693" s="48"/>
+      <c r="B693" s="49"/>
+      <c r="C693" s="48"/>
+      <c r="D693" s="52"/>
+      <c r="E693" s="53"/>
+      <c r="F693" s="56"/>
       <c r="I693" s="19"/>
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A694" s="49"/>
-      <c r="B694" s="50"/>
-      <c r="C694" s="49"/>
-      <c r="D694" s="53"/>
-      <c r="E694" s="54"/>
-      <c r="F694" s="57"/>
+      <c r="A694" s="48"/>
+      <c r="B694" s="49"/>
+      <c r="C694" s="48"/>
+      <c r="D694" s="52"/>
+      <c r="E694" s="53"/>
+      <c r="F694" s="56"/>
       <c r="I694" s="19"/>
     </row>
     <row r="695" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A695" s="49"/>
-      <c r="B695" s="50"/>
-      <c r="C695" s="49"/>
-      <c r="D695" s="53"/>
-      <c r="E695" s="54"/>
-      <c r="F695" s="57"/>
+      <c r="A695" s="48"/>
+      <c r="B695" s="49"/>
+      <c r="C695" s="48"/>
+      <c r="D695" s="52"/>
+      <c r="E695" s="53"/>
+      <c r="F695" s="56"/>
       <c r="I695" s="19"/>
     </row>
     <row r="696" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A696" s="49"/>
-      <c r="B696" s="50"/>
-      <c r="C696" s="49"/>
-      <c r="D696" s="53"/>
-      <c r="E696" s="54"/>
-      <c r="F696" s="57"/>
+      <c r="A696" s="48"/>
+      <c r="B696" s="49"/>
+      <c r="C696" s="48"/>
+      <c r="D696" s="52"/>
+      <c r="E696" s="53"/>
+      <c r="F696" s="56"/>
       <c r="I696" s="19"/>
     </row>
     <row r="697" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A697" s="49"/>
-      <c r="B697" s="50"/>
-      <c r="C697" s="49"/>
-      <c r="D697" s="53"/>
-      <c r="E697" s="54"/>
-      <c r="F697" s="57"/>
+      <c r="A697" s="48"/>
+      <c r="B697" s="49"/>
+      <c r="C697" s="48"/>
+      <c r="D697" s="52"/>
+      <c r="E697" s="53"/>
+      <c r="F697" s="56"/>
       <c r="I697" s="19"/>
     </row>
     <row r="698" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A698" s="49"/>
-      <c r="B698" s="50"/>
-      <c r="C698" s="49"/>
-      <c r="D698" s="53"/>
-      <c r="E698" s="54"/>
-      <c r="F698" s="57"/>
+      <c r="A698" s="48"/>
+      <c r="B698" s="49"/>
+      <c r="C698" s="48"/>
+      <c r="D698" s="52"/>
+      <c r="E698" s="53"/>
+      <c r="F698" s="56"/>
       <c r="I698" s="19"/>
     </row>
     <row r="699" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A699" s="49"/>
-      <c r="B699" s="50"/>
-      <c r="C699" s="49"/>
-      <c r="D699" s="53"/>
-      <c r="E699" s="54"/>
-      <c r="F699" s="57"/>
+      <c r="A699" s="48"/>
+      <c r="B699" s="49"/>
+      <c r="C699" s="48"/>
+      <c r="D699" s="52"/>
+      <c r="E699" s="53"/>
+      <c r="F699" s="56"/>
       <c r="I699" s="19"/>
     </row>
     <row r="700" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A700" s="49"/>
-      <c r="B700" s="50"/>
-      <c r="C700" s="49"/>
-      <c r="D700" s="53"/>
-      <c r="E700" s="54"/>
-      <c r="F700" s="57"/>
+      <c r="A700" s="48"/>
+      <c r="B700" s="49"/>
+      <c r="C700" s="48"/>
+      <c r="D700" s="52"/>
+      <c r="E700" s="53"/>
+      <c r="F700" s="56"/>
       <c r="I700" s="19"/>
     </row>
     <row r="701" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A701" s="49"/>
-      <c r="B701" s="50"/>
-      <c r="C701" s="49"/>
-      <c r="D701" s="53"/>
-      <c r="E701" s="54"/>
-      <c r="F701" s="57"/>
+      <c r="A701" s="48"/>
+      <c r="B701" s="49"/>
+      <c r="C701" s="48"/>
+      <c r="D701" s="52"/>
+      <c r="E701" s="53"/>
+      <c r="F701" s="56"/>
       <c r="I701" s="19"/>
     </row>
     <row r="702" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A702" s="49"/>
-      <c r="B702" s="50"/>
-      <c r="C702" s="49"/>
-      <c r="D702" s="53"/>
-      <c r="E702" s="54"/>
-      <c r="F702" s="57"/>
+      <c r="A702" s="48"/>
+      <c r="B702" s="49"/>
+      <c r="C702" s="48"/>
+      <c r="D702" s="52"/>
+      <c r="E702" s="53"/>
+      <c r="F702" s="56"/>
       <c r="I702" s="19"/>
     </row>
     <row r="703" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A703" s="49"/>
-      <c r="B703" s="50"/>
-      <c r="C703" s="49"/>
-      <c r="D703" s="53"/>
-      <c r="E703" s="54"/>
-      <c r="F703" s="57"/>
+      <c r="A703" s="48"/>
+      <c r="B703" s="49"/>
+      <c r="C703" s="48"/>
+      <c r="D703" s="52"/>
+      <c r="E703" s="53"/>
+      <c r="F703" s="56"/>
       <c r="I703" s="19"/>
     </row>
     <row r="704" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A704" s="49"/>
-      <c r="B704" s="50"/>
-      <c r="C704" s="49"/>
-      <c r="D704" s="53"/>
-      <c r="E704" s="54"/>
-      <c r="F704" s="57"/>
+      <c r="A704" s="48"/>
+      <c r="B704" s="49"/>
+      <c r="C704" s="48"/>
+      <c r="D704" s="52"/>
+      <c r="E704" s="53"/>
+      <c r="F704" s="56"/>
       <c r="I704" s="19"/>
     </row>
     <row r="705" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A705" s="49"/>
-      <c r="B705" s="50"/>
-      <c r="C705" s="49"/>
-      <c r="D705" s="53"/>
-      <c r="E705" s="54"/>
-      <c r="F705" s="57"/>
+      <c r="A705" s="48"/>
+      <c r="B705" s="49"/>
+      <c r="C705" s="48"/>
+      <c r="D705" s="52"/>
+      <c r="E705" s="53"/>
+      <c r="F705" s="56"/>
       <c r="I705" s="19"/>
     </row>
     <row r="706" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A706" s="49"/>
-      <c r="B706" s="50"/>
-      <c r="C706" s="49"/>
-      <c r="D706" s="53"/>
-      <c r="E706" s="54"/>
-      <c r="F706" s="57"/>
+      <c r="A706" s="48"/>
+      <c r="B706" s="49"/>
+      <c r="C706" s="48"/>
+      <c r="D706" s="52"/>
+      <c r="E706" s="53"/>
+      <c r="F706" s="56"/>
       <c r="I706" s="19"/>
     </row>
     <row r="707" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A707" s="49"/>
-      <c r="B707" s="50"/>
-      <c r="C707" s="49"/>
-      <c r="D707" s="53"/>
-      <c r="E707" s="54"/>
-      <c r="F707" s="57"/>
+      <c r="A707" s="48"/>
+      <c r="B707" s="49"/>
+      <c r="C707" s="48"/>
+      <c r="D707" s="52"/>
+      <c r="E707" s="53"/>
+      <c r="F707" s="56"/>
       <c r="I707" s="19"/>
     </row>
     <row r="708" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A708" s="49"/>
-      <c r="B708" s="50"/>
-      <c r="C708" s="49"/>
-      <c r="D708" s="53"/>
-      <c r="E708" s="54"/>
-      <c r="F708" s="57"/>
+      <c r="A708" s="48"/>
+      <c r="B708" s="49"/>
+      <c r="C708" s="48"/>
+      <c r="D708" s="52"/>
+      <c r="E708" s="53"/>
+      <c r="F708" s="56"/>
       <c r="I708" s="19"/>
     </row>
     <row r="709" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A709" s="49"/>
-      <c r="B709" s="50"/>
-      <c r="C709" s="49"/>
-      <c r="D709" s="53"/>
-      <c r="E709" s="54"/>
-      <c r="F709" s="57"/>
+      <c r="A709" s="48"/>
+      <c r="B709" s="49"/>
+      <c r="C709" s="48"/>
+      <c r="D709" s="52"/>
+      <c r="E709" s="53"/>
+      <c r="F709" s="56"/>
       <c r="I709" s="19"/>
     </row>
     <row r="710" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A710" s="49"/>
-      <c r="B710" s="50"/>
-      <c r="C710" s="49"/>
-      <c r="D710" s="53"/>
-      <c r="E710" s="54"/>
-      <c r="F710" s="57"/>
+      <c r="A710" s="48"/>
+      <c r="B710" s="49"/>
+      <c r="C710" s="48"/>
+      <c r="D710" s="52"/>
+      <c r="E710" s="53"/>
+      <c r="F710" s="56"/>
       <c r="I710" s="19"/>
     </row>
     <row r="711" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A711" s="49"/>
-      <c r="B711" s="50"/>
-      <c r="C711" s="49"/>
-      <c r="D711" s="53"/>
-      <c r="E711" s="54"/>
-      <c r="F711" s="57"/>
+      <c r="A711" s="48"/>
+      <c r="B711" s="49"/>
+      <c r="C711" s="48"/>
+      <c r="D711" s="52"/>
+      <c r="E711" s="53"/>
+      <c r="F711" s="56"/>
       <c r="I711" s="19"/>
     </row>
     <row r="712" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A712" s="49"/>
-      <c r="B712" s="50"/>
-      <c r="C712" s="49"/>
-      <c r="D712" s="53"/>
-      <c r="E712" s="54"/>
-      <c r="F712" s="57"/>
+      <c r="A712" s="48"/>
+      <c r="B712" s="49"/>
+      <c r="C712" s="48"/>
+      <c r="D712" s="52"/>
+      <c r="E712" s="53"/>
+      <c r="F712" s="56"/>
       <c r="I712" s="19"/>
     </row>
     <row r="713" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A713" s="49"/>
-      <c r="B713" s="50"/>
-      <c r="C713" s="49"/>
-      <c r="D713" s="53"/>
-      <c r="E713" s="54"/>
-      <c r="F713" s="57"/>
+      <c r="A713" s="48"/>
+      <c r="B713" s="49"/>
+      <c r="C713" s="48"/>
+      <c r="D713" s="52"/>
+      <c r="E713" s="53"/>
+      <c r="F713" s="56"/>
       <c r="I713" s="19"/>
     </row>
     <row r="714" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A714" s="49"/>
-      <c r="B714" s="50"/>
-      <c r="C714" s="49"/>
-      <c r="D714" s="53"/>
-      <c r="E714" s="54"/>
-      <c r="F714" s="57"/>
+      <c r="A714" s="48"/>
+      <c r="B714" s="49"/>
+      <c r="C714" s="48"/>
+      <c r="D714" s="52"/>
+      <c r="E714" s="53"/>
+      <c r="F714" s="56"/>
       <c r="I714" s="19"/>
     </row>
     <row r="715" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A715" s="49"/>
-      <c r="B715" s="50"/>
-      <c r="C715" s="49"/>
-      <c r="D715" s="53"/>
-      <c r="E715" s="54"/>
-      <c r="F715" s="57"/>
+      <c r="A715" s="48"/>
+      <c r="B715" s="49"/>
+      <c r="C715" s="48"/>
+      <c r="D715" s="52"/>
+      <c r="E715" s="53"/>
+      <c r="F715" s="56"/>
       <c r="I715" s="19"/>
     </row>
     <row r="716" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A716" s="49"/>
-      <c r="B716" s="50"/>
-      <c r="C716" s="49"/>
-      <c r="D716" s="53"/>
-      <c r="E716" s="54"/>
-      <c r="F716" s="57"/>
+      <c r="A716" s="48"/>
+      <c r="B716" s="49"/>
+      <c r="C716" s="48"/>
+      <c r="D716" s="52"/>
+      <c r="E716" s="53"/>
+      <c r="F716" s="56"/>
       <c r="I716" s="19"/>
     </row>
     <row r="717" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A717" s="49"/>
-      <c r="B717" s="50"/>
-      <c r="C717" s="49"/>
-      <c r="D717" s="53"/>
-      <c r="E717" s="54"/>
-      <c r="F717" s="57"/>
+      <c r="A717" s="48"/>
+      <c r="B717" s="49"/>
+      <c r="C717" s="48"/>
+      <c r="D717" s="52"/>
+      <c r="E717" s="53"/>
+      <c r="F717" s="56"/>
       <c r="I717" s="19"/>
     </row>
     <row r="718" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A718" s="49"/>
-      <c r="B718" s="50"/>
-      <c r="C718" s="49"/>
-      <c r="D718" s="53"/>
-      <c r="E718" s="54"/>
-      <c r="F718" s="57"/>
+      <c r="A718" s="48"/>
+      <c r="B718" s="49"/>
+      <c r="C718" s="48"/>
+      <c r="D718" s="52"/>
+      <c r="E718" s="53"/>
+      <c r="F718" s="56"/>
       <c r="I718" s="19"/>
     </row>
     <row r="719" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A719" s="49"/>
-      <c r="B719" s="50"/>
-      <c r="C719" s="49"/>
-      <c r="D719" s="53"/>
-      <c r="E719" s="54"/>
-      <c r="F719" s="57"/>
+      <c r="A719" s="48"/>
+      <c r="B719" s="49"/>
+      <c r="C719" s="48"/>
+      <c r="D719" s="52"/>
+      <c r="E719" s="53"/>
+      <c r="F719" s="56"/>
       <c r="I719" s="19"/>
     </row>
     <row r="720" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A720" s="49"/>
-      <c r="B720" s="50"/>
-      <c r="C720" s="49"/>
-      <c r="D720" s="53"/>
-      <c r="E720" s="54"/>
-      <c r="F720" s="57"/>
+      <c r="A720" s="48"/>
+      <c r="B720" s="49"/>
+      <c r="C720" s="48"/>
+      <c r="D720" s="52"/>
+      <c r="E720" s="53"/>
+      <c r="F720" s="56"/>
       <c r="I720" s="19"/>
     </row>
     <row r="721" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A721" s="49"/>
-      <c r="B721" s="50"/>
-      <c r="C721" s="49"/>
-      <c r="D721" s="53"/>
-      <c r="E721" s="54"/>
-      <c r="F721" s="57"/>
+      <c r="A721" s="48"/>
+      <c r="B721" s="49"/>
+      <c r="C721" s="48"/>
+      <c r="D721" s="52"/>
+      <c r="E721" s="53"/>
+      <c r="F721" s="56"/>
       <c r="I721" s="19"/>
     </row>
     <row r="722" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A722" s="49"/>
-      <c r="B722" s="50"/>
-      <c r="C722" s="49"/>
-      <c r="D722" s="53"/>
-      <c r="E722" s="54"/>
-      <c r="F722" s="57"/>
+      <c r="A722" s="48"/>
+      <c r="B722" s="49"/>
+      <c r="C722" s="48"/>
+      <c r="D722" s="52"/>
+      <c r="E722" s="53"/>
+      <c r="F722" s="56"/>
       <c r="I722" s="19"/>
     </row>
     <row r="723" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A723" s="49"/>
-      <c r="B723" s="50"/>
-      <c r="C723" s="49"/>
-      <c r="D723" s="53"/>
-      <c r="E723" s="54"/>
-      <c r="F723" s="57"/>
+      <c r="A723" s="48"/>
+      <c r="B723" s="49"/>
+      <c r="C723" s="48"/>
+      <c r="D723" s="52"/>
+      <c r="E723" s="53"/>
+      <c r="F723" s="56"/>
       <c r="I723" s="19"/>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A724" s="49"/>
-      <c r="B724" s="50"/>
-      <c r="C724" s="49"/>
-      <c r="D724" s="53"/>
-      <c r="E724" s="54"/>
-      <c r="F724" s="57"/>
+      <c r="A724" s="48"/>
+      <c r="B724" s="49"/>
+      <c r="C724" s="48"/>
+      <c r="D724" s="52"/>
+      <c r="E724" s="53"/>
+      <c r="F724" s="56"/>
       <c r="I724" s="19"/>
     </row>
     <row r="725" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A725" s="49"/>
-      <c r="B725" s="50"/>
-      <c r="C725" s="49"/>
-      <c r="D725" s="53"/>
-      <c r="E725" s="54"/>
-      <c r="F725" s="57"/>
+      <c r="A725" s="48"/>
+      <c r="B725" s="49"/>
+      <c r="C725" s="48"/>
+      <c r="D725" s="52"/>
+      <c r="E725" s="53"/>
+      <c r="F725" s="56"/>
       <c r="I725" s="19"/>
     </row>
     <row r="726" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A726" s="49"/>
-      <c r="B726" s="50"/>
-      <c r="C726" s="49"/>
-      <c r="D726" s="53"/>
-      <c r="E726" s="54"/>
-      <c r="F726" s="57"/>
+      <c r="A726" s="48"/>
+      <c r="B726" s="49"/>
+      <c r="C726" s="48"/>
+      <c r="D726" s="52"/>
+      <c r="E726" s="53"/>
+      <c r="F726" s="56"/>
       <c r="I726" s="19"/>
     </row>
     <row r="727" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A727" s="49"/>
-      <c r="B727" s="50"/>
-      <c r="C727" s="49"/>
-      <c r="D727" s="53"/>
-      <c r="E727" s="54"/>
-      <c r="F727" s="57"/>
+      <c r="A727" s="48"/>
+      <c r="B727" s="49"/>
+      <c r="C727" s="48"/>
+      <c r="D727" s="52"/>
+      <c r="E727" s="53"/>
+      <c r="F727" s="56"/>
       <c r="I727" s="19"/>
     </row>
     <row r="728" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A728" s="49"/>
-      <c r="B728" s="50"/>
-      <c r="C728" s="49"/>
-      <c r="D728" s="53"/>
-      <c r="E728" s="54"/>
-      <c r="F728" s="57"/>
+      <c r="A728" s="48"/>
+      <c r="B728" s="49"/>
+      <c r="C728" s="48"/>
+      <c r="D728" s="52"/>
+      <c r="E728" s="53"/>
+      <c r="F728" s="56"/>
       <c r="I728" s="19"/>
     </row>
     <row r="729" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A729" s="49"/>
-      <c r="B729" s="50"/>
-      <c r="C729" s="49"/>
-      <c r="D729" s="53"/>
-      <c r="E729" s="54"/>
-      <c r="F729" s="57"/>
+      <c r="A729" s="48"/>
+      <c r="B729" s="49"/>
+      <c r="C729" s="48"/>
+      <c r="D729" s="52"/>
+      <c r="E729" s="53"/>
+      <c r="F729" s="56"/>
       <c r="I729" s="19"/>
     </row>
     <row r="730" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A730" s="49"/>
-      <c r="B730" s="50"/>
-      <c r="C730" s="49"/>
-      <c r="D730" s="53"/>
-      <c r="E730" s="54"/>
-      <c r="F730" s="57"/>
+      <c r="A730" s="48"/>
+      <c r="B730" s="49"/>
+      <c r="C730" s="48"/>
+      <c r="D730" s="52"/>
+      <c r="E730" s="53"/>
+      <c r="F730" s="56"/>
       <c r="I730" s="19"/>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A731" s="49"/>
-      <c r="B731" s="50"/>
-      <c r="C731" s="49"/>
-      <c r="D731" s="53"/>
-      <c r="E731" s="54"/>
-      <c r="F731" s="57"/>
+      <c r="A731" s="48"/>
+      <c r="B731" s="49"/>
+      <c r="C731" s="48"/>
+      <c r="D731" s="52"/>
+      <c r="E731" s="53"/>
+      <c r="F731" s="56"/>
     </row>
     <row r="732" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A732" s="49"/>
-      <c r="B732" s="50"/>
-      <c r="C732" s="49"/>
-      <c r="D732" s="53"/>
-      <c r="E732" s="54"/>
-      <c r="F732" s="57"/>
+      <c r="A732" s="48"/>
+      <c r="B732" s="49"/>
+      <c r="C732" s="48"/>
+      <c r="D732" s="52"/>
+      <c r="E732" s="53"/>
+      <c r="F732" s="56"/>
     </row>
     <row r="733" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A733" s="49"/>
-      <c r="B733" s="50"/>
-      <c r="C733" s="49"/>
-      <c r="D733" s="53"/>
-      <c r="E733" s="54"/>
-      <c r="F733" s="57"/>
+      <c r="A733" s="48"/>
+      <c r="B733" s="49"/>
+      <c r="C733" s="48"/>
+      <c r="D733" s="52"/>
+      <c r="E733" s="53"/>
+      <c r="F733" s="56"/>
     </row>
     <row r="734" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A734" s="49"/>
-      <c r="B734" s="52">
+      <c r="A734" s="48"/>
+      <c r="B734" s="51">
         <v>12</v>
       </c>
-      <c r="C734" s="49"/>
-      <c r="D734" s="53"/>
-      <c r="E734" s="56">
+      <c r="C734" s="48"/>
+      <c r="D734" s="52"/>
+      <c r="E734" s="55">
         <f>N513</f>
         <v>0</v>
       </c>
-      <c r="F734" s="57"/>
+      <c r="F734" s="56"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F734" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -22252,9 +22256,10 @@
     <hyperlink ref="F92" r:id="rId213" xr:uid="{7BD3346D-C133-4F85-BA8B-06E893A5AA15}"/>
     <hyperlink ref="F236" r:id="rId214" xr:uid="{A89FDFBB-71B2-4738-9E20-379D288195B3}"/>
     <hyperlink ref="F237" r:id="rId215" xr:uid="{71BBAFA0-9838-4AE0-B1A3-8148C5047B22}"/>
+    <hyperlink ref="F430" r:id="rId216" xr:uid="{CE9B73F7-6206-43BE-A0D7-238A375EF8C2}"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId216"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId217"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;C&amp;8EC_Not_technical&amp;8
 </oddHeader>

--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B5A879-5E2D-45BF-9D40-89A843F7209F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A948A5-A683-4D20-B81C-7049D4011A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$F$734</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$F$733</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateCount="1"/>
   <extLst>
@@ -1505,9 +1506,6 @@
     <t>THE TIME - Get it up</t>
   </si>
   <si>
-    <t>Mass Production - Come And Get Some Of This</t>
-  </si>
-  <si>
     <t>The Dukes Bugatti &amp; Musker - Fate</t>
   </si>
   <si>
@@ -2469,6 +2467,9 @@
   </si>
   <si>
     <t>https://www.discogs.com/fr/release/2177186-Surface-Lately/image/SW1hZ2U6OTk4MTU5NTk=</t>
+  </si>
+  <si>
+    <t>MASS PRODUCTION - Come And Get Some Of This</t>
   </si>
 </sst>
 </file>
@@ -3245,7 +3246,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N734"/>
+  <dimension ref="A1:N733"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.140625" bestFit="1" customWidth="1"/>
@@ -3279,7 +3280,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="81" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G1" s="76" t="s">
         <v>266</v>
@@ -3305,18 +3306,18 @@
       <c r="F2" s="82"/>
       <c r="G2" s="77"/>
       <c r="H2" s="10">
-        <f>SUM(G3:G562)</f>
-        <v>506</v>
+        <f>SUM(G3:G561)</f>
+        <v>505</v>
       </c>
       <c r="I2" s="74"/>
       <c r="J2" s="11">
-        <f>SUM(I3:I562)</f>
+        <f>SUM(I3:I561)</f>
         <v>301</v>
       </c>
       <c r="K2" s="17"/>
       <c r="L2" s="12">
         <f>H2-J2</f>
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -3326,11 +3327,11 @@
       <c r="B3" s="21"/>
       <c r="C3" s="3"/>
       <c r="D3" s="14" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="45" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G3" s="20">
         <f>COUNTA(A3)</f>
@@ -3423,7 +3424,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B6" s="59"/>
       <c r="C6" s="59"/>
@@ -3434,7 +3435,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G6" s="20">
         <f t="shared" si="2"/>
@@ -3534,7 +3535,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E9" s="30">
         <v>15</v>
@@ -3563,10 +3564,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C10" s="60"/>
       <c r="D10" s="61" t="s">
@@ -3576,7 +3577,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G10" s="20">
         <f t="shared" si="2"/>
@@ -3596,13 +3597,13 @@
         <v>197</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="14"/>
       <c r="E11" s="31"/>
       <c r="F11" s="45" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G11" s="20">
         <f t="shared" si="2"/>
@@ -3634,7 +3635,7 @@
       <c r="D12" s="14"/>
       <c r="E12" s="31"/>
       <c r="F12" s="45" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G12" s="20">
         <f t="shared" si="2"/>
@@ -3666,7 +3667,7 @@
       <c r="D13" s="14"/>
       <c r="E13" s="31"/>
       <c r="F13" s="45" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G13" s="20">
         <f t="shared" si="2"/>
@@ -3691,16 +3692,16 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="3"/>
       <c r="D14" s="14" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="45" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G14" s="20">
         <f t="shared" si="2"/>
@@ -3732,7 +3733,7 @@
       <c r="D15" s="14"/>
       <c r="E15" s="31"/>
       <c r="F15" s="45" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G15" s="20">
         <f t="shared" si="2"/>
@@ -3756,7 +3757,7 @@
       <c r="D16" s="14"/>
       <c r="E16" s="31"/>
       <c r="F16" s="45" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G16" s="20">
         <f t="shared" si="2"/>
@@ -3960,7 +3961,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E22" s="30"/>
       <c r="F22" s="43"/>
@@ -3994,7 +3995,7 @@
       <c r="D23" s="14"/>
       <c r="E23" s="31"/>
       <c r="F23" s="45" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G23" s="20">
         <f t="shared" si="2"/>
@@ -4058,11 +4059,11 @@
         <v>5</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="46" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G25" s="20">
         <f t="shared" si="2"/>
@@ -4094,7 +4095,7 @@
       <c r="D26" s="14"/>
       <c r="E26" s="31"/>
       <c r="F26" s="45" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G26" s="20">
         <f t="shared" si="2"/>
@@ -4158,7 +4159,7 @@
       <c r="D28" s="14"/>
       <c r="E28" s="31"/>
       <c r="F28" s="45" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G28" s="20">
         <f t="shared" si="2"/>
@@ -4256,7 +4257,7 @@
       <c r="D31" s="14"/>
       <c r="E31" s="31"/>
       <c r="F31" s="45" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G31" s="20">
         <f t="shared" si="2"/>
@@ -4384,11 +4385,11 @@
       <c r="B35" s="21"/>
       <c r="C35" s="3"/>
       <c r="D35" s="14" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E35" s="31"/>
       <c r="F35" s="45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G35" s="20">
         <f t="shared" si="2"/>
@@ -4483,7 +4484,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="3"/>
@@ -4494,7 +4495,7 @@
         <v>8</v>
       </c>
       <c r="F38" s="45" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G38" s="20">
         <f t="shared" si="2"/>
@@ -4564,7 +4565,7 @@
         <v>11</v>
       </c>
       <c r="F40" s="46" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G40" s="20">
         <f t="shared" si="2"/>
@@ -4589,14 +4590,14 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E41" s="30">
         <v>15</v>
@@ -4632,7 +4633,7 @@
       <c r="D42" s="14"/>
       <c r="E42" s="31"/>
       <c r="F42" s="45" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G42" s="20">
         <f t="shared" si="2"/>
@@ -4666,7 +4667,7 @@
       </c>
       <c r="E43" s="31"/>
       <c r="F43" s="45" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" si="2"/>
@@ -4698,7 +4699,7 @@
         <v>5</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E44" s="30">
         <v>6.73</v>
@@ -4736,7 +4737,7 @@
       <c r="D45" s="13"/>
       <c r="E45" s="30"/>
       <c r="F45" s="46" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G45" s="20">
         <f t="shared" si="2"/>
@@ -4792,7 +4793,7 @@
       <c r="D47" s="14"/>
       <c r="E47" s="31"/>
       <c r="F47" s="45" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G47" s="20">
         <f t="shared" si="2"/>
@@ -4817,7 +4818,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="5" t="s">
@@ -4830,7 +4831,7 @@
         <v>13.5</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G48" s="20">
         <f t="shared" si="2"/>
@@ -4855,7 +4856,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="5" t="s">
@@ -4868,7 +4869,7 @@
         <v>12</v>
       </c>
       <c r="F49" s="46" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G49" s="20">
         <f t="shared" si="2"/>
@@ -5004,7 +5005,7 @@
       <c r="D53" s="14"/>
       <c r="E53" s="31"/>
       <c r="F53" s="45" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G53" s="20">
         <f t="shared" si="2"/>
@@ -5021,16 +5022,16 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="3"/>
       <c r="D54" s="14" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E54" s="31"/>
       <c r="F54" s="45" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G54" s="20">
         <f t="shared" si="2"/>
@@ -5222,7 +5223,7 @@
       <c r="D60" s="14"/>
       <c r="E60" s="31"/>
       <c r="F60" s="45" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G60" s="20">
         <f t="shared" si="2"/>
@@ -5313,14 +5314,14 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="3"/>
       <c r="D63" s="14"/>
       <c r="E63" s="31"/>
       <c r="F63" s="45" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G63" s="20">
         <f t="shared" si="2"/>
@@ -5386,11 +5387,11 @@
       <c r="B65" s="21"/>
       <c r="C65" s="3"/>
       <c r="D65" s="14" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E65" s="31"/>
       <c r="F65" s="45" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G65" s="20">
         <f t="shared" si="2"/>
@@ -5415,16 +5416,16 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B66" s="21"/>
       <c r="C66" s="3"/>
       <c r="D66" s="14" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E66" s="31"/>
       <c r="F66" s="45" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G66" s="20">
         <f t="shared" si="2"/>
@@ -5456,7 +5457,7 @@
       <c r="D67" s="14"/>
       <c r="E67" s="31"/>
       <c r="F67" s="45" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G67" s="20">
         <f t="shared" si="2"/>
@@ -5520,7 +5521,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E69" s="30">
         <v>17.690000000000001</v>
@@ -5605,14 +5606,14 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="3"/>
       <c r="D72" s="14"/>
       <c r="E72" s="31"/>
       <c r="F72" s="45" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G72" s="20">
         <f t="shared" si="6"/>
@@ -5637,14 +5638,14 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B73" s="21"/>
       <c r="C73" s="3"/>
       <c r="D73" s="14"/>
       <c r="E73" s="31"/>
       <c r="F73" s="45" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G73" s="20">
         <f t="shared" si="6"/>
@@ -5676,7 +5677,7 @@
       <c r="D74" s="14"/>
       <c r="E74" s="31"/>
       <c r="F74" s="45" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G74" s="20">
         <f t="shared" si="6"/>
@@ -5708,7 +5709,7 @@
       <c r="D75" s="14"/>
       <c r="E75" s="31"/>
       <c r="F75" s="45" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G75" s="20">
         <f t="shared" si="6"/>
@@ -5840,7 +5841,7 @@
       <c r="D79" s="14"/>
       <c r="E79" s="31"/>
       <c r="F79" s="45" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G79" s="20">
         <f t="shared" si="6"/>
@@ -5933,14 +5934,14 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B82" s="21"/>
       <c r="C82" s="3"/>
       <c r="D82" s="14"/>
       <c r="E82" s="31"/>
       <c r="F82" s="45" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G82" s="20">
         <f t="shared" si="6"/>
@@ -5972,7 +5973,7 @@
       <c r="D83" s="14"/>
       <c r="E83" s="31"/>
       <c r="F83" s="45" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G83" s="20">
         <f t="shared" si="6"/>
@@ -6036,7 +6037,7 @@
         <v>5</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E85" s="30">
         <v>10</v>
@@ -6097,16 +6098,16 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B87" s="21"/>
       <c r="C87" s="3"/>
       <c r="D87" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E87" s="31"/>
       <c r="F87" s="45" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G87" s="20">
         <f t="shared" si="6"/>
@@ -6138,7 +6139,7 @@
       <c r="D88" s="14"/>
       <c r="E88" s="31"/>
       <c r="F88" s="45" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G88" s="20">
         <f t="shared" si="6"/>
@@ -6170,7 +6171,7 @@
       <c r="D89" s="14"/>
       <c r="E89" s="31"/>
       <c r="F89" s="45" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G89" s="20">
         <f t="shared" si="6"/>
@@ -6202,7 +6203,7 @@
       <c r="D90" s="14"/>
       <c r="E90" s="31"/>
       <c r="F90" s="45" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G90" s="20">
         <f t="shared" si="6"/>
@@ -6234,7 +6235,7 @@
       <c r="D91" s="14"/>
       <c r="E91" s="31"/>
       <c r="F91" s="45" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G91" s="20">
         <f t="shared" si="6"/>
@@ -6264,11 +6265,11 @@
       <c r="B92" s="21"/>
       <c r="C92" s="3"/>
       <c r="D92" s="14" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E92" s="31"/>
       <c r="F92" s="45" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G92" s="20">
         <f t="shared" si="6"/>
@@ -6329,14 +6330,14 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E94" s="30">
         <v>20.74</v>
@@ -6572,7 +6573,7 @@
         <v>15</v>
       </c>
       <c r="F101" s="69" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G101" s="20">
         <f t="shared" si="6"/>
@@ -6597,14 +6598,14 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="34" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B102" s="25"/>
       <c r="C102" s="35"/>
       <c r="D102" s="36"/>
       <c r="E102" s="37"/>
       <c r="F102" s="70" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G102" s="20">
         <f t="shared" si="6"/>
@@ -6636,7 +6637,7 @@
       <c r="D103" s="14"/>
       <c r="E103" s="31"/>
       <c r="F103" s="45" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G103" s="20">
         <f t="shared" si="6"/>
@@ -6700,7 +6701,7 @@
       <c r="D105" s="14"/>
       <c r="E105" s="31"/>
       <c r="F105" s="45" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G105" s="20">
         <f t="shared" si="6"/>
@@ -6732,7 +6733,7 @@
       <c r="D106" s="14"/>
       <c r="E106" s="31"/>
       <c r="F106" s="45" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G106" s="20">
         <f t="shared" si="6"/>
@@ -6764,7 +6765,7 @@
       <c r="D107" s="14"/>
       <c r="E107" s="31"/>
       <c r="F107" s="45" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G107" s="20">
         <f t="shared" si="6"/>
@@ -6788,7 +6789,7 @@
         <v>5</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E108" s="30">
         <v>20</v>
@@ -6824,7 +6825,7 @@
       <c r="D109" s="14"/>
       <c r="E109" s="31"/>
       <c r="F109" s="45" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G109" s="20">
         <f t="shared" si="6"/>
@@ -6888,7 +6889,7 @@
       <c r="D111" s="14"/>
       <c r="E111" s="31"/>
       <c r="F111" s="45" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G111" s="20">
         <f t="shared" si="6"/>
@@ -6920,7 +6921,7 @@
       <c r="D112" s="14"/>
       <c r="E112" s="31"/>
       <c r="F112" s="45" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G112" s="20">
         <f t="shared" si="6"/>
@@ -6984,7 +6985,7 @@
         <v>5</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E114" s="30">
         <v>15</v>
@@ -7056,7 +7057,7 @@
       <c r="D116" s="14"/>
       <c r="E116" s="31"/>
       <c r="F116" s="45" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G116" s="20">
         <f t="shared" si="6"/>
@@ -7088,7 +7089,7 @@
         <v>5</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E117" s="30">
         <v>7.63</v>
@@ -7194,7 +7195,7 @@
       <c r="D120" s="14"/>
       <c r="E120" s="31"/>
       <c r="F120" s="45" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G120" s="20">
         <f t="shared" si="6"/>
@@ -7251,14 +7252,14 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B122" s="21"/>
       <c r="C122" s="3"/>
       <c r="D122" s="14"/>
       <c r="E122" s="31"/>
       <c r="F122" s="45" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G122" s="20">
         <f t="shared" si="6"/>
@@ -7290,7 +7291,7 @@
         <v>5</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E123" s="30">
         <v>17.54</v>
@@ -7319,10 +7320,10 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="26" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B124" s="27" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C124" s="28"/>
       <c r="D124" s="29" t="s">
@@ -7332,7 +7333,7 @@
         <v>39</v>
       </c>
       <c r="F124" s="71" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G124" s="20">
         <f t="shared" si="6"/>
@@ -7364,7 +7365,7 @@
       <c r="D125" s="14"/>
       <c r="E125" s="31"/>
       <c r="F125" s="45" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G125" s="20">
         <f t="shared" si="6"/>
@@ -7392,15 +7393,15 @@
         <v>63</v>
       </c>
       <c r="B126" s="27" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C126" s="28"/>
       <c r="D126" s="29" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E126" s="32"/>
       <c r="F126" s="71" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G126" s="20">
         <f t="shared" si="6"/>
@@ -7649,7 +7650,7 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="5" t="s">
@@ -7662,7 +7663,7 @@
         <v>29</v>
       </c>
       <c r="F134" s="46" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G134" s="20">
         <f t="shared" si="6"/>
@@ -7687,14 +7688,14 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E135" s="30">
         <v>15</v>
@@ -7758,7 +7759,7 @@
       <c r="D137" s="14"/>
       <c r="E137" s="31"/>
       <c r="F137" s="45" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G137" s="20">
         <f t="shared" si="10"/>
@@ -7790,7 +7791,7 @@
       <c r="D138" s="14"/>
       <c r="E138" s="31"/>
       <c r="F138" s="45" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G138" s="20">
         <f t="shared" si="10"/>
@@ -7815,14 +7816,14 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B139" s="21"/>
       <c r="C139" s="3"/>
       <c r="D139" s="14"/>
       <c r="E139" s="31"/>
       <c r="F139" s="45" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G139" s="20">
         <f t="shared" si="10"/>
@@ -7854,7 +7855,7 @@
       <c r="D140" s="14"/>
       <c r="E140" s="31"/>
       <c r="F140" s="45" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G140" s="20">
         <f t="shared" si="10"/>
@@ -7878,7 +7879,7 @@
       <c r="D141" s="14"/>
       <c r="E141" s="31"/>
       <c r="F141" s="45" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G141" s="20">
         <f t="shared" si="10"/>
@@ -7903,14 +7904,14 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B142" s="21"/>
       <c r="C142" s="3"/>
       <c r="D142" s="14"/>
       <c r="E142" s="31"/>
       <c r="F142" s="45" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G142" s="20">
         <f t="shared" si="10"/>
@@ -8046,11 +8047,11 @@
         <v>5</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E146" s="30"/>
       <c r="F146" s="46" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G146" s="20">
         <f t="shared" si="10"/>
@@ -8111,16 +8112,16 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B148" s="21"/>
       <c r="C148" s="3"/>
       <c r="D148" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E148" s="31"/>
       <c r="F148" s="45" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G148" s="20">
         <f t="shared" si="10"/>
@@ -8220,7 +8221,7 @@
       <c r="D151" s="14"/>
       <c r="E151" s="31"/>
       <c r="F151" s="45" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G151" s="20">
         <f t="shared" si="10"/>
@@ -8252,7 +8253,7 @@
       <c r="D152" s="14"/>
       <c r="E152" s="31"/>
       <c r="F152" s="45" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G152" s="20">
         <f t="shared" si="10"/>
@@ -8309,14 +8310,14 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E154" s="30">
         <v>10.1</v>
@@ -8337,14 +8338,14 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B155" s="1"/>
       <c r="C155" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E155" s="30">
         <v>10</v>
@@ -8382,7 +8383,7 @@
         <v>5</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E156" s="30">
         <v>7.85</v>
@@ -8418,7 +8419,7 @@
       <c r="D157" s="14"/>
       <c r="E157" s="31"/>
       <c r="F157" s="45" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G157" s="20">
         <f t="shared" si="10"/>
@@ -8576,11 +8577,11 @@
       <c r="B162" s="21"/>
       <c r="C162" s="3"/>
       <c r="D162" s="14" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E162" s="31"/>
       <c r="F162" s="45" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G162" s="20">
         <f t="shared" si="10"/>
@@ -8612,7 +8613,7 @@
       <c r="D163" s="14"/>
       <c r="E163" s="31"/>
       <c r="F163" s="45" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G163" s="20">
         <f t="shared" si="10"/>
@@ -8644,7 +8645,7 @@
       <c r="D164" s="14"/>
       <c r="E164" s="31"/>
       <c r="F164" s="45" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G164" s="20">
         <f t="shared" si="10"/>
@@ -8776,7 +8777,7 @@
       <c r="D168" s="14"/>
       <c r="E168" s="31"/>
       <c r="F168" s="45" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G168" s="20">
         <f t="shared" si="10"/>
@@ -8801,14 +8802,14 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B169" s="21"/>
       <c r="C169" s="3"/>
       <c r="D169" s="14"/>
       <c r="E169" s="31"/>
       <c r="F169" s="45" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G169" s="20">
         <f t="shared" si="10"/>
@@ -8840,7 +8841,7 @@
       <c r="D170" s="14"/>
       <c r="E170" s="31"/>
       <c r="F170" s="45" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G170" s="20">
         <f t="shared" si="10"/>
@@ -8865,7 +8866,7 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B171" s="1"/>
       <c r="C171" s="5" t="s">
@@ -8938,7 +8939,7 @@
         <v>5</v>
       </c>
       <c r="D173" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E173" s="30"/>
       <c r="F173" s="43"/>
@@ -8972,7 +8973,7 @@
       <c r="D174" s="14"/>
       <c r="E174" s="31"/>
       <c r="F174" s="45" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G174" s="20">
         <f t="shared" si="10"/>
@@ -9004,7 +9005,7 @@
       <c r="D175" s="14"/>
       <c r="E175" s="31"/>
       <c r="F175" s="45" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G175" s="20">
         <f t="shared" si="10"/>
@@ -9036,7 +9037,7 @@
       <c r="D176" s="14"/>
       <c r="E176" s="31"/>
       <c r="F176" s="45" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G176" s="20">
         <f t="shared" si="10"/>
@@ -9068,7 +9069,7 @@
       <c r="D177" s="14"/>
       <c r="E177" s="31"/>
       <c r="F177" s="45" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G177" s="20">
         <f t="shared" si="10"/>
@@ -9134,7 +9135,7 @@
       <c r="D179" s="14"/>
       <c r="E179" s="31"/>
       <c r="F179" s="45" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G179" s="20">
         <f t="shared" si="10"/>
@@ -9198,7 +9199,7 @@
       <c r="D181" s="14"/>
       <c r="E181" s="31"/>
       <c r="F181" s="45" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G181" s="20">
         <f t="shared" si="10"/>
@@ -9230,7 +9231,7 @@
       <c r="D182" s="14"/>
       <c r="E182" s="31"/>
       <c r="F182" s="45" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G182" s="20">
         <f t="shared" si="10"/>
@@ -9330,7 +9331,7 @@
       <c r="D185" s="14"/>
       <c r="E185" s="31"/>
       <c r="F185" s="45" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G185" s="20">
         <f t="shared" si="10"/>
@@ -9396,7 +9397,7 @@
       </c>
       <c r="E187" s="31"/>
       <c r="F187" s="45" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G187" s="20">
         <f t="shared" si="10"/>
@@ -9460,7 +9461,7 @@
         <v>5</v>
       </c>
       <c r="D189" s="13" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E189" s="30"/>
       <c r="F189" s="43"/>
@@ -9526,7 +9527,7 @@
         <v>5</v>
       </c>
       <c r="D191" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E191" s="30">
         <v>10.1</v>
@@ -9587,14 +9588,14 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B193" s="21"/>
       <c r="C193" s="3"/>
       <c r="D193" s="14"/>
       <c r="E193" s="31"/>
       <c r="F193" s="45" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G193" s="20">
         <f t="shared" si="10"/>
@@ -9626,7 +9627,7 @@
         <v>5</v>
       </c>
       <c r="D194" s="13" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E194" s="30">
         <v>8</v>
@@ -9864,7 +9865,7 @@
         <v>5</v>
       </c>
       <c r="D201" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E201" s="30"/>
       <c r="F201" s="43"/>
@@ -9932,7 +9933,7 @@
         <v>5</v>
       </c>
       <c r="D203" s="13" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E203" s="30">
         <v>19</v>
@@ -10000,7 +10001,7 @@
       <c r="D205" s="14"/>
       <c r="E205" s="31"/>
       <c r="F205" s="45" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G205" s="20">
         <f t="shared" si="15"/>
@@ -10160,7 +10161,7 @@
         <v>5</v>
       </c>
       <c r="D210" s="13" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E210" s="30"/>
       <c r="F210" s="43"/>
@@ -10258,7 +10259,7 @@
       <c r="D213" s="14"/>
       <c r="E213" s="31"/>
       <c r="F213" s="45" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G213" s="20">
         <f t="shared" si="15"/>
@@ -10326,7 +10327,7 @@
       <c r="D215" s="14"/>
       <c r="E215" s="31"/>
       <c r="F215" s="45" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G215" s="20">
         <f t="shared" si="15"/>
@@ -10362,7 +10363,7 @@
       </c>
       <c r="E216" s="30"/>
       <c r="F216" s="46" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G216" s="20">
         <f t="shared" si="15"/>
@@ -10426,7 +10427,7 @@
       <c r="D218" s="14"/>
       <c r="E218" s="31"/>
       <c r="F218" s="45" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G218" s="20">
         <f t="shared" si="15"/>
@@ -10458,7 +10459,7 @@
         <v>5</v>
       </c>
       <c r="D219" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E219" s="30">
         <v>5.68</v>
@@ -10551,14 +10552,14 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B222" s="21"/>
       <c r="C222" s="3"/>
       <c r="D222" s="14"/>
       <c r="E222" s="31"/>
       <c r="F222" s="45" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G222" s="20">
         <f t="shared" si="15"/>
@@ -10583,14 +10584,14 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B223" s="21"/>
       <c r="C223" s="3"/>
       <c r="D223" s="14"/>
       <c r="E223" s="31"/>
       <c r="F223" s="45" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G223" s="20">
         <f t="shared" si="15"/>
@@ -10686,7 +10687,7 @@
       <c r="D226" s="14"/>
       <c r="E226" s="31"/>
       <c r="F226" s="45" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G226" s="20">
         <f t="shared" si="15"/>
@@ -10722,7 +10723,7 @@
         <v>15</v>
       </c>
       <c r="F227" s="45" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G227" s="20">
         <f t="shared" si="15"/>
@@ -10788,7 +10789,7 @@
       <c r="D229" s="14"/>
       <c r="E229" s="31"/>
       <c r="F229" s="45" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G229" s="20">
         <f t="shared" si="15"/>
@@ -10914,7 +10915,7 @@
       <c r="D233" s="14"/>
       <c r="E233" s="31"/>
       <c r="F233" s="45" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G233" s="20">
         <f t="shared" si="15"/>
@@ -10939,7 +10940,7 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B234" s="1"/>
       <c r="C234" s="5" t="s">
@@ -11007,14 +11008,14 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="34" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B236" s="25"/>
       <c r="C236" s="35"/>
       <c r="D236" s="36"/>
       <c r="E236" s="37"/>
       <c r="F236" s="70" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G236" s="20">
         <f t="shared" ref="G236:G237" si="19">COUNTA(A236)</f>
@@ -11031,14 +11032,14 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="34" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B237" s="25"/>
       <c r="C237" s="35"/>
       <c r="D237" s="36"/>
       <c r="E237" s="37"/>
       <c r="F237" s="70" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G237" s="20">
         <f t="shared" si="19"/>
@@ -11118,7 +11119,7 @@
       <c r="D240" s="14"/>
       <c r="E240" s="31"/>
       <c r="F240" s="45" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G240" s="20">
         <f t="shared" si="15"/>
@@ -11150,7 +11151,7 @@
       <c r="D241" s="14"/>
       <c r="E241" s="31"/>
       <c r="F241" s="45" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G241" s="20">
         <f t="shared" si="15"/>
@@ -11182,7 +11183,7 @@
       <c r="D242" s="14"/>
       <c r="E242" s="31"/>
       <c r="F242" s="45" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G242" s="20">
         <f t="shared" si="15"/>
@@ -11207,7 +11208,7 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B243" s="1"/>
       <c r="C243" s="5" t="s">
@@ -11220,7 +11221,7 @@
         <v>15</v>
       </c>
       <c r="F243" s="46" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G243" s="20">
         <f t="shared" si="15"/>
@@ -11252,7 +11253,7 @@
       <c r="D244" s="14"/>
       <c r="E244" s="31"/>
       <c r="F244" s="45" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G244" s="20">
         <f t="shared" si="15"/>
@@ -11277,14 +11278,14 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B245" s="21"/>
       <c r="C245" s="3"/>
       <c r="D245" s="14"/>
       <c r="E245" s="31"/>
       <c r="F245" s="45" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G245" s="20">
         <f t="shared" si="15"/>
@@ -11340,7 +11341,7 @@
       <c r="D247" s="14"/>
       <c r="E247" s="31"/>
       <c r="F247" s="45" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G247" s="20">
         <f t="shared" si="15"/>
@@ -11364,7 +11365,7 @@
       <c r="D248" s="14"/>
       <c r="E248" s="31"/>
       <c r="F248" s="45" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G248" s="20">
         <f t="shared" si="15"/>
@@ -11396,7 +11397,7 @@
       <c r="D249" s="14"/>
       <c r="E249" s="31"/>
       <c r="F249" s="45" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G249" s="20">
         <f t="shared" si="15"/>
@@ -11466,7 +11467,7 @@
         <v>129</v>
       </c>
       <c r="F251" s="46" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G251" s="20">
         <f t="shared" si="15"/>
@@ -11496,11 +11497,11 @@
       <c r="B252" s="21"/>
       <c r="C252" s="3"/>
       <c r="D252" s="14" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E252" s="31"/>
       <c r="F252" s="45" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G252" s="20">
         <f t="shared" si="15"/>
@@ -11660,7 +11661,7 @@
       <c r="D257" s="14"/>
       <c r="E257" s="31"/>
       <c r="F257" s="45" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G257" s="20">
         <f t="shared" si="15"/>
@@ -11756,7 +11757,7 @@
       <c r="D260" s="14"/>
       <c r="E260" s="31"/>
       <c r="F260" s="45" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G260" s="20">
         <f t="shared" si="15"/>
@@ -11877,14 +11878,14 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B264" s="21"/>
       <c r="C264" s="3"/>
       <c r="D264" s="14"/>
       <c r="E264" s="31"/>
       <c r="F264" s="45" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G264" s="20">
         <f t="shared" si="15"/>
@@ -11916,7 +11917,7 @@
       <c r="D265" s="14"/>
       <c r="E265" s="31"/>
       <c r="F265" s="45" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G265" s="20">
         <f t="shared" si="15"/>
@@ -11948,15 +11949,15 @@
       <c r="D266" s="14"/>
       <c r="E266" s="31"/>
       <c r="F266" s="45" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G266" s="20">
-        <f t="shared" ref="G266:G328" si="21">COUNTA(A266)</f>
+        <f t="shared" ref="G266:G327" si="21">COUNTA(A266)</f>
         <v>1</v>
       </c>
       <c r="H266" s="18"/>
       <c r="I266" s="19">
-        <f t="shared" ref="I266:I328" si="22">COUNTA(C266)</f>
+        <f t="shared" ref="I266:I327" si="22">COUNTA(C266)</f>
         <v>0</v>
       </c>
       <c r="J266" s="19"/>
@@ -11980,7 +11981,7 @@
       <c r="D267" s="14"/>
       <c r="E267" s="31"/>
       <c r="F267" s="45" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G267" s="20">
         <f t="shared" si="21"/>
@@ -12012,7 +12013,7 @@
       <c r="D268" s="14"/>
       <c r="E268" s="31"/>
       <c r="F268" s="45" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G268" s="20">
         <f t="shared" si="21"/>
@@ -12044,7 +12045,7 @@
       <c r="D269" s="14"/>
       <c r="E269" s="31"/>
       <c r="F269" s="45" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G269" s="20">
         <f t="shared" si="21"/>
@@ -12133,14 +12134,14 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B272" s="1"/>
       <c r="C272" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D272" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E272" s="30">
         <v>19.329999999999998</v>
@@ -12176,7 +12177,7 @@
       <c r="D273" s="14"/>
       <c r="E273" s="31"/>
       <c r="F273" s="45" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G273" s="20">
         <f t="shared" si="21"/>
@@ -12208,7 +12209,7 @@
       <c r="D274" s="14"/>
       <c r="E274" s="31"/>
       <c r="F274" s="45" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G274" s="20">
         <f t="shared" si="21"/>
@@ -12272,11 +12273,11 @@
       <c r="B276" s="21"/>
       <c r="C276" s="3"/>
       <c r="D276" s="14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E276" s="31"/>
       <c r="F276" s="45" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G276" s="20">
         <f t="shared" si="21"/>
@@ -12291,11 +12292,11 @@
       <c r="K276" s="20"/>
       <c r="L276" s="19"/>
       <c r="M276" t="str">
-        <f t="shared" ref="M276:M342" si="23">IF(B276=1,E276,"")</f>
+        <f t="shared" ref="M276:M341" si="23">IF(B276=1,E276,"")</f>
         <v/>
       </c>
       <c r="N276" t="str">
-        <f t="shared" ref="N276:N342" si="24">IF(B276=2,E276,"")</f>
+        <f t="shared" ref="N276:N341" si="24">IF(B276=2,E276,"")</f>
         <v/>
       </c>
     </row>
@@ -12308,7 +12309,7 @@
       <c r="D277" s="14"/>
       <c r="E277" s="31"/>
       <c r="F277" s="45" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G277" s="20">
         <f t="shared" si="21"/>
@@ -12340,7 +12341,7 @@
       <c r="D278" s="14"/>
       <c r="E278" s="31"/>
       <c r="F278" s="45" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G278" s="20">
         <f t="shared" si="21"/>
@@ -12406,7 +12407,7 @@
       <c r="D280" s="14"/>
       <c r="E280" s="31"/>
       <c r="F280" s="45" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G280" s="20">
         <f t="shared" si="21"/>
@@ -12465,14 +12466,14 @@
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B282" s="1"/>
       <c r="C282" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D282" s="13" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E282" s="30"/>
       <c r="F282" s="43"/>
@@ -12499,14 +12500,14 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B283" s="1"/>
       <c r="C283" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D283" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E283" s="30">
         <v>15</v>
@@ -12573,14 +12574,14 @@
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B285" s="1"/>
       <c r="C285" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E285" s="30">
         <v>15</v>
@@ -12618,7 +12619,7 @@
       <c r="D286" s="14"/>
       <c r="E286" s="31"/>
       <c r="F286" s="45" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G286" s="20">
         <f t="shared" si="21"/>
@@ -12686,7 +12687,7 @@
       </c>
       <c r="E288" s="31"/>
       <c r="F288" s="45" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G288" s="20">
         <f t="shared" si="21"/>
@@ -12720,7 +12721,7 @@
       </c>
       <c r="E289" s="31"/>
       <c r="F289" s="45" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G289" s="20">
         <f t="shared" si="21"/>
@@ -12802,7 +12803,7 @@
       <c r="D292" s="14"/>
       <c r="E292" s="31"/>
       <c r="F292" s="45" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G292" s="20">
         <f t="shared" si="21"/>
@@ -12834,7 +12835,7 @@
       <c r="D293" s="14"/>
       <c r="E293" s="31"/>
       <c r="F293" s="45" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G293" s="20">
         <f t="shared" si="21"/>
@@ -12866,7 +12867,7 @@
       <c r="D294" s="14"/>
       <c r="E294" s="31"/>
       <c r="F294" s="45" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G294" s="20">
         <f t="shared" si="21"/>
@@ -12898,7 +12899,7 @@
       <c r="D295" s="14"/>
       <c r="E295" s="31"/>
       <c r="F295" s="45" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G295" s="20">
         <f t="shared" si="21"/>
@@ -12930,7 +12931,7 @@
       <c r="D296" s="14"/>
       <c r="E296" s="31"/>
       <c r="F296" s="45" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G296" s="20">
         <f t="shared" si="21"/>
@@ -12962,7 +12963,7 @@
         <v>5</v>
       </c>
       <c r="D297" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E297" s="30">
         <v>11.41</v>
@@ -13034,7 +13035,7 @@
       <c r="D299" s="14"/>
       <c r="E299" s="31"/>
       <c r="F299" s="45" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G299" s="20">
         <f t="shared" si="21"/>
@@ -13125,14 +13126,14 @@
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" s="34" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B302" s="25"/>
       <c r="C302" s="35"/>
       <c r="D302" s="36"/>
       <c r="E302" s="37"/>
       <c r="F302" s="70" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G302" s="20">
         <f t="shared" si="21"/>
@@ -13156,18 +13157,16 @@
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A303" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B303" s="21"/>
-      <c r="C303" s="3"/>
-      <c r="D303" s="14" t="s">
-        <v>702</v>
-      </c>
-      <c r="E303" s="31"/>
-      <c r="F303" s="45" t="s">
-        <v>703</v>
-      </c>
+      <c r="A303" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B303" s="1"/>
+      <c r="C303" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D303" s="13"/>
+      <c r="E303" s="30"/>
+      <c r="F303" s="43"/>
       <c r="G303" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13175,7 +13174,7 @@
       <c r="H303" s="18"/>
       <c r="I303" s="19">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J303" s="19"/>
       <c r="K303" s="20"/>
@@ -13191,7 +13190,7 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B304" s="1"/>
       <c r="C304" s="5" t="s">
@@ -13222,16 +13221,18 @@
       </c>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A305" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B305" s="1"/>
-      <c r="C305" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D305" s="13"/>
-      <c r="E305" s="30"/>
-      <c r="F305" s="43"/>
+      <c r="A305" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B305" s="21"/>
+      <c r="C305" s="3"/>
+      <c r="D305" s="14" t="s">
+        <v>701</v>
+      </c>
+      <c r="E305" s="31"/>
+      <c r="F305" s="45" t="s">
+        <v>703</v>
+      </c>
       <c r="G305" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13239,7 +13240,7 @@
       <c r="H305" s="18"/>
       <c r="I305" s="19">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J305" s="19"/>
       <c r="K305" s="20"/>
@@ -13255,13 +13256,11 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>325</v>
+        <v>209</v>
       </c>
       <c r="B306" s="21"/>
       <c r="C306" s="3"/>
-      <c r="D306" s="14" t="s">
-        <v>702</v>
-      </c>
+      <c r="D306" s="14"/>
       <c r="E306" s="31"/>
       <c r="F306" s="45" t="s">
         <v>704</v>
@@ -13289,7 +13288,7 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>209</v>
+        <v>348</v>
       </c>
       <c r="B307" s="21"/>
       <c r="C307" s="3"/>
@@ -13321,7 +13320,7 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>348</v>
+        <v>808</v>
       </c>
       <c r="B308" s="21"/>
       <c r="C308" s="3"/>
@@ -13352,16 +13351,16 @@
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A309" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="B309" s="21"/>
-      <c r="C309" s="3"/>
-      <c r="D309" s="14"/>
-      <c r="E309" s="31"/>
-      <c r="F309" s="45" t="s">
-        <v>707</v>
-      </c>
+      <c r="A309" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B309" s="1"/>
+      <c r="C309" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D309" s="13"/>
+      <c r="E309" s="30"/>
+      <c r="F309" s="43"/>
       <c r="G309" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13369,7 +13368,7 @@
       <c r="H309" s="18"/>
       <c r="I309" s="19">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J309" s="19"/>
       <c r="K309" s="20"/>
@@ -13385,7 +13384,7 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
-        <v>336</v>
+        <v>12</v>
       </c>
       <c r="B310" s="1"/>
       <c r="C310" s="5" t="s">
@@ -13416,16 +13415,16 @@
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A311" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B311" s="1"/>
-      <c r="C311" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D311" s="13"/>
-      <c r="E311" s="30"/>
-      <c r="F311" s="43"/>
+      <c r="A311" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B311" s="21"/>
+      <c r="C311" s="3"/>
+      <c r="D311" s="14"/>
+      <c r="E311" s="31"/>
+      <c r="F311" s="45" t="s">
+        <v>707</v>
+      </c>
       <c r="G311" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13433,7 +13432,7 @@
       <c r="H311" s="18"/>
       <c r="I311" s="19">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J311" s="19"/>
       <c r="K311" s="20"/>
@@ -13449,7 +13448,7 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="B312" s="21"/>
       <c r="C312" s="3"/>
@@ -13481,7 +13480,7 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>339</v>
+        <v>280</v>
       </c>
       <c r="B313" s="21"/>
       <c r="C313" s="3"/>
@@ -13513,7 +13512,7 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="B314" s="21"/>
       <c r="C314" s="3"/>
@@ -13545,7 +13544,7 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>350</v>
+        <v>484</v>
       </c>
       <c r="B315" s="21"/>
       <c r="C315" s="3"/>
@@ -13576,16 +13575,20 @@
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A316" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B316" s="21"/>
-      <c r="C316" s="3"/>
-      <c r="D316" s="14"/>
-      <c r="E316" s="31"/>
-      <c r="F316" s="45" t="s">
-        <v>712</v>
-      </c>
+      <c r="A316" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B316" s="1"/>
+      <c r="C316" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D316" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E316" s="30">
+        <v>15</v>
+      </c>
+      <c r="F316" s="43"/>
       <c r="G316" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13593,7 +13596,7 @@
       <c r="H316" s="18"/>
       <c r="I316" s="19">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J316" s="19"/>
       <c r="K316" s="20"/>
@@ -13608,20 +13611,16 @@
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A317" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B317" s="1"/>
-      <c r="C317" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D317" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E317" s="30">
-        <v>15</v>
-      </c>
-      <c r="F317" s="43"/>
+      <c r="A317" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B317" s="21"/>
+      <c r="C317" s="3"/>
+      <c r="D317" s="14"/>
+      <c r="E317" s="31"/>
+      <c r="F317" s="45" t="s">
+        <v>712</v>
+      </c>
       <c r="G317" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13629,7 +13628,7 @@
       <c r="H317" s="18"/>
       <c r="I317" s="19">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J317" s="19"/>
       <c r="K317" s="20"/>
@@ -13645,7 +13644,7 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B318" s="21"/>
       <c r="C318" s="3"/>
@@ -13677,7 +13676,7 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>284</v>
+        <v>441</v>
       </c>
       <c r="B319" s="21"/>
       <c r="C319" s="3"/>
@@ -13709,11 +13708,13 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>441</v>
+        <v>221</v>
       </c>
       <c r="B320" s="21"/>
       <c r="C320" s="3"/>
-      <c r="D320" s="14"/>
+      <c r="D320" s="14" t="s">
+        <v>465</v>
+      </c>
       <c r="E320" s="31"/>
       <c r="F320" s="45" t="s">
         <v>715</v>
@@ -13741,13 +13742,11 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B321" s="21"/>
       <c r="C321" s="3"/>
-      <c r="D321" s="14" t="s">
-        <v>465</v>
-      </c>
+      <c r="D321" s="14"/>
       <c r="E321" s="31"/>
       <c r="F321" s="45" t="s">
         <v>716</v>
@@ -13774,16 +13773,20 @@
       </c>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A322" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B322" s="21"/>
-      <c r="C322" s="3"/>
-      <c r="D322" s="14"/>
-      <c r="E322" s="31"/>
-      <c r="F322" s="45" t="s">
-        <v>717</v>
-      </c>
+      <c r="A322" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B322" s="1"/>
+      <c r="C322" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D322" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E322" s="30">
+        <v>15</v>
+      </c>
+      <c r="F322" s="43"/>
       <c r="G322" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13791,7 +13794,7 @@
       <c r="H322" s="18"/>
       <c r="I322" s="19">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J322" s="19"/>
       <c r="K322" s="20"/>
@@ -13806,20 +13809,18 @@
       </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A323" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B323" s="1"/>
-      <c r="C323" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D323" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E323" s="30">
-        <v>15</v>
-      </c>
-      <c r="F323" s="43"/>
+      <c r="A323" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B323" s="21"/>
+      <c r="C323" s="3"/>
+      <c r="D323" s="14" t="s">
+        <v>718</v>
+      </c>
+      <c r="E323" s="31"/>
+      <c r="F323" s="45" t="s">
+        <v>717</v>
+      </c>
       <c r="G323" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13827,32 +13828,22 @@
       <c r="H323" s="18"/>
       <c r="I323" s="19">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J323" s="19"/>
       <c r="K323" s="20"/>
       <c r="L323" s="19"/>
-      <c r="M323" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N323" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="B324" s="21"/>
       <c r="C324" s="3"/>
-      <c r="D324" s="14" t="s">
-        <v>719</v>
-      </c>
+      <c r="D324" s="14"/>
       <c r="E324" s="31"/>
       <c r="F324" s="45" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G324" s="20">
         <f t="shared" si="21"/>
@@ -13866,18 +13857,26 @@
       <c r="J324" s="19"/>
       <c r="K324" s="20"/>
       <c r="L324" s="19"/>
+      <c r="M324" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N324" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A325" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B325" s="21"/>
-      <c r="C325" s="3"/>
-      <c r="D325" s="14"/>
-      <c r="E325" s="31"/>
-      <c r="F325" s="45" t="s">
-        <v>720</v>
-      </c>
+      <c r="A325" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B325" s="1"/>
+      <c r="C325" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D325" s="13"/>
+      <c r="E325" s="30"/>
+      <c r="F325" s="43"/>
       <c r="G325" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13885,7 +13884,7 @@
       <c r="H325" s="18"/>
       <c r="I325" s="19">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J325" s="19"/>
       <c r="K325" s="20"/>
@@ -13901,7 +13900,7 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="B326" s="1"/>
       <c r="C326" s="5" t="s">
@@ -13933,14 +13932,18 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
-        <v>233</v>
+        <v>444</v>
       </c>
       <c r="B327" s="1"/>
       <c r="C327" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D327" s="13"/>
-      <c r="E327" s="30"/>
+      <c r="D327" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E327" s="30">
+        <v>12</v>
+      </c>
       <c r="F327" s="43"/>
       <c r="G327" s="20">
         <f t="shared" si="21"/>
@@ -13964,28 +13967,24 @@
       </c>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A328" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="B328" s="1"/>
-      <c r="C328" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D328" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="E328" s="30">
-        <v>12</v>
-      </c>
-      <c r="F328" s="43"/>
+      <c r="A328" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B328" s="21"/>
+      <c r="C328" s="3"/>
+      <c r="D328" s="14"/>
+      <c r="E328" s="31"/>
+      <c r="F328" s="45" t="s">
+        <v>720</v>
+      </c>
       <c r="G328" s="20">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G328:G390" si="25">COUNTA(A328)</f>
         <v>1</v>
       </c>
       <c r="H328" s="18"/>
       <c r="I328" s="19">
-        <f t="shared" si="22"/>
-        <v>1</v>
+        <f t="shared" ref="I328:I390" si="26">COUNTA(C328)</f>
+        <v>0</v>
       </c>
       <c r="J328" s="19"/>
       <c r="K328" s="20"/>
@@ -14000,24 +13999,28 @@
       </c>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A329" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B329" s="21"/>
-      <c r="C329" s="3"/>
-      <c r="D329" s="14"/>
-      <c r="E329" s="31"/>
-      <c r="F329" s="45" t="s">
-        <v>721</v>
-      </c>
+      <c r="A329" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B329" s="1"/>
+      <c r="C329" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D329" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="E329" s="30">
+        <v>23</v>
+      </c>
+      <c r="F329" s="43"/>
       <c r="G329" s="20">
-        <f t="shared" ref="G329:G391" si="25">COUNTA(A329)</f>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="H329" s="18"/>
       <c r="I329" s="19">
-        <f t="shared" ref="I329:I391" si="26">COUNTA(C329)</f>
-        <v>0</v>
+        <f t="shared" si="26"/>
+        <v>1</v>
       </c>
       <c r="J329" s="19"/>
       <c r="K329" s="20"/>
@@ -14032,20 +14035,16 @@
       </c>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A330" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B330" s="1"/>
-      <c r="C330" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D330" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="E330" s="30">
-        <v>23</v>
-      </c>
-      <c r="F330" s="43"/>
+      <c r="A330" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B330" s="21"/>
+      <c r="C330" s="3"/>
+      <c r="D330" s="14"/>
+      <c r="E330" s="31"/>
+      <c r="F330" s="45" t="s">
+        <v>721</v>
+      </c>
       <c r="G330" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14053,7 +14052,7 @@
       <c r="H330" s="18"/>
       <c r="I330" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J330" s="19"/>
       <c r="K330" s="20"/>
@@ -14068,16 +14067,20 @@
       </c>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A331" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B331" s="21"/>
-      <c r="C331" s="3"/>
-      <c r="D331" s="14"/>
-      <c r="E331" s="31"/>
-      <c r="F331" s="45" t="s">
-        <v>722</v>
-      </c>
+      <c r="A331" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B331" s="1"/>
+      <c r="C331" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D331" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E331" s="30">
+        <v>25</v>
+      </c>
+      <c r="F331" s="43"/>
       <c r="G331" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14085,7 +14088,7 @@
       <c r="H331" s="18"/>
       <c r="I331" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J331" s="19"/>
       <c r="K331" s="20"/>
@@ -14101,18 +14104,14 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B332" s="1"/>
       <c r="C332" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D332" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E332" s="30">
-        <v>25</v>
-      </c>
+      <c r="D332" s="13"/>
+      <c r="E332" s="30"/>
       <c r="F332" s="43"/>
       <c r="G332" s="20">
         <f t="shared" si="25"/>
@@ -14136,16 +14135,16 @@
       </c>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A333" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B333" s="1"/>
-      <c r="C333" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D333" s="13"/>
-      <c r="E333" s="30"/>
-      <c r="F333" s="43"/>
+      <c r="A333" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B333" s="21"/>
+      <c r="C333" s="3"/>
+      <c r="D333" s="14"/>
+      <c r="E333" s="31"/>
+      <c r="F333" s="45" t="s">
+        <v>722</v>
+      </c>
       <c r="G333" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14153,7 +14152,7 @@
       <c r="H333" s="18"/>
       <c r="I333" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J333" s="19"/>
       <c r="K333" s="20"/>
@@ -14168,16 +14167,16 @@
       </c>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A334" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B334" s="21"/>
-      <c r="C334" s="3"/>
-      <c r="D334" s="14"/>
-      <c r="E334" s="31"/>
-      <c r="F334" s="45" t="s">
-        <v>723</v>
-      </c>
+      <c r="A334" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B334" s="1"/>
+      <c r="C334" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D334" s="13"/>
+      <c r="E334" s="30"/>
+      <c r="F334" s="43"/>
       <c r="G334" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14185,7 +14184,7 @@
       <c r="H334" s="18"/>
       <c r="I334" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J334" s="19"/>
       <c r="K334" s="20"/>
@@ -14201,15 +14200,21 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
-        <v>121</v>
+        <v>529</v>
       </c>
       <c r="B335" s="1"/>
       <c r="C335" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D335" s="13"/>
-      <c r="E335" s="30"/>
-      <c r="F335" s="43"/>
+      <c r="D335" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E335" s="30">
+        <v>15</v>
+      </c>
+      <c r="F335" s="43">
+        <v>6</v>
+      </c>
       <c r="G335" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14233,21 +14238,15 @@
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
-        <v>530</v>
+        <v>287</v>
       </c>
       <c r="B336" s="1"/>
       <c r="C336" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D336" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="E336" s="30">
-        <v>15</v>
-      </c>
-      <c r="F336" s="43">
-        <v>6</v>
-      </c>
+      <c r="D336" s="13"/>
+      <c r="E336" s="30"/>
+      <c r="F336" s="43"/>
       <c r="G336" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14271,7 +14270,7 @@
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="B337" s="1"/>
       <c r="C337" s="5" t="s">
@@ -14302,16 +14301,16 @@
       </c>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A338" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B338" s="1"/>
-      <c r="C338" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D338" s="13"/>
-      <c r="E338" s="30"/>
-      <c r="F338" s="43"/>
+      <c r="A338" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B338" s="21"/>
+      <c r="C338" s="3"/>
+      <c r="D338" s="14"/>
+      <c r="E338" s="31"/>
+      <c r="F338" s="45" t="s">
+        <v>723</v>
+      </c>
       <c r="G338" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14319,7 +14318,7 @@
       <c r="H338" s="18"/>
       <c r="I338" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J338" s="19"/>
       <c r="K338" s="20"/>
@@ -14335,14 +14334,14 @@
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>355</v>
+        <v>770</v>
       </c>
       <c r="B339" s="21"/>
       <c r="C339" s="3"/>
       <c r="D339" s="14"/>
       <c r="E339" s="31"/>
       <c r="F339" s="45" t="s">
-        <v>724</v>
+        <v>769</v>
       </c>
       <c r="G339" s="20">
         <f t="shared" si="25"/>
@@ -14366,16 +14365,16 @@
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A340" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="B340" s="21"/>
-      <c r="C340" s="3"/>
-      <c r="D340" s="14"/>
-      <c r="E340" s="31"/>
-      <c r="F340" s="45" t="s">
-        <v>770</v>
-      </c>
+      <c r="A340" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B340" s="1"/>
+      <c r="C340" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D340" s="13"/>
+      <c r="E340" s="30"/>
+      <c r="F340" s="43"/>
       <c r="G340" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14383,7 +14382,7 @@
       <c r="H340" s="18"/>
       <c r="I340" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J340" s="19"/>
       <c r="K340" s="20"/>
@@ -14399,7 +14398,7 @@
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="B341" s="1"/>
       <c r="C341" s="5" t="s">
@@ -14431,7 +14430,7 @@
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
-        <v>17</v>
+        <v>226</v>
       </c>
       <c r="B342" s="1"/>
       <c r="C342" s="5" t="s">
@@ -14453,24 +14452,28 @@
       <c r="K342" s="20"/>
       <c r="L342" s="19"/>
       <c r="M342" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="M342:M405" si="27">IF(B342=1,E342,"")</f>
         <v/>
       </c>
       <c r="N342" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="N342:N405" si="28">IF(B342=2,E342,"")</f>
         <v/>
       </c>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="B343" s="1"/>
       <c r="C343" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D343" s="13"/>
-      <c r="E343" s="30"/>
+        <v>303</v>
+      </c>
+      <c r="D343" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E343" s="30">
+        <v>25</v>
+      </c>
       <c r="F343" s="43"/>
       <c r="G343" s="20">
         <f t="shared" si="25"/>
@@ -14485,28 +14488,26 @@
       <c r="K343" s="20"/>
       <c r="L343" s="19"/>
       <c r="M343" t="str">
-        <f t="shared" ref="M343:M406" si="27">IF(B343=1,E343,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="N343" t="str">
-        <f t="shared" ref="N343:N406" si="28">IF(B343=2,E343,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B344" s="1"/>
       <c r="C344" s="5" t="s">
-        <v>303</v>
+        <v>5</v>
       </c>
       <c r="D344" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E344" s="30">
-        <v>25</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="E344" s="30"/>
       <c r="F344" s="43"/>
       <c r="G344" s="20">
         <f t="shared" si="25"/>
@@ -14531,7 +14532,7 @@
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
-        <v>124</v>
+        <v>411</v>
       </c>
       <c r="B345" s="1"/>
       <c r="C345" s="5" t="s">
@@ -14565,15 +14566,13 @@
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
-        <v>411</v>
+        <v>245</v>
       </c>
       <c r="B346" s="1"/>
       <c r="C346" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D346" s="13" t="s">
-        <v>546</v>
-      </c>
+      <c r="D346" s="13"/>
       <c r="E346" s="30"/>
       <c r="F346" s="43"/>
       <c r="G346" s="20">
@@ -14599,13 +14598,15 @@
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="B347" s="1"/>
       <c r="C347" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D347" s="13"/>
+      <c r="D347" s="13" t="s">
+        <v>474</v>
+      </c>
       <c r="E347" s="30"/>
       <c r="F347" s="43"/>
       <c r="G347" s="20">
@@ -14630,18 +14631,16 @@
       </c>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A348" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B348" s="1"/>
-      <c r="C348" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D348" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="E348" s="30"/>
-      <c r="F348" s="43"/>
+      <c r="A348" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B348" s="21"/>
+      <c r="C348" s="3"/>
+      <c r="D348" s="14"/>
+      <c r="E348" s="31"/>
+      <c r="F348" s="45" t="s">
+        <v>724</v>
+      </c>
       <c r="G348" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14649,7 +14648,7 @@
       <c r="H348" s="18"/>
       <c r="I348" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J348" s="19"/>
       <c r="K348" s="20"/>
@@ -14664,16 +14663,16 @@
       </c>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A349" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B349" s="21"/>
-      <c r="C349" s="3"/>
-      <c r="D349" s="14"/>
-      <c r="E349" s="31"/>
-      <c r="F349" s="45" t="s">
-        <v>725</v>
-      </c>
+      <c r="A349" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B349" s="1"/>
+      <c r="C349" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D349" s="13"/>
+      <c r="E349" s="30"/>
+      <c r="F349" s="43"/>
       <c r="G349" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14681,7 +14680,7 @@
       <c r="H349" s="18"/>
       <c r="I349" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J349" s="19"/>
       <c r="K349" s="20"/>
@@ -14696,16 +14695,16 @@
       </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A350" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B350" s="1"/>
-      <c r="C350" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D350" s="13"/>
-      <c r="E350" s="30"/>
-      <c r="F350" s="43"/>
+      <c r="A350" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B350" s="21"/>
+      <c r="C350" s="3"/>
+      <c r="D350" s="14"/>
+      <c r="E350" s="31"/>
+      <c r="F350" s="45" t="s">
+        <v>725</v>
+      </c>
       <c r="G350" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14713,7 +14712,7 @@
       <c r="H350" s="18"/>
       <c r="I350" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J350" s="19"/>
       <c r="K350" s="20"/>
@@ -14728,16 +14727,16 @@
       </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A351" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B351" s="21"/>
-      <c r="C351" s="3"/>
-      <c r="D351" s="14"/>
-      <c r="E351" s="31"/>
-      <c r="F351" s="45" t="s">
-        <v>726</v>
-      </c>
+      <c r="A351" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B351" s="1"/>
+      <c r="C351" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D351" s="13"/>
+      <c r="E351" s="30"/>
+      <c r="F351" s="43"/>
       <c r="G351" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14745,7 +14744,7 @@
       <c r="H351" s="18"/>
       <c r="I351" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J351" s="19"/>
       <c r="K351" s="20"/>
@@ -14761,7 +14760,7 @@
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B352" s="1"/>
       <c r="C352" s="5" t="s">
@@ -14793,7 +14792,7 @@
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B353" s="1"/>
       <c r="C353" s="5" t="s">
@@ -14824,16 +14823,16 @@
       </c>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A354" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B354" s="1"/>
-      <c r="C354" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D354" s="13"/>
-      <c r="E354" s="30"/>
-      <c r="F354" s="43"/>
+      <c r="A354" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B354" s="21"/>
+      <c r="C354" s="3"/>
+      <c r="D354" s="14"/>
+      <c r="E354" s="31"/>
+      <c r="F354" s="45" t="s">
+        <v>726</v>
+      </c>
       <c r="G354" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14841,7 +14840,7 @@
       <c r="H354" s="18"/>
       <c r="I354" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J354" s="19"/>
       <c r="K354" s="20"/>
@@ -14856,16 +14855,16 @@
       </c>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A355" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B355" s="21"/>
-      <c r="C355" s="3"/>
-      <c r="D355" s="14"/>
-      <c r="E355" s="31"/>
-      <c r="F355" s="45" t="s">
-        <v>727</v>
-      </c>
+      <c r="A355" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B355" s="1"/>
+      <c r="C355" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D355" s="13"/>
+      <c r="E355" s="30"/>
+      <c r="F355" s="43"/>
       <c r="G355" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -14873,7 +14872,7 @@
       <c r="H355" s="18"/>
       <c r="I355" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J355" s="19"/>
       <c r="K355" s="20"/>
@@ -14889,7 +14888,7 @@
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="B356" s="1"/>
       <c r="C356" s="5" t="s">
@@ -14921,7 +14920,7 @@
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
-        <v>182</v>
+        <v>376</v>
       </c>
       <c r="B357" s="1"/>
       <c r="C357" s="5" t="s">
@@ -14953,7 +14952,7 @@
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
-        <v>376</v>
+        <v>126</v>
       </c>
       <c r="B358" s="1"/>
       <c r="C358" s="5" t="s">
@@ -14985,13 +14984,15 @@
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
-        <v>126</v>
+        <v>302</v>
       </c>
       <c r="B359" s="1"/>
       <c r="C359" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D359" s="13"/>
+      <c r="D359" s="13" t="s">
+        <v>310</v>
+      </c>
       <c r="E359" s="30"/>
       <c r="F359" s="43"/>
       <c r="G359" s="20">
@@ -15017,15 +15018,13 @@
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="B360" s="1"/>
       <c r="C360" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D360" s="13" t="s">
-        <v>310</v>
-      </c>
+      <c r="D360" s="13"/>
       <c r="E360" s="30"/>
       <c r="F360" s="43"/>
       <c r="G360" s="20">
@@ -15050,16 +15049,16 @@
       </c>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A361" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B361" s="1"/>
-      <c r="C361" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D361" s="13"/>
-      <c r="E361" s="30"/>
-      <c r="F361" s="43"/>
+      <c r="A361" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B361" s="21"/>
+      <c r="C361" s="3"/>
+      <c r="D361" s="14"/>
+      <c r="E361" s="31"/>
+      <c r="F361" s="45" t="s">
+        <v>727</v>
+      </c>
       <c r="G361" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15067,7 +15066,7 @@
       <c r="H361" s="18"/>
       <c r="I361" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J361" s="19"/>
       <c r="K361" s="20"/>
@@ -15082,16 +15081,18 @@
       </c>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A362" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B362" s="21"/>
-      <c r="C362" s="3"/>
-      <c r="D362" s="14"/>
-      <c r="E362" s="31"/>
-      <c r="F362" s="45" t="s">
-        <v>728</v>
-      </c>
+      <c r="A362" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B362" s="1"/>
+      <c r="C362" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D362" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="E362" s="30"/>
+      <c r="F362" s="43"/>
       <c r="G362" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15099,7 +15100,7 @@
       <c r="H362" s="18"/>
       <c r="I362" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J362" s="19"/>
       <c r="K362" s="20"/>
@@ -15115,15 +15116,13 @@
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
-        <v>462</v>
+        <v>127</v>
       </c>
       <c r="B363" s="1"/>
       <c r="C363" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D363" s="13" t="s">
-        <v>463</v>
-      </c>
+      <c r="D363" s="13"/>
       <c r="E363" s="30"/>
       <c r="F363" s="43"/>
       <c r="G363" s="20">
@@ -15149,7 +15148,7 @@
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B364" s="1"/>
       <c r="C364" s="5" t="s">
@@ -15157,7 +15156,7 @@
       </c>
       <c r="D364" s="13"/>
       <c r="E364" s="30"/>
-      <c r="F364" s="43"/>
+      <c r="F364" s="46"/>
       <c r="G364" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15180,16 +15179,16 @@
       </c>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A365" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B365" s="1"/>
-      <c r="C365" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D365" s="13"/>
-      <c r="E365" s="30"/>
-      <c r="F365" s="46"/>
+      <c r="A365" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B365" s="21"/>
+      <c r="C365" s="3"/>
+      <c r="D365" s="14"/>
+      <c r="E365" s="31"/>
+      <c r="F365" s="45" t="s">
+        <v>728</v>
+      </c>
       <c r="G365" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15197,7 +15196,7 @@
       <c r="H365" s="18"/>
       <c r="I365" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J365" s="19"/>
       <c r="K365" s="20"/>
@@ -15213,7 +15212,7 @@
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>129</v>
+        <v>481</v>
       </c>
       <c r="B366" s="21"/>
       <c r="C366" s="3"/>
@@ -15245,11 +15244,13 @@
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>481</v>
+        <v>380</v>
       </c>
       <c r="B367" s="21"/>
       <c r="C367" s="3"/>
-      <c r="D367" s="14"/>
+      <c r="D367" s="14" t="s">
+        <v>488</v>
+      </c>
       <c r="E367" s="31"/>
       <c r="F367" s="45" t="s">
         <v>730</v>
@@ -15277,13 +15278,11 @@
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>380</v>
+        <v>212</v>
       </c>
       <c r="B368" s="21"/>
       <c r="C368" s="3"/>
-      <c r="D368" s="14" t="s">
-        <v>489</v>
-      </c>
+      <c r="D368" s="14"/>
       <c r="E368" s="31"/>
       <c r="F368" s="45" t="s">
         <v>731</v>
@@ -15310,16 +15309,20 @@
       </c>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A369" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B369" s="21"/>
-      <c r="C369" s="3"/>
-      <c r="D369" s="14"/>
-      <c r="E369" s="31"/>
-      <c r="F369" s="45" t="s">
-        <v>732</v>
-      </c>
+      <c r="A369" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B369" s="1"/>
+      <c r="C369" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D369" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="E369" s="30">
+        <v>15.25</v>
+      </c>
+      <c r="F369" s="46"/>
       <c r="G369" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15327,7 +15330,7 @@
       <c r="H369" s="18"/>
       <c r="I369" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J369" s="19"/>
       <c r="K369" s="20"/>
@@ -15343,19 +15346,15 @@
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="B370" s="1"/>
       <c r="C370" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D370" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="E370" s="30">
-        <v>15.25</v>
-      </c>
-      <c r="F370" s="46"/>
+      <c r="D370" s="13"/>
+      <c r="E370" s="30"/>
+      <c r="F370" s="43"/>
       <c r="G370" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15379,14 +15378,18 @@
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="B371" s="1"/>
       <c r="C371" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D371" s="13"/>
-      <c r="E371" s="30"/>
+        <v>303</v>
+      </c>
+      <c r="D371" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E371" s="30">
+        <v>24</v>
+      </c>
       <c r="F371" s="43"/>
       <c r="G371" s="20">
         <f t="shared" si="25"/>
@@ -15411,18 +15414,14 @@
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
-        <v>131</v>
+        <v>246</v>
       </c>
       <c r="B372" s="1"/>
       <c r="C372" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D372" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E372" s="30">
-        <v>24</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D372" s="13"/>
+      <c r="E372" s="30"/>
       <c r="F372" s="43"/>
       <c r="G372" s="20">
         <f t="shared" si="25"/>
@@ -15446,16 +15445,16 @@
       </c>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A373" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B373" s="1"/>
-      <c r="C373" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D373" s="13"/>
-      <c r="E373" s="30"/>
-      <c r="F373" s="43"/>
+      <c r="A373" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B373" s="21"/>
+      <c r="C373" s="3"/>
+      <c r="D373" s="14"/>
+      <c r="E373" s="31"/>
+      <c r="F373" s="45" t="s">
+        <v>732</v>
+      </c>
       <c r="G373" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15463,7 +15462,7 @@
       <c r="H373" s="18"/>
       <c r="I373" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J373" s="19"/>
       <c r="K373" s="20"/>
@@ -15478,16 +15477,16 @@
       </c>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A374" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B374" s="21"/>
-      <c r="C374" s="3"/>
-      <c r="D374" s="14"/>
-      <c r="E374" s="31"/>
-      <c r="F374" s="45" t="s">
-        <v>733</v>
-      </c>
+      <c r="A374" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B374" s="1"/>
+      <c r="C374" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D374" s="13"/>
+      <c r="E374" s="30"/>
+      <c r="F374" s="43"/>
       <c r="G374" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15495,7 +15494,7 @@
       <c r="H374" s="18"/>
       <c r="I374" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J374" s="19"/>
       <c r="K374" s="20"/>
@@ -15510,16 +15509,16 @@
       </c>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A375" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B375" s="1"/>
-      <c r="C375" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D375" s="13"/>
-      <c r="E375" s="30"/>
-      <c r="F375" s="43"/>
+      <c r="A375" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B375" s="21"/>
+      <c r="C375" s="3"/>
+      <c r="D375" s="14"/>
+      <c r="E375" s="31"/>
+      <c r="F375" s="45" t="s">
+        <v>733</v>
+      </c>
       <c r="G375" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15527,7 +15526,7 @@
       <c r="H375" s="18"/>
       <c r="I375" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J375" s="19"/>
       <c r="K375" s="20"/>
@@ -15542,16 +15541,20 @@
       </c>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A376" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B376" s="21"/>
-      <c r="C376" s="3"/>
-      <c r="D376" s="14"/>
-      <c r="E376" s="31"/>
-      <c r="F376" s="45" t="s">
-        <v>734</v>
-      </c>
+      <c r="A376" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B376" s="1"/>
+      <c r="C376" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D376" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E376" s="30">
+        <v>17</v>
+      </c>
+      <c r="F376" s="43"/>
       <c r="G376" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15559,7 +15562,7 @@
       <c r="H376" s="18"/>
       <c r="I376" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J376" s="19"/>
       <c r="K376" s="20"/>
@@ -15574,20 +15577,16 @@
       </c>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A377" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B377" s="1"/>
-      <c r="C377" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D377" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E377" s="30">
-        <v>17</v>
-      </c>
-      <c r="F377" s="43"/>
+      <c r="A377" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B377" s="21"/>
+      <c r="C377" s="3"/>
+      <c r="D377" s="14"/>
+      <c r="E377" s="31"/>
+      <c r="F377" s="45" t="s">
+        <v>734</v>
+      </c>
       <c r="G377" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15595,7 +15594,7 @@
       <c r="H377" s="18"/>
       <c r="I377" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J377" s="19"/>
       <c r="K377" s="20"/>
@@ -15611,14 +15610,16 @@
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>298</v>
+        <v>542</v>
       </c>
       <c r="B378" s="21"/>
       <c r="C378" s="3"/>
-      <c r="D378" s="14"/>
+      <c r="D378" s="14" t="s">
+        <v>735</v>
+      </c>
       <c r="E378" s="31"/>
       <c r="F378" s="45" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G378" s="20">
         <f t="shared" si="25"/>
@@ -15643,13 +15644,11 @@
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>543</v>
+        <v>133</v>
       </c>
       <c r="B379" s="21"/>
       <c r="C379" s="3"/>
-      <c r="D379" s="14" t="s">
-        <v>736</v>
-      </c>
+      <c r="D379" s="14"/>
       <c r="E379" s="31"/>
       <c r="F379" s="45" t="s">
         <v>737</v>
@@ -15677,14 +15676,16 @@
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>133</v>
+        <v>738</v>
       </c>
       <c r="B380" s="21"/>
       <c r="C380" s="3"/>
-      <c r="D380" s="14"/>
+      <c r="D380" s="14" t="s">
+        <v>740</v>
+      </c>
       <c r="E380" s="31"/>
       <c r="F380" s="45" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="G380" s="20">
         <f t="shared" si="25"/>
@@ -15709,16 +15710,18 @@
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>739</v>
+        <v>213</v>
       </c>
       <c r="B381" s="21"/>
       <c r="C381" s="3"/>
       <c r="D381" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="E381" s="31">
+        <v>15</v>
+      </c>
+      <c r="F381" s="45" t="s">
         <v>741</v>
-      </c>
-      <c r="E381" s="31"/>
-      <c r="F381" s="45" t="s">
-        <v>740</v>
       </c>
       <c r="G381" s="20">
         <f t="shared" si="25"/>
@@ -15743,16 +15746,12 @@
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>213</v>
+        <v>393</v>
       </c>
       <c r="B382" s="21"/>
       <c r="C382" s="3"/>
-      <c r="D382" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="E382" s="31">
-        <v>15</v>
-      </c>
+      <c r="D382" s="14"/>
+      <c r="E382" s="31"/>
       <c r="F382" s="45" t="s">
         <v>742</v>
       </c>
@@ -15778,16 +15777,18 @@
       </c>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A383" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="B383" s="21"/>
-      <c r="C383" s="3"/>
-      <c r="D383" s="14"/>
-      <c r="E383" s="31"/>
-      <c r="F383" s="45" t="s">
-        <v>743</v>
-      </c>
+      <c r="A383" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B383" s="1"/>
+      <c r="C383" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D383" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="E383" s="30"/>
+      <c r="F383" s="43"/>
       <c r="G383" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15795,7 +15796,7 @@
       <c r="H383" s="18"/>
       <c r="I383" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J383" s="19"/>
       <c r="K383" s="20"/>
@@ -15811,16 +15812,18 @@
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
-        <v>134</v>
+        <v>539</v>
       </c>
       <c r="B384" s="1"/>
       <c r="C384" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D384" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="E384" s="30"/>
+        <v>493</v>
+      </c>
+      <c r="E384" s="30">
+        <v>10</v>
+      </c>
       <c r="F384" s="43"/>
       <c r="G384" s="20">
         <f t="shared" si="25"/>
@@ -15845,19 +15848,15 @@
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
-        <v>540</v>
+        <v>135</v>
       </c>
       <c r="B385" s="1"/>
       <c r="C385" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D385" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="E385" s="30">
-        <v>10</v>
-      </c>
-      <c r="F385" s="43"/>
+      <c r="D385" s="13"/>
+      <c r="E385" s="30"/>
+      <c r="F385" s="46"/>
       <c r="G385" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15881,7 +15880,7 @@
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="B386" s="1"/>
       <c r="C386" s="5" t="s">
@@ -15913,15 +15912,19 @@
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B387" s="1"/>
       <c r="C387" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D387" s="13"/>
-      <c r="E387" s="30"/>
-      <c r="F387" s="46"/>
+      <c r="D387" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E387" s="30">
+        <v>11</v>
+      </c>
+      <c r="F387" s="43"/>
       <c r="G387" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15944,20 +15947,16 @@
       </c>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A388" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B388" s="1"/>
-      <c r="C388" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D388" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E388" s="30">
-        <v>11</v>
-      </c>
-      <c r="F388" s="43"/>
+      <c r="A388" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B388" s="21"/>
+      <c r="C388" s="3"/>
+      <c r="D388" s="14"/>
+      <c r="E388" s="31"/>
+      <c r="F388" s="45" t="s">
+        <v>743</v>
+      </c>
       <c r="G388" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -15965,7 +15964,7 @@
       <c r="H388" s="18"/>
       <c r="I388" s="19">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J388" s="19"/>
       <c r="K388" s="20"/>
@@ -15981,7 +15980,7 @@
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>248</v>
+        <v>412</v>
       </c>
       <c r="B389" s="21"/>
       <c r="C389" s="3"/>
@@ -16012,16 +16011,16 @@
       </c>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A390" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="B390" s="21"/>
-      <c r="C390" s="3"/>
-      <c r="D390" s="14"/>
-      <c r="E390" s="31"/>
-      <c r="F390" s="45" t="s">
-        <v>745</v>
-      </c>
+      <c r="A390" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B390" s="1"/>
+      <c r="C390" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D390" s="13"/>
+      <c r="E390" s="30"/>
+      <c r="F390" s="43"/>
       <c r="G390" s="20">
         <f t="shared" si="25"/>
         <v>1</v>
@@ -16029,7 +16028,7 @@
       <c r="H390" s="18"/>
       <c r="I390" s="19">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J390" s="19"/>
       <c r="K390" s="20"/>
@@ -16044,24 +16043,24 @@
       </c>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A391" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B391" s="1"/>
-      <c r="C391" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D391" s="13"/>
-      <c r="E391" s="30"/>
-      <c r="F391" s="43"/>
+      <c r="A391" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B391" s="21"/>
+      <c r="C391" s="3"/>
+      <c r="D391" s="14"/>
+      <c r="E391" s="31"/>
+      <c r="F391" s="45" t="s">
+        <v>745</v>
+      </c>
       <c r="G391" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G391:G454" si="29">COUNTA(A391)</f>
         <v>1</v>
       </c>
       <c r="H391" s="18"/>
       <c r="I391" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" ref="I391:I454" si="30">COUNTA(C391)</f>
+        <v>0</v>
       </c>
       <c r="J391" s="19"/>
       <c r="K391" s="20"/>
@@ -16076,24 +16075,24 @@
       </c>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A392" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B392" s="21"/>
-      <c r="C392" s="3"/>
-      <c r="D392" s="14"/>
-      <c r="E392" s="31"/>
-      <c r="F392" s="45" t="s">
-        <v>746</v>
-      </c>
+      <c r="A392" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B392" s="1"/>
+      <c r="C392" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D392" s="13"/>
+      <c r="E392" s="30"/>
+      <c r="F392" s="43"/>
       <c r="G392" s="20">
-        <f t="shared" ref="G392:G455" si="29">COUNTA(A392)</f>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H392" s="18"/>
       <c r="I392" s="19">
-        <f t="shared" ref="I392:I455" si="30">COUNTA(C392)</f>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J392" s="19"/>
       <c r="K392" s="20"/>
@@ -16109,7 +16108,7 @@
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B393" s="1"/>
       <c r="C393" s="5" t="s">
@@ -16141,14 +16140,18 @@
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B394" s="1"/>
       <c r="C394" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D394" s="13"/>
-      <c r="E394" s="30"/>
+      <c r="D394" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E394" s="30">
+        <v>18</v>
+      </c>
       <c r="F394" s="43"/>
       <c r="G394" s="20">
         <f t="shared" si="29"/>
@@ -16172,20 +16175,16 @@
       </c>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A395" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B395" s="1"/>
-      <c r="C395" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D395" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E395" s="30">
-        <v>18</v>
-      </c>
-      <c r="F395" s="43"/>
+      <c r="A395" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B395" s="21"/>
+      <c r="C395" s="3"/>
+      <c r="D395" s="14"/>
+      <c r="E395" s="31"/>
+      <c r="F395" s="45" t="s">
+        <v>746</v>
+      </c>
       <c r="G395" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16193,7 +16192,7 @@
       <c r="H395" s="18"/>
       <c r="I395" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J395" s="19"/>
       <c r="K395" s="20"/>
@@ -16209,7 +16208,7 @@
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>490</v>
+        <v>140</v>
       </c>
       <c r="B396" s="21"/>
       <c r="C396" s="3"/>
@@ -16241,7 +16240,7 @@
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>140</v>
+        <v>442</v>
       </c>
       <c r="B397" s="21"/>
       <c r="C397" s="3"/>
@@ -16272,16 +16271,20 @@
       </c>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A398" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="B398" s="21"/>
-      <c r="C398" s="3"/>
-      <c r="D398" s="14"/>
-      <c r="E398" s="31"/>
-      <c r="F398" s="45" t="s">
-        <v>749</v>
-      </c>
+      <c r="A398" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="B398" s="1"/>
+      <c r="C398" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D398" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E398" s="30">
+        <v>10</v>
+      </c>
+      <c r="F398" s="43"/>
       <c r="G398" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16289,34 +16292,22 @@
       <c r="H398" s="18"/>
       <c r="I398" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J398" s="19"/>
       <c r="K398" s="20"/>
       <c r="L398" s="19"/>
-      <c r="M398" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="N398" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
-        <v>533</v>
+        <v>299</v>
       </c>
       <c r="B399" s="1"/>
       <c r="C399" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D399" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="E399" s="30">
-        <v>10</v>
-      </c>
+      <c r="D399" s="13"/>
+      <c r="E399" s="30"/>
       <c r="F399" s="43"/>
       <c r="G399" s="20">
         <f t="shared" si="29"/>
@@ -16330,10 +16321,18 @@
       <c r="J399" s="19"/>
       <c r="K399" s="20"/>
       <c r="L399" s="19"/>
+      <c r="M399" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="N399" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="B400" s="1"/>
       <c r="C400" s="5" t="s">
@@ -16364,16 +16363,20 @@
       </c>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A401" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B401" s="1"/>
-      <c r="C401" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D401" s="13"/>
-      <c r="E401" s="30"/>
-      <c r="F401" s="43"/>
+      <c r="A401" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B401" s="21"/>
+      <c r="C401" s="3"/>
+      <c r="D401" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="E401" s="31">
+        <v>19</v>
+      </c>
+      <c r="F401" s="45" t="s">
+        <v>749</v>
+      </c>
       <c r="G401" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16381,7 +16384,7 @@
       <c r="H401" s="18"/>
       <c r="I401" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J401" s="19"/>
       <c r="K401" s="20"/>
@@ -16397,16 +16400,12 @@
     </row>
     <row r="402" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B402" s="21"/>
       <c r="C402" s="3"/>
-      <c r="D402" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="E402" s="31">
-        <v>19</v>
-      </c>
+      <c r="D402" s="14"/>
+      <c r="E402" s="31"/>
       <c r="F402" s="45" t="s">
         <v>750</v>
       </c>
@@ -16433,7 +16432,7 @@
     </row>
     <row r="403" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>391</v>
+        <v>141</v>
       </c>
       <c r="B403" s="21"/>
       <c r="C403" s="3"/>
@@ -16464,14 +16463,20 @@
       </c>
     </row>
     <row r="404" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A404" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B404" s="21"/>
-      <c r="C404" s="3"/>
-      <c r="D404" s="14"/>
-      <c r="E404" s="31"/>
-      <c r="F404" s="45" t="s">
+      <c r="A404" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="B404" s="27" t="s">
+        <v>522</v>
+      </c>
+      <c r="C404" s="28"/>
+      <c r="D404" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="E404" s="32">
+        <v>24</v>
+      </c>
+      <c r="F404" s="71" t="s">
         <v>752</v>
       </c>
       <c r="G404" s="20">
@@ -16496,20 +16501,14 @@
       </c>
     </row>
     <row r="405" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A405" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="B405" s="27" t="s">
-        <v>523</v>
-      </c>
-      <c r="C405" s="28"/>
-      <c r="D405" s="29" t="s">
-        <v>519</v>
-      </c>
-      <c r="E405" s="32">
-        <v>24</v>
-      </c>
-      <c r="F405" s="71" t="s">
+      <c r="A405" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B405" s="21"/>
+      <c r="C405" s="3"/>
+      <c r="D405" s="14"/>
+      <c r="E405" s="31"/>
+      <c r="F405" s="45" t="s">
         <v>753</v>
       </c>
       <c r="G405" s="20">
@@ -16535,14 +16534,14 @@
     </row>
     <row r="406" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="B406" s="21"/>
       <c r="C406" s="3"/>
       <c r="D406" s="14"/>
       <c r="E406" s="31"/>
       <c r="F406" s="45" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G406" s="20">
         <f t="shared" si="29"/>
@@ -16557,25 +16556,25 @@
       <c r="K406" s="20"/>
       <c r="L406" s="19"/>
       <c r="M406" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="M406:M472" si="31">IF(B406=1,E406,"")</f>
         <v/>
       </c>
       <c r="N406" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="N406:N472" si="32">IF(B406=2,E406,"")</f>
         <v/>
       </c>
     </row>
     <row r="407" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A407" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B407" s="21"/>
-      <c r="C407" s="3"/>
-      <c r="D407" s="14"/>
-      <c r="E407" s="31"/>
-      <c r="F407" s="45" t="s">
-        <v>754</v>
-      </c>
+      <c r="A407" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B407" s="1"/>
+      <c r="C407" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D407" s="13"/>
+      <c r="E407" s="30"/>
+      <c r="F407" s="43"/>
       <c r="G407" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16583,30 +16582,34 @@
       <c r="H407" s="18"/>
       <c r="I407" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J407" s="19"/>
       <c r="K407" s="20"/>
       <c r="L407" s="19"/>
       <c r="M407" t="str">
-        <f t="shared" ref="M407:M473" si="31">IF(B407=1,E407,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N407" t="str">
-        <f t="shared" ref="N407:N473" si="32">IF(B407=2,E407,"")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
-        <v>249</v>
+        <v>406</v>
       </c>
       <c r="B408" s="1"/>
       <c r="C408" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D408" s="13"/>
-      <c r="E408" s="30"/>
+      <c r="D408" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="E408" s="30">
+        <v>12</v>
+      </c>
       <c r="F408" s="43"/>
       <c r="G408" s="20">
         <f t="shared" si="29"/>
@@ -16630,20 +16633,16 @@
       </c>
     </row>
     <row r="409" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A409" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="B409" s="1"/>
-      <c r="C409" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D409" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="E409" s="30">
-        <v>12</v>
-      </c>
-      <c r="F409" s="43"/>
+      <c r="A409" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B409" s="21"/>
+      <c r="C409" s="3"/>
+      <c r="D409" s="14"/>
+      <c r="E409" s="31"/>
+      <c r="F409" s="45" t="s">
+        <v>754</v>
+      </c>
       <c r="G409" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16651,7 +16650,7 @@
       <c r="H409" s="18"/>
       <c r="I409" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J409" s="19"/>
       <c r="K409" s="20"/>
@@ -16666,16 +16665,18 @@
       </c>
     </row>
     <row r="410" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A410" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B410" s="21"/>
-      <c r="C410" s="3"/>
-      <c r="D410" s="14"/>
-      <c r="E410" s="31"/>
-      <c r="F410" s="45" t="s">
-        <v>755</v>
-      </c>
+      <c r="A410" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B410" s="1"/>
+      <c r="C410" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D410" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="E410" s="30"/>
+      <c r="F410" s="43"/>
       <c r="G410" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16683,7 +16684,7 @@
       <c r="H410" s="18"/>
       <c r="I410" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J410" s="19"/>
       <c r="K410" s="20"/>
@@ -16699,15 +16700,13 @@
     </row>
     <row r="411" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A411" s="4" t="s">
-        <v>464</v>
+        <v>143</v>
       </c>
       <c r="B411" s="1"/>
       <c r="C411" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D411" s="13" t="s">
-        <v>465</v>
-      </c>
+      <c r="D411" s="13"/>
       <c r="E411" s="30"/>
       <c r="F411" s="43"/>
       <c r="G411" s="20">
@@ -16733,7 +16732,7 @@
     </row>
     <row r="412" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A412" s="4" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="B412" s="1"/>
       <c r="C412" s="5" t="s">
@@ -16765,14 +16764,18 @@
     </row>
     <row r="413" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B413" s="1"/>
       <c r="C413" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D413" s="13"/>
-      <c r="E413" s="30"/>
+      <c r="D413" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="E413" s="30">
+        <v>17.190000000000001</v>
+      </c>
       <c r="F413" s="43"/>
       <c r="G413" s="20">
         <f t="shared" si="29"/>
@@ -16796,20 +16799,18 @@
       </c>
     </row>
     <row r="414" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A414" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B414" s="1"/>
-      <c r="C414" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D414" s="13" t="s">
-        <v>510</v>
-      </c>
-      <c r="E414" s="30">
-        <v>17.190000000000001</v>
-      </c>
-      <c r="F414" s="43"/>
+      <c r="A414" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B414" s="21"/>
+      <c r="C414" s="3"/>
+      <c r="D414" s="14">
+        <v>558</v>
+      </c>
+      <c r="E414" s="31"/>
+      <c r="F414" s="45" t="s">
+        <v>755</v>
+      </c>
       <c r="G414" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16817,29 +16818,19 @@
       <c r="H414" s="18"/>
       <c r="I414" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J414" s="19"/>
       <c r="K414" s="20"/>
       <c r="L414" s="19"/>
-      <c r="M414" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N414" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
     </row>
     <row r="415" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="B415" s="21"/>
       <c r="C415" s="3"/>
-      <c r="D415" s="14">
-        <v>558</v>
-      </c>
+      <c r="D415" s="14"/>
       <c r="E415" s="31"/>
       <c r="F415" s="45" t="s">
         <v>756</v>
@@ -16856,18 +16847,26 @@
       <c r="J415" s="19"/>
       <c r="K415" s="20"/>
       <c r="L415" s="19"/>
+      <c r="M415" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="N415" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
     </row>
     <row r="416" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A416" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B416" s="21"/>
-      <c r="C416" s="3"/>
-      <c r="D416" s="14"/>
-      <c r="E416" s="31"/>
-      <c r="F416" s="45" t="s">
-        <v>757</v>
-      </c>
+      <c r="A416" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B416" s="1"/>
+      <c r="C416" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D416" s="13"/>
+      <c r="E416" s="30"/>
+      <c r="F416" s="43"/>
       <c r="G416" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -16875,7 +16874,7 @@
       <c r="H416" s="18"/>
       <c r="I416" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J416" s="19"/>
       <c r="K416" s="20"/>
@@ -16891,14 +16890,18 @@
     </row>
     <row r="417" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="B417" s="1"/>
       <c r="C417" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D417" s="13"/>
-      <c r="E417" s="30"/>
+      <c r="D417" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="E417" s="30">
+        <v>23</v>
+      </c>
       <c r="F417" s="43"/>
       <c r="G417" s="20">
         <f t="shared" si="29"/>
@@ -16923,18 +16926,14 @@
     </row>
     <row r="418" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
-        <v>275</v>
+        <v>497</v>
       </c>
       <c r="B418" s="1"/>
       <c r="C418" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D418" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="E418" s="30">
-        <v>23</v>
-      </c>
+      <c r="D418" s="13"/>
+      <c r="E418" s="30"/>
       <c r="F418" s="43"/>
       <c r="G418" s="20">
         <f t="shared" si="29"/>
@@ -16959,13 +16958,15 @@
     </row>
     <row r="419" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
-        <v>498</v>
+        <v>229</v>
       </c>
       <c r="B419" s="1"/>
       <c r="C419" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D419" s="13"/>
+      <c r="D419" s="13">
+        <v>8</v>
+      </c>
       <c r="E419" s="30"/>
       <c r="F419" s="43"/>
       <c r="G419" s="20">
@@ -16991,14 +16992,14 @@
     </row>
     <row r="420" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
-        <v>229</v>
+        <v>146</v>
       </c>
       <c r="B420" s="1"/>
       <c r="C420" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D420" s="13">
-        <v>8</v>
+      <c r="D420" s="13" t="s">
+        <v>422</v>
       </c>
       <c r="E420" s="30"/>
       <c r="F420" s="43"/>
@@ -17024,18 +17025,16 @@
       </c>
     </row>
     <row r="421" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A421" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B421" s="1"/>
-      <c r="C421" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D421" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="E421" s="30"/>
-      <c r="F421" s="43"/>
+      <c r="A421" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B421" s="21"/>
+      <c r="C421" s="3"/>
+      <c r="D421" s="14"/>
+      <c r="E421" s="31"/>
+      <c r="F421" s="45" t="s">
+        <v>757</v>
+      </c>
       <c r="G421" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17043,7 +17042,7 @@
       <c r="H421" s="18"/>
       <c r="I421" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J421" s="19"/>
       <c r="K421" s="20"/>
@@ -17059,7 +17058,7 @@
     </row>
     <row r="422" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>383</v>
+        <v>230</v>
       </c>
       <c r="B422" s="21"/>
       <c r="C422" s="3"/>
@@ -17090,16 +17089,20 @@
       </c>
     </row>
     <row r="423" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A423" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B423" s="21"/>
-      <c r="C423" s="3"/>
-      <c r="D423" s="14"/>
-      <c r="E423" s="31"/>
-      <c r="F423" s="45" t="s">
-        <v>759</v>
-      </c>
+      <c r="A423" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B423" s="1"/>
+      <c r="C423" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D423" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E423" s="30">
+        <v>12</v>
+      </c>
+      <c r="F423" s="43"/>
       <c r="G423" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17107,7 +17110,7 @@
       <c r="H423" s="18"/>
       <c r="I423" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J423" s="19"/>
       <c r="K423" s="20"/>
@@ -17123,18 +17126,14 @@
     </row>
     <row r="424" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
-        <v>147</v>
+        <v>399</v>
       </c>
       <c r="B424" s="1"/>
       <c r="C424" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D424" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E424" s="30">
-        <v>12</v>
-      </c>
+      <c r="D424" s="13"/>
+      <c r="E424" s="30"/>
       <c r="F424" s="43"/>
       <c r="G424" s="20">
         <f t="shared" si="29"/>
@@ -17159,7 +17158,7 @@
     </row>
     <row r="425" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
-        <v>399</v>
+        <v>276</v>
       </c>
       <c r="B425" s="1"/>
       <c r="C425" s="5" t="s">
@@ -17191,14 +17190,18 @@
     </row>
     <row r="426" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
-        <v>276</v>
+        <v>507</v>
       </c>
       <c r="B426" s="1"/>
       <c r="C426" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D426" s="13"/>
-      <c r="E426" s="30"/>
+      <c r="D426" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E426" s="30">
+        <v>8.8800000000000008</v>
+      </c>
       <c r="F426" s="43"/>
       <c r="G426" s="20">
         <f t="shared" si="29"/>
@@ -17222,20 +17225,18 @@
       </c>
     </row>
     <row r="427" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A427" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="B427" s="1"/>
-      <c r="C427" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D427" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="E427" s="30">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="F427" s="43"/>
+      <c r="A427" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B427" s="21"/>
+      <c r="C427" s="3"/>
+      <c r="D427" s="14" t="s">
+        <v>760</v>
+      </c>
+      <c r="E427" s="31"/>
+      <c r="F427" s="45" t="s">
+        <v>759</v>
+      </c>
       <c r="G427" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17243,33 +17244,23 @@
       <c r="H427" s="18"/>
       <c r="I427" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J427" s="19"/>
       <c r="K427" s="20"/>
       <c r="L427" s="19"/>
-      <c r="M427" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N427" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
     </row>
     <row r="428" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A428" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B428" s="21"/>
-      <c r="C428" s="3"/>
-      <c r="D428" s="14" t="s">
-        <v>761</v>
-      </c>
-      <c r="E428" s="31"/>
-      <c r="F428" s="45" t="s">
-        <v>760</v>
-      </c>
+      <c r="A428" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B428" s="1"/>
+      <c r="C428" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D428" s="13"/>
+      <c r="E428" s="30"/>
+      <c r="F428" s="43"/>
       <c r="G428" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17277,23 +17268,33 @@
       <c r="H428" s="18"/>
       <c r="I428" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J428" s="19"/>
       <c r="K428" s="20"/>
       <c r="L428" s="19"/>
+      <c r="M428" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="N428" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
     </row>
     <row r="429" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A429" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B429" s="1"/>
-      <c r="C429" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D429" s="13"/>
-      <c r="E429" s="30"/>
-      <c r="F429" s="43"/>
+      <c r="A429" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B429" s="21"/>
+      <c r="C429" s="3"/>
+      <c r="D429" s="14" t="s">
+        <v>762</v>
+      </c>
+      <c r="E429" s="31"/>
+      <c r="F429" s="45" t="s">
+        <v>807</v>
+      </c>
       <c r="G429" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17301,7 +17302,7 @@
       <c r="H429" s="18"/>
       <c r="I429" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J429" s="19"/>
       <c r="K429" s="20"/>
@@ -17317,16 +17318,14 @@
     </row>
     <row r="430" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B430" s="21"/>
       <c r="C430" s="3"/>
-      <c r="D430" s="14" t="s">
-        <v>763</v>
-      </c>
+      <c r="D430" s="14"/>
       <c r="E430" s="31"/>
       <c r="F430" s="45" t="s">
-        <v>808</v>
+        <v>761</v>
       </c>
       <c r="G430" s="20">
         <f t="shared" si="29"/>
@@ -17350,16 +17349,16 @@
       </c>
     </row>
     <row r="431" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A431" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B431" s="21"/>
-      <c r="C431" s="3"/>
-      <c r="D431" s="14"/>
-      <c r="E431" s="31"/>
-      <c r="F431" s="45" t="s">
-        <v>762</v>
-      </c>
+      <c r="A431" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B431" s="1"/>
+      <c r="C431" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D431" s="13"/>
+      <c r="E431" s="30"/>
+      <c r="F431" s="43"/>
       <c r="G431" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17367,7 +17366,7 @@
       <c r="H431" s="18"/>
       <c r="I431" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J431" s="19"/>
       <c r="K431" s="20"/>
@@ -17383,7 +17382,7 @@
     </row>
     <row r="432" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
-        <v>294</v>
+        <v>236</v>
       </c>
       <c r="B432" s="1"/>
       <c r="C432" s="5" t="s">
@@ -17415,7 +17414,7 @@
     </row>
     <row r="433" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
-        <v>236</v>
+        <v>372</v>
       </c>
       <c r="B433" s="1"/>
       <c r="C433" s="5" t="s">
@@ -17446,16 +17445,16 @@
       </c>
     </row>
     <row r="434" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A434" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B434" s="1"/>
-      <c r="C434" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D434" s="13"/>
-      <c r="E434" s="30"/>
-      <c r="F434" s="43"/>
+      <c r="A434" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B434" s="21"/>
+      <c r="C434" s="3"/>
+      <c r="D434" s="14"/>
+      <c r="E434" s="31"/>
+      <c r="F434" s="45" t="s">
+        <v>763</v>
+      </c>
       <c r="G434" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17463,7 +17462,7 @@
       <c r="H434" s="18"/>
       <c r="I434" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J434" s="19"/>
       <c r="K434" s="20"/>
@@ -17478,16 +17477,18 @@
       </c>
     </row>
     <row r="435" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A435" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B435" s="21"/>
-      <c r="C435" s="3"/>
-      <c r="D435" s="14"/>
-      <c r="E435" s="31"/>
-      <c r="F435" s="45" t="s">
-        <v>764</v>
-      </c>
+      <c r="A435" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B435" s="1"/>
+      <c r="C435" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D435" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="E435" s="30"/>
+      <c r="F435" s="43"/>
       <c r="G435" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17495,7 +17496,7 @@
       <c r="H435" s="18"/>
       <c r="I435" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J435" s="19"/>
       <c r="K435" s="20"/>
@@ -17511,15 +17512,13 @@
     </row>
     <row r="436" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A436" s="4" t="s">
-        <v>353</v>
+        <v>251</v>
       </c>
       <c r="B436" s="1"/>
       <c r="C436" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D436" s="13" t="s">
-        <v>422</v>
-      </c>
+      <c r="D436" s="13"/>
       <c r="E436" s="30"/>
       <c r="F436" s="43"/>
       <c r="G436" s="20">
@@ -17544,16 +17543,16 @@
       </c>
     </row>
     <row r="437" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A437" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="B437" s="1"/>
-      <c r="C437" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D437" s="13"/>
-      <c r="E437" s="30"/>
-      <c r="F437" s="43"/>
+      <c r="A437" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B437" s="21"/>
+      <c r="C437" s="3"/>
+      <c r="D437" s="14"/>
+      <c r="E437" s="31"/>
+      <c r="F437" s="45" t="s">
+        <v>764</v>
+      </c>
       <c r="G437" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17561,7 +17560,7 @@
       <c r="H437" s="18"/>
       <c r="I437" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J437" s="19"/>
       <c r="K437" s="20"/>
@@ -17576,16 +17575,18 @@
       </c>
     </row>
     <row r="438" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A438" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="B438" s="21"/>
-      <c r="C438" s="3"/>
-      <c r="D438" s="14"/>
-      <c r="E438" s="31"/>
-      <c r="F438" s="45" t="s">
-        <v>765</v>
-      </c>
+      <c r="A438" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B438" s="1"/>
+      <c r="C438" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D438" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="E438" s="30"/>
+      <c r="F438" s="43"/>
       <c r="G438" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17593,30 +17594,22 @@
       <c r="H438" s="18"/>
       <c r="I438" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J438" s="19"/>
       <c r="K438" s="20"/>
       <c r="L438" s="19"/>
-      <c r="M438" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N438" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
     </row>
     <row r="439" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B439" s="1"/>
       <c r="C439" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D439" s="13" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="E439" s="30"/>
       <c r="F439" s="43"/>
@@ -17632,20 +17625,28 @@
       <c r="J439" s="19"/>
       <c r="K439" s="20"/>
       <c r="L439" s="19"/>
+      <c r="M439" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="N439" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
     </row>
     <row r="440" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A440" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B440" s="1"/>
-      <c r="C440" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D440" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="E440" s="30"/>
-      <c r="F440" s="43"/>
+      <c r="A440" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B440" s="21"/>
+      <c r="C440" s="3"/>
+      <c r="D440" s="14" t="s">
+        <v>760</v>
+      </c>
+      <c r="E440" s="31"/>
+      <c r="F440" s="45" t="s">
+        <v>766</v>
+      </c>
       <c r="G440" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17653,7 +17654,7 @@
       <c r="H440" s="18"/>
       <c r="I440" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J440" s="19"/>
       <c r="K440" s="20"/>
@@ -17668,18 +17669,16 @@
       </c>
     </row>
     <row r="441" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A441" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B441" s="21"/>
-      <c r="C441" s="3"/>
-      <c r="D441" s="14" t="s">
-        <v>761</v>
-      </c>
-      <c r="E441" s="31"/>
-      <c r="F441" s="45" t="s">
-        <v>767</v>
-      </c>
+      <c r="A441" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B441" s="1"/>
+      <c r="C441" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D441" s="13"/>
+      <c r="E441" s="30"/>
+      <c r="F441" s="43"/>
       <c r="G441" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17687,7 +17686,7 @@
       <c r="H441" s="18"/>
       <c r="I441" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J441" s="19"/>
       <c r="K441" s="20"/>
@@ -17703,7 +17702,7 @@
     </row>
     <row r="442" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
-        <v>252</v>
+        <v>404</v>
       </c>
       <c r="B442" s="1"/>
       <c r="C442" s="5" t="s">
@@ -17735,13 +17734,15 @@
     </row>
     <row r="443" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
-        <v>404</v>
+        <v>151</v>
       </c>
       <c r="B443" s="1"/>
       <c r="C443" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D443" s="13"/>
+      <c r="D443" s="13" t="s">
+        <v>422</v>
+      </c>
       <c r="E443" s="30"/>
       <c r="F443" s="43"/>
       <c r="G443" s="20">
@@ -17767,17 +17768,19 @@
     </row>
     <row r="444" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B444" s="1"/>
       <c r="C444" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D444" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="E444" s="30"/>
-      <c r="F444" s="43"/>
+        <v>493</v>
+      </c>
+      <c r="E444" s="30">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="F444" s="46"/>
       <c r="G444" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17801,19 +17804,19 @@
     </row>
     <row r="445" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B445" s="1"/>
       <c r="C445" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D445" s="13" t="s">
-        <v>494</v>
+        <v>430</v>
       </c>
       <c r="E445" s="30">
-        <v>16.579999999999998</v>
-      </c>
-      <c r="F445" s="46"/>
+        <v>11</v>
+      </c>
+      <c r="F445" s="43"/>
       <c r="G445" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17837,18 +17840,16 @@
     </row>
     <row r="446" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B446" s="1"/>
       <c r="C446" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D446" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E446" s="30">
-        <v>11</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="E446" s="30"/>
       <c r="F446" s="43"/>
       <c r="G446" s="20">
         <f t="shared" si="29"/>
@@ -17872,18 +17873,18 @@
       </c>
     </row>
     <row r="447" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A447" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B447" s="1"/>
-      <c r="C447" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D447" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="E447" s="30"/>
-      <c r="F447" s="43"/>
+      <c r="A447" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B447" s="21"/>
+      <c r="C447" s="3"/>
+      <c r="D447" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E447" s="31"/>
+      <c r="F447" s="45" t="s">
+        <v>767</v>
+      </c>
       <c r="G447" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17891,7 +17892,7 @@
       <c r="H447" s="18"/>
       <c r="I447" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J447" s="19"/>
       <c r="K447" s="20"/>
@@ -17906,18 +17907,16 @@
       </c>
     </row>
     <row r="448" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A448" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B448" s="21"/>
-      <c r="C448" s="3"/>
-      <c r="D448" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="E448" s="31"/>
-      <c r="F448" s="45" t="s">
-        <v>768</v>
-      </c>
+      <c r="A448" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B448" s="1"/>
+      <c r="C448" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D448" s="13"/>
+      <c r="E448" s="30"/>
+      <c r="F448" s="43"/>
       <c r="G448" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17925,7 +17924,7 @@
       <c r="H448" s="18"/>
       <c r="I448" s="19">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J448" s="19"/>
       <c r="K448" s="20"/>
@@ -17941,15 +17940,21 @@
     </row>
     <row r="449" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
-        <v>155</v>
+        <v>495</v>
       </c>
       <c r="B449" s="1"/>
       <c r="C449" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D449" s="13"/>
-      <c r="E449" s="30"/>
-      <c r="F449" s="43"/>
+      <c r="D449" s="13" t="s">
+        <v>801</v>
+      </c>
+      <c r="E449" s="30">
+        <v>9</v>
+      </c>
+      <c r="F449" s="46" t="s">
+        <v>794</v>
+      </c>
       <c r="G449" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -17973,21 +17978,17 @@
     </row>
     <row r="450" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
-        <v>496</v>
+        <v>405</v>
       </c>
       <c r="B450" s="1"/>
       <c r="C450" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D450" s="13" t="s">
-        <v>802</v>
-      </c>
+      <c r="D450" s="13"/>
       <c r="E450" s="30">
-        <v>9</v>
-      </c>
-      <c r="F450" s="46" t="s">
-        <v>795</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F450" s="43"/>
       <c r="G450" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -18011,16 +18012,14 @@
     </row>
     <row r="451" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
-        <v>405</v>
+        <v>264</v>
       </c>
       <c r="B451" s="1"/>
       <c r="C451" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D451" s="13"/>
-      <c r="E451" s="30">
-        <v>10</v>
-      </c>
+      <c r="E451" s="30"/>
       <c r="F451" s="43"/>
       <c r="G451" s="20">
         <f t="shared" si="29"/>
@@ -18045,14 +18044,18 @@
     </row>
     <row r="452" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
-        <v>264</v>
+        <v>156</v>
       </c>
       <c r="B452" s="1"/>
       <c r="C452" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D452" s="13"/>
-      <c r="E452" s="30"/>
+      <c r="D452" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E452" s="30">
+        <v>8.83</v>
+      </c>
       <c r="F452" s="43"/>
       <c r="G452" s="20">
         <f t="shared" si="29"/>
@@ -18077,19 +18080,21 @@
     </row>
     <row r="453" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
-        <v>156</v>
+        <v>388</v>
       </c>
       <c r="B453" s="1"/>
       <c r="C453" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D453" s="13" t="s">
-        <v>494</v>
+        <v>523</v>
       </c>
       <c r="E453" s="30">
-        <v>8.83</v>
-      </c>
-      <c r="F453" s="43"/>
+        <v>20</v>
+      </c>
+      <c r="F453" s="43">
+        <v>15</v>
+      </c>
       <c r="G453" s="20">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -18112,21 +18117,15 @@
       </c>
     </row>
     <row r="454" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A454" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="B454" s="1"/>
-      <c r="C454" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D454" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="E454" s="30">
-        <v>20</v>
-      </c>
-      <c r="F454" s="43">
-        <v>15</v>
+      <c r="A454" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B454" s="21"/>
+      <c r="C454" s="3"/>
+      <c r="D454" s="14"/>
+      <c r="E454" s="31"/>
+      <c r="F454" s="45" t="s">
+        <v>768</v>
       </c>
       <c r="G454" s="20">
         <f t="shared" si="29"/>
@@ -18135,7 +18134,7 @@
       <c r="H454" s="18"/>
       <c r="I454" s="19">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J454" s="19"/>
       <c r="K454" s="20"/>
@@ -18150,24 +18149,28 @@
       </c>
     </row>
     <row r="455" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A455" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B455" s="21"/>
-      <c r="C455" s="3"/>
-      <c r="D455" s="14"/>
-      <c r="E455" s="31"/>
-      <c r="F455" s="45" t="s">
-        <v>769</v>
-      </c>
+      <c r="A455" s="63" t="s">
+        <v>469</v>
+      </c>
+      <c r="B455" s="64"/>
+      <c r="C455" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D455" s="66" t="s">
+        <v>456</v>
+      </c>
+      <c r="E455" s="67">
+        <v>8</v>
+      </c>
+      <c r="F455" s="68"/>
       <c r="G455" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G455:G511" si="33">COUNTA(A455)</f>
         <v>1</v>
       </c>
       <c r="H455" s="18"/>
       <c r="I455" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" ref="I455:I511" si="34">COUNTA(C455)</f>
+        <v>1</v>
       </c>
       <c r="J455" s="19"/>
       <c r="K455" s="20"/>
@@ -18182,27 +18185,23 @@
       </c>
     </row>
     <row r="456" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A456" s="63" t="s">
-        <v>469</v>
-      </c>
-      <c r="B456" s="64"/>
-      <c r="C456" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="D456" s="66" t="s">
-        <v>456</v>
-      </c>
-      <c r="E456" s="67">
-        <v>8</v>
-      </c>
-      <c r="F456" s="68"/>
+      <c r="A456" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B456" s="1"/>
+      <c r="C456" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D456" s="13"/>
+      <c r="E456" s="30"/>
+      <c r="F456" s="43"/>
       <c r="G456" s="20">
-        <f t="shared" ref="G456:G512" si="33">COUNTA(A456)</f>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H456" s="18"/>
       <c r="I456" s="19">
-        <f t="shared" ref="I456:I512" si="34">COUNTA(C456)</f>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J456" s="19"/>
@@ -18218,16 +18217,20 @@
       </c>
     </row>
     <row r="457" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A457" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="B457" s="1"/>
-      <c r="C457" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D457" s="13"/>
-      <c r="E457" s="30"/>
-      <c r="F457" s="43"/>
+      <c r="A457" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="B457" s="64"/>
+      <c r="C457" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D457" s="66" t="s">
+        <v>430</v>
+      </c>
+      <c r="E457" s="67">
+        <v>14</v>
+      </c>
+      <c r="F457" s="68"/>
       <c r="G457" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18250,20 +18253,16 @@
       </c>
     </row>
     <row r="458" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A458" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="B458" s="64"/>
-      <c r="C458" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="D458" s="66" t="s">
-        <v>430</v>
-      </c>
-      <c r="E458" s="67">
-        <v>14</v>
-      </c>
-      <c r="F458" s="68"/>
+      <c r="A458" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="B458" s="39"/>
+      <c r="C458" s="40"/>
+      <c r="D458" s="41"/>
+      <c r="E458" s="42"/>
+      <c r="F458" s="72" t="s">
+        <v>724</v>
+      </c>
       <c r="G458" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18271,7 +18270,7 @@
       <c r="H458" s="18"/>
       <c r="I458" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J458" s="19"/>
       <c r="K458" s="20"/>
@@ -18286,16 +18285,16 @@
       </c>
     </row>
     <row r="459" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A459" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="B459" s="39"/>
-      <c r="C459" s="40"/>
-      <c r="D459" s="41"/>
-      <c r="E459" s="42"/>
-      <c r="F459" s="72" t="s">
-        <v>725</v>
-      </c>
+      <c r="A459" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B459" s="1"/>
+      <c r="C459" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D459" s="13"/>
+      <c r="E459" s="30"/>
+      <c r="F459" s="43"/>
       <c r="G459" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18303,7 +18302,7 @@
       <c r="H459" s="18"/>
       <c r="I459" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J459" s="19"/>
       <c r="K459" s="20"/>
@@ -18319,7 +18318,7 @@
     </row>
     <row r="460" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
-        <v>377</v>
+        <v>159</v>
       </c>
       <c r="B460" s="1"/>
       <c r="C460" s="5" t="s">
@@ -18350,16 +18349,16 @@
       </c>
     </row>
     <row r="461" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A461" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B461" s="1"/>
-      <c r="C461" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D461" s="13"/>
-      <c r="E461" s="30"/>
-      <c r="F461" s="43"/>
+      <c r="A461" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B461" s="21"/>
+      <c r="C461" s="3"/>
+      <c r="D461" s="14"/>
+      <c r="E461" s="31"/>
+      <c r="F461" s="45" t="s">
+        <v>771</v>
+      </c>
       <c r="G461" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18367,7 +18366,7 @@
       <c r="H461" s="18"/>
       <c r="I461" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J461" s="19"/>
       <c r="K461" s="20"/>
@@ -18383,7 +18382,7 @@
     </row>
     <row r="462" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>506</v>
+        <v>160</v>
       </c>
       <c r="B462" s="21"/>
       <c r="C462" s="3"/>
@@ -18415,14 +18414,16 @@
     </row>
     <row r="463" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="B463" s="21"/>
       <c r="C463" s="3"/>
-      <c r="D463" s="14"/>
+      <c r="D463" s="14" t="s">
+        <v>773</v>
+      </c>
       <c r="E463" s="31"/>
       <c r="F463" s="45" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G463" s="20">
         <f t="shared" si="33"/>
@@ -18446,18 +18447,16 @@
       </c>
     </row>
     <row r="464" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A464" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B464" s="21"/>
-      <c r="C464" s="3"/>
-      <c r="D464" s="14" t="s">
-        <v>774</v>
-      </c>
-      <c r="E464" s="31"/>
-      <c r="F464" s="45" t="s">
-        <v>775</v>
-      </c>
+      <c r="A464" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B464" s="1"/>
+      <c r="C464" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D464" s="13"/>
+      <c r="E464" s="30"/>
+      <c r="F464" s="43"/>
       <c r="G464" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18465,23 +18464,15 @@
       <c r="H464" s="18"/>
       <c r="I464" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J464" s="19"/>
       <c r="K464" s="20"/>
       <c r="L464" s="19"/>
-      <c r="M464" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N464" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
     </row>
     <row r="465" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
-        <v>420</v>
+        <v>186</v>
       </c>
       <c r="B465" s="1"/>
       <c r="C465" s="5" t="s">
@@ -18502,18 +18493,26 @@
       <c r="J465" s="19"/>
       <c r="K465" s="20"/>
       <c r="L465" s="19"/>
+      <c r="M465" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="N465" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
     </row>
     <row r="466" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A466" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B466" s="1"/>
-      <c r="C466" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D466" s="13"/>
-      <c r="E466" s="30"/>
-      <c r="F466" s="43"/>
+      <c r="A466" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B466" s="21"/>
+      <c r="C466" s="3"/>
+      <c r="D466" s="14"/>
+      <c r="E466" s="31"/>
+      <c r="F466" s="45" t="s">
+        <v>775</v>
+      </c>
       <c r="G466" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18521,7 +18520,7 @@
       <c r="H466" s="18"/>
       <c r="I466" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J466" s="19"/>
       <c r="K466" s="20"/>
@@ -18536,16 +18535,18 @@
       </c>
     </row>
     <row r="467" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A467" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B467" s="21"/>
-      <c r="C467" s="3"/>
-      <c r="D467" s="14"/>
-      <c r="E467" s="31"/>
-      <c r="F467" s="45" t="s">
-        <v>776</v>
-      </c>
+      <c r="A467" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B467" s="1"/>
+      <c r="C467" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D467" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E467" s="30"/>
+      <c r="F467" s="43"/>
       <c r="G467" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18553,7 +18554,7 @@
       <c r="H467" s="18"/>
       <c r="I467" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J467" s="19"/>
       <c r="K467" s="20"/>
@@ -18569,15 +18570,13 @@
     </row>
     <row r="468" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
-        <v>472</v>
+        <v>161</v>
       </c>
       <c r="B468" s="1"/>
       <c r="C468" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D468" s="13" t="s">
-        <v>430</v>
-      </c>
+      <c r="D468" s="13"/>
       <c r="E468" s="30"/>
       <c r="F468" s="43"/>
       <c r="G468" s="20">
@@ -18602,16 +18601,18 @@
       </c>
     </row>
     <row r="469" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A469" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B469" s="1"/>
-      <c r="C469" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D469" s="13"/>
-      <c r="E469" s="30"/>
-      <c r="F469" s="43"/>
+      <c r="A469" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B469" s="21"/>
+      <c r="C469" s="3"/>
+      <c r="D469" s="14" t="s">
+        <v>777</v>
+      </c>
+      <c r="E469" s="31"/>
+      <c r="F469" s="45" t="s">
+        <v>776</v>
+      </c>
       <c r="G469" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18619,7 +18620,7 @@
       <c r="H469" s="18"/>
       <c r="I469" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J469" s="19"/>
       <c r="K469" s="20"/>
@@ -18634,18 +18635,20 @@
       </c>
     </row>
     <row r="470" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A470" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B470" s="21"/>
-      <c r="C470" s="3"/>
-      <c r="D470" s="14" t="s">
-        <v>778</v>
-      </c>
-      <c r="E470" s="31"/>
-      <c r="F470" s="45" t="s">
-        <v>777</v>
-      </c>
+      <c r="A470" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B470" s="1"/>
+      <c r="C470" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D470" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="E470" s="30">
+        <v>28</v>
+      </c>
+      <c r="F470" s="43"/>
       <c r="G470" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18653,7 +18656,7 @@
       <c r="H470" s="18"/>
       <c r="I470" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J470" s="19"/>
       <c r="K470" s="20"/>
@@ -18668,20 +18671,16 @@
       </c>
     </row>
     <row r="471" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A471" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B471" s="1"/>
-      <c r="C471" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D471" s="13" t="s">
-        <v>512</v>
-      </c>
-      <c r="E471" s="30">
-        <v>28</v>
-      </c>
-      <c r="F471" s="43"/>
+      <c r="A471" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B471" s="21"/>
+      <c r="C471" s="3"/>
+      <c r="D471" s="14"/>
+      <c r="E471" s="31"/>
+      <c r="F471" s="45" t="s">
+        <v>778</v>
+      </c>
       <c r="G471" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18689,7 +18688,7 @@
       <c r="H471" s="18"/>
       <c r="I471" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J471" s="19"/>
       <c r="K471" s="20"/>
@@ -18704,16 +18703,18 @@
       </c>
     </row>
     <row r="472" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A472" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="B472" s="21"/>
-      <c r="C472" s="3"/>
-      <c r="D472" s="14"/>
-      <c r="E472" s="31"/>
-      <c r="F472" s="45" t="s">
-        <v>779</v>
-      </c>
+      <c r="A472" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B472" s="1"/>
+      <c r="C472" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D472" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E472" s="30"/>
+      <c r="F472" s="43"/>
       <c r="G472" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18721,7 +18722,7 @@
       <c r="H472" s="18"/>
       <c r="I472" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J472" s="19"/>
       <c r="K472" s="20"/>
@@ -18736,18 +18737,16 @@
       </c>
     </row>
     <row r="473" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A473" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="B473" s="1"/>
-      <c r="C473" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D473" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E473" s="30"/>
-      <c r="F473" s="43"/>
+      <c r="A473" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B473" s="21"/>
+      <c r="C473" s="3"/>
+      <c r="D473" s="14"/>
+      <c r="E473" s="31"/>
+      <c r="F473" s="45" t="s">
+        <v>779</v>
+      </c>
       <c r="G473" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18755,30 +18754,30 @@
       <c r="H473" s="18"/>
       <c r="I473" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J473" s="19"/>
       <c r="K473" s="20"/>
       <c r="L473" s="19"/>
       <c r="M473" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="M473:M511" si="35">IF(B473=1,E473,"")</f>
         <v/>
       </c>
       <c r="N473" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="N473:N511" si="36">IF(B473=2,E473,"")</f>
         <v/>
       </c>
     </row>
     <row r="474" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>319</v>
+        <v>780</v>
       </c>
       <c r="B474" s="21"/>
       <c r="C474" s="3"/>
       <c r="D474" s="14"/>
       <c r="E474" s="31"/>
       <c r="F474" s="45" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="G474" s="20">
         <f t="shared" si="33"/>
@@ -18793,25 +18792,25 @@
       <c r="K474" s="20"/>
       <c r="L474" s="19"/>
       <c r="M474" t="str">
-        <f t="shared" ref="M474:M512" si="35">IF(B474=1,E474,"")</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N474" t="str">
-        <f t="shared" ref="N474:N512" si="36">IF(B474=2,E474,"")</f>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A475" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="B475" s="21"/>
-      <c r="C475" s="3"/>
-      <c r="D475" s="14"/>
-      <c r="E475" s="31"/>
-      <c r="F475" s="45" t="s">
-        <v>782</v>
-      </c>
+      <c r="A475" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B475" s="1"/>
+      <c r="C475" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D475" s="13"/>
+      <c r="E475" s="30"/>
+      <c r="F475" s="43"/>
       <c r="G475" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18819,7 +18818,7 @@
       <c r="H475" s="18"/>
       <c r="I475" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J475" s="19"/>
       <c r="K475" s="20"/>
@@ -18835,7 +18834,7 @@
     </row>
     <row r="476" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A476" s="4" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="B476" s="1"/>
       <c r="C476" s="5" t="s">
@@ -18867,14 +18866,18 @@
     </row>
     <row r="477" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
-        <v>214</v>
+        <v>506</v>
       </c>
       <c r="B477" s="1"/>
       <c r="C477" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D477" s="13"/>
-      <c r="E477" s="30"/>
+      <c r="D477" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E477" s="30">
+        <v>13.43</v>
+      </c>
       <c r="F477" s="43"/>
       <c r="G477" s="20">
         <f t="shared" si="33"/>
@@ -18899,18 +18902,14 @@
     </row>
     <row r="478" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
-        <v>507</v>
+        <v>253</v>
       </c>
       <c r="B478" s="1"/>
       <c r="C478" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D478" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="E478" s="30">
-        <v>13.43</v>
-      </c>
+      <c r="D478" s="13"/>
+      <c r="E478" s="30"/>
       <c r="F478" s="43"/>
       <c r="G478" s="20">
         <f t="shared" si="33"/>
@@ -18934,16 +18933,16 @@
       </c>
     </row>
     <row r="479" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A479" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B479" s="1"/>
-      <c r="C479" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D479" s="13"/>
-      <c r="E479" s="30"/>
-      <c r="F479" s="43"/>
+      <c r="A479" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B479" s="21"/>
+      <c r="C479" s="3"/>
+      <c r="D479" s="14"/>
+      <c r="E479" s="31"/>
+      <c r="F479" s="45" t="s">
+        <v>782</v>
+      </c>
       <c r="G479" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18951,7 +18950,7 @@
       <c r="H479" s="18"/>
       <c r="I479" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J479" s="19"/>
       <c r="K479" s="20"/>
@@ -18966,16 +18965,20 @@
       </c>
     </row>
     <row r="480" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A480" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B480" s="21"/>
-      <c r="C480" s="3"/>
-      <c r="D480" s="14"/>
-      <c r="E480" s="31"/>
-      <c r="F480" s="45" t="s">
-        <v>783</v>
-      </c>
+      <c r="A480" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B480" s="1"/>
+      <c r="C480" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D480" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E480" s="30">
+        <v>29</v>
+      </c>
+      <c r="F480" s="43"/>
       <c r="G480" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18983,34 +18986,24 @@
       <c r="H480" s="18"/>
       <c r="I480" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J480" s="19"/>
       <c r="K480" s="20"/>
       <c r="L480" s="19"/>
-      <c r="M480" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N480" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
     </row>
     <row r="481" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
-        <v>479</v>
+        <v>254</v>
       </c>
       <c r="B481" s="1"/>
       <c r="C481" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D481" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E481" s="30">
-        <v>29</v>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="E481" s="30"/>
       <c r="F481" s="43"/>
       <c r="G481" s="20">
         <f t="shared" si="33"/>
@@ -19024,20 +19017,32 @@
       <c r="J481" s="19"/>
       <c r="K481" s="20"/>
       <c r="L481" s="19"/>
+      <c r="M481" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="N481" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
     </row>
     <row r="482" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
-        <v>254</v>
+        <v>528</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D482" s="13" t="s">
-        <v>784</v>
-      </c>
-      <c r="E482" s="30"/>
-      <c r="F482" s="43"/>
+        <v>523</v>
+      </c>
+      <c r="E482" s="30">
+        <v>15</v>
+      </c>
+      <c r="F482" s="43">
+        <v>40</v>
+      </c>
       <c r="G482" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19060,21 +19065,17 @@
       </c>
     </row>
     <row r="483" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A483" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="B483" s="1"/>
-      <c r="C483" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D483" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="E483" s="30">
-        <v>15</v>
-      </c>
-      <c r="F483" s="43">
-        <v>40</v>
+      <c r="A483" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B483" s="21"/>
+      <c r="C483" s="3"/>
+      <c r="D483" s="14" t="s">
+        <v>785</v>
+      </c>
+      <c r="E483" s="31"/>
+      <c r="F483" s="45" t="s">
+        <v>784</v>
       </c>
       <c r="G483" s="20">
         <f t="shared" si="33"/>
@@ -19083,7 +19084,7 @@
       <c r="H483" s="18"/>
       <c r="I483" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J483" s="19"/>
       <c r="K483" s="20"/>
@@ -19099,16 +19100,14 @@
     </row>
     <row r="484" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>326</v>
+        <v>162</v>
       </c>
       <c r="B484" s="21"/>
       <c r="C484" s="3"/>
-      <c r="D484" s="14" t="s">
-        <v>786</v>
-      </c>
+      <c r="D484" s="14"/>
       <c r="E484" s="31"/>
       <c r="F484" s="45" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G484" s="20">
         <f t="shared" si="33"/>
@@ -19132,16 +19131,16 @@
       </c>
     </row>
     <row r="485" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A485" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B485" s="21"/>
-      <c r="C485" s="3"/>
-      <c r="D485" s="14"/>
-      <c r="E485" s="31"/>
-      <c r="F485" s="45" t="s">
-        <v>787</v>
-      </c>
+      <c r="A485" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B485" s="1"/>
+      <c r="C485" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D485" s="13"/>
+      <c r="E485" s="30"/>
+      <c r="F485" s="43"/>
       <c r="G485" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19149,23 +19148,15 @@
       <c r="H485" s="18"/>
       <c r="I485" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J485" s="19"/>
       <c r="K485" s="20"/>
       <c r="L485" s="19"/>
-      <c r="M485" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N485" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
     </row>
     <row r="486" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="B486" s="1"/>
       <c r="C486" s="5" t="s">
@@ -19186,10 +19177,18 @@
       <c r="J486" s="19"/>
       <c r="K486" s="20"/>
       <c r="L486" s="19"/>
+      <c r="M486" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="N486" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
     </row>
     <row r="487" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="B487" s="1"/>
       <c r="C487" s="5" t="s">
@@ -19197,7 +19196,7 @@
       </c>
       <c r="D487" s="13"/>
       <c r="E487" s="30"/>
-      <c r="F487" s="43"/>
+      <c r="F487" s="46"/>
       <c r="G487" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19221,15 +19220,17 @@
     </row>
     <row r="488" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B488" s="1"/>
       <c r="C488" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D488" s="13"/>
+      <c r="D488" s="13" t="s">
+        <v>422</v>
+      </c>
       <c r="E488" s="30"/>
-      <c r="F488" s="46"/>
+      <c r="F488" s="43"/>
       <c r="G488" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19253,7 +19254,7 @@
     </row>
     <row r="489" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B489" s="1"/>
       <c r="C489" s="5" t="s">
@@ -19286,18 +19287,16 @@
       </c>
     </row>
     <row r="490" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A490" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B490" s="1"/>
-      <c r="C490" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D490" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="E490" s="30"/>
-      <c r="F490" s="43"/>
+      <c r="A490" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B490" s="21"/>
+      <c r="C490" s="3"/>
+      <c r="D490" s="14"/>
+      <c r="E490" s="31"/>
+      <c r="F490" s="45" t="s">
+        <v>787</v>
+      </c>
       <c r="G490" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19305,7 +19304,7 @@
       <c r="H490" s="18"/>
       <c r="I490" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J490" s="19"/>
       <c r="K490" s="20"/>
@@ -19320,16 +19319,16 @@
       </c>
     </row>
     <row r="491" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A491" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="B491" s="21"/>
-      <c r="C491" s="3"/>
-      <c r="D491" s="14"/>
-      <c r="E491" s="31"/>
-      <c r="F491" s="45" t="s">
-        <v>788</v>
-      </c>
+      <c r="A491" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B491" s="1"/>
+      <c r="C491" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D491" s="13"/>
+      <c r="E491" s="30"/>
+      <c r="F491" s="43"/>
       <c r="G491" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19337,7 +19336,7 @@
       <c r="H491" s="18"/>
       <c r="I491" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J491" s="19"/>
       <c r="K491" s="20"/>
@@ -19353,7 +19352,7 @@
     </row>
     <row r="492" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="B492" s="1"/>
       <c r="C492" s="5" t="s">
@@ -19385,7 +19384,7 @@
     </row>
     <row r="493" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
-        <v>371</v>
+        <v>7</v>
       </c>
       <c r="B493" s="1"/>
       <c r="C493" s="5" t="s">
@@ -19417,7 +19416,7 @@
     </row>
     <row r="494" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A494" s="4" t="s">
-        <v>7</v>
+        <v>255</v>
       </c>
       <c r="B494" s="1"/>
       <c r="C494" s="5" t="s">
@@ -19449,13 +19448,15 @@
     </row>
     <row r="495" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A495" s="4" t="s">
-        <v>255</v>
+        <v>167</v>
       </c>
       <c r="B495" s="1"/>
       <c r="C495" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D495" s="13"/>
+      <c r="D495" s="13" t="s">
+        <v>401</v>
+      </c>
       <c r="E495" s="30"/>
       <c r="F495" s="43"/>
       <c r="G495" s="20">
@@ -19481,16 +19482,18 @@
     </row>
     <row r="496" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A496" s="4" t="s">
-        <v>167</v>
+        <v>331</v>
       </c>
       <c r="B496" s="1"/>
       <c r="C496" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D496" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="E496" s="30"/>
+        <v>430</v>
+      </c>
+      <c r="E496" s="30">
+        <v>10</v>
+      </c>
       <c r="F496" s="43"/>
       <c r="G496" s="20">
         <f t="shared" si="33"/>
@@ -19515,18 +19518,14 @@
     </row>
     <row r="497" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="B497" s="1"/>
       <c r="C497" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D497" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E497" s="30">
-        <v>10</v>
-      </c>
+      <c r="D497" s="13"/>
+      <c r="E497" s="30"/>
       <c r="F497" s="43"/>
       <c r="G497" s="20">
         <f t="shared" si="33"/>
@@ -19550,16 +19549,16 @@
       </c>
     </row>
     <row r="498" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A498" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B498" s="1"/>
-      <c r="C498" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D498" s="13"/>
-      <c r="E498" s="30"/>
-      <c r="F498" s="43"/>
+      <c r="A498" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B498" s="21"/>
+      <c r="C498" s="3"/>
+      <c r="D498" s="14"/>
+      <c r="E498" s="31"/>
+      <c r="F498" s="45" t="s">
+        <v>788</v>
+      </c>
       <c r="G498" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19567,7 +19566,7 @@
       <c r="H498" s="18"/>
       <c r="I498" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J498" s="19"/>
       <c r="K498" s="20"/>
@@ -19582,16 +19581,20 @@
       </c>
     </row>
     <row r="499" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A499" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B499" s="21"/>
-      <c r="C499" s="3"/>
-      <c r="D499" s="14"/>
-      <c r="E499" s="31"/>
-      <c r="F499" s="45" t="s">
-        <v>789</v>
-      </c>
+      <c r="A499" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B499" s="1"/>
+      <c r="C499" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D499" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="E499" s="30">
+        <v>19</v>
+      </c>
+      <c r="F499" s="43"/>
       <c r="G499" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19599,7 +19602,7 @@
       <c r="H499" s="18"/>
       <c r="I499" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J499" s="19"/>
       <c r="K499" s="20"/>
@@ -19615,18 +19618,14 @@
     </row>
     <row r="500" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A500" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B500" s="1"/>
       <c r="C500" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D500" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="E500" s="30">
-        <v>19</v>
-      </c>
+      <c r="D500" s="13"/>
+      <c r="E500" s="30"/>
       <c r="F500" s="43"/>
       <c r="G500" s="20">
         <f t="shared" si="33"/>
@@ -19650,16 +19649,16 @@
       </c>
     </row>
     <row r="501" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A501" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B501" s="1"/>
-      <c r="C501" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D501" s="13"/>
-      <c r="E501" s="30"/>
-      <c r="F501" s="43"/>
+      <c r="A501" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B501" s="21"/>
+      <c r="C501" s="3"/>
+      <c r="D501" s="14"/>
+      <c r="E501" s="31"/>
+      <c r="F501" s="45" t="s">
+        <v>789</v>
+      </c>
       <c r="G501" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19667,7 +19666,7 @@
       <c r="H501" s="18"/>
       <c r="I501" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J501" s="19"/>
       <c r="K501" s="20"/>
@@ -19682,16 +19681,16 @@
       </c>
     </row>
     <row r="502" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A502" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B502" s="21"/>
-      <c r="C502" s="3"/>
-      <c r="D502" s="14"/>
-      <c r="E502" s="31"/>
-      <c r="F502" s="45" t="s">
-        <v>790</v>
-      </c>
+      <c r="A502" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B502" s="1"/>
+      <c r="C502" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D502" s="13"/>
+      <c r="E502" s="30"/>
+      <c r="F502" s="43"/>
       <c r="G502" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19699,7 +19698,7 @@
       <c r="H502" s="18"/>
       <c r="I502" s="19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J502" s="19"/>
       <c r="K502" s="20"/>
@@ -19715,7 +19714,7 @@
     </row>
     <row r="503" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A503" s="4" t="s">
-        <v>256</v>
+        <v>171</v>
       </c>
       <c r="B503" s="1"/>
       <c r="C503" s="5" t="s">
@@ -19747,13 +19746,15 @@
     </row>
     <row r="504" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A504" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B504" s="1"/>
       <c r="C504" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D504" s="13"/>
+      <c r="D504" s="13" t="s">
+        <v>422</v>
+      </c>
       <c r="E504" s="30"/>
       <c r="F504" s="43"/>
       <c r="G504" s="20">
@@ -19778,18 +19779,16 @@
       </c>
     </row>
     <row r="505" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A505" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B505" s="1"/>
-      <c r="C505" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D505" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="E505" s="30"/>
-      <c r="F505" s="43"/>
+      <c r="A505" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B505" s="21"/>
+      <c r="C505" s="3"/>
+      <c r="D505" s="14"/>
+      <c r="E505" s="31"/>
+      <c r="F505" s="45" t="s">
+        <v>790</v>
+      </c>
       <c r="G505" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -19797,7 +19796,7 @@
       <c r="H505" s="18"/>
       <c r="I505" s="19">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J505" s="19"/>
       <c r="K505" s="20"/>
@@ -19813,7 +19812,7 @@
     </row>
     <row r="506" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>483</v>
+        <v>274</v>
       </c>
       <c r="B506" s="21"/>
       <c r="C506" s="3"/>
@@ -19845,11 +19844,13 @@
     </row>
     <row r="507" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>274</v>
+        <v>173</v>
       </c>
       <c r="B507" s="21"/>
       <c r="C507" s="3"/>
-      <c r="D507" s="14"/>
+      <c r="D507" s="14" t="s">
+        <v>793</v>
+      </c>
       <c r="E507" s="31"/>
       <c r="F507" s="45" t="s">
         <v>792</v>
@@ -19876,21 +19877,15 @@
       </c>
     </row>
     <row r="508" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A508" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B508" s="21"/>
-      <c r="C508" s="3"/>
-      <c r="D508" s="14" t="s">
-        <v>794</v>
-      </c>
-      <c r="E508" s="31"/>
-      <c r="F508" s="45" t="s">
-        <v>793</v>
-      </c>
+      <c r="A508" s="34"/>
+      <c r="B508" s="25"/>
+      <c r="C508" s="35"/>
+      <c r="D508" s="36"/>
+      <c r="E508" s="37"/>
+      <c r="F508" s="44"/>
       <c r="G508" s="20">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H508" s="18"/>
       <c r="I508" s="19">
@@ -19994,49 +19989,30 @@
       </c>
     </row>
     <row r="512" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A512" s="34"/>
-      <c r="B512" s="25"/>
-      <c r="C512" s="35"/>
-      <c r="D512" s="36"/>
-      <c r="E512" s="37"/>
-      <c r="F512" s="44"/>
-      <c r="G512" s="20">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="H512" s="18"/>
-      <c r="I512" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="J512" s="19"/>
-      <c r="K512" s="20"/>
-      <c r="L512" s="19"/>
-      <c r="M512" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N512" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-    </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A512" s="48"/>
+      <c r="B512" s="50"/>
+      <c r="C512" s="48"/>
+      <c r="D512" s="52"/>
+      <c r="E512" s="54"/>
+      <c r="F512" s="57"/>
+      <c r="G512" s="78"/>
+      <c r="H512" s="24"/>
+      <c r="I512" s="75"/>
+      <c r="J512" s="24"/>
+      <c r="K512" s="24"/>
+      <c r="L512" s="24"/>
+      <c r="M512" s="23"/>
+    </row>
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" s="48"/>
-      <c r="B513" s="50"/>
+      <c r="B513" s="49"/>
       <c r="C513" s="48"/>
       <c r="D513" s="52"/>
-      <c r="E513" s="54"/>
-      <c r="F513" s="57"/>
-      <c r="G513" s="78"/>
-      <c r="H513" s="24"/>
-      <c r="I513" s="75"/>
-      <c r="J513" s="24"/>
-      <c r="K513" s="24"/>
-      <c r="L513" s="24"/>
-      <c r="M513" s="23"/>
-    </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E513" s="53"/>
+      <c r="F513" s="56"/>
+      <c r="I513" s="19"/>
+    </row>
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" s="48"/>
       <c r="B514" s="49"/>
       <c r="C514" s="48"/>
@@ -20045,7 +20021,7 @@
       <c r="F514" s="56"/>
       <c r="I514" s="19"/>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" s="48"/>
       <c r="B515" s="49"/>
       <c r="C515" s="48"/>
@@ -20054,7 +20030,7 @@
       <c r="F515" s="56"/>
       <c r="I515" s="19"/>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" s="48"/>
       <c r="B516" s="49"/>
       <c r="C516" s="48"/>
@@ -20063,7 +20039,7 @@
       <c r="F516" s="56"/>
       <c r="I516" s="19"/>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" s="48"/>
       <c r="B517" s="49"/>
       <c r="C517" s="48"/>
@@ -20072,7 +20048,7 @@
       <c r="F517" s="56"/>
       <c r="I517" s="19"/>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" s="48"/>
       <c r="B518" s="49"/>
       <c r="C518" s="48"/>
@@ -20081,7 +20057,7 @@
       <c r="F518" s="56"/>
       <c r="I518" s="19"/>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" s="48"/>
       <c r="B519" s="49"/>
       <c r="C519" s="48"/>
@@ -20090,7 +20066,7 @@
       <c r="F519" s="56"/>
       <c r="I519" s="19"/>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" s="48"/>
       <c r="B520" s="49"/>
       <c r="C520" s="48"/>
@@ -20099,7 +20075,7 @@
       <c r="F520" s="56"/>
       <c r="I520" s="19"/>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" s="48"/>
       <c r="B521" s="49"/>
       <c r="C521" s="48"/>
@@ -20108,7 +20084,7 @@
       <c r="F521" s="56"/>
       <c r="I521" s="19"/>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" s="48"/>
       <c r="B522" s="49"/>
       <c r="C522" s="48"/>
@@ -20117,7 +20093,7 @@
       <c r="F522" s="56"/>
       <c r="I522" s="19"/>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" s="48"/>
       <c r="B523" s="49"/>
       <c r="C523" s="48"/>
@@ -20126,7 +20102,7 @@
       <c r="F523" s="56"/>
       <c r="I523" s="19"/>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" s="48"/>
       <c r="B524" s="49"/>
       <c r="C524" s="48"/>
@@ -20135,7 +20111,7 @@
       <c r="F524" s="56"/>
       <c r="I524" s="19"/>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" s="48"/>
       <c r="B525" s="49"/>
       <c r="C525" s="48"/>
@@ -20144,7 +20120,7 @@
       <c r="F525" s="56"/>
       <c r="I525" s="19"/>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" s="48"/>
       <c r="B526" s="49"/>
       <c r="C526" s="48"/>
@@ -20153,7 +20129,7 @@
       <c r="F526" s="56"/>
       <c r="I526" s="19"/>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" s="48"/>
       <c r="B527" s="49"/>
       <c r="C527" s="48"/>
@@ -20162,7 +20138,7 @@
       <c r="F527" s="56"/>
       <c r="I527" s="19"/>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" s="48"/>
       <c r="B528" s="49"/>
       <c r="C528" s="48"/>
@@ -21987,7 +21963,6 @@
       <c r="D730" s="52"/>
       <c r="E730" s="53"/>
       <c r="F730" s="56"/>
-      <c r="I730" s="19"/>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" s="48"/>
@@ -22007,29 +21982,21 @@
     </row>
     <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" s="48"/>
-      <c r="B733" s="49"/>
+      <c r="B733" s="51">
+        <v>12</v>
+      </c>
       <c r="C733" s="48"/>
       <c r="D733" s="52"/>
-      <c r="E733" s="53"/>
+      <c r="E733" s="55">
+        <f>N512</f>
+        <v>0</v>
+      </c>
       <c r="F733" s="56"/>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A734" s="48"/>
-      <c r="B734" s="51">
-        <v>12</v>
-      </c>
-      <c r="C734" s="48"/>
-      <c r="D734" s="52"/>
-      <c r="E734" s="55">
-        <f>N513</f>
-        <v>0</v>
-      </c>
-      <c r="F734" s="56"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F734" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F734">
-      <sortCondition ref="A1:A734"/>
+  <autoFilter ref="A1:F733" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F733">
+      <sortCondition ref="A1:A733"/>
     </sortState>
   </autoFilter>
   <mergeCells count="6">
@@ -22169,101 +22136,127 @@
     <hyperlink ref="F296" r:id="rId126" xr:uid="{F8E811E4-C56E-4020-8515-CA14E5BC6E3C}"/>
     <hyperlink ref="F299" r:id="rId127" xr:uid="{8169F733-8E2D-4AC1-9A4F-A49A54D41A52}"/>
     <hyperlink ref="F302" r:id="rId128" xr:uid="{0CE762D6-744B-40A7-8F98-8AF1053C4C20}"/>
-    <hyperlink ref="F303" r:id="rId129" xr:uid="{7A40BCF1-3293-4CA7-9013-B050AE19741A}"/>
-    <hyperlink ref="F306" r:id="rId130" xr:uid="{091067F1-8D60-40C3-B79B-EDA05B5A7DA4}"/>
-    <hyperlink ref="F307" r:id="rId131" xr:uid="{AC3C0A2F-C850-4DC8-B816-62B521573541}"/>
-    <hyperlink ref="F308" r:id="rId132" xr:uid="{BD4C4423-9801-48B9-BE4A-6FA8B9B411A4}"/>
-    <hyperlink ref="F309" r:id="rId133" xr:uid="{03558391-13D5-417E-8518-5A118844CD95}"/>
-    <hyperlink ref="F312" r:id="rId134" xr:uid="{2005E731-59D7-4620-B28C-434266F6022D}"/>
-    <hyperlink ref="F313" r:id="rId135" xr:uid="{2FD5242C-CF0A-4A63-816A-EA2A83984E64}"/>
-    <hyperlink ref="F314" r:id="rId136" xr:uid="{3123CD08-C684-4CC9-AB12-F9105EA97288}"/>
-    <hyperlink ref="F315" r:id="rId137" xr:uid="{2213C59C-4A61-40A9-A06B-1FEF17A027B0}"/>
-    <hyperlink ref="F316" r:id="rId138" xr:uid="{68B28FC2-AA1F-41B6-9A23-516E9B83B6E0}"/>
-    <hyperlink ref="F318" r:id="rId139" xr:uid="{B5599032-4454-4E2C-A68F-8CFFE50F4FDA}"/>
-    <hyperlink ref="F319" r:id="rId140" xr:uid="{A0B5737A-A70A-4218-B2E1-A76C8720DB56}"/>
-    <hyperlink ref="F320" r:id="rId141" xr:uid="{D4B5840E-77B4-47E2-8436-CD2E572AF2B8}"/>
-    <hyperlink ref="F321" r:id="rId142" xr:uid="{BD67BD55-40E9-45BF-A3F6-8F5115DDB229}"/>
-    <hyperlink ref="F322" r:id="rId143" xr:uid="{006FB328-F8E9-4758-AE01-3843E2E75398}"/>
-    <hyperlink ref="F324" r:id="rId144" xr:uid="{D8274070-5E6A-448F-BE2B-E62287C27B7F}"/>
-    <hyperlink ref="F325" r:id="rId145" xr:uid="{3107A474-1B13-410C-98D5-4BDFF1B318A0}"/>
-    <hyperlink ref="F329" r:id="rId146" xr:uid="{AEE59407-C7BF-4741-8788-B6DE8B5B56F0}"/>
-    <hyperlink ref="F331" r:id="rId147" xr:uid="{9E43F2AF-CA8D-45AD-8AF2-43E79516D8C4}"/>
-    <hyperlink ref="F334" r:id="rId148" xr:uid="{527DB674-2191-4390-A5E3-AF104DB8B4DD}"/>
-    <hyperlink ref="F339" r:id="rId149" xr:uid="{6CBC3A1F-EFB9-4C79-8568-CA7B9F4AE2C5}"/>
-    <hyperlink ref="F349" r:id="rId150" xr:uid="{15A14E1E-9440-4524-8E71-E2F0B928B953}"/>
-    <hyperlink ref="F351" r:id="rId151" xr:uid="{C92EA61B-8F06-42A1-A7F9-7F45453FF60F}"/>
-    <hyperlink ref="F355" r:id="rId152" xr:uid="{8A245E57-176A-4426-987A-230A824E21F5}"/>
-    <hyperlink ref="F362" r:id="rId153" xr:uid="{E66A3719-554E-4E28-86A4-324883D73CAE}"/>
-    <hyperlink ref="F366" r:id="rId154" xr:uid="{7BDE2C38-EC1A-4C17-B1C6-1E4D17FC0EE5}"/>
-    <hyperlink ref="F367" r:id="rId155" xr:uid="{00F24AF7-BECF-42F0-AB31-2C0DED0C37A2}"/>
-    <hyperlink ref="F368" r:id="rId156" xr:uid="{5852A063-4D20-4FBB-B346-BF786AFC86EC}"/>
-    <hyperlink ref="F369" r:id="rId157" xr:uid="{B67214DC-0A47-4AD1-BF86-5DC069815DE1}"/>
-    <hyperlink ref="F374" r:id="rId158" xr:uid="{8299AD99-FFD7-4B97-A788-030B31407DDD}"/>
-    <hyperlink ref="F376" r:id="rId159" xr:uid="{78971510-8CDC-4BF5-AE19-0D07D647D047}"/>
-    <hyperlink ref="F378" r:id="rId160" xr:uid="{A0C94A52-B22E-4392-9DAE-3EA37FFA5A46}"/>
-    <hyperlink ref="F379" r:id="rId161" xr:uid="{3B87B23F-40F6-462E-9110-A5A9A19D2232}"/>
-    <hyperlink ref="F380" r:id="rId162" xr:uid="{292120C3-4914-44B9-9098-59807C6E7C6C}"/>
-    <hyperlink ref="F381" r:id="rId163" xr:uid="{5B5091B4-FEAA-4CAD-8FAF-43B120B259B8}"/>
-    <hyperlink ref="F382" r:id="rId164" xr:uid="{B4A8D738-F438-4B79-8C25-2D43D085BC71}"/>
-    <hyperlink ref="F383" r:id="rId165" xr:uid="{9C2371F9-4C06-48FC-AD5B-9E5916618520}"/>
-    <hyperlink ref="F389" r:id="rId166" xr:uid="{2C42E22B-0DD1-40FA-8493-10406BA7A1D9}"/>
-    <hyperlink ref="F390" r:id="rId167" xr:uid="{70286227-A588-43E1-91FC-1EB348F42574}"/>
-    <hyperlink ref="F392" r:id="rId168" xr:uid="{D1A39FB3-D165-4B56-88B9-CFB02C80378B}"/>
-    <hyperlink ref="F396" r:id="rId169" xr:uid="{86B3426F-8CFE-45AB-9DE6-873C49E7DB80}"/>
-    <hyperlink ref="F397" r:id="rId170" xr:uid="{6F07A94A-75BF-4D0C-A155-1F147D55686D}"/>
-    <hyperlink ref="F398" r:id="rId171" xr:uid="{925770DF-4D55-4F2C-B57F-546C6CF49F83}"/>
-    <hyperlink ref="F402" r:id="rId172" xr:uid="{86833F34-D3B8-49A2-B048-9143D1D268E1}"/>
-    <hyperlink ref="F403" r:id="rId173" xr:uid="{DC475E94-CED6-4041-A19D-421EDEC91083}"/>
-    <hyperlink ref="F404" r:id="rId174" xr:uid="{8CE58332-34FE-45F0-B53E-D28E50ECC3F5}"/>
-    <hyperlink ref="F405" r:id="rId175" xr:uid="{DD0386C7-D589-4779-A82D-1F72C4B6FBDD}"/>
-    <hyperlink ref="F406" r:id="rId176" xr:uid="{BC460B10-00B8-4916-B3EF-7D1ED959A78B}"/>
-    <hyperlink ref="F407" r:id="rId177" xr:uid="{40729791-C768-4D88-821E-9253252FB0F3}"/>
-    <hyperlink ref="F410" r:id="rId178" xr:uid="{BCA7C023-C424-401D-88B3-107FB2ACBF81}"/>
-    <hyperlink ref="F415" r:id="rId179" xr:uid="{43A41B2A-DEFE-495E-997D-ED085CF2FC91}"/>
-    <hyperlink ref="F416" r:id="rId180" xr:uid="{B12F044C-CB46-4CCB-89F1-EB0C8F7EB892}"/>
-    <hyperlink ref="F422" r:id="rId181" xr:uid="{28D016CB-3B77-415C-8166-D13FE68341D1}"/>
-    <hyperlink ref="F423" r:id="rId182" xr:uid="{CD429C9A-749F-491E-9E58-B9CB7A90A2FB}"/>
-    <hyperlink ref="F428" r:id="rId183" xr:uid="{5CC5C5A2-EE60-4284-8128-2E87C488D632}"/>
-    <hyperlink ref="F431" r:id="rId184" xr:uid="{C2BD70BB-F593-4AF0-B6A4-B32D5304C625}"/>
-    <hyperlink ref="F435" r:id="rId185" xr:uid="{F6E6F0EA-9817-4AA3-BC4A-B1ED8E6931ED}"/>
-    <hyperlink ref="F438" r:id="rId186" xr:uid="{5EB5671F-FF63-475A-9238-21AD45B4C5EE}"/>
-    <hyperlink ref="F441" r:id="rId187" xr:uid="{B97349D3-8379-49CF-AB1C-503D2A28FCDC}"/>
-    <hyperlink ref="F448" r:id="rId188" xr:uid="{DCBAF156-741D-4CDD-A1BB-BEE3DCAFC7E4}"/>
-    <hyperlink ref="F455" r:id="rId189" xr:uid="{8B8F94DD-ABB2-4320-920C-216E8ECE661F}"/>
-    <hyperlink ref="F340" r:id="rId190" xr:uid="{A1876CDA-D2D9-4ACE-9E52-75F2A87E4D4F}"/>
-    <hyperlink ref="F459" r:id="rId191" xr:uid="{21AFB719-500D-49EA-9A94-E1F0F8DEAF1D}"/>
-    <hyperlink ref="F462" r:id="rId192" xr:uid="{9FB30793-74F5-4EE1-997B-A29276854B0F}"/>
-    <hyperlink ref="F463" r:id="rId193" xr:uid="{F7D721C1-6EE7-431C-825B-C14B050040BE}"/>
-    <hyperlink ref="F464" r:id="rId194" xr:uid="{E82C3262-E183-4FD0-A624-6B9CBBA13E22}"/>
-    <hyperlink ref="F467" r:id="rId195" xr:uid="{2F3A224E-996D-44F2-BB99-EC5746F0E81D}"/>
-    <hyperlink ref="F470" r:id="rId196" xr:uid="{66281EB3-1C84-4327-8A41-AC8CB05AAABD}"/>
-    <hyperlink ref="F472" r:id="rId197" xr:uid="{E3C74E77-C496-4510-8806-2D2606716F78}"/>
-    <hyperlink ref="F474" r:id="rId198" xr:uid="{9BE712DE-053D-4691-8A07-B0D3C3304A32}"/>
-    <hyperlink ref="F475" r:id="rId199" xr:uid="{97572BBD-E6D2-4CFC-B983-6629083AAA30}"/>
-    <hyperlink ref="F480" r:id="rId200" xr:uid="{F9FBA57F-7D2B-4679-A566-A492ECEF9035}"/>
-    <hyperlink ref="F484" r:id="rId201" xr:uid="{5942006B-880C-4C23-9ED8-EE6DF160CAFC}"/>
-    <hyperlink ref="F485" r:id="rId202" xr:uid="{93B54EDE-1866-4706-A5FE-E39688316329}"/>
-    <hyperlink ref="F491" r:id="rId203" xr:uid="{D1F916D6-B062-4FD4-9C02-9546DAF97B5D}"/>
-    <hyperlink ref="F499" r:id="rId204" xr:uid="{82BB8238-8B3C-44CF-B8DB-8B220659D0F1}"/>
-    <hyperlink ref="F502" r:id="rId205" xr:uid="{BC41CEBA-AAE5-49A0-8216-3B4403811C0B}"/>
-    <hyperlink ref="F506" r:id="rId206" xr:uid="{3ED9D9C9-88BD-4D38-8C17-2147C43DCA41}"/>
-    <hyperlink ref="F507" r:id="rId207" xr:uid="{8EE4BBCE-100C-422D-A8AE-E1855B7531DD}"/>
-    <hyperlink ref="F508" r:id="rId208" xr:uid="{7393F241-1EE0-4975-B705-3BB32A866045}"/>
-    <hyperlink ref="F450" r:id="rId209" xr:uid="{80AE22F1-0F21-450E-BE5A-444AA127014C}"/>
-    <hyperlink ref="F45" r:id="rId210" xr:uid="{9166A086-6452-4A3C-AEE1-EA61B6F0040C}"/>
-    <hyperlink ref="F63" r:id="rId211" xr:uid="{C3D2727A-54A4-4ABC-BE29-C663282CB00F}"/>
-    <hyperlink ref="F65" r:id="rId212" xr:uid="{290EDB11-A937-4642-B4C4-762CABC87A86}"/>
-    <hyperlink ref="F92" r:id="rId213" xr:uid="{7BD3346D-C133-4F85-BA8B-06E893A5AA15}"/>
-    <hyperlink ref="F236" r:id="rId214" xr:uid="{A89FDFBB-71B2-4738-9E20-379D288195B3}"/>
-    <hyperlink ref="F237" r:id="rId215" xr:uid="{71BBAFA0-9838-4AE0-B1A3-8148C5047B22}"/>
-    <hyperlink ref="F430" r:id="rId216" xr:uid="{CE9B73F7-6206-43BE-A0D7-238A375EF8C2}"/>
+    <hyperlink ref="F305" r:id="rId129" xr:uid="{091067F1-8D60-40C3-B79B-EDA05B5A7DA4}"/>
+    <hyperlink ref="F306" r:id="rId130" xr:uid="{AC3C0A2F-C850-4DC8-B816-62B521573541}"/>
+    <hyperlink ref="F307" r:id="rId131" xr:uid="{BD4C4423-9801-48B9-BE4A-6FA8B9B411A4}"/>
+    <hyperlink ref="F308" r:id="rId132" xr:uid="{03558391-13D5-417E-8518-5A118844CD95}"/>
+    <hyperlink ref="F311" r:id="rId133" xr:uid="{2005E731-59D7-4620-B28C-434266F6022D}"/>
+    <hyperlink ref="F312" r:id="rId134" xr:uid="{2FD5242C-CF0A-4A63-816A-EA2A83984E64}"/>
+    <hyperlink ref="F313" r:id="rId135" xr:uid="{3123CD08-C684-4CC9-AB12-F9105EA97288}"/>
+    <hyperlink ref="F314" r:id="rId136" xr:uid="{2213C59C-4A61-40A9-A06B-1FEF17A027B0}"/>
+    <hyperlink ref="F315" r:id="rId137" xr:uid="{68B28FC2-AA1F-41B6-9A23-516E9B83B6E0}"/>
+    <hyperlink ref="F317" r:id="rId138" xr:uid="{B5599032-4454-4E2C-A68F-8CFFE50F4FDA}"/>
+    <hyperlink ref="F318" r:id="rId139" xr:uid="{A0B5737A-A70A-4218-B2E1-A76C8720DB56}"/>
+    <hyperlink ref="F319" r:id="rId140" xr:uid="{D4B5840E-77B4-47E2-8436-CD2E572AF2B8}"/>
+    <hyperlink ref="F320" r:id="rId141" xr:uid="{BD67BD55-40E9-45BF-A3F6-8F5115DDB229}"/>
+    <hyperlink ref="F321" r:id="rId142" xr:uid="{006FB328-F8E9-4758-AE01-3843E2E75398}"/>
+    <hyperlink ref="F323" r:id="rId143" xr:uid="{D8274070-5E6A-448F-BE2B-E62287C27B7F}"/>
+    <hyperlink ref="F324" r:id="rId144" xr:uid="{3107A474-1B13-410C-98D5-4BDFF1B318A0}"/>
+    <hyperlink ref="F328" r:id="rId145" xr:uid="{AEE59407-C7BF-4741-8788-B6DE8B5B56F0}"/>
+    <hyperlink ref="F330" r:id="rId146" xr:uid="{9E43F2AF-CA8D-45AD-8AF2-43E79516D8C4}"/>
+    <hyperlink ref="F333" r:id="rId147" xr:uid="{527DB674-2191-4390-A5E3-AF104DB8B4DD}"/>
+    <hyperlink ref="F338" r:id="rId148" xr:uid="{6CBC3A1F-EFB9-4C79-8568-CA7B9F4AE2C5}"/>
+    <hyperlink ref="F348" r:id="rId149" xr:uid="{15A14E1E-9440-4524-8E71-E2F0B928B953}"/>
+    <hyperlink ref="F350" r:id="rId150" xr:uid="{C92EA61B-8F06-42A1-A7F9-7F45453FF60F}"/>
+    <hyperlink ref="F354" r:id="rId151" xr:uid="{8A245E57-176A-4426-987A-230A824E21F5}"/>
+    <hyperlink ref="F361" r:id="rId152" xr:uid="{E66A3719-554E-4E28-86A4-324883D73CAE}"/>
+    <hyperlink ref="F365" r:id="rId153" xr:uid="{7BDE2C38-EC1A-4C17-B1C6-1E4D17FC0EE5}"/>
+    <hyperlink ref="F366" r:id="rId154" xr:uid="{00F24AF7-BECF-42F0-AB31-2C0DED0C37A2}"/>
+    <hyperlink ref="F367" r:id="rId155" xr:uid="{5852A063-4D20-4FBB-B346-BF786AFC86EC}"/>
+    <hyperlink ref="F368" r:id="rId156" xr:uid="{B67214DC-0A47-4AD1-BF86-5DC069815DE1}"/>
+    <hyperlink ref="F373" r:id="rId157" xr:uid="{8299AD99-FFD7-4B97-A788-030B31407DDD}"/>
+    <hyperlink ref="F375" r:id="rId158" xr:uid="{78971510-8CDC-4BF5-AE19-0D07D647D047}"/>
+    <hyperlink ref="F377" r:id="rId159" xr:uid="{A0C94A52-B22E-4392-9DAE-3EA37FFA5A46}"/>
+    <hyperlink ref="F378" r:id="rId160" xr:uid="{3B87B23F-40F6-462E-9110-A5A9A19D2232}"/>
+    <hyperlink ref="F379" r:id="rId161" xr:uid="{292120C3-4914-44B9-9098-59807C6E7C6C}"/>
+    <hyperlink ref="F380" r:id="rId162" xr:uid="{5B5091B4-FEAA-4CAD-8FAF-43B120B259B8}"/>
+    <hyperlink ref="F381" r:id="rId163" xr:uid="{B4A8D738-F438-4B79-8C25-2D43D085BC71}"/>
+    <hyperlink ref="F382" r:id="rId164" xr:uid="{9C2371F9-4C06-48FC-AD5B-9E5916618520}"/>
+    <hyperlink ref="F388" r:id="rId165" xr:uid="{2C42E22B-0DD1-40FA-8493-10406BA7A1D9}"/>
+    <hyperlink ref="F389" r:id="rId166" xr:uid="{70286227-A588-43E1-91FC-1EB348F42574}"/>
+    <hyperlink ref="F391" r:id="rId167" xr:uid="{D1A39FB3-D165-4B56-88B9-CFB02C80378B}"/>
+    <hyperlink ref="F395" r:id="rId168" xr:uid="{86B3426F-8CFE-45AB-9DE6-873C49E7DB80}"/>
+    <hyperlink ref="F396" r:id="rId169" xr:uid="{6F07A94A-75BF-4D0C-A155-1F147D55686D}"/>
+    <hyperlink ref="F397" r:id="rId170" xr:uid="{925770DF-4D55-4F2C-B57F-546C6CF49F83}"/>
+    <hyperlink ref="F401" r:id="rId171" xr:uid="{86833F34-D3B8-49A2-B048-9143D1D268E1}"/>
+    <hyperlink ref="F402" r:id="rId172" xr:uid="{DC475E94-CED6-4041-A19D-421EDEC91083}"/>
+    <hyperlink ref="F403" r:id="rId173" xr:uid="{8CE58332-34FE-45F0-B53E-D28E50ECC3F5}"/>
+    <hyperlink ref="F404" r:id="rId174" xr:uid="{DD0386C7-D589-4779-A82D-1F72C4B6FBDD}"/>
+    <hyperlink ref="F405" r:id="rId175" xr:uid="{BC460B10-00B8-4916-B3EF-7D1ED959A78B}"/>
+    <hyperlink ref="F406" r:id="rId176" xr:uid="{40729791-C768-4D88-821E-9253252FB0F3}"/>
+    <hyperlink ref="F409" r:id="rId177" xr:uid="{BCA7C023-C424-401D-88B3-107FB2ACBF81}"/>
+    <hyperlink ref="F414" r:id="rId178" xr:uid="{43A41B2A-DEFE-495E-997D-ED085CF2FC91}"/>
+    <hyperlink ref="F415" r:id="rId179" xr:uid="{B12F044C-CB46-4CCB-89F1-EB0C8F7EB892}"/>
+    <hyperlink ref="F421" r:id="rId180" xr:uid="{28D016CB-3B77-415C-8166-D13FE68341D1}"/>
+    <hyperlink ref="F422" r:id="rId181" xr:uid="{CD429C9A-749F-491E-9E58-B9CB7A90A2FB}"/>
+    <hyperlink ref="F427" r:id="rId182" xr:uid="{5CC5C5A2-EE60-4284-8128-2E87C488D632}"/>
+    <hyperlink ref="F430" r:id="rId183" xr:uid="{C2BD70BB-F593-4AF0-B6A4-B32D5304C625}"/>
+    <hyperlink ref="F434" r:id="rId184" xr:uid="{F6E6F0EA-9817-4AA3-BC4A-B1ED8E6931ED}"/>
+    <hyperlink ref="F437" r:id="rId185" xr:uid="{5EB5671F-FF63-475A-9238-21AD45B4C5EE}"/>
+    <hyperlink ref="F440" r:id="rId186" xr:uid="{B97349D3-8379-49CF-AB1C-503D2A28FCDC}"/>
+    <hyperlink ref="F447" r:id="rId187" xr:uid="{DCBAF156-741D-4CDD-A1BB-BEE3DCAFC7E4}"/>
+    <hyperlink ref="F454" r:id="rId188" xr:uid="{8B8F94DD-ABB2-4320-920C-216E8ECE661F}"/>
+    <hyperlink ref="F339" r:id="rId189" xr:uid="{A1876CDA-D2D9-4ACE-9E52-75F2A87E4D4F}"/>
+    <hyperlink ref="F458" r:id="rId190" xr:uid="{21AFB719-500D-49EA-9A94-E1F0F8DEAF1D}"/>
+    <hyperlink ref="F461" r:id="rId191" xr:uid="{9FB30793-74F5-4EE1-997B-A29276854B0F}"/>
+    <hyperlink ref="F462" r:id="rId192" xr:uid="{F7D721C1-6EE7-431C-825B-C14B050040BE}"/>
+    <hyperlink ref="F463" r:id="rId193" xr:uid="{E82C3262-E183-4FD0-A624-6B9CBBA13E22}"/>
+    <hyperlink ref="F466" r:id="rId194" xr:uid="{2F3A224E-996D-44F2-BB99-EC5746F0E81D}"/>
+    <hyperlink ref="F469" r:id="rId195" xr:uid="{66281EB3-1C84-4327-8A41-AC8CB05AAABD}"/>
+    <hyperlink ref="F471" r:id="rId196" xr:uid="{E3C74E77-C496-4510-8806-2D2606716F78}"/>
+    <hyperlink ref="F473" r:id="rId197" xr:uid="{9BE712DE-053D-4691-8A07-B0D3C3304A32}"/>
+    <hyperlink ref="F474" r:id="rId198" xr:uid="{97572BBD-E6D2-4CFC-B983-6629083AAA30}"/>
+    <hyperlink ref="F479" r:id="rId199" xr:uid="{F9FBA57F-7D2B-4679-A566-A492ECEF9035}"/>
+    <hyperlink ref="F483" r:id="rId200" xr:uid="{5942006B-880C-4C23-9ED8-EE6DF160CAFC}"/>
+    <hyperlink ref="F484" r:id="rId201" xr:uid="{93B54EDE-1866-4706-A5FE-E39688316329}"/>
+    <hyperlink ref="F490" r:id="rId202" xr:uid="{D1F916D6-B062-4FD4-9C02-9546DAF97B5D}"/>
+    <hyperlink ref="F498" r:id="rId203" xr:uid="{82BB8238-8B3C-44CF-B8DB-8B220659D0F1}"/>
+    <hyperlink ref="F501" r:id="rId204" xr:uid="{BC41CEBA-AAE5-49A0-8216-3B4403811C0B}"/>
+    <hyperlink ref="F505" r:id="rId205" xr:uid="{3ED9D9C9-88BD-4D38-8C17-2147C43DCA41}"/>
+    <hyperlink ref="F506" r:id="rId206" xr:uid="{8EE4BBCE-100C-422D-A8AE-E1855B7531DD}"/>
+    <hyperlink ref="F507" r:id="rId207" xr:uid="{7393F241-1EE0-4975-B705-3BB32A866045}"/>
+    <hyperlink ref="F449" r:id="rId208" xr:uid="{80AE22F1-0F21-450E-BE5A-444AA127014C}"/>
+    <hyperlink ref="F45" r:id="rId209" xr:uid="{9166A086-6452-4A3C-AEE1-EA61B6F0040C}"/>
+    <hyperlink ref="F63" r:id="rId210" xr:uid="{C3D2727A-54A4-4ABC-BE29-C663282CB00F}"/>
+    <hyperlink ref="F65" r:id="rId211" xr:uid="{290EDB11-A937-4642-B4C4-762CABC87A86}"/>
+    <hyperlink ref="F92" r:id="rId212" xr:uid="{7BD3346D-C133-4F85-BA8B-06E893A5AA15}"/>
+    <hyperlink ref="F236" r:id="rId213" xr:uid="{A89FDFBB-71B2-4738-9E20-379D288195B3}"/>
+    <hyperlink ref="F237" r:id="rId214" xr:uid="{71BBAFA0-9838-4AE0-B1A3-8148C5047B22}"/>
+    <hyperlink ref="F429" r:id="rId215" xr:uid="{CE9B73F7-6206-43BE-A0D7-238A375EF8C2}"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId217"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId216"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;C&amp;8EC_Not_technical&amp;8
 </oddHeader>
   </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D10EB7F1-BB9A-4297-BCE2-8D99EAA662AA}">
+  <dimension ref="A3:F3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="14" t="s">
+        <v>701</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="45" t="s">
+        <v>702</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{66FA5EAD-8E35-482C-AB1D-66A8C86055A3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A948A5-A683-4D20-B81C-7049D4011A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCE8CDE-E68E-4422-BD00-A7BC3AEC993C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$F$733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$F$734</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateCount="1"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="809">
   <si>
     <t>Artistes / Titres</t>
   </si>
@@ -3246,7 +3246,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N733"/>
+  <dimension ref="A1:N734"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.140625" bestFit="1" customWidth="1"/>
@@ -3306,18 +3306,18 @@
       <c r="F2" s="82"/>
       <c r="G2" s="77"/>
       <c r="H2" s="10">
-        <f>SUM(G3:G561)</f>
-        <v>505</v>
+        <f>SUM(G3:G562)</f>
+        <v>506</v>
       </c>
       <c r="I2" s="74"/>
       <c r="J2" s="11">
-        <f>SUM(I3:I561)</f>
+        <f>SUM(I3:I562)</f>
         <v>301</v>
       </c>
       <c r="K2" s="17"/>
       <c r="L2" s="12">
         <f>H2-J2</f>
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -11952,12 +11952,12 @@
         <v>680</v>
       </c>
       <c r="G266" s="20">
-        <f t="shared" ref="G266:G327" si="21">COUNTA(A266)</f>
+        <f t="shared" ref="G266:G328" si="21">COUNTA(A266)</f>
         <v>1</v>
       </c>
       <c r="H266" s="18"/>
       <c r="I266" s="19">
-        <f t="shared" ref="I266:I327" si="22">COUNTA(C266)</f>
+        <f t="shared" ref="I266:I328" si="22">COUNTA(C266)</f>
         <v>0</v>
       </c>
       <c r="J266" s="19"/>
@@ -12292,11 +12292,11 @@
       <c r="K276" s="20"/>
       <c r="L276" s="19"/>
       <c r="M276" t="str">
-        <f t="shared" ref="M276:M341" si="23">IF(B276=1,E276,"")</f>
+        <f t="shared" ref="M276:M342" si="23">IF(B276=1,E276,"")</f>
         <v/>
       </c>
       <c r="N276" t="str">
-        <f t="shared" ref="N276:N341" si="24">IF(B276=2,E276,"")</f>
+        <f t="shared" ref="N276:N342" si="24">IF(B276=2,E276,"")</f>
         <v/>
       </c>
     </row>
@@ -13157,40 +13157,42 @@
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A303" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B303" s="1"/>
-      <c r="C303" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D303" s="13"/>
-      <c r="E303" s="30"/>
-      <c r="F303" s="43"/>
+      <c r="A303" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B303" s="21"/>
+      <c r="C303" s="3"/>
+      <c r="D303" s="14" t="s">
+        <v>701</v>
+      </c>
+      <c r="E303" s="31"/>
+      <c r="F303" s="45" t="s">
+        <v>702</v>
+      </c>
       <c r="G303" s="20">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G303" si="25">COUNTA(A303)</f>
         <v>1</v>
       </c>
       <c r="H303" s="18"/>
       <c r="I303" s="19">
-        <f t="shared" si="22"/>
-        <v>1</v>
+        <f t="shared" ref="I303" si="26">COUNTA(C303)</f>
+        <v>0</v>
       </c>
       <c r="J303" s="19"/>
       <c r="K303" s="20"/>
       <c r="L303" s="19"/>
       <c r="M303" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="M303" si="27">IF(B303=1,E303,"")</f>
         <v/>
       </c>
       <c r="N303" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="N303" si="28">IF(B303=2,E303,"")</f>
         <v/>
       </c>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B304" s="1"/>
       <c r="C304" s="5" t="s">
@@ -13221,18 +13223,16 @@
       </c>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A305" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B305" s="21"/>
-      <c r="C305" s="3"/>
-      <c r="D305" s="14" t="s">
-        <v>701</v>
-      </c>
-      <c r="E305" s="31"/>
-      <c r="F305" s="45" t="s">
-        <v>703</v>
-      </c>
+      <c r="A305" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B305" s="1"/>
+      <c r="C305" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D305" s="13"/>
+      <c r="E305" s="30"/>
+      <c r="F305" s="43"/>
       <c r="G305" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13240,7 +13240,7 @@
       <c r="H305" s="18"/>
       <c r="I305" s="19">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J305" s="19"/>
       <c r="K305" s="20"/>
@@ -13256,14 +13256,16 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>209</v>
+        <v>325</v>
       </c>
       <c r="B306" s="21"/>
       <c r="C306" s="3"/>
-      <c r="D306" s="14"/>
+      <c r="D306" s="14" t="s">
+        <v>701</v>
+      </c>
       <c r="E306" s="31"/>
       <c r="F306" s="45" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G306" s="20">
         <f t="shared" si="21"/>
@@ -13288,14 +13290,14 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>348</v>
+        <v>209</v>
       </c>
       <c r="B307" s="21"/>
       <c r="C307" s="3"/>
       <c r="D307" s="14"/>
       <c r="E307" s="31"/>
       <c r="F307" s="45" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G307" s="20">
         <f t="shared" si="21"/>
@@ -13320,14 +13322,14 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>808</v>
+        <v>348</v>
       </c>
       <c r="B308" s="21"/>
       <c r="C308" s="3"/>
       <c r="D308" s="14"/>
       <c r="E308" s="31"/>
       <c r="F308" s="45" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G308" s="20">
         <f t="shared" si="21"/>
@@ -13351,16 +13353,16 @@
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A309" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B309" s="1"/>
-      <c r="C309" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D309" s="13"/>
-      <c r="E309" s="30"/>
-      <c r="F309" s="43"/>
+      <c r="A309" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B309" s="21"/>
+      <c r="C309" s="3"/>
+      <c r="D309" s="14"/>
+      <c r="E309" s="31"/>
+      <c r="F309" s="45" t="s">
+        <v>706</v>
+      </c>
       <c r="G309" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13368,7 +13370,7 @@
       <c r="H309" s="18"/>
       <c r="I309" s="19">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J309" s="19"/>
       <c r="K309" s="20"/>
@@ -13384,7 +13386,7 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
-        <v>12</v>
+        <v>336</v>
       </c>
       <c r="B310" s="1"/>
       <c r="C310" s="5" t="s">
@@ -13415,16 +13417,16 @@
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A311" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B311" s="21"/>
-      <c r="C311" s="3"/>
-      <c r="D311" s="14"/>
-      <c r="E311" s="31"/>
-      <c r="F311" s="45" t="s">
-        <v>707</v>
-      </c>
+      <c r="A311" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B311" s="1"/>
+      <c r="C311" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D311" s="13"/>
+      <c r="E311" s="30"/>
+      <c r="F311" s="43"/>
       <c r="G311" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13432,7 +13434,7 @@
       <c r="H311" s="18"/>
       <c r="I311" s="19">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J311" s="19"/>
       <c r="K311" s="20"/>
@@ -13448,14 +13450,14 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="B312" s="21"/>
       <c r="C312" s="3"/>
       <c r="D312" s="14"/>
       <c r="E312" s="31"/>
       <c r="F312" s="45" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G312" s="20">
         <f t="shared" si="21"/>
@@ -13480,14 +13482,14 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>280</v>
+        <v>339</v>
       </c>
       <c r="B313" s="21"/>
       <c r="C313" s="3"/>
       <c r="D313" s="14"/>
       <c r="E313" s="31"/>
       <c r="F313" s="45" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G313" s="20">
         <f t="shared" si="21"/>
@@ -13512,14 +13514,14 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="B314" s="21"/>
       <c r="C314" s="3"/>
       <c r="D314" s="14"/>
       <c r="E314" s="31"/>
       <c r="F314" s="45" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G314" s="20">
         <f t="shared" si="21"/>
@@ -13544,14 +13546,14 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>484</v>
+        <v>350</v>
       </c>
       <c r="B315" s="21"/>
       <c r="C315" s="3"/>
       <c r="D315" s="14"/>
       <c r="E315" s="31"/>
       <c r="F315" s="45" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G315" s="20">
         <f t="shared" si="21"/>
@@ -13575,20 +13577,16 @@
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A316" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B316" s="1"/>
-      <c r="C316" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D316" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E316" s="30">
-        <v>15</v>
-      </c>
-      <c r="F316" s="43"/>
+      <c r="A316" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B316" s="21"/>
+      <c r="C316" s="3"/>
+      <c r="D316" s="14"/>
+      <c r="E316" s="31"/>
+      <c r="F316" s="45" t="s">
+        <v>711</v>
+      </c>
       <c r="G316" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13596,7 +13594,7 @@
       <c r="H316" s="18"/>
       <c r="I316" s="19">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J316" s="19"/>
       <c r="K316" s="20"/>
@@ -13611,16 +13609,20 @@
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A317" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="B317" s="21"/>
-      <c r="C317" s="3"/>
-      <c r="D317" s="14"/>
-      <c r="E317" s="31"/>
-      <c r="F317" s="45" t="s">
-        <v>712</v>
-      </c>
+      <c r="A317" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B317" s="1"/>
+      <c r="C317" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D317" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E317" s="30">
+        <v>15</v>
+      </c>
+      <c r="F317" s="43"/>
       <c r="G317" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13628,7 +13630,7 @@
       <c r="H317" s="18"/>
       <c r="I317" s="19">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J317" s="19"/>
       <c r="K317" s="20"/>
@@ -13644,14 +13646,14 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B318" s="21"/>
       <c r="C318" s="3"/>
       <c r="D318" s="14"/>
       <c r="E318" s="31"/>
       <c r="F318" s="45" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G318" s="20">
         <f t="shared" si="21"/>
@@ -13676,14 +13678,14 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>441</v>
+        <v>284</v>
       </c>
       <c r="B319" s="21"/>
       <c r="C319" s="3"/>
       <c r="D319" s="14"/>
       <c r="E319" s="31"/>
       <c r="F319" s="45" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G319" s="20">
         <f t="shared" si="21"/>
@@ -13708,16 +13710,14 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>221</v>
+        <v>441</v>
       </c>
       <c r="B320" s="21"/>
       <c r="C320" s="3"/>
-      <c r="D320" s="14" t="s">
-        <v>465</v>
-      </c>
+      <c r="D320" s="14"/>
       <c r="E320" s="31"/>
       <c r="F320" s="45" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G320" s="20">
         <f t="shared" si="21"/>
@@ -13742,14 +13742,16 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B321" s="21"/>
       <c r="C321" s="3"/>
-      <c r="D321" s="14"/>
+      <c r="D321" s="14" t="s">
+        <v>465</v>
+      </c>
       <c r="E321" s="31"/>
       <c r="F321" s="45" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G321" s="20">
         <f t="shared" si="21"/>
@@ -13773,20 +13775,16 @@
       </c>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A322" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B322" s="1"/>
-      <c r="C322" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D322" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E322" s="30">
-        <v>15</v>
-      </c>
-      <c r="F322" s="43"/>
+      <c r="A322" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B322" s="21"/>
+      <c r="C322" s="3"/>
+      <c r="D322" s="14"/>
+      <c r="E322" s="31"/>
+      <c r="F322" s="45" t="s">
+        <v>716</v>
+      </c>
       <c r="G322" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13794,7 +13792,7 @@
       <c r="H322" s="18"/>
       <c r="I322" s="19">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J322" s="19"/>
       <c r="K322" s="20"/>
@@ -13809,18 +13807,20 @@
       </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A323" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="B323" s="21"/>
-      <c r="C323" s="3"/>
-      <c r="D323" s="14" t="s">
-        <v>718</v>
-      </c>
-      <c r="E323" s="31"/>
-      <c r="F323" s="45" t="s">
-        <v>717</v>
-      </c>
+      <c r="A323" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B323" s="1"/>
+      <c r="C323" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D323" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E323" s="30">
+        <v>15</v>
+      </c>
+      <c r="F323" s="43"/>
       <c r="G323" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13828,22 +13828,32 @@
       <c r="H323" s="18"/>
       <c r="I323" s="19">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J323" s="19"/>
       <c r="K323" s="20"/>
       <c r="L323" s="19"/>
+      <c r="M323" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N323" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>14</v>
+        <v>499</v>
       </c>
       <c r="B324" s="21"/>
       <c r="C324" s="3"/>
-      <c r="D324" s="14"/>
+      <c r="D324" s="14" t="s">
+        <v>718</v>
+      </c>
       <c r="E324" s="31"/>
       <c r="F324" s="45" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G324" s="20">
         <f t="shared" si="21"/>
@@ -13857,26 +13867,18 @@
       <c r="J324" s="19"/>
       <c r="K324" s="20"/>
       <c r="L324" s="19"/>
-      <c r="M324" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N324" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A325" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B325" s="1"/>
-      <c r="C325" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D325" s="13"/>
-      <c r="E325" s="30"/>
-      <c r="F325" s="43"/>
+      <c r="A325" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B325" s="21"/>
+      <c r="C325" s="3"/>
+      <c r="D325" s="14"/>
+      <c r="E325" s="31"/>
+      <c r="F325" s="45" t="s">
+        <v>719</v>
+      </c>
       <c r="G325" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
@@ -13884,7 +13886,7 @@
       <c r="H325" s="18"/>
       <c r="I325" s="19">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J325" s="19"/>
       <c r="K325" s="20"/>
@@ -13900,7 +13902,7 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B326" s="1"/>
       <c r="C326" s="5" t="s">
@@ -13932,18 +13934,14 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
-        <v>444</v>
+        <v>233</v>
       </c>
       <c r="B327" s="1"/>
       <c r="C327" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D327" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="E327" s="30">
-        <v>12</v>
-      </c>
+      <c r="D327" s="13"/>
+      <c r="E327" s="30"/>
       <c r="F327" s="43"/>
       <c r="G327" s="20">
         <f t="shared" si="21"/>
@@ -13967,24 +13965,28 @@
       </c>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A328" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B328" s="21"/>
-      <c r="C328" s="3"/>
-      <c r="D328" s="14"/>
-      <c r="E328" s="31"/>
-      <c r="F328" s="45" t="s">
-        <v>720</v>
-      </c>
+      <c r="A328" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B328" s="1"/>
+      <c r="C328" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D328" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E328" s="30">
+        <v>12</v>
+      </c>
+      <c r="F328" s="43"/>
       <c r="G328" s="20">
-        <f t="shared" ref="G328:G390" si="25">COUNTA(A328)</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="H328" s="18"/>
       <c r="I328" s="19">
-        <f t="shared" ref="I328:I390" si="26">COUNTA(C328)</f>
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>1</v>
       </c>
       <c r="J328" s="19"/>
       <c r="K328" s="20"/>
@@ -13999,28 +14001,24 @@
       </c>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A329" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B329" s="1"/>
-      <c r="C329" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D329" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="E329" s="30">
-        <v>23</v>
-      </c>
-      <c r="F329" s="43"/>
+      <c r="A329" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B329" s="21"/>
+      <c r="C329" s="3"/>
+      <c r="D329" s="14"/>
+      <c r="E329" s="31"/>
+      <c r="F329" s="45" t="s">
+        <v>720</v>
+      </c>
       <c r="G329" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G329:G391" si="29">COUNTA(A329)</f>
         <v>1</v>
       </c>
       <c r="H329" s="18"/>
       <c r="I329" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" ref="I329:I391" si="30">COUNTA(C329)</f>
+        <v>0</v>
       </c>
       <c r="J329" s="19"/>
       <c r="K329" s="20"/>
@@ -14035,24 +14033,28 @@
       </c>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A330" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B330" s="21"/>
-      <c r="C330" s="3"/>
-      <c r="D330" s="14"/>
-      <c r="E330" s="31"/>
-      <c r="F330" s="45" t="s">
-        <v>721</v>
-      </c>
+      <c r="A330" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B330" s="1"/>
+      <c r="C330" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D330" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="E330" s="30">
+        <v>23</v>
+      </c>
+      <c r="F330" s="43"/>
       <c r="G330" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H330" s="18"/>
       <c r="I330" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J330" s="19"/>
       <c r="K330" s="20"/>
@@ -14067,28 +14069,24 @@
       </c>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A331" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B331" s="1"/>
-      <c r="C331" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D331" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E331" s="30">
-        <v>25</v>
-      </c>
-      <c r="F331" s="43"/>
+      <c r="A331" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B331" s="21"/>
+      <c r="C331" s="3"/>
+      <c r="D331" s="14"/>
+      <c r="E331" s="31"/>
+      <c r="F331" s="45" t="s">
+        <v>721</v>
+      </c>
       <c r="G331" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H331" s="18"/>
       <c r="I331" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J331" s="19"/>
       <c r="K331" s="20"/>
@@ -14104,22 +14102,26 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B332" s="1"/>
       <c r="C332" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D332" s="13"/>
-      <c r="E332" s="30"/>
+      <c r="D332" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E332" s="30">
+        <v>25</v>
+      </c>
       <c r="F332" s="43"/>
       <c r="G332" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H332" s="18"/>
       <c r="I332" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J332" s="19"/>
@@ -14135,24 +14137,24 @@
       </c>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A333" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B333" s="21"/>
-      <c r="C333" s="3"/>
-      <c r="D333" s="14"/>
-      <c r="E333" s="31"/>
-      <c r="F333" s="45" t="s">
-        <v>722</v>
-      </c>
+      <c r="A333" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B333" s="1"/>
+      <c r="C333" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D333" s="13"/>
+      <c r="E333" s="30"/>
+      <c r="F333" s="43"/>
       <c r="G333" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H333" s="18"/>
       <c r="I333" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J333" s="19"/>
       <c r="K333" s="20"/>
@@ -14167,24 +14169,24 @@
       </c>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A334" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B334" s="1"/>
-      <c r="C334" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D334" s="13"/>
-      <c r="E334" s="30"/>
-      <c r="F334" s="43"/>
+      <c r="A334" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B334" s="21"/>
+      <c r="C334" s="3"/>
+      <c r="D334" s="14"/>
+      <c r="E334" s="31"/>
+      <c r="F334" s="45" t="s">
+        <v>722</v>
+      </c>
       <c r="G334" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H334" s="18"/>
       <c r="I334" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J334" s="19"/>
       <c r="K334" s="20"/>
@@ -14200,28 +14202,22 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
-        <v>529</v>
+        <v>121</v>
       </c>
       <c r="B335" s="1"/>
       <c r="C335" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D335" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E335" s="30">
-        <v>15</v>
-      </c>
-      <c r="F335" s="43">
-        <v>6</v>
-      </c>
+      <c r="D335" s="13"/>
+      <c r="E335" s="30"/>
+      <c r="F335" s="43"/>
       <c r="G335" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H335" s="18"/>
       <c r="I335" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J335" s="19"/>
@@ -14238,22 +14234,28 @@
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
-        <v>287</v>
+        <v>529</v>
       </c>
       <c r="B336" s="1"/>
       <c r="C336" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D336" s="13"/>
-      <c r="E336" s="30"/>
-      <c r="F336" s="43"/>
+      <c r="D336" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E336" s="30">
+        <v>15</v>
+      </c>
+      <c r="F336" s="43">
+        <v>6</v>
+      </c>
       <c r="G336" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H336" s="18"/>
       <c r="I336" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J336" s="19"/>
@@ -14270,7 +14272,7 @@
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="B337" s="1"/>
       <c r="C337" s="5" t="s">
@@ -14280,12 +14282,12 @@
       <c r="E337" s="30"/>
       <c r="F337" s="43"/>
       <c r="G337" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H337" s="18"/>
       <c r="I337" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J337" s="19"/>
@@ -14301,24 +14303,24 @@
       </c>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A338" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B338" s="21"/>
-      <c r="C338" s="3"/>
-      <c r="D338" s="14"/>
-      <c r="E338" s="31"/>
-      <c r="F338" s="45" t="s">
-        <v>723</v>
-      </c>
+      <c r="A338" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B338" s="1"/>
+      <c r="C338" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D338" s="13"/>
+      <c r="E338" s="30"/>
+      <c r="F338" s="43"/>
       <c r="G338" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H338" s="18"/>
       <c r="I338" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J338" s="19"/>
       <c r="K338" s="20"/>
@@ -14334,22 +14336,22 @@
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>770</v>
+        <v>355</v>
       </c>
       <c r="B339" s="21"/>
       <c r="C339" s="3"/>
       <c r="D339" s="14"/>
       <c r="E339" s="31"/>
       <c r="F339" s="45" t="s">
-        <v>769</v>
+        <v>723</v>
       </c>
       <c r="G339" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H339" s="18"/>
       <c r="I339" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J339" s="19"/>
@@ -14365,24 +14367,24 @@
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A340" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B340" s="1"/>
-      <c r="C340" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D340" s="13"/>
-      <c r="E340" s="30"/>
-      <c r="F340" s="43"/>
+      <c r="A340" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B340" s="21"/>
+      <c r="C340" s="3"/>
+      <c r="D340" s="14"/>
+      <c r="E340" s="31"/>
+      <c r="F340" s="45" t="s">
+        <v>769</v>
+      </c>
       <c r="G340" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H340" s="18"/>
       <c r="I340" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J340" s="19"/>
       <c r="K340" s="20"/>
@@ -14398,7 +14400,7 @@
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="B341" s="1"/>
       <c r="C341" s="5" t="s">
@@ -14408,12 +14410,12 @@
       <c r="E341" s="30"/>
       <c r="F341" s="43"/>
       <c r="G341" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H341" s="18"/>
       <c r="I341" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J341" s="19"/>
@@ -14430,7 +14432,7 @@
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
-        <v>226</v>
+        <v>17</v>
       </c>
       <c r="B342" s="1"/>
       <c r="C342" s="5" t="s">
@@ -14440,327 +14442,327 @@
       <c r="E342" s="30"/>
       <c r="F342" s="43"/>
       <c r="G342" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H342" s="18"/>
       <c r="I342" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J342" s="19"/>
       <c r="K342" s="20"/>
       <c r="L342" s="19"/>
       <c r="M342" t="str">
-        <f t="shared" ref="M342:M405" si="27">IF(B342=1,E342,"")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="N342" t="str">
-        <f t="shared" ref="N342:N405" si="28">IF(B342=2,E342,"")</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="B343" s="1"/>
       <c r="C343" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D343" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E343" s="30">
-        <v>25</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D343" s="13"/>
+      <c r="E343" s="30"/>
       <c r="F343" s="43"/>
       <c r="G343" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H343" s="18"/>
       <c r="I343" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J343" s="19"/>
       <c r="K343" s="20"/>
       <c r="L343" s="19"/>
       <c r="M343" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="M343:M406" si="31">IF(B343=1,E343,"")</f>
         <v/>
       </c>
       <c r="N343" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="N343:N406" si="32">IF(B343=2,E343,"")</f>
         <v/>
       </c>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B344" s="1"/>
       <c r="C344" s="5" t="s">
-        <v>5</v>
+        <v>303</v>
       </c>
       <c r="D344" s="13" t="s">
-        <v>544</v>
-      </c>
-      <c r="E344" s="30"/>
+        <v>430</v>
+      </c>
+      <c r="E344" s="30">
+        <v>25</v>
+      </c>
       <c r="F344" s="43"/>
       <c r="G344" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H344" s="18"/>
       <c r="I344" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J344" s="19"/>
       <c r="K344" s="20"/>
       <c r="L344" s="19"/>
       <c r="M344" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N344" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
-        <v>411</v>
+        <v>124</v>
       </c>
       <c r="B345" s="1"/>
       <c r="C345" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D345" s="13" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E345" s="30"/>
       <c r="F345" s="43"/>
       <c r="G345" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H345" s="18"/>
       <c r="I345" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J345" s="19"/>
       <c r="K345" s="20"/>
       <c r="L345" s="19"/>
       <c r="M345" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N345" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
-        <v>245</v>
+        <v>411</v>
       </c>
       <c r="B346" s="1"/>
       <c r="C346" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D346" s="13"/>
+      <c r="D346" s="13" t="s">
+        <v>545</v>
+      </c>
       <c r="E346" s="30"/>
       <c r="F346" s="43"/>
       <c r="G346" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H346" s="18"/>
       <c r="I346" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J346" s="19"/>
       <c r="K346" s="20"/>
       <c r="L346" s="19"/>
       <c r="M346" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N346" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="B347" s="1"/>
       <c r="C347" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D347" s="13" t="s">
-        <v>474</v>
-      </c>
+      <c r="D347" s="13"/>
       <c r="E347" s="30"/>
       <c r="F347" s="43"/>
       <c r="G347" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H347" s="18"/>
       <c r="I347" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J347" s="19"/>
       <c r="K347" s="20"/>
       <c r="L347" s="19"/>
       <c r="M347" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N347" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A348" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B348" s="21"/>
-      <c r="C348" s="3"/>
-      <c r="D348" s="14"/>
-      <c r="E348" s="31"/>
-      <c r="F348" s="45" t="s">
-        <v>724</v>
-      </c>
+      <c r="A348" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B348" s="1"/>
+      <c r="C348" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D348" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="E348" s="30"/>
+      <c r="F348" s="43"/>
       <c r="G348" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H348" s="18"/>
       <c r="I348" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J348" s="19"/>
       <c r="K348" s="20"/>
       <c r="L348" s="19"/>
       <c r="M348" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N348" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A349" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B349" s="1"/>
-      <c r="C349" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D349" s="13"/>
-      <c r="E349" s="30"/>
-      <c r="F349" s="43"/>
+      <c r="A349" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B349" s="21"/>
+      <c r="C349" s="3"/>
+      <c r="D349" s="14"/>
+      <c r="E349" s="31"/>
+      <c r="F349" s="45" t="s">
+        <v>724</v>
+      </c>
       <c r="G349" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H349" s="18"/>
       <c r="I349" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J349" s="19"/>
       <c r="K349" s="20"/>
       <c r="L349" s="19"/>
       <c r="M349" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N349" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A350" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B350" s="21"/>
-      <c r="C350" s="3"/>
-      <c r="D350" s="14"/>
-      <c r="E350" s="31"/>
-      <c r="F350" s="45" t="s">
-        <v>725</v>
-      </c>
+      <c r="A350" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B350" s="1"/>
+      <c r="C350" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D350" s="13"/>
+      <c r="E350" s="30"/>
+      <c r="F350" s="43"/>
       <c r="G350" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H350" s="18"/>
       <c r="I350" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J350" s="19"/>
       <c r="K350" s="20"/>
       <c r="L350" s="19"/>
       <c r="M350" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N350" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A351" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B351" s="1"/>
-      <c r="C351" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D351" s="13"/>
-      <c r="E351" s="30"/>
-      <c r="F351" s="43"/>
+      <c r="A351" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B351" s="21"/>
+      <c r="C351" s="3"/>
+      <c r="D351" s="14"/>
+      <c r="E351" s="31"/>
+      <c r="F351" s="45" t="s">
+        <v>725</v>
+      </c>
       <c r="G351" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H351" s="18"/>
       <c r="I351" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J351" s="19"/>
       <c r="K351" s="20"/>
       <c r="L351" s="19"/>
       <c r="M351" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N351" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B352" s="1"/>
       <c r="C352" s="5" t="s">
@@ -14770,29 +14772,29 @@
       <c r="E352" s="30"/>
       <c r="F352" s="43"/>
       <c r="G352" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H352" s="18"/>
       <c r="I352" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J352" s="19"/>
       <c r="K352" s="20"/>
       <c r="L352" s="19"/>
       <c r="M352" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N352" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="B353" s="1"/>
       <c r="C353" s="5" t="s">
@@ -14802,93 +14804,93 @@
       <c r="E353" s="30"/>
       <c r="F353" s="43"/>
       <c r="G353" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H353" s="18"/>
       <c r="I353" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J353" s="19"/>
       <c r="K353" s="20"/>
       <c r="L353" s="19"/>
       <c r="M353" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N353" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A354" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B354" s="21"/>
-      <c r="C354" s="3"/>
-      <c r="D354" s="14"/>
-      <c r="E354" s="31"/>
-      <c r="F354" s="45" t="s">
-        <v>726</v>
-      </c>
+      <c r="A354" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B354" s="1"/>
+      <c r="C354" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D354" s="13"/>
+      <c r="E354" s="30"/>
+      <c r="F354" s="43"/>
       <c r="G354" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H354" s="18"/>
       <c r="I354" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J354" s="19"/>
       <c r="K354" s="20"/>
       <c r="L354" s="19"/>
       <c r="M354" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N354" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A355" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B355" s="1"/>
-      <c r="C355" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D355" s="13"/>
-      <c r="E355" s="30"/>
-      <c r="F355" s="43"/>
+      <c r="A355" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B355" s="21"/>
+      <c r="C355" s="3"/>
+      <c r="D355" s="14"/>
+      <c r="E355" s="31"/>
+      <c r="F355" s="45" t="s">
+        <v>726</v>
+      </c>
       <c r="G355" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H355" s="18"/>
       <c r="I355" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J355" s="19"/>
       <c r="K355" s="20"/>
       <c r="L355" s="19"/>
       <c r="M355" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N355" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="B356" s="1"/>
       <c r="C356" s="5" t="s">
@@ -14898,29 +14900,29 @@
       <c r="E356" s="30"/>
       <c r="F356" s="43"/>
       <c r="G356" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H356" s="18"/>
       <c r="I356" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J356" s="19"/>
       <c r="K356" s="20"/>
       <c r="L356" s="19"/>
       <c r="M356" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N356" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
-        <v>376</v>
+        <v>182</v>
       </c>
       <c r="B357" s="1"/>
       <c r="C357" s="5" t="s">
@@ -14930,29 +14932,29 @@
       <c r="E357" s="30"/>
       <c r="F357" s="43"/>
       <c r="G357" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H357" s="18"/>
       <c r="I357" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J357" s="19"/>
       <c r="K357" s="20"/>
       <c r="L357" s="19"/>
       <c r="M357" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N357" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
-        <v>126</v>
+        <v>376</v>
       </c>
       <c r="B358" s="1"/>
       <c r="C358" s="5" t="s">
@@ -14962,193 +14964,193 @@
       <c r="E358" s="30"/>
       <c r="F358" s="43"/>
       <c r="G358" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H358" s="18"/>
       <c r="I358" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J358" s="19"/>
       <c r="K358" s="20"/>
       <c r="L358" s="19"/>
       <c r="M358" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N358" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
-        <v>302</v>
+        <v>126</v>
       </c>
       <c r="B359" s="1"/>
       <c r="C359" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D359" s="13" t="s">
-        <v>310</v>
-      </c>
+      <c r="D359" s="13"/>
       <c r="E359" s="30"/>
       <c r="F359" s="43"/>
       <c r="G359" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H359" s="18"/>
       <c r="I359" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J359" s="19"/>
       <c r="K359" s="20"/>
       <c r="L359" s="19"/>
       <c r="M359" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N359" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="B360" s="1"/>
       <c r="C360" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D360" s="13"/>
+      <c r="D360" s="13" t="s">
+        <v>310</v>
+      </c>
       <c r="E360" s="30"/>
       <c r="F360" s="43"/>
       <c r="G360" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H360" s="18"/>
       <c r="I360" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J360" s="19"/>
       <c r="K360" s="20"/>
       <c r="L360" s="19"/>
       <c r="M360" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N360" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A361" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B361" s="21"/>
-      <c r="C361" s="3"/>
-      <c r="D361" s="14"/>
-      <c r="E361" s="31"/>
-      <c r="F361" s="45" t="s">
-        <v>727</v>
-      </c>
+      <c r="A361" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B361" s="1"/>
+      <c r="C361" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D361" s="13"/>
+      <c r="E361" s="30"/>
+      <c r="F361" s="43"/>
       <c r="G361" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H361" s="18"/>
       <c r="I361" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J361" s="19"/>
       <c r="K361" s="20"/>
       <c r="L361" s="19"/>
       <c r="M361" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N361" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A362" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="B362" s="1"/>
-      <c r="C362" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D362" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="E362" s="30"/>
-      <c r="F362" s="43"/>
+      <c r="A362" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B362" s="21"/>
+      <c r="C362" s="3"/>
+      <c r="D362" s="14"/>
+      <c r="E362" s="31"/>
+      <c r="F362" s="45" t="s">
+        <v>727</v>
+      </c>
       <c r="G362" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H362" s="18"/>
       <c r="I362" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J362" s="19"/>
       <c r="K362" s="20"/>
       <c r="L362" s="19"/>
       <c r="M362" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N362" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
-        <v>127</v>
+        <v>462</v>
       </c>
       <c r="B363" s="1"/>
       <c r="C363" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D363" s="13"/>
+      <c r="D363" s="13" t="s">
+        <v>463</v>
+      </c>
       <c r="E363" s="30"/>
       <c r="F363" s="43"/>
       <c r="G363" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H363" s="18"/>
       <c r="I363" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J363" s="19"/>
       <c r="K363" s="20"/>
       <c r="L363" s="19"/>
       <c r="M363" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N363" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B364" s="1"/>
       <c r="C364" s="5" t="s">
@@ -15156,731 +15158,731 @@
       </c>
       <c r="D364" s="13"/>
       <c r="E364" s="30"/>
-      <c r="F364" s="46"/>
+      <c r="F364" s="43"/>
       <c r="G364" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H364" s="18"/>
       <c r="I364" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J364" s="19"/>
       <c r="K364" s="20"/>
       <c r="L364" s="19"/>
       <c r="M364" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N364" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A365" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B365" s="21"/>
-      <c r="C365" s="3"/>
-      <c r="D365" s="14"/>
-      <c r="E365" s="31"/>
-      <c r="F365" s="45" t="s">
-        <v>728</v>
-      </c>
+      <c r="A365" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B365" s="1"/>
+      <c r="C365" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D365" s="13"/>
+      <c r="E365" s="30"/>
+      <c r="F365" s="46"/>
       <c r="G365" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H365" s="18"/>
       <c r="I365" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J365" s="19"/>
       <c r="K365" s="20"/>
       <c r="L365" s="19"/>
       <c r="M365" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N365" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>481</v>
+        <v>129</v>
       </c>
       <c r="B366" s="21"/>
       <c r="C366" s="3"/>
       <c r="D366" s="14"/>
       <c r="E366" s="31"/>
       <c r="F366" s="45" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G366" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H366" s="18"/>
       <c r="I366" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J366" s="19"/>
       <c r="K366" s="20"/>
       <c r="L366" s="19"/>
       <c r="M366" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N366" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>380</v>
+        <v>481</v>
       </c>
       <c r="B367" s="21"/>
       <c r="C367" s="3"/>
-      <c r="D367" s="14" t="s">
-        <v>488</v>
-      </c>
+      <c r="D367" s="14"/>
       <c r="E367" s="31"/>
       <c r="F367" s="45" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G367" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H367" s="18"/>
       <c r="I367" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J367" s="19"/>
       <c r="K367" s="20"/>
       <c r="L367" s="19"/>
       <c r="M367" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N367" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>212</v>
+        <v>380</v>
       </c>
       <c r="B368" s="21"/>
       <c r="C368" s="3"/>
-      <c r="D368" s="14"/>
+      <c r="D368" s="14" t="s">
+        <v>488</v>
+      </c>
       <c r="E368" s="31"/>
       <c r="F368" s="45" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G368" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H368" s="18"/>
       <c r="I368" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J368" s="19"/>
       <c r="K368" s="20"/>
       <c r="L368" s="19"/>
       <c r="M368" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N368" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A369" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B369" s="1"/>
-      <c r="C369" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D369" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="E369" s="30">
-        <v>15.25</v>
-      </c>
-      <c r="F369" s="46"/>
+      <c r="A369" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B369" s="21"/>
+      <c r="C369" s="3"/>
+      <c r="D369" s="14"/>
+      <c r="E369" s="31"/>
+      <c r="F369" s="45" t="s">
+        <v>731</v>
+      </c>
       <c r="G369" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H369" s="18"/>
       <c r="I369" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J369" s="19"/>
       <c r="K369" s="20"/>
       <c r="L369" s="19"/>
       <c r="M369" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N369" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="B370" s="1"/>
       <c r="C370" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D370" s="13"/>
-      <c r="E370" s="30"/>
-      <c r="F370" s="43"/>
+      <c r="D370" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="E370" s="30">
+        <v>15.25</v>
+      </c>
+      <c r="F370" s="46"/>
       <c r="G370" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H370" s="18"/>
       <c r="I370" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J370" s="19"/>
       <c r="K370" s="20"/>
       <c r="L370" s="19"/>
       <c r="M370" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N370" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="B371" s="1"/>
       <c r="C371" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D371" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E371" s="30">
-        <v>24</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D371" s="13"/>
+      <c r="E371" s="30"/>
       <c r="F371" s="43"/>
       <c r="G371" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H371" s="18"/>
       <c r="I371" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J371" s="19"/>
       <c r="K371" s="20"/>
       <c r="L371" s="19"/>
       <c r="M371" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N371" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
-        <v>246</v>
+        <v>131</v>
       </c>
       <c r="B372" s="1"/>
       <c r="C372" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D372" s="13"/>
-      <c r="E372" s="30"/>
+        <v>303</v>
+      </c>
+      <c r="D372" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E372" s="30">
+        <v>24</v>
+      </c>
       <c r="F372" s="43"/>
       <c r="G372" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H372" s="18"/>
       <c r="I372" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J372" s="19"/>
       <c r="K372" s="20"/>
       <c r="L372" s="19"/>
       <c r="M372" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N372" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A373" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B373" s="21"/>
-      <c r="C373" s="3"/>
-      <c r="D373" s="14"/>
-      <c r="E373" s="31"/>
-      <c r="F373" s="45" t="s">
-        <v>732</v>
-      </c>
+      <c r="A373" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B373" s="1"/>
+      <c r="C373" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D373" s="13"/>
+      <c r="E373" s="30"/>
+      <c r="F373" s="43"/>
       <c r="G373" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H373" s="18"/>
       <c r="I373" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J373" s="19"/>
       <c r="K373" s="20"/>
       <c r="L373" s="19"/>
       <c r="M373" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N373" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A374" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B374" s="1"/>
-      <c r="C374" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D374" s="13"/>
-      <c r="E374" s="30"/>
-      <c r="F374" s="43"/>
+      <c r="A374" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B374" s="21"/>
+      <c r="C374" s="3"/>
+      <c r="D374" s="14"/>
+      <c r="E374" s="31"/>
+      <c r="F374" s="45" t="s">
+        <v>732</v>
+      </c>
       <c r="G374" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H374" s="18"/>
       <c r="I374" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J374" s="19"/>
       <c r="K374" s="20"/>
       <c r="L374" s="19"/>
       <c r="M374" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N374" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A375" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B375" s="21"/>
-      <c r="C375" s="3"/>
-      <c r="D375" s="14"/>
-      <c r="E375" s="31"/>
-      <c r="F375" s="45" t="s">
-        <v>733</v>
-      </c>
+      <c r="A375" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B375" s="1"/>
+      <c r="C375" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D375" s="13"/>
+      <c r="E375" s="30"/>
+      <c r="F375" s="43"/>
       <c r="G375" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H375" s="18"/>
       <c r="I375" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J375" s="19"/>
       <c r="K375" s="20"/>
       <c r="L375" s="19"/>
       <c r="M375" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N375" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A376" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B376" s="1"/>
-      <c r="C376" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D376" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E376" s="30">
-        <v>17</v>
-      </c>
-      <c r="F376" s="43"/>
+      <c r="A376" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B376" s="21"/>
+      <c r="C376" s="3"/>
+      <c r="D376" s="14"/>
+      <c r="E376" s="31"/>
+      <c r="F376" s="45" t="s">
+        <v>733</v>
+      </c>
       <c r="G376" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H376" s="18"/>
       <c r="I376" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J376" s="19"/>
       <c r="K376" s="20"/>
       <c r="L376" s="19"/>
       <c r="M376" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N376" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A377" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B377" s="21"/>
-      <c r="C377" s="3"/>
-      <c r="D377" s="14"/>
-      <c r="E377" s="31"/>
-      <c r="F377" s="45" t="s">
-        <v>734</v>
-      </c>
+      <c r="A377" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B377" s="1"/>
+      <c r="C377" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D377" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E377" s="30">
+        <v>17</v>
+      </c>
+      <c r="F377" s="43"/>
       <c r="G377" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H377" s="18"/>
       <c r="I377" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J377" s="19"/>
       <c r="K377" s="20"/>
       <c r="L377" s="19"/>
       <c r="M377" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N377" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>542</v>
+        <v>298</v>
       </c>
       <c r="B378" s="21"/>
       <c r="C378" s="3"/>
-      <c r="D378" s="14" t="s">
-        <v>735</v>
-      </c>
+      <c r="D378" s="14"/>
       <c r="E378" s="31"/>
       <c r="F378" s="45" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="G378" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H378" s="18"/>
       <c r="I378" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J378" s="19"/>
       <c r="K378" s="20"/>
       <c r="L378" s="19"/>
       <c r="M378" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N378" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>133</v>
+        <v>542</v>
       </c>
       <c r="B379" s="21"/>
       <c r="C379" s="3"/>
-      <c r="D379" s="14"/>
+      <c r="D379" s="14" t="s">
+        <v>735</v>
+      </c>
       <c r="E379" s="31"/>
       <c r="F379" s="45" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G379" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H379" s="18"/>
       <c r="I379" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J379" s="19"/>
       <c r="K379" s="20"/>
       <c r="L379" s="19"/>
       <c r="M379" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N379" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>738</v>
+        <v>133</v>
       </c>
       <c r="B380" s="21"/>
       <c r="C380" s="3"/>
-      <c r="D380" s="14" t="s">
-        <v>740</v>
-      </c>
+      <c r="D380" s="14"/>
       <c r="E380" s="31"/>
       <c r="F380" s="45" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G380" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H380" s="18"/>
       <c r="I380" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J380" s="19"/>
       <c r="K380" s="20"/>
       <c r="L380" s="19"/>
       <c r="M380" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N380" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>213</v>
+        <v>738</v>
       </c>
       <c r="B381" s="21"/>
       <c r="C381" s="3"/>
       <c r="D381" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="E381" s="31">
-        <v>15</v>
-      </c>
+        <v>740</v>
+      </c>
+      <c r="E381" s="31"/>
       <c r="F381" s="45" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G381" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H381" s="18"/>
       <c r="I381" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J381" s="19"/>
       <c r="K381" s="20"/>
       <c r="L381" s="19"/>
       <c r="M381" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N381" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>393</v>
+        <v>213</v>
       </c>
       <c r="B382" s="21"/>
       <c r="C382" s="3"/>
-      <c r="D382" s="14"/>
-      <c r="E382" s="31"/>
+      <c r="D382" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="E382" s="31">
+        <v>15</v>
+      </c>
       <c r="F382" s="45" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G382" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H382" s="18"/>
       <c r="I382" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J382" s="19"/>
       <c r="K382" s="20"/>
       <c r="L382" s="19"/>
       <c r="M382" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N382" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A383" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B383" s="1"/>
-      <c r="C383" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D383" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="E383" s="30"/>
-      <c r="F383" s="43"/>
+      <c r="A383" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B383" s="21"/>
+      <c r="C383" s="3"/>
+      <c r="D383" s="14"/>
+      <c r="E383" s="31"/>
+      <c r="F383" s="45" t="s">
+        <v>742</v>
+      </c>
       <c r="G383" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H383" s="18"/>
       <c r="I383" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J383" s="19"/>
       <c r="K383" s="20"/>
       <c r="L383" s="19"/>
       <c r="M383" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N383" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
-        <v>539</v>
+        <v>134</v>
       </c>
       <c r="B384" s="1"/>
       <c r="C384" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D384" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="E384" s="30">
-        <v>10</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="E384" s="30"/>
       <c r="F384" s="43"/>
       <c r="G384" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H384" s="18"/>
       <c r="I384" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J384" s="19"/>
       <c r="K384" s="20"/>
       <c r="L384" s="19"/>
       <c r="M384" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N384" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
-        <v>135</v>
+        <v>539</v>
       </c>
       <c r="B385" s="1"/>
       <c r="C385" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D385" s="13"/>
-      <c r="E385" s="30"/>
-      <c r="F385" s="46"/>
+      <c r="D385" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E385" s="30">
+        <v>10</v>
+      </c>
+      <c r="F385" s="43"/>
       <c r="G385" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H385" s="18"/>
       <c r="I385" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J385" s="19"/>
       <c r="K385" s="20"/>
       <c r="L385" s="19"/>
       <c r="M385" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N385" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="B386" s="1"/>
       <c r="C386" s="5" t="s">
@@ -15890,225 +15892,225 @@
       <c r="E386" s="30"/>
       <c r="F386" s="46"/>
       <c r="G386" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H386" s="18"/>
       <c r="I386" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J386" s="19"/>
       <c r="K386" s="20"/>
       <c r="L386" s="19"/>
       <c r="M386" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N386" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B387" s="1"/>
       <c r="C387" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D387" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E387" s="30">
-        <v>11</v>
-      </c>
-      <c r="F387" s="43"/>
+      <c r="D387" s="13"/>
+      <c r="E387" s="30"/>
+      <c r="F387" s="46"/>
       <c r="G387" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H387" s="18"/>
       <c r="I387" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J387" s="19"/>
       <c r="K387" s="20"/>
       <c r="L387" s="19"/>
       <c r="M387" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N387" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A388" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B388" s="21"/>
-      <c r="C388" s="3"/>
-      <c r="D388" s="14"/>
-      <c r="E388" s="31"/>
-      <c r="F388" s="45" t="s">
-        <v>743</v>
-      </c>
+      <c r="A388" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B388" s="1"/>
+      <c r="C388" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D388" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E388" s="30">
+        <v>11</v>
+      </c>
+      <c r="F388" s="43"/>
       <c r="G388" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H388" s="18"/>
       <c r="I388" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J388" s="19"/>
       <c r="K388" s="20"/>
       <c r="L388" s="19"/>
       <c r="M388" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N388" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>412</v>
+        <v>248</v>
       </c>
       <c r="B389" s="21"/>
       <c r="C389" s="3"/>
       <c r="D389" s="14"/>
       <c r="E389" s="31"/>
       <c r="F389" s="45" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G389" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H389" s="18"/>
       <c r="I389" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J389" s="19"/>
       <c r="K389" s="20"/>
       <c r="L389" s="19"/>
       <c r="M389" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N389" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A390" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B390" s="1"/>
-      <c r="C390" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D390" s="13"/>
-      <c r="E390" s="30"/>
-      <c r="F390" s="43"/>
+      <c r="A390" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B390" s="21"/>
+      <c r="C390" s="3"/>
+      <c r="D390" s="14"/>
+      <c r="E390" s="31"/>
+      <c r="F390" s="45" t="s">
+        <v>744</v>
+      </c>
       <c r="G390" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H390" s="18"/>
       <c r="I390" s="19">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="30"/>
+        <v>0</v>
       </c>
       <c r="J390" s="19"/>
       <c r="K390" s="20"/>
       <c r="L390" s="19"/>
       <c r="M390" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N390" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A391" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B391" s="21"/>
-      <c r="C391" s="3"/>
-      <c r="D391" s="14"/>
-      <c r="E391" s="31"/>
-      <c r="F391" s="45" t="s">
-        <v>745</v>
-      </c>
+      <c r="A391" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B391" s="1"/>
+      <c r="C391" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D391" s="13"/>
+      <c r="E391" s="30"/>
+      <c r="F391" s="43"/>
       <c r="G391" s="20">
-        <f t="shared" ref="G391:G454" si="29">COUNTA(A391)</f>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H391" s="18"/>
       <c r="I391" s="19">
-        <f t="shared" ref="I391:I454" si="30">COUNTA(C391)</f>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>1</v>
       </c>
       <c r="J391" s="19"/>
       <c r="K391" s="20"/>
       <c r="L391" s="19"/>
       <c r="M391" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N391" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A392" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B392" s="1"/>
-      <c r="C392" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D392" s="13"/>
-      <c r="E392" s="30"/>
-      <c r="F392" s="43"/>
+      <c r="A392" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B392" s="21"/>
+      <c r="C392" s="3"/>
+      <c r="D392" s="14"/>
+      <c r="E392" s="31"/>
+      <c r="F392" s="45" t="s">
+        <v>745</v>
+      </c>
       <c r="G392" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G392:G455" si="33">COUNTA(A392)</f>
         <v>1</v>
       </c>
       <c r="H392" s="18"/>
       <c r="I392" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" ref="I392:I455" si="34">COUNTA(C392)</f>
+        <v>0</v>
       </c>
       <c r="J392" s="19"/>
       <c r="K392" s="20"/>
       <c r="L392" s="19"/>
       <c r="M392" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N392" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B393" s="1"/>
       <c r="C393" s="5" t="s">
@@ -16118,221 +16120,221 @@
       <c r="E393" s="30"/>
       <c r="F393" s="43"/>
       <c r="G393" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H393" s="18"/>
       <c r="I393" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J393" s="19"/>
       <c r="K393" s="20"/>
       <c r="L393" s="19"/>
       <c r="M393" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N393" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B394" s="1"/>
       <c r="C394" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D394" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E394" s="30">
-        <v>18</v>
-      </c>
+      <c r="D394" s="13"/>
+      <c r="E394" s="30"/>
       <c r="F394" s="43"/>
       <c r="G394" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H394" s="18"/>
       <c r="I394" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J394" s="19"/>
       <c r="K394" s="20"/>
       <c r="L394" s="19"/>
       <c r="M394" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N394" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A395" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="B395" s="21"/>
-      <c r="C395" s="3"/>
-      <c r="D395" s="14"/>
-      <c r="E395" s="31"/>
-      <c r="F395" s="45" t="s">
-        <v>746</v>
-      </c>
+      <c r="A395" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B395" s="1"/>
+      <c r="C395" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D395" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E395" s="30">
+        <v>18</v>
+      </c>
+      <c r="F395" s="43"/>
       <c r="G395" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H395" s="18"/>
       <c r="I395" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J395" s="19"/>
       <c r="K395" s="20"/>
       <c r="L395" s="19"/>
       <c r="M395" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N395" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>140</v>
+        <v>489</v>
       </c>
       <c r="B396" s="21"/>
       <c r="C396" s="3"/>
       <c r="D396" s="14"/>
       <c r="E396" s="31"/>
       <c r="F396" s="45" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G396" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H396" s="18"/>
       <c r="I396" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J396" s="19"/>
       <c r="K396" s="20"/>
       <c r="L396" s="19"/>
       <c r="M396" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N396" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>442</v>
+        <v>140</v>
       </c>
       <c r="B397" s="21"/>
       <c r="C397" s="3"/>
       <c r="D397" s="14"/>
       <c r="E397" s="31"/>
       <c r="F397" s="45" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G397" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H397" s="18"/>
       <c r="I397" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J397" s="19"/>
       <c r="K397" s="20"/>
       <c r="L397" s="19"/>
       <c r="M397" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N397" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A398" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="B398" s="1"/>
-      <c r="C398" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D398" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E398" s="30">
-        <v>10</v>
-      </c>
-      <c r="F398" s="43"/>
+      <c r="A398" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B398" s="21"/>
+      <c r="C398" s="3"/>
+      <c r="D398" s="14"/>
+      <c r="E398" s="31"/>
+      <c r="F398" s="45" t="s">
+        <v>748</v>
+      </c>
       <c r="G398" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H398" s="18"/>
       <c r="I398" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J398" s="19"/>
       <c r="K398" s="20"/>
       <c r="L398" s="19"/>
+      <c r="M398" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="N398" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
-        <v>299</v>
+        <v>532</v>
       </c>
       <c r="B399" s="1"/>
       <c r="C399" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D399" s="13"/>
-      <c r="E399" s="30"/>
+      <c r="D399" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E399" s="30">
+        <v>10</v>
+      </c>
       <c r="F399" s="43"/>
       <c r="G399" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H399" s="18"/>
       <c r="I399" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J399" s="19"/>
       <c r="K399" s="20"/>
       <c r="L399" s="19"/>
-      <c r="M399" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="N399" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="B400" s="1"/>
       <c r="C400" s="5" t="s">
@@ -16342,199 +16344,199 @@
       <c r="E400" s="30"/>
       <c r="F400" s="43"/>
       <c r="G400" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H400" s="18"/>
       <c r="I400" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J400" s="19"/>
       <c r="K400" s="20"/>
       <c r="L400" s="19"/>
       <c r="M400" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N400" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A401" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B401" s="21"/>
-      <c r="C401" s="3"/>
-      <c r="D401" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="E401" s="31">
-        <v>19</v>
-      </c>
-      <c r="F401" s="45" t="s">
-        <v>749</v>
-      </c>
+      <c r="A401" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B401" s="1"/>
+      <c r="C401" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D401" s="13"/>
+      <c r="E401" s="30"/>
+      <c r="F401" s="43"/>
       <c r="G401" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H401" s="18"/>
       <c r="I401" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J401" s="19"/>
       <c r="K401" s="20"/>
       <c r="L401" s="19"/>
       <c r="M401" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N401" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B402" s="21"/>
       <c r="C402" s="3"/>
-      <c r="D402" s="14"/>
-      <c r="E402" s="31"/>
+      <c r="D402" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="E402" s="31">
+        <v>19</v>
+      </c>
       <c r="F402" s="45" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G402" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H402" s="18"/>
       <c r="I402" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J402" s="19"/>
       <c r="K402" s="20"/>
       <c r="L402" s="19"/>
       <c r="M402" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N402" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>141</v>
+        <v>391</v>
       </c>
       <c r="B403" s="21"/>
       <c r="C403" s="3"/>
       <c r="D403" s="14"/>
       <c r="E403" s="31"/>
       <c r="F403" s="45" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G403" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H403" s="18"/>
       <c r="I403" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J403" s="19"/>
       <c r="K403" s="20"/>
       <c r="L403" s="19"/>
       <c r="M403" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N403" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A404" s="26" t="s">
-        <v>496</v>
-      </c>
-      <c r="B404" s="27" t="s">
-        <v>522</v>
-      </c>
-      <c r="C404" s="28"/>
-      <c r="D404" s="29" t="s">
-        <v>518</v>
-      </c>
-      <c r="E404" s="32">
-        <v>24</v>
-      </c>
-      <c r="F404" s="71" t="s">
-        <v>752</v>
+      <c r="A404" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B404" s="21"/>
+      <c r="C404" s="3"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="31"/>
+      <c r="F404" s="45" t="s">
+        <v>751</v>
       </c>
       <c r="G404" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H404" s="18"/>
       <c r="I404" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J404" s="19"/>
       <c r="K404" s="20"/>
       <c r="L404" s="19"/>
       <c r="M404" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N404" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A405" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B405" s="21"/>
-      <c r="C405" s="3"/>
-      <c r="D405" s="14"/>
-      <c r="E405" s="31"/>
-      <c r="F405" s="45" t="s">
-        <v>753</v>
+      <c r="A405" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="B405" s="27" t="s">
+        <v>522</v>
+      </c>
+      <c r="C405" s="28"/>
+      <c r="D405" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="E405" s="32">
+        <v>24</v>
+      </c>
+      <c r="F405" s="71" t="s">
+        <v>752</v>
       </c>
       <c r="G405" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H405" s="18"/>
       <c r="I405" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J405" s="19"/>
       <c r="K405" s="20"/>
       <c r="L405" s="19"/>
       <c r="M405" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N405" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="B406" s="21"/>
       <c r="C406" s="3"/>
@@ -16544,195 +16546,195 @@
         <v>753</v>
       </c>
       <c r="G406" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H406" s="18"/>
       <c r="I406" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J406" s="19"/>
       <c r="K406" s="20"/>
       <c r="L406" s="19"/>
       <c r="M406" t="str">
-        <f t="shared" ref="M406:M472" si="31">IF(B406=1,E406,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N406" t="str">
-        <f t="shared" ref="N406:N472" si="32">IF(B406=2,E406,"")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A407" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B407" s="1"/>
-      <c r="C407" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D407" s="13"/>
-      <c r="E407" s="30"/>
-      <c r="F407" s="43"/>
+      <c r="A407" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B407" s="21"/>
+      <c r="C407" s="3"/>
+      <c r="D407" s="14"/>
+      <c r="E407" s="31"/>
+      <c r="F407" s="45" t="s">
+        <v>753</v>
+      </c>
       <c r="G407" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H407" s="18"/>
       <c r="I407" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J407" s="19"/>
       <c r="K407" s="20"/>
       <c r="L407" s="19"/>
       <c r="M407" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="M407:M473" si="35">IF(B407=1,E407,"")</f>
         <v/>
       </c>
       <c r="N407" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="N407:N473" si="36">IF(B407=2,E407,"")</f>
         <v/>
       </c>
     </row>
     <row r="408" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
-        <v>406</v>
+        <v>249</v>
       </c>
       <c r="B408" s="1"/>
       <c r="C408" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D408" s="13" t="s">
-        <v>530</v>
-      </c>
-      <c r="E408" s="30">
-        <v>12</v>
-      </c>
+      <c r="D408" s="13"/>
+      <c r="E408" s="30"/>
       <c r="F408" s="43"/>
       <c r="G408" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H408" s="18"/>
       <c r="I408" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J408" s="19"/>
       <c r="K408" s="20"/>
       <c r="L408" s="19"/>
       <c r="M408" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N408" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A409" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B409" s="21"/>
-      <c r="C409" s="3"/>
-      <c r="D409" s="14"/>
-      <c r="E409" s="31"/>
-      <c r="F409" s="45" t="s">
-        <v>754</v>
-      </c>
+      <c r="A409" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B409" s="1"/>
+      <c r="C409" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D409" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="E409" s="30">
+        <v>12</v>
+      </c>
+      <c r="F409" s="43"/>
       <c r="G409" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H409" s="18"/>
       <c r="I409" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J409" s="19"/>
       <c r="K409" s="20"/>
       <c r="L409" s="19"/>
       <c r="M409" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N409" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A410" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="B410" s="1"/>
-      <c r="C410" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D410" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="E410" s="30"/>
-      <c r="F410" s="43"/>
+      <c r="A410" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B410" s="21"/>
+      <c r="C410" s="3"/>
+      <c r="D410" s="14"/>
+      <c r="E410" s="31"/>
+      <c r="F410" s="45" t="s">
+        <v>754</v>
+      </c>
       <c r="G410" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H410" s="18"/>
       <c r="I410" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J410" s="19"/>
       <c r="K410" s="20"/>
       <c r="L410" s="19"/>
       <c r="M410" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N410" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A411" s="4" t="s">
-        <v>143</v>
+        <v>464</v>
       </c>
       <c r="B411" s="1"/>
       <c r="C411" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D411" s="13"/>
+      <c r="D411" s="13" t="s">
+        <v>465</v>
+      </c>
       <c r="E411" s="30"/>
       <c r="F411" s="43"/>
       <c r="G411" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H411" s="18"/>
       <c r="I411" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J411" s="19"/>
       <c r="K411" s="20"/>
       <c r="L411" s="19"/>
       <c r="M411" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N411" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A412" s="4" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="B412" s="1"/>
       <c r="C412" s="5" t="s">
@@ -16742,423 +16744,423 @@
       <c r="E412" s="30"/>
       <c r="F412" s="43"/>
       <c r="G412" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H412" s="18"/>
       <c r="I412" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J412" s="19"/>
       <c r="K412" s="20"/>
       <c r="L412" s="19"/>
       <c r="M412" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N412" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="B413" s="1"/>
       <c r="C413" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D413" s="13" t="s">
-        <v>509</v>
-      </c>
-      <c r="E413" s="30">
-        <v>17.190000000000001</v>
-      </c>
+      <c r="D413" s="13"/>
+      <c r="E413" s="30"/>
       <c r="F413" s="43"/>
       <c r="G413" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H413" s="18"/>
       <c r="I413" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J413" s="19"/>
       <c r="K413" s="20"/>
       <c r="L413" s="19"/>
       <c r="M413" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N413" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A414" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B414" s="21"/>
-      <c r="C414" s="3"/>
-      <c r="D414" s="14">
-        <v>558</v>
-      </c>
-      <c r="E414" s="31"/>
-      <c r="F414" s="45" t="s">
-        <v>755</v>
-      </c>
+      <c r="A414" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B414" s="1"/>
+      <c r="C414" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D414" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="E414" s="30">
+        <v>17.190000000000001</v>
+      </c>
+      <c r="F414" s="43"/>
       <c r="G414" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H414" s="18"/>
       <c r="I414" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J414" s="19"/>
       <c r="K414" s="20"/>
       <c r="L414" s="19"/>
+      <c r="M414" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="N414" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
     </row>
     <row r="415" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>300</v>
+        <v>145</v>
       </c>
       <c r="B415" s="21"/>
       <c r="C415" s="3"/>
-      <c r="D415" s="14"/>
+      <c r="D415" s="14">
+        <v>558</v>
+      </c>
       <c r="E415" s="31"/>
       <c r="F415" s="45" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G415" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H415" s="18"/>
       <c r="I415" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J415" s="19"/>
       <c r="K415" s="20"/>
       <c r="L415" s="19"/>
-      <c r="M415" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N415" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
     </row>
     <row r="416" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A416" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B416" s="1"/>
-      <c r="C416" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D416" s="13"/>
-      <c r="E416" s="30"/>
-      <c r="F416" s="43"/>
+      <c r="A416" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B416" s="21"/>
+      <c r="C416" s="3"/>
+      <c r="D416" s="14"/>
+      <c r="E416" s="31"/>
+      <c r="F416" s="45" t="s">
+        <v>756</v>
+      </c>
       <c r="G416" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H416" s="18"/>
       <c r="I416" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J416" s="19"/>
       <c r="K416" s="20"/>
       <c r="L416" s="19"/>
       <c r="M416" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N416" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="B417" s="1"/>
       <c r="C417" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D417" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="E417" s="30">
-        <v>23</v>
-      </c>
+      <c r="D417" s="13"/>
+      <c r="E417" s="30"/>
       <c r="F417" s="43"/>
       <c r="G417" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H417" s="18"/>
       <c r="I417" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J417" s="19"/>
       <c r="K417" s="20"/>
       <c r="L417" s="19"/>
       <c r="M417" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N417" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="418" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
-        <v>497</v>
+        <v>275</v>
       </c>
       <c r="B418" s="1"/>
       <c r="C418" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D418" s="13"/>
-      <c r="E418" s="30"/>
+      <c r="D418" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="E418" s="30">
+        <v>23</v>
+      </c>
       <c r="F418" s="43"/>
       <c r="G418" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H418" s="18"/>
       <c r="I418" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J418" s="19"/>
       <c r="K418" s="20"/>
       <c r="L418" s="19"/>
       <c r="M418" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N418" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
-        <v>229</v>
+        <v>497</v>
       </c>
       <c r="B419" s="1"/>
       <c r="C419" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D419" s="13">
-        <v>8</v>
-      </c>
+      <c r="D419" s="13"/>
       <c r="E419" s="30"/>
       <c r="F419" s="43"/>
       <c r="G419" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H419" s="18"/>
       <c r="I419" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J419" s="19"/>
       <c r="K419" s="20"/>
       <c r="L419" s="19"/>
       <c r="M419" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N419" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
-        <v>146</v>
+        <v>229</v>
       </c>
       <c r="B420" s="1"/>
       <c r="C420" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D420" s="13" t="s">
-        <v>422</v>
+      <c r="D420" s="13">
+        <v>8</v>
       </c>
       <c r="E420" s="30"/>
       <c r="F420" s="43"/>
       <c r="G420" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H420" s="18"/>
       <c r="I420" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J420" s="19"/>
       <c r="K420" s="20"/>
       <c r="L420" s="19"/>
       <c r="M420" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N420" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A421" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B421" s="21"/>
-      <c r="C421" s="3"/>
-      <c r="D421" s="14"/>
-      <c r="E421" s="31"/>
-      <c r="F421" s="45" t="s">
-        <v>757</v>
-      </c>
+      <c r="A421" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B421" s="1"/>
+      <c r="C421" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D421" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="E421" s="30"/>
+      <c r="F421" s="43"/>
       <c r="G421" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H421" s="18"/>
       <c r="I421" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J421" s="19"/>
       <c r="K421" s="20"/>
       <c r="L421" s="19"/>
       <c r="M421" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N421" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>230</v>
+        <v>383</v>
       </c>
       <c r="B422" s="21"/>
       <c r="C422" s="3"/>
       <c r="D422" s="14"/>
       <c r="E422" s="31"/>
       <c r="F422" s="45" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G422" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H422" s="18"/>
       <c r="I422" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J422" s="19"/>
       <c r="K422" s="20"/>
       <c r="L422" s="19"/>
       <c r="M422" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N422" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A423" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B423" s="1"/>
-      <c r="C423" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D423" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E423" s="30">
-        <v>12</v>
-      </c>
-      <c r="F423" s="43"/>
+      <c r="A423" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B423" s="21"/>
+      <c r="C423" s="3"/>
+      <c r="D423" s="14"/>
+      <c r="E423" s="31"/>
+      <c r="F423" s="45" t="s">
+        <v>758</v>
+      </c>
       <c r="G423" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H423" s="18"/>
       <c r="I423" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J423" s="19"/>
       <c r="K423" s="20"/>
       <c r="L423" s="19"/>
       <c r="M423" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N423" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
-        <v>399</v>
+        <v>147</v>
       </c>
       <c r="B424" s="1"/>
       <c r="C424" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D424" s="13"/>
-      <c r="E424" s="30"/>
+      <c r="D424" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E424" s="30">
+        <v>12</v>
+      </c>
       <c r="F424" s="43"/>
       <c r="G424" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H424" s="18"/>
       <c r="I424" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J424" s="19"/>
       <c r="K424" s="20"/>
       <c r="L424" s="19"/>
       <c r="M424" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N424" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
-        <v>276</v>
+        <v>399</v>
       </c>
       <c r="B425" s="1"/>
       <c r="C425" s="5" t="s">
@@ -17168,221 +17170,221 @@
       <c r="E425" s="30"/>
       <c r="F425" s="43"/>
       <c r="G425" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H425" s="18"/>
       <c r="I425" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J425" s="19"/>
       <c r="K425" s="20"/>
       <c r="L425" s="19"/>
       <c r="M425" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N425" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
-        <v>507</v>
+        <v>276</v>
       </c>
       <c r="B426" s="1"/>
       <c r="C426" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D426" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="E426" s="30">
-        <v>8.8800000000000008</v>
-      </c>
+      <c r="D426" s="13"/>
+      <c r="E426" s="30"/>
       <c r="F426" s="43"/>
       <c r="G426" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H426" s="18"/>
       <c r="I426" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J426" s="19"/>
       <c r="K426" s="20"/>
       <c r="L426" s="19"/>
       <c r="M426" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N426" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A427" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B427" s="21"/>
-      <c r="C427" s="3"/>
-      <c r="D427" s="14" t="s">
-        <v>760</v>
-      </c>
-      <c r="E427" s="31"/>
-      <c r="F427" s="45" t="s">
-        <v>759</v>
-      </c>
+      <c r="A427" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B427" s="1"/>
+      <c r="C427" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D427" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E427" s="30">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="F427" s="43"/>
       <c r="G427" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H427" s="18"/>
       <c r="I427" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J427" s="19"/>
       <c r="K427" s="20"/>
       <c r="L427" s="19"/>
+      <c r="M427" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="N427" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
     </row>
     <row r="428" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A428" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B428" s="1"/>
-      <c r="C428" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D428" s="13"/>
-      <c r="E428" s="30"/>
-      <c r="F428" s="43"/>
+      <c r="A428" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B428" s="21"/>
+      <c r="C428" s="3"/>
+      <c r="D428" s="14" t="s">
+        <v>760</v>
+      </c>
+      <c r="E428" s="31"/>
+      <c r="F428" s="45" t="s">
+        <v>759</v>
+      </c>
       <c r="G428" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H428" s="18"/>
       <c r="I428" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J428" s="19"/>
       <c r="K428" s="20"/>
       <c r="L428" s="19"/>
-      <c r="M428" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N428" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
     </row>
     <row r="429" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A429" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B429" s="21"/>
-      <c r="C429" s="3"/>
-      <c r="D429" s="14" t="s">
-        <v>762</v>
-      </c>
-      <c r="E429" s="31"/>
-      <c r="F429" s="45" t="s">
-        <v>807</v>
-      </c>
+      <c r="A429" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B429" s="1"/>
+      <c r="C429" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D429" s="13"/>
+      <c r="E429" s="30"/>
+      <c r="F429" s="43"/>
       <c r="G429" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H429" s="18"/>
       <c r="I429" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J429" s="19"/>
       <c r="K429" s="20"/>
       <c r="L429" s="19"/>
       <c r="M429" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N429" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B430" s="21"/>
       <c r="C430" s="3"/>
-      <c r="D430" s="14"/>
+      <c r="D430" s="14" t="s">
+        <v>762</v>
+      </c>
       <c r="E430" s="31"/>
       <c r="F430" s="45" t="s">
-        <v>761</v>
+        <v>807</v>
       </c>
       <c r="G430" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H430" s="18"/>
       <c r="I430" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J430" s="19"/>
       <c r="K430" s="20"/>
       <c r="L430" s="19"/>
       <c r="M430" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N430" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A431" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B431" s="1"/>
-      <c r="C431" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D431" s="13"/>
-      <c r="E431" s="30"/>
-      <c r="F431" s="43"/>
+      <c r="A431" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B431" s="21"/>
+      <c r="C431" s="3"/>
+      <c r="D431" s="14"/>
+      <c r="E431" s="31"/>
+      <c r="F431" s="45" t="s">
+        <v>761</v>
+      </c>
       <c r="G431" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H431" s="18"/>
       <c r="I431" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J431" s="19"/>
       <c r="K431" s="20"/>
       <c r="L431" s="19"/>
       <c r="M431" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N431" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
-        <v>236</v>
+        <v>294</v>
       </c>
       <c r="B432" s="1"/>
       <c r="C432" s="5" t="s">
@@ -17392,29 +17394,29 @@
       <c r="E432" s="30"/>
       <c r="F432" s="43"/>
       <c r="G432" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H432" s="18"/>
       <c r="I432" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J432" s="19"/>
       <c r="K432" s="20"/>
       <c r="L432" s="19"/>
       <c r="M432" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N432" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
-        <v>372</v>
+        <v>236</v>
       </c>
       <c r="B433" s="1"/>
       <c r="C433" s="5" t="s">
@@ -17424,285 +17426,285 @@
       <c r="E433" s="30"/>
       <c r="F433" s="43"/>
       <c r="G433" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H433" s="18"/>
       <c r="I433" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J433" s="19"/>
       <c r="K433" s="20"/>
       <c r="L433" s="19"/>
       <c r="M433" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N433" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A434" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B434" s="21"/>
-      <c r="C434" s="3"/>
-      <c r="D434" s="14"/>
-      <c r="E434" s="31"/>
-      <c r="F434" s="45" t="s">
-        <v>763</v>
-      </c>
+      <c r="A434" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B434" s="1"/>
+      <c r="C434" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D434" s="13"/>
+      <c r="E434" s="30"/>
+      <c r="F434" s="43"/>
       <c r="G434" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H434" s="18"/>
       <c r="I434" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J434" s="19"/>
       <c r="K434" s="20"/>
       <c r="L434" s="19"/>
       <c r="M434" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N434" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A435" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="B435" s="1"/>
-      <c r="C435" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D435" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="E435" s="30"/>
-      <c r="F435" s="43"/>
+      <c r="A435" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B435" s="21"/>
+      <c r="C435" s="3"/>
+      <c r="D435" s="14"/>
+      <c r="E435" s="31"/>
+      <c r="F435" s="45" t="s">
+        <v>763</v>
+      </c>
       <c r="G435" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H435" s="18"/>
       <c r="I435" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J435" s="19"/>
       <c r="K435" s="20"/>
       <c r="L435" s="19"/>
       <c r="M435" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N435" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A436" s="4" t="s">
-        <v>251</v>
+        <v>353</v>
       </c>
       <c r="B436" s="1"/>
       <c r="C436" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D436" s="13"/>
+      <c r="D436" s="13" t="s">
+        <v>422</v>
+      </c>
       <c r="E436" s="30"/>
       <c r="F436" s="43"/>
       <c r="G436" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H436" s="18"/>
       <c r="I436" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J436" s="19"/>
       <c r="K436" s="20"/>
       <c r="L436" s="19"/>
       <c r="M436" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N436" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A437" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B437" s="21"/>
-      <c r="C437" s="3"/>
-      <c r="D437" s="14"/>
-      <c r="E437" s="31"/>
-      <c r="F437" s="45" t="s">
-        <v>764</v>
-      </c>
+      <c r="A437" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B437" s="1"/>
+      <c r="C437" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D437" s="13"/>
+      <c r="E437" s="30"/>
+      <c r="F437" s="43"/>
       <c r="G437" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H437" s="18"/>
       <c r="I437" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J437" s="19"/>
       <c r="K437" s="20"/>
       <c r="L437" s="19"/>
       <c r="M437" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N437" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A438" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B438" s="1"/>
-      <c r="C438" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D438" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="E438" s="30"/>
-      <c r="F438" s="43"/>
+      <c r="A438" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B438" s="21"/>
+      <c r="C438" s="3"/>
+      <c r="D438" s="14"/>
+      <c r="E438" s="31"/>
+      <c r="F438" s="45" t="s">
+        <v>764</v>
+      </c>
       <c r="G438" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H438" s="18"/>
       <c r="I438" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J438" s="19"/>
       <c r="K438" s="20"/>
       <c r="L438" s="19"/>
+      <c r="M438" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="N438" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
     </row>
     <row r="439" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B439" s="1"/>
       <c r="C439" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D439" s="13" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="E439" s="30"/>
       <c r="F439" s="43"/>
       <c r="G439" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H439" s="18"/>
       <c r="I439" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J439" s="19"/>
       <c r="K439" s="20"/>
       <c r="L439" s="19"/>
-      <c r="M439" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N439" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
     </row>
     <row r="440" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A440" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B440" s="21"/>
-      <c r="C440" s="3"/>
-      <c r="D440" s="14" t="s">
-        <v>760</v>
-      </c>
-      <c r="E440" s="31"/>
-      <c r="F440" s="45" t="s">
-        <v>766</v>
-      </c>
+      <c r="A440" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B440" s="1"/>
+      <c r="C440" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D440" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="E440" s="30"/>
+      <c r="F440" s="43"/>
       <c r="G440" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H440" s="18"/>
       <c r="I440" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J440" s="19"/>
       <c r="K440" s="20"/>
       <c r="L440" s="19"/>
       <c r="M440" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N440" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A441" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B441" s="1"/>
-      <c r="C441" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D441" s="13"/>
-      <c r="E441" s="30"/>
-      <c r="F441" s="43"/>
+      <c r="A441" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B441" s="21"/>
+      <c r="C441" s="3"/>
+      <c r="D441" s="14" t="s">
+        <v>760</v>
+      </c>
+      <c r="E441" s="31"/>
+      <c r="F441" s="45" t="s">
+        <v>766</v>
+      </c>
       <c r="G441" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H441" s="18"/>
       <c r="I441" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J441" s="19"/>
       <c r="K441" s="20"/>
       <c r="L441" s="19"/>
       <c r="M441" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N441" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
-        <v>404</v>
+        <v>252</v>
       </c>
       <c r="B442" s="1"/>
       <c r="C442" s="5" t="s">
@@ -17712,613 +17714,613 @@
       <c r="E442" s="30"/>
       <c r="F442" s="43"/>
       <c r="G442" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H442" s="18"/>
       <c r="I442" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J442" s="19"/>
       <c r="K442" s="20"/>
       <c r="L442" s="19"/>
       <c r="M442" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N442" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
-        <v>151</v>
+        <v>404</v>
       </c>
       <c r="B443" s="1"/>
       <c r="C443" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D443" s="13" t="s">
-        <v>422</v>
-      </c>
+      <c r="D443" s="13"/>
       <c r="E443" s="30"/>
       <c r="F443" s="43"/>
       <c r="G443" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H443" s="18"/>
       <c r="I443" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J443" s="19"/>
       <c r="K443" s="20"/>
       <c r="L443" s="19"/>
       <c r="M443" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N443" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B444" s="1"/>
       <c r="C444" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D444" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="E444" s="30">
-        <v>16.579999999999998</v>
-      </c>
-      <c r="F444" s="46"/>
+        <v>422</v>
+      </c>
+      <c r="E444" s="30"/>
+      <c r="F444" s="43"/>
       <c r="G444" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H444" s="18"/>
       <c r="I444" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J444" s="19"/>
       <c r="K444" s="20"/>
       <c r="L444" s="19"/>
       <c r="M444" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N444" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B445" s="1"/>
       <c r="C445" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D445" s="13" t="s">
-        <v>430</v>
+        <v>493</v>
       </c>
       <c r="E445" s="30">
-        <v>11</v>
-      </c>
-      <c r="F445" s="43"/>
+        <v>16.579999999999998</v>
+      </c>
+      <c r="F445" s="46"/>
       <c r="G445" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H445" s="18"/>
       <c r="I445" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J445" s="19"/>
       <c r="K445" s="20"/>
       <c r="L445" s="19"/>
       <c r="M445" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N445" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B446" s="1"/>
       <c r="C446" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D446" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="E446" s="30"/>
+        <v>430</v>
+      </c>
+      <c r="E446" s="30">
+        <v>11</v>
+      </c>
       <c r="F446" s="43"/>
       <c r="G446" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H446" s="18"/>
       <c r="I446" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J446" s="19"/>
       <c r="K446" s="20"/>
       <c r="L446" s="19"/>
       <c r="M446" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N446" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A447" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="B447" s="21"/>
-      <c r="C447" s="3"/>
-      <c r="D447" s="14" t="s">
-        <v>488</v>
-      </c>
-      <c r="E447" s="31"/>
-      <c r="F447" s="45" t="s">
-        <v>767</v>
-      </c>
+      <c r="A447" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B447" s="1"/>
+      <c r="C447" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D447" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="E447" s="30"/>
+      <c r="F447" s="43"/>
       <c r="G447" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H447" s="18"/>
       <c r="I447" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J447" s="19"/>
       <c r="K447" s="20"/>
       <c r="L447" s="19"/>
       <c r="M447" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N447" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A448" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B448" s="1"/>
-      <c r="C448" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D448" s="13"/>
-      <c r="E448" s="30"/>
-      <c r="F448" s="43"/>
+      <c r="A448" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B448" s="21"/>
+      <c r="C448" s="3"/>
+      <c r="D448" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="E448" s="31"/>
+      <c r="F448" s="45" t="s">
+        <v>767</v>
+      </c>
       <c r="G448" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H448" s="18"/>
       <c r="I448" s="19">
-        <f t="shared" si="30"/>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J448" s="19"/>
       <c r="K448" s="20"/>
       <c r="L448" s="19"/>
       <c r="M448" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N448" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
-        <v>495</v>
+        <v>155</v>
       </c>
       <c r="B449" s="1"/>
       <c r="C449" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D449" s="13" t="s">
-        <v>801</v>
-      </c>
-      <c r="E449" s="30">
-        <v>9</v>
-      </c>
-      <c r="F449" s="46" t="s">
-        <v>794</v>
-      </c>
+      <c r="D449" s="13"/>
+      <c r="E449" s="30"/>
+      <c r="F449" s="43"/>
       <c r="G449" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H449" s="18"/>
       <c r="I449" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J449" s="19"/>
       <c r="K449" s="20"/>
       <c r="L449" s="19"/>
       <c r="M449" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N449" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
-        <v>405</v>
+        <v>495</v>
       </c>
       <c r="B450" s="1"/>
       <c r="C450" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D450" s="13"/>
+      <c r="D450" s="13" t="s">
+        <v>801</v>
+      </c>
       <c r="E450" s="30">
-        <v>10</v>
-      </c>
-      <c r="F450" s="43"/>
+        <v>9</v>
+      </c>
+      <c r="F450" s="46" t="s">
+        <v>794</v>
+      </c>
       <c r="G450" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H450" s="18"/>
       <c r="I450" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J450" s="19"/>
       <c r="K450" s="20"/>
       <c r="L450" s="19"/>
       <c r="M450" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N450" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
-        <v>264</v>
+        <v>405</v>
       </c>
       <c r="B451" s="1"/>
       <c r="C451" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D451" s="13"/>
-      <c r="E451" s="30"/>
+      <c r="E451" s="30">
+        <v>10</v>
+      </c>
       <c r="F451" s="43"/>
       <c r="G451" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H451" s="18"/>
       <c r="I451" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J451" s="19"/>
       <c r="K451" s="20"/>
       <c r="L451" s="19"/>
       <c r="M451" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N451" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
-        <v>156</v>
+        <v>264</v>
       </c>
       <c r="B452" s="1"/>
       <c r="C452" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D452" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="E452" s="30">
-        <v>8.83</v>
-      </c>
+      <c r="D452" s="13"/>
+      <c r="E452" s="30"/>
       <c r="F452" s="43"/>
       <c r="G452" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H452" s="18"/>
       <c r="I452" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J452" s="19"/>
       <c r="K452" s="20"/>
       <c r="L452" s="19"/>
       <c r="M452" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N452" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
-        <v>388</v>
+        <v>156</v>
       </c>
       <c r="B453" s="1"/>
       <c r="C453" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D453" s="13" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="E453" s="30">
-        <v>20</v>
-      </c>
-      <c r="F453" s="43">
-        <v>15</v>
-      </c>
+        <v>8.83</v>
+      </c>
+      <c r="F453" s="43"/>
       <c r="G453" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H453" s="18"/>
       <c r="I453" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="J453" s="19"/>
       <c r="K453" s="20"/>
       <c r="L453" s="19"/>
       <c r="M453" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N453" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A454" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B454" s="21"/>
-      <c r="C454" s="3"/>
-      <c r="D454" s="14"/>
-      <c r="E454" s="31"/>
-      <c r="F454" s="45" t="s">
-        <v>768</v>
+      <c r="A454" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B454" s="1"/>
+      <c r="C454" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D454" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E454" s="30">
+        <v>20</v>
+      </c>
+      <c r="F454" s="43">
+        <v>15</v>
       </c>
       <c r="G454" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H454" s="18"/>
       <c r="I454" s="19">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>1</v>
       </c>
       <c r="J454" s="19"/>
       <c r="K454" s="20"/>
       <c r="L454" s="19"/>
       <c r="M454" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N454" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A455" s="63" t="s">
-        <v>469</v>
-      </c>
-      <c r="B455" s="64"/>
-      <c r="C455" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="D455" s="66" t="s">
-        <v>456</v>
-      </c>
-      <c r="E455" s="67">
-        <v>8</v>
-      </c>
-      <c r="F455" s="68"/>
+      <c r="A455" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B455" s="21"/>
+      <c r="C455" s="3"/>
+      <c r="D455" s="14"/>
+      <c r="E455" s="31"/>
+      <c r="F455" s="45" t="s">
+        <v>768</v>
+      </c>
       <c r="G455" s="20">
-        <f t="shared" ref="G455:G511" si="33">COUNTA(A455)</f>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H455" s="18"/>
       <c r="I455" s="19">
-        <f t="shared" ref="I455:I511" si="34">COUNTA(C455)</f>
-        <v>1</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
       <c r="J455" s="19"/>
       <c r="K455" s="20"/>
       <c r="L455" s="19"/>
       <c r="M455" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N455" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A456" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="B456" s="1"/>
-      <c r="C456" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D456" s="13"/>
-      <c r="E456" s="30"/>
-      <c r="F456" s="43"/>
+      <c r="A456" s="63" t="s">
+        <v>469</v>
+      </c>
+      <c r="B456" s="64"/>
+      <c r="C456" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D456" s="66" t="s">
+        <v>456</v>
+      </c>
+      <c r="E456" s="67">
+        <v>8</v>
+      </c>
+      <c r="F456" s="68"/>
       <c r="G456" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="G456:G512" si="37">COUNTA(A456)</f>
         <v>1</v>
       </c>
       <c r="H456" s="18"/>
       <c r="I456" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="I456:I512" si="38">COUNTA(C456)</f>
         <v>1</v>
       </c>
       <c r="J456" s="19"/>
       <c r="K456" s="20"/>
       <c r="L456" s="19"/>
       <c r="M456" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N456" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A457" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="B457" s="64"/>
-      <c r="C457" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="D457" s="66" t="s">
-        <v>430</v>
-      </c>
-      <c r="E457" s="67">
-        <v>14</v>
-      </c>
-      <c r="F457" s="68"/>
+      <c r="A457" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B457" s="1"/>
+      <c r="C457" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D457" s="13"/>
+      <c r="E457" s="30"/>
+      <c r="F457" s="43"/>
       <c r="G457" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H457" s="18"/>
       <c r="I457" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J457" s="19"/>
       <c r="K457" s="20"/>
       <c r="L457" s="19"/>
       <c r="M457" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N457" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A458" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="B458" s="39"/>
-      <c r="C458" s="40"/>
-      <c r="D458" s="41"/>
-      <c r="E458" s="42"/>
-      <c r="F458" s="72" t="s">
-        <v>724</v>
-      </c>
+      <c r="A458" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="B458" s="64"/>
+      <c r="C458" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D458" s="66" t="s">
+        <v>430</v>
+      </c>
+      <c r="E458" s="67">
+        <v>14</v>
+      </c>
+      <c r="F458" s="68"/>
       <c r="G458" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H458" s="18"/>
       <c r="I458" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J458" s="19"/>
       <c r="K458" s="20"/>
       <c r="L458" s="19"/>
       <c r="M458" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N458" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A459" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="B459" s="1"/>
-      <c r="C459" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D459" s="13"/>
-      <c r="E459" s="30"/>
-      <c r="F459" s="43"/>
+      <c r="A459" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="B459" s="39"/>
+      <c r="C459" s="40"/>
+      <c r="D459" s="41"/>
+      <c r="E459" s="42"/>
+      <c r="F459" s="72" t="s">
+        <v>724</v>
+      </c>
       <c r="G459" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H459" s="18"/>
       <c r="I459" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J459" s="19"/>
       <c r="K459" s="20"/>
       <c r="L459" s="19"/>
       <c r="M459" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N459" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
-        <v>159</v>
+        <v>377</v>
       </c>
       <c r="B460" s="1"/>
       <c r="C460" s="5" t="s">
@@ -18328,151 +18330,159 @@
       <c r="E460" s="30"/>
       <c r="F460" s="43"/>
       <c r="G460" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H460" s="18"/>
       <c r="I460" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J460" s="19"/>
       <c r="K460" s="20"/>
       <c r="L460" s="19"/>
       <c r="M460" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N460" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A461" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="B461" s="21"/>
-      <c r="C461" s="3"/>
-      <c r="D461" s="14"/>
-      <c r="E461" s="31"/>
-      <c r="F461" s="45" t="s">
-        <v>771</v>
-      </c>
+      <c r="A461" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B461" s="1"/>
+      <c r="C461" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D461" s="13"/>
+      <c r="E461" s="30"/>
+      <c r="F461" s="43"/>
       <c r="G461" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H461" s="18"/>
       <c r="I461" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J461" s="19"/>
       <c r="K461" s="20"/>
       <c r="L461" s="19"/>
       <c r="M461" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N461" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>160</v>
+        <v>505</v>
       </c>
       <c r="B462" s="21"/>
       <c r="C462" s="3"/>
       <c r="D462" s="14"/>
       <c r="E462" s="31"/>
       <c r="F462" s="45" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G462" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H462" s="18"/>
       <c r="I462" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J462" s="19"/>
       <c r="K462" s="20"/>
       <c r="L462" s="19"/>
       <c r="M462" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N462" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="B463" s="21"/>
       <c r="C463" s="3"/>
-      <c r="D463" s="14" t="s">
-        <v>773</v>
-      </c>
+      <c r="D463" s="14"/>
       <c r="E463" s="31"/>
       <c r="F463" s="45" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G463" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H463" s="18"/>
       <c r="I463" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J463" s="19"/>
       <c r="K463" s="20"/>
       <c r="L463" s="19"/>
       <c r="M463" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N463" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A464" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="B464" s="1"/>
-      <c r="C464" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D464" s="13"/>
-      <c r="E464" s="30"/>
-      <c r="F464" s="43"/>
+      <c r="A464" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B464" s="21"/>
+      <c r="C464" s="3"/>
+      <c r="D464" s="14" t="s">
+        <v>773</v>
+      </c>
+      <c r="E464" s="31"/>
+      <c r="F464" s="45" t="s">
+        <v>774</v>
+      </c>
       <c r="G464" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H464" s="18"/>
       <c r="I464" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J464" s="19"/>
       <c r="K464" s="20"/>
       <c r="L464" s="19"/>
+      <c r="M464" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="N464" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
     </row>
     <row r="465" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
-        <v>186</v>
+        <v>420</v>
       </c>
       <c r="B465" s="1"/>
       <c r="C465" s="5" t="s">
@@ -18482,359 +18492,351 @@
       <c r="E465" s="30"/>
       <c r="F465" s="43"/>
       <c r="G465" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H465" s="18"/>
       <c r="I465" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J465" s="19"/>
       <c r="K465" s="20"/>
       <c r="L465" s="19"/>
-      <c r="M465" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N465" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
     </row>
     <row r="466" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A466" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B466" s="21"/>
-      <c r="C466" s="3"/>
-      <c r="D466" s="14"/>
-      <c r="E466" s="31"/>
-      <c r="F466" s="45" t="s">
-        <v>775</v>
-      </c>
+      <c r="A466" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B466" s="1"/>
+      <c r="C466" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D466" s="13"/>
+      <c r="E466" s="30"/>
+      <c r="F466" s="43"/>
       <c r="G466" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H466" s="18"/>
       <c r="I466" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J466" s="19"/>
       <c r="K466" s="20"/>
       <c r="L466" s="19"/>
       <c r="M466" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N466" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A467" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="B467" s="1"/>
-      <c r="C467" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D467" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E467" s="30"/>
-      <c r="F467" s="43"/>
+      <c r="A467" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B467" s="21"/>
+      <c r="C467" s="3"/>
+      <c r="D467" s="14"/>
+      <c r="E467" s="31"/>
+      <c r="F467" s="45" t="s">
+        <v>775</v>
+      </c>
       <c r="G467" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H467" s="18"/>
       <c r="I467" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J467" s="19"/>
       <c r="K467" s="20"/>
       <c r="L467" s="19"/>
       <c r="M467" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N467" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
-        <v>161</v>
+        <v>472</v>
       </c>
       <c r="B468" s="1"/>
       <c r="C468" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D468" s="13"/>
+      <c r="D468" s="13" t="s">
+        <v>430</v>
+      </c>
       <c r="E468" s="30"/>
       <c r="F468" s="43"/>
       <c r="G468" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H468" s="18"/>
       <c r="I468" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J468" s="19"/>
       <c r="K468" s="20"/>
       <c r="L468" s="19"/>
       <c r="M468" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N468" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A469" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B469" s="21"/>
-      <c r="C469" s="3"/>
-      <c r="D469" s="14" t="s">
-        <v>777</v>
-      </c>
-      <c r="E469" s="31"/>
-      <c r="F469" s="45" t="s">
-        <v>776</v>
-      </c>
+      <c r="A469" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B469" s="1"/>
+      <c r="C469" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D469" s="13"/>
+      <c r="E469" s="30"/>
+      <c r="F469" s="43"/>
       <c r="G469" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H469" s="18"/>
       <c r="I469" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J469" s="19"/>
       <c r="K469" s="20"/>
       <c r="L469" s="19"/>
       <c r="M469" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N469" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A470" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B470" s="1"/>
-      <c r="C470" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D470" s="13" t="s">
-        <v>511</v>
-      </c>
-      <c r="E470" s="30">
-        <v>28</v>
-      </c>
-      <c r="F470" s="43"/>
+      <c r="A470" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B470" s="21"/>
+      <c r="C470" s="3"/>
+      <c r="D470" s="14" t="s">
+        <v>777</v>
+      </c>
+      <c r="E470" s="31"/>
+      <c r="F470" s="45" t="s">
+        <v>776</v>
+      </c>
       <c r="G470" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H470" s="18"/>
       <c r="I470" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J470" s="19"/>
       <c r="K470" s="20"/>
       <c r="L470" s="19"/>
       <c r="M470" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N470" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A471" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="B471" s="21"/>
-      <c r="C471" s="3"/>
-      <c r="D471" s="14"/>
-      <c r="E471" s="31"/>
-      <c r="F471" s="45" t="s">
-        <v>778</v>
-      </c>
+      <c r="A471" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B471" s="1"/>
+      <c r="C471" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D471" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="E471" s="30">
+        <v>28</v>
+      </c>
+      <c r="F471" s="43"/>
       <c r="G471" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H471" s="18"/>
       <c r="I471" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J471" s="19"/>
       <c r="K471" s="20"/>
       <c r="L471" s="19"/>
       <c r="M471" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N471" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A472" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="B472" s="1"/>
-      <c r="C472" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D472" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E472" s="30"/>
-      <c r="F472" s="43"/>
+      <c r="A472" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B472" s="21"/>
+      <c r="C472" s="3"/>
+      <c r="D472" s="14"/>
+      <c r="E472" s="31"/>
+      <c r="F472" s="45" t="s">
+        <v>778</v>
+      </c>
       <c r="G472" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H472" s="18"/>
       <c r="I472" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J472" s="19"/>
       <c r="K472" s="20"/>
       <c r="L472" s="19"/>
       <c r="M472" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N472" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A473" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B473" s="21"/>
-      <c r="C473" s="3"/>
-      <c r="D473" s="14"/>
-      <c r="E473" s="31"/>
-      <c r="F473" s="45" t="s">
-        <v>779</v>
-      </c>
+      <c r="A473" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B473" s="1"/>
+      <c r="C473" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D473" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E473" s="30"/>
+      <c r="F473" s="43"/>
       <c r="G473" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H473" s="18"/>
       <c r="I473" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J473" s="19"/>
       <c r="K473" s="20"/>
       <c r="L473" s="19"/>
       <c r="M473" t="str">
-        <f t="shared" ref="M473:M511" si="35">IF(B473=1,E473,"")</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N473" t="str">
-        <f t="shared" ref="N473:N511" si="36">IF(B473=2,E473,"")</f>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>780</v>
+        <v>319</v>
       </c>
       <c r="B474" s="21"/>
       <c r="C474" s="3"/>
       <c r="D474" s="14"/>
       <c r="E474" s="31"/>
       <c r="F474" s="45" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G474" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H474" s="18"/>
       <c r="I474" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J474" s="19"/>
       <c r="K474" s="20"/>
       <c r="L474" s="19"/>
       <c r="M474" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="M474:M512" si="39">IF(B474=1,E474,"")</f>
         <v/>
       </c>
       <c r="N474" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="N474:N512" si="40">IF(B474=2,E474,"")</f>
         <v/>
       </c>
     </row>
     <row r="475" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A475" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B475" s="1"/>
-      <c r="C475" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D475" s="13"/>
-      <c r="E475" s="30"/>
-      <c r="F475" s="43"/>
+      <c r="A475" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B475" s="21"/>
+      <c r="C475" s="3"/>
+      <c r="D475" s="14"/>
+      <c r="E475" s="31"/>
+      <c r="F475" s="45" t="s">
+        <v>781</v>
+      </c>
       <c r="G475" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H475" s="18"/>
       <c r="I475" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J475" s="19"/>
       <c r="K475" s="20"/>
       <c r="L475" s="19"/>
       <c r="M475" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N475" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A476" s="4" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
       <c r="B476" s="1"/>
       <c r="C476" s="5" t="s">
@@ -18844,319 +18846,327 @@
       <c r="E476" s="30"/>
       <c r="F476" s="43"/>
       <c r="G476" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H476" s="18"/>
       <c r="I476" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J476" s="19"/>
       <c r="K476" s="20"/>
       <c r="L476" s="19"/>
       <c r="M476" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N476" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
-        <v>506</v>
+        <v>214</v>
       </c>
       <c r="B477" s="1"/>
       <c r="C477" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D477" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="E477" s="30">
-        <v>13.43</v>
-      </c>
+      <c r="D477" s="13"/>
+      <c r="E477" s="30"/>
       <c r="F477" s="43"/>
       <c r="G477" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H477" s="18"/>
       <c r="I477" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J477" s="19"/>
       <c r="K477" s="20"/>
       <c r="L477" s="19"/>
       <c r="M477" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N477" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
-        <v>253</v>
+        <v>506</v>
       </c>
       <c r="B478" s="1"/>
       <c r="C478" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D478" s="13"/>
-      <c r="E478" s="30"/>
+      <c r="D478" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E478" s="30">
+        <v>13.43</v>
+      </c>
       <c r="F478" s="43"/>
       <c r="G478" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H478" s="18"/>
       <c r="I478" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J478" s="19"/>
       <c r="K478" s="20"/>
       <c r="L478" s="19"/>
       <c r="M478" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N478" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A479" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B479" s="21"/>
-      <c r="C479" s="3"/>
-      <c r="D479" s="14"/>
-      <c r="E479" s="31"/>
-      <c r="F479" s="45" t="s">
-        <v>782</v>
-      </c>
+      <c r="A479" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B479" s="1"/>
+      <c r="C479" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D479" s="13"/>
+      <c r="E479" s="30"/>
+      <c r="F479" s="43"/>
       <c r="G479" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H479" s="18"/>
       <c r="I479" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J479" s="19"/>
       <c r="K479" s="20"/>
       <c r="L479" s="19"/>
       <c r="M479" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N479" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A480" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="B480" s="1"/>
-      <c r="C480" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D480" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E480" s="30">
-        <v>29</v>
-      </c>
-      <c r="F480" s="43"/>
+      <c r="A480" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B480" s="21"/>
+      <c r="C480" s="3"/>
+      <c r="D480" s="14"/>
+      <c r="E480" s="31"/>
+      <c r="F480" s="45" t="s">
+        <v>782</v>
+      </c>
       <c r="G480" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H480" s="18"/>
       <c r="I480" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J480" s="19"/>
       <c r="K480" s="20"/>
       <c r="L480" s="19"/>
+      <c r="M480" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="N480" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
     </row>
     <row r="481" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
-        <v>254</v>
+        <v>479</v>
       </c>
       <c r="B481" s="1"/>
       <c r="C481" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D481" s="13" t="s">
-        <v>783</v>
-      </c>
-      <c r="E481" s="30"/>
+        <v>430</v>
+      </c>
+      <c r="E481" s="30">
+        <v>29</v>
+      </c>
       <c r="F481" s="43"/>
       <c r="G481" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H481" s="18"/>
       <c r="I481" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J481" s="19"/>
       <c r="K481" s="20"/>
       <c r="L481" s="19"/>
-      <c r="M481" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N481" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
     </row>
     <row r="482" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
-        <v>528</v>
+        <v>254</v>
       </c>
       <c r="B482" s="1"/>
       <c r="C482" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D482" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E482" s="30">
-        <v>15</v>
-      </c>
-      <c r="F482" s="43">
-        <v>40</v>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="E482" s="30"/>
+      <c r="F482" s="43"/>
       <c r="G482" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H482" s="18"/>
       <c r="I482" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J482" s="19"/>
       <c r="K482" s="20"/>
       <c r="L482" s="19"/>
       <c r="M482" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N482" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A483" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B483" s="21"/>
-      <c r="C483" s="3"/>
-      <c r="D483" s="14" t="s">
-        <v>785</v>
-      </c>
-      <c r="E483" s="31"/>
-      <c r="F483" s="45" t="s">
-        <v>784</v>
+      <c r="A483" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B483" s="1"/>
+      <c r="C483" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D483" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E483" s="30">
+        <v>15</v>
+      </c>
+      <c r="F483" s="43">
+        <v>40</v>
       </c>
       <c r="G483" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H483" s="18"/>
       <c r="I483" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J483" s="19"/>
       <c r="K483" s="20"/>
       <c r="L483" s="19"/>
       <c r="M483" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N483" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>162</v>
+        <v>326</v>
       </c>
       <c r="B484" s="21"/>
       <c r="C484" s="3"/>
-      <c r="D484" s="14"/>
+      <c r="D484" s="14" t="s">
+        <v>785</v>
+      </c>
       <c r="E484" s="31"/>
       <c r="F484" s="45" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G484" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H484" s="18"/>
       <c r="I484" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J484" s="19"/>
       <c r="K484" s="20"/>
       <c r="L484" s="19"/>
       <c r="M484" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N484" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A485" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B485" s="1"/>
-      <c r="C485" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D485" s="13"/>
-      <c r="E485" s="30"/>
-      <c r="F485" s="43"/>
+      <c r="A485" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B485" s="21"/>
+      <c r="C485" s="3"/>
+      <c r="D485" s="14"/>
+      <c r="E485" s="31"/>
+      <c r="F485" s="45" t="s">
+        <v>786</v>
+      </c>
       <c r="G485" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H485" s="18"/>
       <c r="I485" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J485" s="19"/>
       <c r="K485" s="20"/>
       <c r="L485" s="19"/>
+      <c r="M485" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="N485" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
     </row>
     <row r="486" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
-        <v>231</v>
+        <v>163</v>
       </c>
       <c r="B486" s="1"/>
       <c r="C486" s="5" t="s">
@@ -19166,29 +19176,21 @@
       <c r="E486" s="30"/>
       <c r="F486" s="43"/>
       <c r="G486" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H486" s="18"/>
       <c r="I486" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J486" s="19"/>
       <c r="K486" s="20"/>
       <c r="L486" s="19"/>
-      <c r="M486" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N486" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
     </row>
     <row r="487" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="B487" s="1"/>
       <c r="C487" s="5" t="s">
@@ -19196,65 +19198,63 @@
       </c>
       <c r="D487" s="13"/>
       <c r="E487" s="30"/>
-      <c r="F487" s="46"/>
+      <c r="F487" s="43"/>
       <c r="G487" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H487" s="18"/>
       <c r="I487" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J487" s="19"/>
       <c r="K487" s="20"/>
       <c r="L487" s="19"/>
       <c r="M487" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N487" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B488" s="1"/>
       <c r="C488" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D488" s="13" t="s">
-        <v>422</v>
-      </c>
+      <c r="D488" s="13"/>
       <c r="E488" s="30"/>
-      <c r="F488" s="43"/>
+      <c r="F488" s="46"/>
       <c r="G488" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H488" s="18"/>
       <c r="I488" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J488" s="19"/>
       <c r="K488" s="20"/>
       <c r="L488" s="19"/>
       <c r="M488" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N488" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B489" s="1"/>
       <c r="C489" s="5" t="s">
@@ -19266,93 +19266,95 @@
       <c r="E489" s="30"/>
       <c r="F489" s="43"/>
       <c r="G489" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H489" s="18"/>
       <c r="I489" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J489" s="19"/>
       <c r="K489" s="20"/>
       <c r="L489" s="19"/>
       <c r="M489" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N489" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A490" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="B490" s="21"/>
-      <c r="C490" s="3"/>
-      <c r="D490" s="14"/>
-      <c r="E490" s="31"/>
-      <c r="F490" s="45" t="s">
-        <v>787</v>
-      </c>
+      <c r="A490" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B490" s="1"/>
+      <c r="C490" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D490" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="E490" s="30"/>
+      <c r="F490" s="43"/>
       <c r="G490" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H490" s="18"/>
       <c r="I490" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J490" s="19"/>
       <c r="K490" s="20"/>
       <c r="L490" s="19"/>
       <c r="M490" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N490" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A491" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B491" s="1"/>
-      <c r="C491" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D491" s="13"/>
-      <c r="E491" s="30"/>
-      <c r="F491" s="43"/>
+      <c r="A491" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B491" s="21"/>
+      <c r="C491" s="3"/>
+      <c r="D491" s="14"/>
+      <c r="E491" s="31"/>
+      <c r="F491" s="45" t="s">
+        <v>787</v>
+      </c>
       <c r="G491" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H491" s="18"/>
       <c r="I491" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J491" s="19"/>
       <c r="K491" s="20"/>
       <c r="L491" s="19"/>
       <c r="M491" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N491" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
-        <v>371</v>
+        <v>311</v>
       </c>
       <c r="B492" s="1"/>
       <c r="C492" s="5" t="s">
@@ -19362,29 +19364,29 @@
       <c r="E492" s="30"/>
       <c r="F492" s="43"/>
       <c r="G492" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H492" s="18"/>
       <c r="I492" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J492" s="19"/>
       <c r="K492" s="20"/>
       <c r="L492" s="19"/>
       <c r="M492" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N492" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
-        <v>7</v>
+        <v>371</v>
       </c>
       <c r="B493" s="1"/>
       <c r="C493" s="5" t="s">
@@ -19394,29 +19396,29 @@
       <c r="E493" s="30"/>
       <c r="F493" s="43"/>
       <c r="G493" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H493" s="18"/>
       <c r="I493" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J493" s="19"/>
       <c r="K493" s="20"/>
       <c r="L493" s="19"/>
       <c r="M493" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N493" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A494" s="4" t="s">
-        <v>255</v>
+        <v>7</v>
       </c>
       <c r="B494" s="1"/>
       <c r="C494" s="5" t="s">
@@ -19426,295 +19428,295 @@
       <c r="E494" s="30"/>
       <c r="F494" s="43"/>
       <c r="G494" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H494" s="18"/>
       <c r="I494" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J494" s="19"/>
       <c r="K494" s="20"/>
       <c r="L494" s="19"/>
       <c r="M494" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N494" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A495" s="4" t="s">
-        <v>167</v>
+        <v>255</v>
       </c>
       <c r="B495" s="1"/>
       <c r="C495" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D495" s="13" t="s">
-        <v>401</v>
-      </c>
+      <c r="D495" s="13"/>
       <c r="E495" s="30"/>
       <c r="F495" s="43"/>
       <c r="G495" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H495" s="18"/>
       <c r="I495" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J495" s="19"/>
       <c r="K495" s="20"/>
       <c r="L495" s="19"/>
       <c r="M495" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N495" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A496" s="4" t="s">
-        <v>331</v>
+        <v>167</v>
       </c>
       <c r="B496" s="1"/>
       <c r="C496" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D496" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="E496" s="30">
-        <v>10</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="E496" s="30"/>
       <c r="F496" s="43"/>
       <c r="G496" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H496" s="18"/>
       <c r="I496" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J496" s="19"/>
       <c r="K496" s="20"/>
       <c r="L496" s="19"/>
       <c r="M496" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N496" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="B497" s="1"/>
       <c r="C497" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D497" s="13"/>
-      <c r="E497" s="30"/>
+      <c r="D497" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E497" s="30">
+        <v>10</v>
+      </c>
       <c r="F497" s="43"/>
       <c r="G497" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H497" s="18"/>
       <c r="I497" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J497" s="19"/>
       <c r="K497" s="20"/>
       <c r="L497" s="19"/>
       <c r="M497" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N497" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A498" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B498" s="21"/>
-      <c r="C498" s="3"/>
-      <c r="D498" s="14"/>
-      <c r="E498" s="31"/>
-      <c r="F498" s="45" t="s">
-        <v>788</v>
-      </c>
+      <c r="A498" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B498" s="1"/>
+      <c r="C498" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D498" s="13"/>
+      <c r="E498" s="30"/>
+      <c r="F498" s="43"/>
       <c r="G498" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H498" s="18"/>
       <c r="I498" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J498" s="19"/>
       <c r="K498" s="20"/>
       <c r="L498" s="19"/>
       <c r="M498" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N498" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A499" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B499" s="1"/>
-      <c r="C499" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D499" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="E499" s="30">
-        <v>19</v>
-      </c>
-      <c r="F499" s="43"/>
+      <c r="A499" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B499" s="21"/>
+      <c r="C499" s="3"/>
+      <c r="D499" s="14"/>
+      <c r="E499" s="31"/>
+      <c r="F499" s="45" t="s">
+        <v>788</v>
+      </c>
       <c r="G499" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H499" s="18"/>
       <c r="I499" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J499" s="19"/>
       <c r="K499" s="20"/>
       <c r="L499" s="19"/>
       <c r="M499" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N499" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A500" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B500" s="1"/>
       <c r="C500" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D500" s="13"/>
-      <c r="E500" s="30"/>
+      <c r="D500" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="E500" s="30">
+        <v>19</v>
+      </c>
       <c r="F500" s="43"/>
       <c r="G500" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H500" s="18"/>
       <c r="I500" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J500" s="19"/>
       <c r="K500" s="20"/>
       <c r="L500" s="19"/>
       <c r="M500" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N500" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A501" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B501" s="21"/>
-      <c r="C501" s="3"/>
-      <c r="D501" s="14"/>
-      <c r="E501" s="31"/>
-      <c r="F501" s="45" t="s">
-        <v>789</v>
-      </c>
+      <c r="A501" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B501" s="1"/>
+      <c r="C501" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D501" s="13"/>
+      <c r="E501" s="30"/>
+      <c r="F501" s="43"/>
       <c r="G501" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H501" s="18"/>
       <c r="I501" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J501" s="19"/>
       <c r="K501" s="20"/>
       <c r="L501" s="19"/>
       <c r="M501" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N501" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A502" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B502" s="1"/>
-      <c r="C502" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D502" s="13"/>
-      <c r="E502" s="30"/>
-      <c r="F502" s="43"/>
+      <c r="A502" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B502" s="21"/>
+      <c r="C502" s="3"/>
+      <c r="D502" s="14"/>
+      <c r="E502" s="31"/>
+      <c r="F502" s="45" t="s">
+        <v>789</v>
+      </c>
       <c r="G502" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H502" s="18"/>
       <c r="I502" s="19">
-        <f t="shared" si="34"/>
-        <v>1</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
       </c>
       <c r="J502" s="19"/>
       <c r="K502" s="20"/>
       <c r="L502" s="19"/>
       <c r="M502" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N502" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A503" s="4" t="s">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="B503" s="1"/>
       <c r="C503" s="5" t="s">
@@ -19724,183 +19726,187 @@
       <c r="E503" s="30"/>
       <c r="F503" s="43"/>
       <c r="G503" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H503" s="18"/>
       <c r="I503" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J503" s="19"/>
       <c r="K503" s="20"/>
       <c r="L503" s="19"/>
       <c r="M503" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N503" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A504" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B504" s="1"/>
       <c r="C504" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D504" s="13" t="s">
-        <v>422</v>
-      </c>
+      <c r="D504" s="13"/>
       <c r="E504" s="30"/>
       <c r="F504" s="43"/>
       <c r="G504" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H504" s="18"/>
       <c r="I504" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="J504" s="19"/>
       <c r="K504" s="20"/>
       <c r="L504" s="19"/>
       <c r="M504" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N504" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A505" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B505" s="21"/>
-      <c r="C505" s="3"/>
-      <c r="D505" s="14"/>
-      <c r="E505" s="31"/>
-      <c r="F505" s="45" t="s">
-        <v>790</v>
-      </c>
+      <c r="A505" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B505" s="1"/>
+      <c r="C505" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D505" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="E505" s="30"/>
+      <c r="F505" s="43"/>
       <c r="G505" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H505" s="18"/>
       <c r="I505" s="19">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1</v>
       </c>
       <c r="J505" s="19"/>
       <c r="K505" s="20"/>
       <c r="L505" s="19"/>
       <c r="M505" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N505" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>274</v>
+        <v>483</v>
       </c>
       <c r="B506" s="21"/>
       <c r="C506" s="3"/>
       <c r="D506" s="14"/>
       <c r="E506" s="31"/>
       <c r="F506" s="45" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="G506" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H506" s="18"/>
       <c r="I506" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J506" s="19"/>
       <c r="K506" s="20"/>
       <c r="L506" s="19"/>
       <c r="M506" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N506" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>173</v>
+        <v>274</v>
       </c>
       <c r="B507" s="21"/>
       <c r="C507" s="3"/>
-      <c r="D507" s="14" t="s">
-        <v>793</v>
-      </c>
+      <c r="D507" s="14"/>
       <c r="E507" s="31"/>
       <c r="F507" s="45" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G507" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H507" s="18"/>
       <c r="I507" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J507" s="19"/>
       <c r="K507" s="20"/>
       <c r="L507" s="19"/>
       <c r="M507" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N507" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A508" s="34"/>
-      <c r="B508" s="25"/>
-      <c r="C508" s="35"/>
-      <c r="D508" s="36"/>
-      <c r="E508" s="37"/>
-      <c r="F508" s="44"/>
+      <c r="A508" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B508" s="21"/>
+      <c r="C508" s="3"/>
+      <c r="D508" s="14" t="s">
+        <v>793</v>
+      </c>
+      <c r="E508" s="31"/>
+      <c r="F508" s="45" t="s">
+        <v>792</v>
+      </c>
       <c r="G508" s="20">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>1</v>
       </c>
       <c r="H508" s="18"/>
       <c r="I508" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J508" s="19"/>
       <c r="K508" s="20"/>
       <c r="L508" s="19"/>
       <c r="M508" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N508" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -19912,23 +19918,23 @@
       <c r="E509" s="37"/>
       <c r="F509" s="44"/>
       <c r="G509" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="H509" s="18"/>
       <c r="I509" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J509" s="19"/>
       <c r="K509" s="20"/>
       <c r="L509" s="19"/>
       <c r="M509" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N509" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -19940,23 +19946,23 @@
       <c r="E510" s="37"/>
       <c r="F510" s="44"/>
       <c r="G510" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="H510" s="18"/>
       <c r="I510" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J510" s="19"/>
       <c r="K510" s="20"/>
       <c r="L510" s="19"/>
       <c r="M510" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N510" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -19968,51 +19974,70 @@
       <c r="E511" s="37"/>
       <c r="F511" s="44"/>
       <c r="G511" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="H511" s="18"/>
       <c r="I511" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J511" s="19"/>
       <c r="K511" s="20"/>
       <c r="L511" s="19"/>
       <c r="M511" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N511" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A512" s="48"/>
-      <c r="B512" s="50"/>
-      <c r="C512" s="48"/>
-      <c r="D512" s="52"/>
-      <c r="E512" s="54"/>
-      <c r="F512" s="57"/>
-      <c r="G512" s="78"/>
-      <c r="H512" s="24"/>
-      <c r="I512" s="75"/>
-      <c r="J512" s="24"/>
-      <c r="K512" s="24"/>
-      <c r="L512" s="24"/>
-      <c r="M512" s="23"/>
-    </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A512" s="34"/>
+      <c r="B512" s="25"/>
+      <c r="C512" s="35"/>
+      <c r="D512" s="36"/>
+      <c r="E512" s="37"/>
+      <c r="F512" s="44"/>
+      <c r="G512" s="20">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="H512" s="18"/>
+      <c r="I512" s="19">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="J512" s="19"/>
+      <c r="K512" s="20"/>
+      <c r="L512" s="19"/>
+      <c r="M512" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="N512" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A513" s="48"/>
-      <c r="B513" s="49"/>
+      <c r="B513" s="50"/>
       <c r="C513" s="48"/>
       <c r="D513" s="52"/>
-      <c r="E513" s="53"/>
-      <c r="F513" s="56"/>
-      <c r="I513" s="19"/>
-    </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E513" s="54"/>
+      <c r="F513" s="57"/>
+      <c r="G513" s="78"/>
+      <c r="H513" s="24"/>
+      <c r="I513" s="75"/>
+      <c r="J513" s="24"/>
+      <c r="K513" s="24"/>
+      <c r="L513" s="24"/>
+      <c r="M513" s="23"/>
+    </row>
+    <row r="514" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A514" s="48"/>
       <c r="B514" s="49"/>
       <c r="C514" s="48"/>
@@ -20021,7 +20046,7 @@
       <c r="F514" s="56"/>
       <c r="I514" s="19"/>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A515" s="48"/>
       <c r="B515" s="49"/>
       <c r="C515" s="48"/>
@@ -20030,7 +20055,7 @@
       <c r="F515" s="56"/>
       <c r="I515" s="19"/>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A516" s="48"/>
       <c r="B516" s="49"/>
       <c r="C516" s="48"/>
@@ -20039,7 +20064,7 @@
       <c r="F516" s="56"/>
       <c r="I516" s="19"/>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A517" s="48"/>
       <c r="B517" s="49"/>
       <c r="C517" s="48"/>
@@ -20048,7 +20073,7 @@
       <c r="F517" s="56"/>
       <c r="I517" s="19"/>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A518" s="48"/>
       <c r="B518" s="49"/>
       <c r="C518" s="48"/>
@@ -20057,7 +20082,7 @@
       <c r="F518" s="56"/>
       <c r="I518" s="19"/>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A519" s="48"/>
       <c r="B519" s="49"/>
       <c r="C519" s="48"/>
@@ -20066,7 +20091,7 @@
       <c r="F519" s="56"/>
       <c r="I519" s="19"/>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A520" s="48"/>
       <c r="B520" s="49"/>
       <c r="C520" s="48"/>
@@ -20075,7 +20100,7 @@
       <c r="F520" s="56"/>
       <c r="I520" s="19"/>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A521" s="48"/>
       <c r="B521" s="49"/>
       <c r="C521" s="48"/>
@@ -20084,7 +20109,7 @@
       <c r="F521" s="56"/>
       <c r="I521" s="19"/>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A522" s="48"/>
       <c r="B522" s="49"/>
       <c r="C522" s="48"/>
@@ -20093,7 +20118,7 @@
       <c r="F522" s="56"/>
       <c r="I522" s="19"/>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A523" s="48"/>
       <c r="B523" s="49"/>
       <c r="C523" s="48"/>
@@ -20102,7 +20127,7 @@
       <c r="F523" s="56"/>
       <c r="I523" s="19"/>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A524" s="48"/>
       <c r="B524" s="49"/>
       <c r="C524" s="48"/>
@@ -20111,7 +20136,7 @@
       <c r="F524" s="56"/>
       <c r="I524" s="19"/>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A525" s="48"/>
       <c r="B525" s="49"/>
       <c r="C525" s="48"/>
@@ -20120,7 +20145,7 @@
       <c r="F525" s="56"/>
       <c r="I525" s="19"/>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A526" s="48"/>
       <c r="B526" s="49"/>
       <c r="C526" s="48"/>
@@ -20129,7 +20154,7 @@
       <c r="F526" s="56"/>
       <c r="I526" s="19"/>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A527" s="48"/>
       <c r="B527" s="49"/>
       <c r="C527" s="48"/>
@@ -20138,7 +20163,7 @@
       <c r="F527" s="56"/>
       <c r="I527" s="19"/>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A528" s="48"/>
       <c r="B528" s="49"/>
       <c r="C528" s="48"/>
@@ -21963,6 +21988,7 @@
       <c r="D730" s="52"/>
       <c r="E730" s="53"/>
       <c r="F730" s="56"/>
+      <c r="I730" s="19"/>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" s="48"/>
@@ -21982,21 +22008,29 @@
     </row>
     <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" s="48"/>
-      <c r="B733" s="51">
-        <v>12</v>
-      </c>
+      <c r="B733" s="49"/>
       <c r="C733" s="48"/>
       <c r="D733" s="52"/>
-      <c r="E733" s="55">
-        <f>N512</f>
+      <c r="E733" s="53"/>
+      <c r="F733" s="56"/>
+    </row>
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A734" s="48"/>
+      <c r="B734" s="51">
+        <v>12</v>
+      </c>
+      <c r="C734" s="48"/>
+      <c r="D734" s="52"/>
+      <c r="E734" s="55">
+        <f>N513</f>
         <v>0</v>
       </c>
-      <c r="F733" s="56"/>
+      <c r="F734" s="56"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F733" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F733">
-      <sortCondition ref="A1:A733"/>
+  <autoFilter ref="A1:F734" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F734">
+      <sortCondition ref="A1:A734"/>
     </sortState>
   </autoFilter>
   <mergeCells count="6">
@@ -22136,96 +22170,97 @@
     <hyperlink ref="F296" r:id="rId126" xr:uid="{F8E811E4-C56E-4020-8515-CA14E5BC6E3C}"/>
     <hyperlink ref="F299" r:id="rId127" xr:uid="{8169F733-8E2D-4AC1-9A4F-A49A54D41A52}"/>
     <hyperlink ref="F302" r:id="rId128" xr:uid="{0CE762D6-744B-40A7-8F98-8AF1053C4C20}"/>
-    <hyperlink ref="F305" r:id="rId129" xr:uid="{091067F1-8D60-40C3-B79B-EDA05B5A7DA4}"/>
-    <hyperlink ref="F306" r:id="rId130" xr:uid="{AC3C0A2F-C850-4DC8-B816-62B521573541}"/>
-    <hyperlink ref="F307" r:id="rId131" xr:uid="{BD4C4423-9801-48B9-BE4A-6FA8B9B411A4}"/>
-    <hyperlink ref="F308" r:id="rId132" xr:uid="{03558391-13D5-417E-8518-5A118844CD95}"/>
-    <hyperlink ref="F311" r:id="rId133" xr:uid="{2005E731-59D7-4620-B28C-434266F6022D}"/>
-    <hyperlink ref="F312" r:id="rId134" xr:uid="{2FD5242C-CF0A-4A63-816A-EA2A83984E64}"/>
-    <hyperlink ref="F313" r:id="rId135" xr:uid="{3123CD08-C684-4CC9-AB12-F9105EA97288}"/>
-    <hyperlink ref="F314" r:id="rId136" xr:uid="{2213C59C-4A61-40A9-A06B-1FEF17A027B0}"/>
-    <hyperlink ref="F315" r:id="rId137" xr:uid="{68B28FC2-AA1F-41B6-9A23-516E9B83B6E0}"/>
-    <hyperlink ref="F317" r:id="rId138" xr:uid="{B5599032-4454-4E2C-A68F-8CFFE50F4FDA}"/>
-    <hyperlink ref="F318" r:id="rId139" xr:uid="{A0B5737A-A70A-4218-B2E1-A76C8720DB56}"/>
-    <hyperlink ref="F319" r:id="rId140" xr:uid="{D4B5840E-77B4-47E2-8436-CD2E572AF2B8}"/>
-    <hyperlink ref="F320" r:id="rId141" xr:uid="{BD67BD55-40E9-45BF-A3F6-8F5115DDB229}"/>
-    <hyperlink ref="F321" r:id="rId142" xr:uid="{006FB328-F8E9-4758-AE01-3843E2E75398}"/>
-    <hyperlink ref="F323" r:id="rId143" xr:uid="{D8274070-5E6A-448F-BE2B-E62287C27B7F}"/>
-    <hyperlink ref="F324" r:id="rId144" xr:uid="{3107A474-1B13-410C-98D5-4BDFF1B318A0}"/>
-    <hyperlink ref="F328" r:id="rId145" xr:uid="{AEE59407-C7BF-4741-8788-B6DE8B5B56F0}"/>
-    <hyperlink ref="F330" r:id="rId146" xr:uid="{9E43F2AF-CA8D-45AD-8AF2-43E79516D8C4}"/>
-    <hyperlink ref="F333" r:id="rId147" xr:uid="{527DB674-2191-4390-A5E3-AF104DB8B4DD}"/>
-    <hyperlink ref="F338" r:id="rId148" xr:uid="{6CBC3A1F-EFB9-4C79-8568-CA7B9F4AE2C5}"/>
-    <hyperlink ref="F348" r:id="rId149" xr:uid="{15A14E1E-9440-4524-8E71-E2F0B928B953}"/>
-    <hyperlink ref="F350" r:id="rId150" xr:uid="{C92EA61B-8F06-42A1-A7F9-7F45453FF60F}"/>
-    <hyperlink ref="F354" r:id="rId151" xr:uid="{8A245E57-176A-4426-987A-230A824E21F5}"/>
-    <hyperlink ref="F361" r:id="rId152" xr:uid="{E66A3719-554E-4E28-86A4-324883D73CAE}"/>
-    <hyperlink ref="F365" r:id="rId153" xr:uid="{7BDE2C38-EC1A-4C17-B1C6-1E4D17FC0EE5}"/>
-    <hyperlink ref="F366" r:id="rId154" xr:uid="{00F24AF7-BECF-42F0-AB31-2C0DED0C37A2}"/>
-    <hyperlink ref="F367" r:id="rId155" xr:uid="{5852A063-4D20-4FBB-B346-BF786AFC86EC}"/>
-    <hyperlink ref="F368" r:id="rId156" xr:uid="{B67214DC-0A47-4AD1-BF86-5DC069815DE1}"/>
-    <hyperlink ref="F373" r:id="rId157" xr:uid="{8299AD99-FFD7-4B97-A788-030B31407DDD}"/>
-    <hyperlink ref="F375" r:id="rId158" xr:uid="{78971510-8CDC-4BF5-AE19-0D07D647D047}"/>
-    <hyperlink ref="F377" r:id="rId159" xr:uid="{A0C94A52-B22E-4392-9DAE-3EA37FFA5A46}"/>
-    <hyperlink ref="F378" r:id="rId160" xr:uid="{3B87B23F-40F6-462E-9110-A5A9A19D2232}"/>
-    <hyperlink ref="F379" r:id="rId161" xr:uid="{292120C3-4914-44B9-9098-59807C6E7C6C}"/>
-    <hyperlink ref="F380" r:id="rId162" xr:uid="{5B5091B4-FEAA-4CAD-8FAF-43B120B259B8}"/>
-    <hyperlink ref="F381" r:id="rId163" xr:uid="{B4A8D738-F438-4B79-8C25-2D43D085BC71}"/>
-    <hyperlink ref="F382" r:id="rId164" xr:uid="{9C2371F9-4C06-48FC-AD5B-9E5916618520}"/>
-    <hyperlink ref="F388" r:id="rId165" xr:uid="{2C42E22B-0DD1-40FA-8493-10406BA7A1D9}"/>
-    <hyperlink ref="F389" r:id="rId166" xr:uid="{70286227-A588-43E1-91FC-1EB348F42574}"/>
-    <hyperlink ref="F391" r:id="rId167" xr:uid="{D1A39FB3-D165-4B56-88B9-CFB02C80378B}"/>
-    <hyperlink ref="F395" r:id="rId168" xr:uid="{86B3426F-8CFE-45AB-9DE6-873C49E7DB80}"/>
-    <hyperlink ref="F396" r:id="rId169" xr:uid="{6F07A94A-75BF-4D0C-A155-1F147D55686D}"/>
-    <hyperlink ref="F397" r:id="rId170" xr:uid="{925770DF-4D55-4F2C-B57F-546C6CF49F83}"/>
-    <hyperlink ref="F401" r:id="rId171" xr:uid="{86833F34-D3B8-49A2-B048-9143D1D268E1}"/>
-    <hyperlink ref="F402" r:id="rId172" xr:uid="{DC475E94-CED6-4041-A19D-421EDEC91083}"/>
-    <hyperlink ref="F403" r:id="rId173" xr:uid="{8CE58332-34FE-45F0-B53E-D28E50ECC3F5}"/>
-    <hyperlink ref="F404" r:id="rId174" xr:uid="{DD0386C7-D589-4779-A82D-1F72C4B6FBDD}"/>
-    <hyperlink ref="F405" r:id="rId175" xr:uid="{BC460B10-00B8-4916-B3EF-7D1ED959A78B}"/>
-    <hyperlink ref="F406" r:id="rId176" xr:uid="{40729791-C768-4D88-821E-9253252FB0F3}"/>
-    <hyperlink ref="F409" r:id="rId177" xr:uid="{BCA7C023-C424-401D-88B3-107FB2ACBF81}"/>
-    <hyperlink ref="F414" r:id="rId178" xr:uid="{43A41B2A-DEFE-495E-997D-ED085CF2FC91}"/>
-    <hyperlink ref="F415" r:id="rId179" xr:uid="{B12F044C-CB46-4CCB-89F1-EB0C8F7EB892}"/>
-    <hyperlink ref="F421" r:id="rId180" xr:uid="{28D016CB-3B77-415C-8166-D13FE68341D1}"/>
-    <hyperlink ref="F422" r:id="rId181" xr:uid="{CD429C9A-749F-491E-9E58-B9CB7A90A2FB}"/>
-    <hyperlink ref="F427" r:id="rId182" xr:uid="{5CC5C5A2-EE60-4284-8128-2E87C488D632}"/>
-    <hyperlink ref="F430" r:id="rId183" xr:uid="{C2BD70BB-F593-4AF0-B6A4-B32D5304C625}"/>
-    <hyperlink ref="F434" r:id="rId184" xr:uid="{F6E6F0EA-9817-4AA3-BC4A-B1ED8E6931ED}"/>
-    <hyperlink ref="F437" r:id="rId185" xr:uid="{5EB5671F-FF63-475A-9238-21AD45B4C5EE}"/>
-    <hyperlink ref="F440" r:id="rId186" xr:uid="{B97349D3-8379-49CF-AB1C-503D2A28FCDC}"/>
-    <hyperlink ref="F447" r:id="rId187" xr:uid="{DCBAF156-741D-4CDD-A1BB-BEE3DCAFC7E4}"/>
-    <hyperlink ref="F454" r:id="rId188" xr:uid="{8B8F94DD-ABB2-4320-920C-216E8ECE661F}"/>
-    <hyperlink ref="F339" r:id="rId189" xr:uid="{A1876CDA-D2D9-4ACE-9E52-75F2A87E4D4F}"/>
-    <hyperlink ref="F458" r:id="rId190" xr:uid="{21AFB719-500D-49EA-9A94-E1F0F8DEAF1D}"/>
-    <hyperlink ref="F461" r:id="rId191" xr:uid="{9FB30793-74F5-4EE1-997B-A29276854B0F}"/>
-    <hyperlink ref="F462" r:id="rId192" xr:uid="{F7D721C1-6EE7-431C-825B-C14B050040BE}"/>
-    <hyperlink ref="F463" r:id="rId193" xr:uid="{E82C3262-E183-4FD0-A624-6B9CBBA13E22}"/>
-    <hyperlink ref="F466" r:id="rId194" xr:uid="{2F3A224E-996D-44F2-BB99-EC5746F0E81D}"/>
-    <hyperlink ref="F469" r:id="rId195" xr:uid="{66281EB3-1C84-4327-8A41-AC8CB05AAABD}"/>
-    <hyperlink ref="F471" r:id="rId196" xr:uid="{E3C74E77-C496-4510-8806-2D2606716F78}"/>
-    <hyperlink ref="F473" r:id="rId197" xr:uid="{9BE712DE-053D-4691-8A07-B0D3C3304A32}"/>
-    <hyperlink ref="F474" r:id="rId198" xr:uid="{97572BBD-E6D2-4CFC-B983-6629083AAA30}"/>
-    <hyperlink ref="F479" r:id="rId199" xr:uid="{F9FBA57F-7D2B-4679-A566-A492ECEF9035}"/>
-    <hyperlink ref="F483" r:id="rId200" xr:uid="{5942006B-880C-4C23-9ED8-EE6DF160CAFC}"/>
-    <hyperlink ref="F484" r:id="rId201" xr:uid="{93B54EDE-1866-4706-A5FE-E39688316329}"/>
-    <hyperlink ref="F490" r:id="rId202" xr:uid="{D1F916D6-B062-4FD4-9C02-9546DAF97B5D}"/>
-    <hyperlink ref="F498" r:id="rId203" xr:uid="{82BB8238-8B3C-44CF-B8DB-8B220659D0F1}"/>
-    <hyperlink ref="F501" r:id="rId204" xr:uid="{BC41CEBA-AAE5-49A0-8216-3B4403811C0B}"/>
-    <hyperlink ref="F505" r:id="rId205" xr:uid="{3ED9D9C9-88BD-4D38-8C17-2147C43DCA41}"/>
-    <hyperlink ref="F506" r:id="rId206" xr:uid="{8EE4BBCE-100C-422D-A8AE-E1855B7531DD}"/>
-    <hyperlink ref="F507" r:id="rId207" xr:uid="{7393F241-1EE0-4975-B705-3BB32A866045}"/>
-    <hyperlink ref="F449" r:id="rId208" xr:uid="{80AE22F1-0F21-450E-BE5A-444AA127014C}"/>
+    <hyperlink ref="F306" r:id="rId129" xr:uid="{091067F1-8D60-40C3-B79B-EDA05B5A7DA4}"/>
+    <hyperlink ref="F307" r:id="rId130" xr:uid="{AC3C0A2F-C850-4DC8-B816-62B521573541}"/>
+    <hyperlink ref="F308" r:id="rId131" xr:uid="{BD4C4423-9801-48B9-BE4A-6FA8B9B411A4}"/>
+    <hyperlink ref="F309" r:id="rId132" xr:uid="{03558391-13D5-417E-8518-5A118844CD95}"/>
+    <hyperlink ref="F312" r:id="rId133" xr:uid="{2005E731-59D7-4620-B28C-434266F6022D}"/>
+    <hyperlink ref="F313" r:id="rId134" xr:uid="{2FD5242C-CF0A-4A63-816A-EA2A83984E64}"/>
+    <hyperlink ref="F314" r:id="rId135" xr:uid="{3123CD08-C684-4CC9-AB12-F9105EA97288}"/>
+    <hyperlink ref="F315" r:id="rId136" xr:uid="{2213C59C-4A61-40A9-A06B-1FEF17A027B0}"/>
+    <hyperlink ref="F316" r:id="rId137" xr:uid="{68B28FC2-AA1F-41B6-9A23-516E9B83B6E0}"/>
+    <hyperlink ref="F318" r:id="rId138" xr:uid="{B5599032-4454-4E2C-A68F-8CFFE50F4FDA}"/>
+    <hyperlink ref="F319" r:id="rId139" xr:uid="{A0B5737A-A70A-4218-B2E1-A76C8720DB56}"/>
+    <hyperlink ref="F320" r:id="rId140" xr:uid="{D4B5840E-77B4-47E2-8436-CD2E572AF2B8}"/>
+    <hyperlink ref="F321" r:id="rId141" xr:uid="{BD67BD55-40E9-45BF-A3F6-8F5115DDB229}"/>
+    <hyperlink ref="F322" r:id="rId142" xr:uid="{006FB328-F8E9-4758-AE01-3843E2E75398}"/>
+    <hyperlink ref="F324" r:id="rId143" xr:uid="{D8274070-5E6A-448F-BE2B-E62287C27B7F}"/>
+    <hyperlink ref="F325" r:id="rId144" xr:uid="{3107A474-1B13-410C-98D5-4BDFF1B318A0}"/>
+    <hyperlink ref="F329" r:id="rId145" xr:uid="{AEE59407-C7BF-4741-8788-B6DE8B5B56F0}"/>
+    <hyperlink ref="F331" r:id="rId146" xr:uid="{9E43F2AF-CA8D-45AD-8AF2-43E79516D8C4}"/>
+    <hyperlink ref="F334" r:id="rId147" xr:uid="{527DB674-2191-4390-A5E3-AF104DB8B4DD}"/>
+    <hyperlink ref="F339" r:id="rId148" xr:uid="{6CBC3A1F-EFB9-4C79-8568-CA7B9F4AE2C5}"/>
+    <hyperlink ref="F349" r:id="rId149" xr:uid="{15A14E1E-9440-4524-8E71-E2F0B928B953}"/>
+    <hyperlink ref="F351" r:id="rId150" xr:uid="{C92EA61B-8F06-42A1-A7F9-7F45453FF60F}"/>
+    <hyperlink ref="F355" r:id="rId151" xr:uid="{8A245E57-176A-4426-987A-230A824E21F5}"/>
+    <hyperlink ref="F362" r:id="rId152" xr:uid="{E66A3719-554E-4E28-86A4-324883D73CAE}"/>
+    <hyperlink ref="F366" r:id="rId153" xr:uid="{7BDE2C38-EC1A-4C17-B1C6-1E4D17FC0EE5}"/>
+    <hyperlink ref="F367" r:id="rId154" xr:uid="{00F24AF7-BECF-42F0-AB31-2C0DED0C37A2}"/>
+    <hyperlink ref="F368" r:id="rId155" xr:uid="{5852A063-4D20-4FBB-B346-BF786AFC86EC}"/>
+    <hyperlink ref="F369" r:id="rId156" xr:uid="{B67214DC-0A47-4AD1-BF86-5DC069815DE1}"/>
+    <hyperlink ref="F374" r:id="rId157" xr:uid="{8299AD99-FFD7-4B97-A788-030B31407DDD}"/>
+    <hyperlink ref="F376" r:id="rId158" xr:uid="{78971510-8CDC-4BF5-AE19-0D07D647D047}"/>
+    <hyperlink ref="F378" r:id="rId159" xr:uid="{A0C94A52-B22E-4392-9DAE-3EA37FFA5A46}"/>
+    <hyperlink ref="F379" r:id="rId160" xr:uid="{3B87B23F-40F6-462E-9110-A5A9A19D2232}"/>
+    <hyperlink ref="F380" r:id="rId161" xr:uid="{292120C3-4914-44B9-9098-59807C6E7C6C}"/>
+    <hyperlink ref="F381" r:id="rId162" xr:uid="{5B5091B4-FEAA-4CAD-8FAF-43B120B259B8}"/>
+    <hyperlink ref="F382" r:id="rId163" xr:uid="{B4A8D738-F438-4B79-8C25-2D43D085BC71}"/>
+    <hyperlink ref="F383" r:id="rId164" xr:uid="{9C2371F9-4C06-48FC-AD5B-9E5916618520}"/>
+    <hyperlink ref="F389" r:id="rId165" xr:uid="{2C42E22B-0DD1-40FA-8493-10406BA7A1D9}"/>
+    <hyperlink ref="F390" r:id="rId166" xr:uid="{70286227-A588-43E1-91FC-1EB348F42574}"/>
+    <hyperlink ref="F392" r:id="rId167" xr:uid="{D1A39FB3-D165-4B56-88B9-CFB02C80378B}"/>
+    <hyperlink ref="F396" r:id="rId168" xr:uid="{86B3426F-8CFE-45AB-9DE6-873C49E7DB80}"/>
+    <hyperlink ref="F397" r:id="rId169" xr:uid="{6F07A94A-75BF-4D0C-A155-1F147D55686D}"/>
+    <hyperlink ref="F398" r:id="rId170" xr:uid="{925770DF-4D55-4F2C-B57F-546C6CF49F83}"/>
+    <hyperlink ref="F402" r:id="rId171" xr:uid="{86833F34-D3B8-49A2-B048-9143D1D268E1}"/>
+    <hyperlink ref="F403" r:id="rId172" xr:uid="{DC475E94-CED6-4041-A19D-421EDEC91083}"/>
+    <hyperlink ref="F404" r:id="rId173" xr:uid="{8CE58332-34FE-45F0-B53E-D28E50ECC3F5}"/>
+    <hyperlink ref="F405" r:id="rId174" xr:uid="{DD0386C7-D589-4779-A82D-1F72C4B6FBDD}"/>
+    <hyperlink ref="F406" r:id="rId175" xr:uid="{BC460B10-00B8-4916-B3EF-7D1ED959A78B}"/>
+    <hyperlink ref="F407" r:id="rId176" xr:uid="{40729791-C768-4D88-821E-9253252FB0F3}"/>
+    <hyperlink ref="F410" r:id="rId177" xr:uid="{BCA7C023-C424-401D-88B3-107FB2ACBF81}"/>
+    <hyperlink ref="F415" r:id="rId178" xr:uid="{43A41B2A-DEFE-495E-997D-ED085CF2FC91}"/>
+    <hyperlink ref="F416" r:id="rId179" xr:uid="{B12F044C-CB46-4CCB-89F1-EB0C8F7EB892}"/>
+    <hyperlink ref="F422" r:id="rId180" xr:uid="{28D016CB-3B77-415C-8166-D13FE68341D1}"/>
+    <hyperlink ref="F423" r:id="rId181" xr:uid="{CD429C9A-749F-491E-9E58-B9CB7A90A2FB}"/>
+    <hyperlink ref="F428" r:id="rId182" xr:uid="{5CC5C5A2-EE60-4284-8128-2E87C488D632}"/>
+    <hyperlink ref="F431" r:id="rId183" xr:uid="{C2BD70BB-F593-4AF0-B6A4-B32D5304C625}"/>
+    <hyperlink ref="F435" r:id="rId184" xr:uid="{F6E6F0EA-9817-4AA3-BC4A-B1ED8E6931ED}"/>
+    <hyperlink ref="F438" r:id="rId185" xr:uid="{5EB5671F-FF63-475A-9238-21AD45B4C5EE}"/>
+    <hyperlink ref="F441" r:id="rId186" xr:uid="{B97349D3-8379-49CF-AB1C-503D2A28FCDC}"/>
+    <hyperlink ref="F448" r:id="rId187" xr:uid="{DCBAF156-741D-4CDD-A1BB-BEE3DCAFC7E4}"/>
+    <hyperlink ref="F455" r:id="rId188" xr:uid="{8B8F94DD-ABB2-4320-920C-216E8ECE661F}"/>
+    <hyperlink ref="F340" r:id="rId189" xr:uid="{A1876CDA-D2D9-4ACE-9E52-75F2A87E4D4F}"/>
+    <hyperlink ref="F459" r:id="rId190" xr:uid="{21AFB719-500D-49EA-9A94-E1F0F8DEAF1D}"/>
+    <hyperlink ref="F462" r:id="rId191" xr:uid="{9FB30793-74F5-4EE1-997B-A29276854B0F}"/>
+    <hyperlink ref="F463" r:id="rId192" xr:uid="{F7D721C1-6EE7-431C-825B-C14B050040BE}"/>
+    <hyperlink ref="F464" r:id="rId193" xr:uid="{E82C3262-E183-4FD0-A624-6B9CBBA13E22}"/>
+    <hyperlink ref="F467" r:id="rId194" xr:uid="{2F3A224E-996D-44F2-BB99-EC5746F0E81D}"/>
+    <hyperlink ref="F470" r:id="rId195" xr:uid="{66281EB3-1C84-4327-8A41-AC8CB05AAABD}"/>
+    <hyperlink ref="F472" r:id="rId196" xr:uid="{E3C74E77-C496-4510-8806-2D2606716F78}"/>
+    <hyperlink ref="F474" r:id="rId197" xr:uid="{9BE712DE-053D-4691-8A07-B0D3C3304A32}"/>
+    <hyperlink ref="F475" r:id="rId198" xr:uid="{97572BBD-E6D2-4CFC-B983-6629083AAA30}"/>
+    <hyperlink ref="F480" r:id="rId199" xr:uid="{F9FBA57F-7D2B-4679-A566-A492ECEF9035}"/>
+    <hyperlink ref="F484" r:id="rId200" xr:uid="{5942006B-880C-4C23-9ED8-EE6DF160CAFC}"/>
+    <hyperlink ref="F485" r:id="rId201" xr:uid="{93B54EDE-1866-4706-A5FE-E39688316329}"/>
+    <hyperlink ref="F491" r:id="rId202" xr:uid="{D1F916D6-B062-4FD4-9C02-9546DAF97B5D}"/>
+    <hyperlink ref="F499" r:id="rId203" xr:uid="{82BB8238-8B3C-44CF-B8DB-8B220659D0F1}"/>
+    <hyperlink ref="F502" r:id="rId204" xr:uid="{BC41CEBA-AAE5-49A0-8216-3B4403811C0B}"/>
+    <hyperlink ref="F506" r:id="rId205" xr:uid="{3ED9D9C9-88BD-4D38-8C17-2147C43DCA41}"/>
+    <hyperlink ref="F507" r:id="rId206" xr:uid="{8EE4BBCE-100C-422D-A8AE-E1855B7531DD}"/>
+    <hyperlink ref="F508" r:id="rId207" xr:uid="{7393F241-1EE0-4975-B705-3BB32A866045}"/>
+    <hyperlink ref="F450" r:id="rId208" xr:uid="{80AE22F1-0F21-450E-BE5A-444AA127014C}"/>
     <hyperlink ref="F45" r:id="rId209" xr:uid="{9166A086-6452-4A3C-AEE1-EA61B6F0040C}"/>
     <hyperlink ref="F63" r:id="rId210" xr:uid="{C3D2727A-54A4-4ABC-BE29-C663282CB00F}"/>
     <hyperlink ref="F65" r:id="rId211" xr:uid="{290EDB11-A937-4642-B4C4-762CABC87A86}"/>
     <hyperlink ref="F92" r:id="rId212" xr:uid="{7BD3346D-C133-4F85-BA8B-06E893A5AA15}"/>
     <hyperlink ref="F236" r:id="rId213" xr:uid="{A89FDFBB-71B2-4738-9E20-379D288195B3}"/>
     <hyperlink ref="F237" r:id="rId214" xr:uid="{71BBAFA0-9838-4AE0-B1A3-8148C5047B22}"/>
-    <hyperlink ref="F429" r:id="rId215" xr:uid="{CE9B73F7-6206-43BE-A0D7-238A375EF8C2}"/>
+    <hyperlink ref="F430" r:id="rId215" xr:uid="{CE9B73F7-6206-43BE-A0D7-238A375EF8C2}"/>
+    <hyperlink ref="F303" r:id="rId216" xr:uid="{95974537-849E-47AD-A8B3-2D3E2FBBC6C7}"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId216"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId217"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;C&amp;8EC_Not_technical&amp;8
 </oddHeader>

--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCE8CDE-E68E-4422-BD00-A7BC3AEC993C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FB8BAB-8C52-4BB3-A0CE-07B701451D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="810">
   <si>
     <t>Artistes / Titres</t>
   </si>
@@ -2470,6 +2470,9 @@
   </si>
   <si>
     <t>MASS PRODUCTION - Come And Get Some Of This</t>
+  </si>
+  <si>
+    <t>LUTHER VANDROSS - She's a super lady</t>
   </si>
 </sst>
 </file>
@@ -13158,7 +13161,7 @@
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>279</v>
+        <v>809</v>
       </c>
       <c r="B303" s="21"/>
       <c r="C303" s="3"/>

--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FB8BAB-8C52-4BB3-A0CE-07B701451D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF27FA1-1C88-4D3F-AD54-1137F4151DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="811">
   <si>
     <t>Artistes / Titres</t>
   </si>
@@ -2473,6 +2473,9 @@
   </si>
   <si>
     <t>LUTHER VANDROSS - She's a super lady</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/fr/release/205940-Luther-Vandross-Never-Too-Much</t>
   </si>
 </sst>
 </file>
@@ -13170,7 +13173,7 @@
       </c>
       <c r="E303" s="31"/>
       <c r="F303" s="45" t="s">
-        <v>702</v>
+        <v>810</v>
       </c>
       <c r="G303" s="20">
         <f t="shared" ref="G303" si="25">COUNTA(A303)</f>

--- a/01_Liste achat.xlsx
+++ b/01_Liste achat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHILIPPE\Desktop\Sauvegarde vinyles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF27FA1-1C88-4D3F-AD54-1137F4151DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B824E557-0D37-40E6-8414-D00275322385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="798">
   <si>
     <t>Artistes / Titres</t>
   </si>
@@ -1692,30 +1692,12 @@
     <t>https://www.discogs.com/release/2952588-Alain-Chamfort-D%C3%A9cha%C3%AEne-moi</t>
   </si>
   <si>
-    <t>https://www.discogs.com/release/492074-Bangles-Walk-Like-An-Egyptian</t>
-  </si>
-  <si>
-    <t>https://www.discogs.com/release/742650-Bill-Baxter-Embrasse-Moi-Idiot</t>
-  </si>
-  <si>
     <t>BILL BAXTER - Ambrasse moi idiot!</t>
   </si>
   <si>
-    <t>https://www.discogs.com/release/875085-Billy-Idol-Flesh-For-Fantasy-Below-The-Belt-Mix</t>
-  </si>
-  <si>
     <t>https://www.discogs.com/release/797208-Clockwork-Im-Your-Candy-Girl</t>
   </si>
   <si>
-    <t>https://www.discogs.com/release/1288289-The-Detroit-Spinners-Ill-Be-Around-City-Full-Of-Memories</t>
-  </si>
-  <si>
-    <t>https://www.discogs.com/release/515963-Instant-Funk-I-Got-My-Mind-Made-Up</t>
-  </si>
-  <si>
-    <t>https://www.discogs.com/release/2108237-Jean-Jacques-Goldman-Il-Suffira-DUn-Signe-Quelque-Chose-De-Bizarre</t>
-  </si>
-  <si>
     <t>https://www.discogs.com/release/245747-A-O-K-Style</t>
   </si>
   <si>
@@ -1746,9 +1728,6 @@
     <t>https://www.discogs.com/release/1279133-Arlana-You-Cant-Keep-Breaking-My-Heart</t>
   </si>
   <si>
-    <t>https://www.discogs.com/release/212463-Armenta-Majik-I-Wanna-Be-With-You</t>
-  </si>
-  <si>
     <t>Part1 et part2 sur le même maxi</t>
   </si>
   <si>
@@ -1920,9 +1899,6 @@
     <t>DONALD BYRD - Love has come around</t>
   </si>
   <si>
-    <t>https://www.discogs.com/release/1155788-Donna-Summer-Four-Seasons-Of-Love</t>
-  </si>
-  <si>
     <t>Seulement sur l'Album "Four Seasons Of Love"</t>
   </si>
   <si>
@@ -2004,15 +1980,6 @@
     <t>https://www.discogs.com/release/524731-Gino-Soccio-What-You-Feel-Is-Real-Hold-Tight</t>
   </si>
   <si>
-    <t>https://www.discogs.com/release/839725-Gino-Soccio-Try-It-Out</t>
-  </si>
-  <si>
-    <t>https://www.discogs.com/release/702902-Gino-Soccio-You-Move-Me</t>
-  </si>
-  <si>
-    <t>https://www.discogs.com/release/1615507-Gladys-Knight-The-Pips-Taste-Of-Bitter-Love</t>
-  </si>
-  <si>
     <t>GWEN McCRAE - Keep the fire burning</t>
   </si>
   <si>
@@ -2379,9 +2346,6 @@
     <t>Sinon même temps sur l'album</t>
   </si>
   <si>
-    <t>https://www.discogs.com/release/1025163-The-Whispers-I-Can-Make-It-Better</t>
-  </si>
-  <si>
     <t>https://www.discogs.com/release/1025159-The-Whispers-This-Kind-Of-Lovin</t>
   </si>
   <si>
@@ -2427,12 +2391,6 @@
     <t>Seulement en album 90€</t>
   </si>
   <si>
-    <t>https://www.discogs.com/release/182273-The-Flirts-Passion</t>
-  </si>
-  <si>
-    <t>https://www.discogs.com/release/6961179-Bee-Gees-You-Should-Be-Dancing-Remix-</t>
-  </si>
-  <si>
     <t>https://www.discogs.com/release/2146190-Breakbot-Baby-Im-Yours</t>
   </si>
   <si>
@@ -2476,6 +2434,9 @@
   </si>
   <si>
     <t>https://www.discogs.com/fr/release/205940-Luther-Vandross-Never-Too-Much</t>
+  </si>
+  <si>
+    <t>Phil BOOGIE TIMES</t>
   </si>
 </sst>
 </file>
@@ -3318,12 +3279,12 @@
       <c r="I2" s="74"/>
       <c r="J2" s="11">
         <f>SUM(I3:I562)</f>
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K2" s="17"/>
       <c r="L2" s="12">
         <f>H2-J2</f>
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -3333,11 +3294,11 @@
       <c r="B3" s="21"/>
       <c r="C3" s="3"/>
       <c r="D3" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="45" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="G3" s="20">
         <f>COUNTA(A3)</f>
@@ -3609,7 +3570,7 @@
       <c r="D11" s="14"/>
       <c r="E11" s="31"/>
       <c r="F11" s="45" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="G11" s="20">
         <f t="shared" si="2"/>
@@ -3641,7 +3602,7 @@
       <c r="D12" s="14"/>
       <c r="E12" s="31"/>
       <c r="F12" s="45" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="G12" s="20">
         <f t="shared" si="2"/>
@@ -3673,7 +3634,7 @@
       <c r="D13" s="14"/>
       <c r="E13" s="31"/>
       <c r="F13" s="45" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="G13" s="20">
         <f t="shared" si="2"/>
@@ -3703,11 +3664,11 @@
       <c r="B14" s="21"/>
       <c r="C14" s="3"/>
       <c r="D14" s="14" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="45" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="G14" s="20">
         <f t="shared" si="2"/>
@@ -3739,7 +3700,7 @@
       <c r="D15" s="14"/>
       <c r="E15" s="31"/>
       <c r="F15" s="45" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="G15" s="20">
         <f t="shared" si="2"/>
@@ -3763,7 +3724,7 @@
       <c r="D16" s="14"/>
       <c r="E16" s="31"/>
       <c r="F16" s="45" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="G16" s="20">
         <f t="shared" si="2"/>
@@ -3967,7 +3928,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="E22" s="30"/>
       <c r="F22" s="43"/>
@@ -4001,7 +3962,7 @@
       <c r="D23" s="14"/>
       <c r="E23" s="31"/>
       <c r="F23" s="45" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="G23" s="20">
         <f t="shared" si="2"/>
@@ -4065,12 +4026,10 @@
         <v>5</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="E25" s="30"/>
-      <c r="F25" s="46" t="s">
-        <v>567</v>
-      </c>
+      <c r="F25" s="46"/>
       <c r="G25" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4101,7 +4060,7 @@
       <c r="D26" s="14"/>
       <c r="E26" s="31"/>
       <c r="F26" s="45" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="G26" s="20">
         <f t="shared" si="2"/>
@@ -4165,7 +4124,7 @@
       <c r="D28" s="14"/>
       <c r="E28" s="31"/>
       <c r="F28" s="45" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="G28" s="20">
         <f t="shared" si="2"/>
@@ -4263,7 +4222,7 @@
       <c r="D31" s="14"/>
       <c r="E31" s="31"/>
       <c r="F31" s="45" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="G31" s="20">
         <f t="shared" si="2"/>
@@ -4391,11 +4350,11 @@
       <c r="B35" s="21"/>
       <c r="C35" s="3"/>
       <c r="D35" s="14" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="E35" s="31"/>
       <c r="F35" s="45" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="G35" s="20">
         <f t="shared" si="2"/>
@@ -4490,7 +4449,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="3"/>
@@ -4501,7 +4460,7 @@
         <v>8</v>
       </c>
       <c r="F38" s="45" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="G38" s="20">
         <f t="shared" si="2"/>
@@ -4570,9 +4529,7 @@
       <c r="E40" s="30">
         <v>11</v>
       </c>
-      <c r="F40" s="46" t="s">
-        <v>549</v>
-      </c>
+      <c r="F40" s="46"/>
       <c r="G40" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4639,7 +4596,7 @@
       <c r="D42" s="14"/>
       <c r="E42" s="31"/>
       <c r="F42" s="45" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="G42" s="20">
         <f t="shared" si="2"/>
@@ -4673,7 +4630,7 @@
       </c>
       <c r="E43" s="31"/>
       <c r="F43" s="45" t="s">
-        <v>802</v>
+        <v>788</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" si="2"/>
@@ -4742,9 +4699,7 @@
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="30"/>
-      <c r="F45" s="46" t="s">
-        <v>795</v>
-      </c>
+      <c r="F45" s="46"/>
       <c r="G45" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4799,7 +4754,7 @@
       <c r="D47" s="14"/>
       <c r="E47" s="31"/>
       <c r="F47" s="45" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="G47" s="20">
         <f t="shared" si="2"/>
@@ -4824,7 +4779,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="5" t="s">
@@ -4836,9 +4791,7 @@
       <c r="E48" s="30">
         <v>13.5</v>
       </c>
-      <c r="F48" s="46" t="s">
-        <v>550</v>
-      </c>
+      <c r="F48" s="46"/>
       <c r="G48" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -4874,9 +4827,7 @@
       <c r="E49" s="30">
         <v>12</v>
       </c>
-      <c r="F49" s="46" t="s">
-        <v>552</v>
-      </c>
+      <c r="F49" s="46"/>
       <c r="G49" s="20">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -5011,7 +4962,7 @@
       <c r="D53" s="14"/>
       <c r="E53" s="31"/>
       <c r="F53" s="45" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="G53" s="20">
         <f t="shared" si="2"/>
@@ -5028,16 +4979,16 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="3"/>
       <c r="D54" s="14" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="E54" s="31"/>
       <c r="F54" s="45" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="G54" s="20">
         <f t="shared" si="2"/>
@@ -5229,7 +5180,7 @@
       <c r="D60" s="14"/>
       <c r="E60" s="31"/>
       <c r="F60" s="45" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="G60" s="20">
         <f t="shared" si="2"/>
@@ -5320,14 +5271,14 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="3"/>
       <c r="D63" s="14"/>
       <c r="E63" s="31"/>
       <c r="F63" s="45" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="G63" s="20">
         <f t="shared" si="2"/>
@@ -5393,11 +5344,11 @@
       <c r="B65" s="21"/>
       <c r="C65" s="3"/>
       <c r="D65" s="14" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="E65" s="31"/>
       <c r="F65" s="45" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="G65" s="20">
         <f t="shared" si="2"/>
@@ -5422,16 +5373,16 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="B66" s="21"/>
       <c r="C66" s="3"/>
       <c r="D66" s="14" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="E66" s="31"/>
       <c r="F66" s="45" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="G66" s="20">
         <f t="shared" si="2"/>
@@ -5463,7 +5414,7 @@
       <c r="D67" s="14"/>
       <c r="E67" s="31"/>
       <c r="F67" s="45" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="G67" s="20">
         <f t="shared" si="2"/>
@@ -5619,7 +5570,7 @@
       <c r="D72" s="14"/>
       <c r="E72" s="31"/>
       <c r="F72" s="45" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="G72" s="20">
         <f t="shared" si="6"/>
@@ -5644,14 +5595,14 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B73" s="21"/>
       <c r="C73" s="3"/>
       <c r="D73" s="14"/>
       <c r="E73" s="31"/>
       <c r="F73" s="45" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="G73" s="20">
         <f t="shared" si="6"/>
@@ -5683,7 +5634,7 @@
       <c r="D74" s="14"/>
       <c r="E74" s="31"/>
       <c r="F74" s="45" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="G74" s="20">
         <f t="shared" si="6"/>
@@ -5715,7 +5666,7 @@
       <c r="D75" s="14"/>
       <c r="E75" s="31"/>
       <c r="F75" s="45" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G75" s="20">
         <f t="shared" si="6"/>
@@ -5847,7 +5798,7 @@
       <c r="D79" s="14"/>
       <c r="E79" s="31"/>
       <c r="F79" s="45" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="G79" s="20">
         <f t="shared" si="6"/>
@@ -5947,7 +5898,7 @@
       <c r="D82" s="14"/>
       <c r="E82" s="31"/>
       <c r="F82" s="45" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G82" s="20">
         <f t="shared" si="6"/>
@@ -5979,7 +5930,7 @@
       <c r="D83" s="14"/>
       <c r="E83" s="31"/>
       <c r="F83" s="45" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G83" s="20">
         <f t="shared" si="6"/>
@@ -6104,16 +6055,16 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="B87" s="21"/>
       <c r="C87" s="3"/>
       <c r="D87" s="14" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="E87" s="31"/>
       <c r="F87" s="45" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="G87" s="20">
         <f t="shared" si="6"/>
@@ -6145,7 +6096,7 @@
       <c r="D88" s="14"/>
       <c r="E88" s="31"/>
       <c r="F88" s="45" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="G88" s="20">
         <f t="shared" si="6"/>
@@ -6177,7 +6128,7 @@
       <c r="D89" s="14"/>
       <c r="E89" s="31"/>
       <c r="F89" s="45" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="G89" s="20">
         <f t="shared" si="6"/>
@@ -6209,7 +6160,7 @@
       <c r="D90" s="14"/>
       <c r="E90" s="31"/>
       <c r="F90" s="45" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G90" s="20">
         <f t="shared" si="6"/>
@@ -6241,7 +6192,7 @@
       <c r="D91" s="14"/>
       <c r="E91" s="31"/>
       <c r="F91" s="45" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="G91" s="20">
         <f t="shared" si="6"/>
@@ -6271,11 +6222,11 @@
       <c r="B92" s="21"/>
       <c r="C92" s="3"/>
       <c r="D92" s="14" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="E92" s="31"/>
       <c r="F92" s="45" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="G92" s="20">
         <f t="shared" si="6"/>
@@ -6579,7 +6530,7 @@
         <v>15</v>
       </c>
       <c r="F101" s="69" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="G101" s="20">
         <f t="shared" si="6"/>
@@ -6611,7 +6562,7 @@
       <c r="D102" s="36"/>
       <c r="E102" s="37"/>
       <c r="F102" s="70" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G102" s="20">
         <f t="shared" si="6"/>
@@ -6643,7 +6594,7 @@
       <c r="D103" s="14"/>
       <c r="E103" s="31"/>
       <c r="F103" s="45" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="G103" s="20">
         <f t="shared" si="6"/>
@@ -6707,7 +6658,7 @@
       <c r="D105" s="14"/>
       <c r="E105" s="31"/>
       <c r="F105" s="45" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="G105" s="20">
         <f t="shared" si="6"/>
@@ -6739,7 +6690,7 @@
       <c r="D106" s="14"/>
       <c r="E106" s="31"/>
       <c r="F106" s="45" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="G106" s="20">
         <f t="shared" si="6"/>
@@ -6771,7 +6722,7 @@
       <c r="D107" s="14"/>
       <c r="E107" s="31"/>
       <c r="F107" s="45" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="G107" s="20">
         <f t="shared" si="6"/>
@@ -6831,7 +6782,7 @@
       <c r="D109" s="14"/>
       <c r="E109" s="31"/>
       <c r="F109" s="45" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="G109" s="20">
         <f t="shared" si="6"/>
@@ -6895,7 +6846,7 @@
       <c r="D111" s="14"/>
       <c r="E111" s="31"/>
       <c r="F111" s="45" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="G111" s="20">
         <f t="shared" si="6"/>
@@ -6927,7 +6878,7 @@
       <c r="D112" s="14"/>
       <c r="E112" s="31"/>
       <c r="F112" s="45" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="G112" s="20">
         <f t="shared" si="6"/>
@@ -7063,7 +7014,7 @@
       <c r="D116" s="14"/>
       <c r="E116" s="31"/>
       <c r="F116" s="45" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="G116" s="20">
         <f t="shared" si="6"/>
@@ -7201,7 +7152,7 @@
       <c r="D120" s="14"/>
       <c r="E120" s="31"/>
       <c r="F120" s="45" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="G120" s="20">
         <f t="shared" si="6"/>
@@ -7265,7 +7216,7 @@
       <c r="D122" s="14"/>
       <c r="E122" s="31"/>
       <c r="F122" s="45" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="G122" s="20">
         <f t="shared" si="6"/>
@@ -7339,7 +7290,7 @@
         <v>39</v>
       </c>
       <c r="F124" s="71" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="G124" s="20">
         <f t="shared" si="6"/>
@@ -7371,7 +7322,7 @@
       <c r="D125" s="14"/>
       <c r="E125" s="31"/>
       <c r="F125" s="45" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="G125" s="20">
         <f t="shared" si="6"/>
@@ -7407,7 +7358,7 @@
       </c>
       <c r="E126" s="32"/>
       <c r="F126" s="71" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="G126" s="20">
         <f t="shared" si="6"/>
@@ -7668,9 +7619,7 @@
       <c r="E134" s="30">
         <v>29</v>
       </c>
-      <c r="F134" s="46" t="s">
-        <v>554</v>
-      </c>
+      <c r="F134" s="46"/>
       <c r="G134" s="20">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -7765,7 +7714,7 @@
       <c r="D137" s="14"/>
       <c r="E137" s="31"/>
       <c r="F137" s="45" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="G137" s="20">
         <f t="shared" si="10"/>
@@ -7797,7 +7746,7 @@
       <c r="D138" s="14"/>
       <c r="E138" s="31"/>
       <c r="F138" s="45" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="G138" s="20">
         <f t="shared" si="10"/>
@@ -7822,14 +7771,14 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="B139" s="21"/>
       <c r="C139" s="3"/>
       <c r="D139" s="14"/>
       <c r="E139" s="31"/>
       <c r="F139" s="45" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="G139" s="20">
         <f t="shared" si="10"/>
@@ -7861,7 +7810,7 @@
       <c r="D140" s="14"/>
       <c r="E140" s="31"/>
       <c r="F140" s="45" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="G140" s="20">
         <f t="shared" si="10"/>
@@ -7885,7 +7834,7 @@
       <c r="D141" s="14"/>
       <c r="E141" s="31"/>
       <c r="F141" s="45" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="G141" s="20">
         <f t="shared" si="10"/>
@@ -7910,14 +7859,14 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="B142" s="21"/>
       <c r="C142" s="3"/>
       <c r="D142" s="14"/>
       <c r="E142" s="31"/>
       <c r="F142" s="45" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="G142" s="20">
         <f t="shared" si="10"/>
@@ -8053,12 +8002,10 @@
         <v>5</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="E146" s="30"/>
-      <c r="F146" s="46" t="s">
-        <v>625</v>
-      </c>
+      <c r="F146" s="46"/>
       <c r="G146" s="20">
         <f t="shared" si="10"/>
         <v>1</v>
@@ -8123,11 +8070,11 @@
       <c r="B148" s="21"/>
       <c r="C148" s="3"/>
       <c r="D148" s="14" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="E148" s="31"/>
       <c r="F148" s="45" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="G148" s="20">
         <f t="shared" si="10"/>
@@ -8227,7 +8174,7 @@
       <c r="D151" s="14"/>
       <c r="E151" s="31"/>
       <c r="F151" s="45" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="G151" s="20">
         <f t="shared" si="10"/>
@@ -8259,7 +8206,7 @@
       <c r="D152" s="14"/>
       <c r="E152" s="31"/>
       <c r="F152" s="45" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="G152" s="20">
         <f t="shared" si="10"/>
@@ -8425,7 +8372,7 @@
       <c r="D157" s="14"/>
       <c r="E157" s="31"/>
       <c r="F157" s="45" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="G157" s="20">
         <f t="shared" si="10"/>
@@ -8583,11 +8530,11 @@
       <c r="B162" s="21"/>
       <c r="C162" s="3"/>
       <c r="D162" s="14" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="E162" s="31"/>
       <c r="F162" s="45" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="G162" s="20">
         <f t="shared" si="10"/>
@@ -8619,7 +8566,7 @@
       <c r="D163" s="14"/>
       <c r="E163" s="31"/>
       <c r="F163" s="45" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="G163" s="20">
         <f t="shared" si="10"/>
@@ -8651,7 +8598,7 @@
       <c r="D164" s="14"/>
       <c r="E164" s="31"/>
       <c r="F164" s="45" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="G164" s="20">
         <f t="shared" si="10"/>
@@ -8783,7 +8730,7 @@
       <c r="D168" s="14"/>
       <c r="E168" s="31"/>
       <c r="F168" s="45" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="G168" s="20">
         <f t="shared" si="10"/>
@@ -8808,14 +8755,14 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="B169" s="21"/>
       <c r="C169" s="3"/>
       <c r="D169" s="14"/>
       <c r="E169" s="31"/>
       <c r="F169" s="45" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="G169" s="20">
         <f t="shared" si="10"/>
@@ -8847,7 +8794,7 @@
       <c r="D170" s="14"/>
       <c r="E170" s="31"/>
       <c r="F170" s="45" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="G170" s="20">
         <f t="shared" si="10"/>
@@ -8979,7 +8926,7 @@
       <c r="D174" s="14"/>
       <c r="E174" s="31"/>
       <c r="F174" s="45" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="G174" s="20">
         <f t="shared" si="10"/>
@@ -9011,7 +8958,7 @@
       <c r="D175" s="14"/>
       <c r="E175" s="31"/>
       <c r="F175" s="45" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="G175" s="20">
         <f t="shared" si="10"/>
@@ -9043,7 +8990,7 @@
       <c r="D176" s="14"/>
       <c r="E176" s="31"/>
       <c r="F176" s="45" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="G176" s="20">
         <f t="shared" si="10"/>
@@ -9075,7 +9022,7 @@
       <c r="D177" s="14"/>
       <c r="E177" s="31"/>
       <c r="F177" s="45" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="G177" s="20">
         <f t="shared" si="10"/>
@@ -9141,7 +9088,7 @@
       <c r="D179" s="14"/>
       <c r="E179" s="31"/>
       <c r="F179" s="45" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="G179" s="20">
         <f t="shared" si="10"/>
@@ -9205,7 +9152,7 @@
       <c r="D181" s="14"/>
       <c r="E181" s="31"/>
       <c r="F181" s="45" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="G181" s="20">
         <f t="shared" si="10"/>
@@ -9237,7 +9184,7 @@
       <c r="D182" s="14"/>
       <c r="E182" s="31"/>
       <c r="F182" s="45" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="G182" s="20">
         <f t="shared" si="10"/>
@@ -9337,7 +9284,7 @@
       <c r="D185" s="14"/>
       <c r="E185" s="31"/>
       <c r="F185" s="45" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="G185" s="20">
         <f t="shared" si="10"/>
@@ -9403,7 +9350,7 @@
       </c>
       <c r="E187" s="31"/>
       <c r="F187" s="45" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="G187" s="20">
         <f t="shared" si="10"/>
@@ -9594,14 +9541,14 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="B193" s="21"/>
       <c r="C193" s="3"/>
       <c r="D193" s="14"/>
       <c r="E193" s="31"/>
       <c r="F193" s="45" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="G193" s="20">
         <f t="shared" si="10"/>
@@ -10007,7 +9954,7 @@
       <c r="D205" s="14"/>
       <c r="E205" s="31"/>
       <c r="F205" s="45" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="G205" s="20">
         <f t="shared" si="15"/>
@@ -10265,7 +10212,7 @@
       <c r="D213" s="14"/>
       <c r="E213" s="31"/>
       <c r="F213" s="45" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="G213" s="20">
         <f t="shared" si="15"/>
@@ -10325,16 +10272,18 @@
       </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
+      <c r="A215" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B215" s="21"/>
-      <c r="C215" s="3"/>
-      <c r="D215" s="14"/>
-      <c r="E215" s="31"/>
-      <c r="F215" s="45" t="s">
-        <v>653</v>
-      </c>
+      <c r="B215" s="1"/>
+      <c r="C215" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D215" s="13" t="s">
+        <v>797</v>
+      </c>
+      <c r="E215" s="30"/>
+      <c r="F215" s="46"/>
       <c r="G215" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10342,7 +10291,7 @@
       <c r="H215" s="18"/>
       <c r="I215" s="19">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J215" s="19"/>
       <c r="K215" s="20"/>
@@ -10368,9 +10317,7 @@
         <v>458</v>
       </c>
       <c r="E216" s="30"/>
-      <c r="F216" s="46" t="s">
-        <v>654</v>
-      </c>
+      <c r="F216" s="46"/>
       <c r="G216" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10425,16 +10372,18 @@
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A218" s="2" t="s">
+      <c r="A218" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B218" s="21"/>
-      <c r="C218" s="3"/>
-      <c r="D218" s="14"/>
-      <c r="E218" s="31"/>
-      <c r="F218" s="45" t="s">
-        <v>655</v>
-      </c>
+      <c r="B218" s="1"/>
+      <c r="C218" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="E218" s="30"/>
+      <c r="F218" s="46"/>
       <c r="G218" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -10442,7 +10391,7 @@
       <c r="H218" s="18"/>
       <c r="I218" s="19">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" s="19"/>
       <c r="K218" s="20"/>
@@ -10558,14 +10507,14 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="B222" s="21"/>
       <c r="C222" s="3"/>
       <c r="D222" s="14"/>
       <c r="E222" s="31"/>
       <c r="F222" s="45" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="G222" s="20">
         <f t="shared" si="15"/>
@@ -10590,14 +10539,14 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="B223" s="21"/>
       <c r="C223" s="3"/>
       <c r="D223" s="14"/>
       <c r="E223" s="31"/>
       <c r="F223" s="45" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="G223" s="20">
         <f t="shared" si="15"/>
@@ -10693,7 +10642,7 @@
       <c r="D226" s="14"/>
       <c r="E226" s="31"/>
       <c r="F226" s="45" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="G226" s="20">
         <f t="shared" si="15"/>
@@ -10729,7 +10678,7 @@
         <v>15</v>
       </c>
       <c r="F227" s="45" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="G227" s="20">
         <f t="shared" si="15"/>
@@ -10795,7 +10744,7 @@
       <c r="D229" s="14"/>
       <c r="E229" s="31"/>
       <c r="F229" s="45" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="G229" s="20">
         <f t="shared" si="15"/>
@@ -10921,7 +10870,7 @@
       <c r="D233" s="14"/>
       <c r="E233" s="31"/>
       <c r="F233" s="45" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="G233" s="20">
         <f t="shared" si="15"/>
@@ -11014,14 +10963,14 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="34" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="B236" s="25"/>
       <c r="C236" s="35"/>
       <c r="D236" s="36"/>
       <c r="E236" s="37"/>
       <c r="F236" s="70" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="G236" s="20">
         <f t="shared" ref="G236:G237" si="19">COUNTA(A236)</f>
@@ -11038,14 +10987,14 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="34" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="B237" s="25"/>
       <c r="C237" s="35"/>
       <c r="D237" s="36"/>
       <c r="E237" s="37"/>
       <c r="F237" s="70" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="G237" s="20">
         <f t="shared" si="19"/>
@@ -11125,7 +11074,7 @@
       <c r="D240" s="14"/>
       <c r="E240" s="31"/>
       <c r="F240" s="45" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="G240" s="20">
         <f t="shared" si="15"/>
@@ -11157,7 +11106,7 @@
       <c r="D241" s="14"/>
       <c r="E241" s="31"/>
       <c r="F241" s="45" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="G241" s="20">
         <f t="shared" si="15"/>
@@ -11189,7 +11138,7 @@
       <c r="D242" s="14"/>
       <c r="E242" s="31"/>
       <c r="F242" s="45" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="G242" s="20">
         <f t="shared" si="15"/>
@@ -11226,9 +11175,7 @@
       <c r="E243" s="30">
         <v>15</v>
       </c>
-      <c r="F243" s="46" t="s">
-        <v>555</v>
-      </c>
+      <c r="F243" s="46"/>
       <c r="G243" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11259,7 +11206,7 @@
       <c r="D244" s="14"/>
       <c r="E244" s="31"/>
       <c r="F244" s="45" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="G244" s="20">
         <f t="shared" si="15"/>
@@ -11284,14 +11231,14 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B245" s="21"/>
       <c r="C245" s="3"/>
       <c r="D245" s="14"/>
       <c r="E245" s="31"/>
       <c r="F245" s="45" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="G245" s="20">
         <f t="shared" si="15"/>
@@ -11347,7 +11294,7 @@
       <c r="D247" s="14"/>
       <c r="E247" s="31"/>
       <c r="F247" s="45" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="G247" s="20">
         <f t="shared" si="15"/>
@@ -11371,7 +11318,7 @@
       <c r="D248" s="14"/>
       <c r="E248" s="31"/>
       <c r="F248" s="45" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="G248" s="20">
         <f t="shared" si="15"/>
@@ -11403,7 +11350,7 @@
       <c r="D249" s="14"/>
       <c r="E249" s="31"/>
       <c r="F249" s="45" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="G249" s="20">
         <f t="shared" si="15"/>
@@ -11472,9 +11419,7 @@
       <c r="E251" s="30">
         <v>129</v>
       </c>
-      <c r="F251" s="46" t="s">
-        <v>556</v>
-      </c>
+      <c r="F251" s="46"/>
       <c r="G251" s="20">
         <f t="shared" si="15"/>
         <v>1</v>
@@ -11503,11 +11448,11 @@
       <c r="B252" s="21"/>
       <c r="C252" s="3"/>
       <c r="D252" s="14" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="E252" s="31"/>
       <c r="F252" s="45" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="G252" s="20">
         <f t="shared" si="15"/>
@@ -11667,7 +11612,7 @@
       <c r="D257" s="14"/>
       <c r="E257" s="31"/>
       <c r="F257" s="45" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="G257" s="20">
         <f t="shared" si="15"/>
@@ -11763,7 +11708,7 @@
       <c r="D260" s="14"/>
       <c r="E260" s="31"/>
       <c r="F260" s="45" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="G260" s="20">
         <f t="shared" si="15"/>
@@ -11884,14 +11829,14 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="B264" s="21"/>
       <c r="C264" s="3"/>
       <c r="D264" s="14"/>
       <c r="E264" s="31"/>
       <c r="F264" s="45" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="G264" s="20">
         <f t="shared" si="15"/>
@@ -11923,7 +11868,7 @@
       <c r="D265" s="14"/>
       <c r="E265" s="31"/>
       <c r="F265" s="45" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="G265" s="20">
         <f t="shared" si="15"/>
@@ -11955,7 +11900,7 @@
       <c r="D266" s="14"/>
       <c r="E266" s="31"/>
       <c r="F266" s="45" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="G266" s="20">
         <f t="shared" ref="G266:G328" si="21">COUNTA(A266)</f>
@@ -11987,7 +11932,7 @@
       <c r="D267" s="14"/>
       <c r="E267" s="31"/>
       <c r="F267" s="45" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="G267" s="20">
         <f t="shared" si="21"/>
@@ -12019,7 +11964,7 @@
       <c r="D268" s="14"/>
       <c r="E268" s="31"/>
       <c r="F268" s="45" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="G268" s="20">
         <f t="shared" si="21"/>
@@ -12051,7 +11996,7 @@
       <c r="D269" s="14"/>
       <c r="E269" s="31"/>
       <c r="F269" s="45" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="G269" s="20">
         <f t="shared" si="21"/>
@@ -12183,7 +12128,7 @@
       <c r="D273" s="14"/>
       <c r="E273" s="31"/>
       <c r="F273" s="45" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="G273" s="20">
         <f t="shared" si="21"/>
@@ -12215,7 +12160,7 @@
       <c r="D274" s="14"/>
       <c r="E274" s="31"/>
       <c r="F274" s="45" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="G274" s="20">
         <f t="shared" si="21"/>
@@ -12279,11 +12224,11 @@
       <c r="B276" s="21"/>
       <c r="C276" s="3"/>
       <c r="D276" s="14" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="E276" s="31"/>
       <c r="F276" s="45" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="G276" s="20">
         <f t="shared" si="21"/>
@@ -12315,7 +12260,7 @@
       <c r="D277" s="14"/>
       <c r="E277" s="31"/>
       <c r="F277" s="45" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="G277" s="20">
         <f t="shared" si="21"/>
@@ -12347,7 +12292,7 @@
       <c r="D278" s="14"/>
       <c r="E278" s="31"/>
       <c r="F278" s="45" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="G278" s="20">
         <f t="shared" si="21"/>
@@ -12413,7 +12358,7 @@
       <c r="D280" s="14"/>
       <c r="E280" s="31"/>
       <c r="F280" s="45" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="G280" s="20">
         <f t="shared" si="21"/>
@@ -12625,7 +12570,7 @@
       <c r="D286" s="14"/>
       <c r="E286" s="31"/>
       <c r="F286" s="45" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="G286" s="20">
         <f t="shared" si="21"/>
@@ -12693,7 +12638,7 @@
       </c>
       <c r="E288" s="31"/>
       <c r="F288" s="45" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="G288" s="20">
         <f t="shared" si="21"/>
@@ -12727,7 +12672,7 @@
       </c>
       <c r="E289" s="31"/>
       <c r="F289" s="45" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="G289" s="20">
         <f t="shared" si="21"/>
@@ -12809,7 +12754,7 @@
       <c r="D292" s="14"/>
       <c r="E292" s="31"/>
       <c r="F292" s="45" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="G292" s="20">
         <f t="shared" si="21"/>
@@ -12841,7 +12786,7 @@
       <c r="D293" s="14"/>
       <c r="E293" s="31"/>
       <c r="F293" s="45" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="G293" s="20">
         <f t="shared" si="21"/>
@@ -12873,7 +12818,7 @@
       <c r="D294" s="14"/>
       <c r="E294" s="31"/>
       <c r="F294" s="45" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="G294" s="20">
         <f t="shared" si="21"/>
@@ -12905,7 +12850,7 @@
       <c r="D295" s="14"/>
       <c r="E295" s="31"/>
       <c r="F295" s="45" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="G295" s="20">
         <f t="shared" si="21"/>
@@ -12937,7 +12882,7 @@
       <c r="D296" s="14"/>
       <c r="E296" s="31"/>
       <c r="F296" s="45" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="G296" s="20">
         <f t="shared" si="21"/>
@@ -13041,7 +12986,7 @@
       <c r="D299" s="14"/>
       <c r="E299" s="31"/>
       <c r="F299" s="45" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="G299" s="20">
         <f t="shared" si="21"/>
@@ -13139,7 +13084,7 @@
       <c r="D302" s="36"/>
       <c r="E302" s="37"/>
       <c r="F302" s="70" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="G302" s="20">
         <f t="shared" si="21"/>
@@ -13164,16 +13109,16 @@
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="B303" s="21"/>
       <c r="C303" s="3"/>
       <c r="D303" s="14" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="E303" s="31"/>
       <c r="F303" s="45" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="G303" s="20">
         <f t="shared" ref="G303" si="25">COUNTA(A303)</f>
@@ -13267,11 +13212,11 @@
       <c r="B306" s="21"/>
       <c r="C306" s="3"/>
       <c r="D306" s="14" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="E306" s="31"/>
       <c r="F306" s="45" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="G306" s="20">
         <f t="shared" si="21"/>
@@ -13303,7 +13248,7 @@
       <c r="D307" s="14"/>
       <c r="E307" s="31"/>
       <c r="F307" s="45" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="G307" s="20">
         <f t="shared" si="21"/>
@@ -13335,7 +13280,7 @@
       <c r="D308" s="14"/>
       <c r="E308" s="31"/>
       <c r="F308" s="45" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="G308" s="20">
         <f t="shared" si="21"/>
@@ -13360,14 +13305,14 @@
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="B309" s="21"/>
       <c r="C309" s="3"/>
       <c r="D309" s="14"/>
       <c r="E309" s="31"/>
       <c r="F309" s="45" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="G309" s="20">
         <f t="shared" si="21"/>
@@ -13463,7 +13408,7 @@
       <c r="D312" s="14"/>
       <c r="E312" s="31"/>
       <c r="F312" s="45" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="G312" s="20">
         <f t="shared" si="21"/>
@@ -13495,7 +13440,7 @@
       <c r="D313" s="14"/>
       <c r="E313" s="31"/>
       <c r="F313" s="45" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="G313" s="20">
         <f t="shared" si="21"/>
@@ -13527,7 +13472,7 @@
       <c r="D314" s="14"/>
       <c r="E314" s="31"/>
       <c r="F314" s="45" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="G314" s="20">
         <f t="shared" si="21"/>
@@ -13559,7 +13504,7 @@
       <c r="D315" s="14"/>
       <c r="E315" s="31"/>
       <c r="F315" s="45" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="G315" s="20">
         <f t="shared" si="21"/>
@@ -13591,7 +13536,7 @@
       <c r="D316" s="14"/>
       <c r="E316" s="31"/>
       <c r="F316" s="45" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="G316" s="20">
         <f t="shared" si="21"/>
@@ -13659,7 +13604,7 @@
       <c r="D318" s="14"/>
       <c r="E318" s="31"/>
       <c r="F318" s="45" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="G318" s="20">
         <f t="shared" si="21"/>
@@ -13691,7 +13636,7 @@
       <c r="D319" s="14"/>
       <c r="E319" s="31"/>
       <c r="F319" s="45" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="G319" s="20">
         <f t="shared" si="21"/>
@@ -13723,7 +13668,7 @@
       <c r="D320" s="14"/>
       <c r="E320" s="31"/>
       <c r="F320" s="45" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="G320" s="20">
         <f t="shared" si="21"/>
@@ -13757,7 +13702,7 @@
       </c>
       <c r="E321" s="31"/>
       <c r="F321" s="45" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="G321" s="20">
         <f t="shared" si="21"/>
@@ -13789,7 +13734,7 @@
       <c r="D322" s="14"/>
       <c r="E322" s="31"/>
       <c r="F322" s="45" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="G322" s="20">
         <f t="shared" si="21"/>
@@ -13855,11 +13800,11 @@
       <c r="B324" s="21"/>
       <c r="C324" s="3"/>
       <c r="D324" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="E324" s="31"/>
       <c r="F324" s="45" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="G324" s="20">
         <f t="shared" si="21"/>
@@ -13883,7 +13828,7 @@
       <c r="D325" s="14"/>
       <c r="E325" s="31"/>
       <c r="F325" s="45" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="G325" s="20">
         <f t="shared" si="21"/>
@@ -14015,7 +13960,7 @@
       <c r="D329" s="14"/>
       <c r="E329" s="31"/>
       <c r="F329" s="45" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="G329" s="20">
         <f t="shared" ref="G329:G391" si="29">COUNTA(A329)</f>
@@ -14083,7 +14028,7 @@
       <c r="D331" s="14"/>
       <c r="E331" s="31"/>
       <c r="F331" s="45" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="G331" s="20">
         <f t="shared" si="29"/>
@@ -14183,7 +14128,7 @@
       <c r="D334" s="14"/>
       <c r="E334" s="31"/>
       <c r="F334" s="45" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="G334" s="20">
         <f t="shared" si="29"/>
@@ -14349,7 +14294,7 @@
       <c r="D339" s="14"/>
       <c r="E339" s="31"/>
       <c r="F339" s="45" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="G339" s="20">
         <f t="shared" si="29"/>
@@ -14374,14 +14319,14 @@
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="B340" s="21"/>
       <c r="C340" s="3"/>
       <c r="D340" s="14"/>
       <c r="E340" s="31"/>
       <c r="F340" s="45" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="G340" s="20">
         <f t="shared" si="29"/>
@@ -14679,7 +14624,7 @@
       <c r="D349" s="14"/>
       <c r="E349" s="31"/>
       <c r="F349" s="45" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="G349" s="20">
         <f t="shared" si="29"/>
@@ -14743,7 +14688,7 @@
       <c r="D351" s="14"/>
       <c r="E351" s="31"/>
       <c r="F351" s="45" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="G351" s="20">
         <f t="shared" si="29"/>
@@ -14871,7 +14816,7 @@
       <c r="D355" s="14"/>
       <c r="E355" s="31"/>
       <c r="F355" s="45" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="G355" s="20">
         <f t="shared" si="29"/>
@@ -15097,7 +15042,7 @@
       <c r="D362" s="14"/>
       <c r="E362" s="31"/>
       <c r="F362" s="45" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="G362" s="20">
         <f t="shared" si="29"/>
@@ -15227,7 +15172,7 @@
       <c r="D366" s="14"/>
       <c r="E366" s="31"/>
       <c r="F366" s="45" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="G366" s="20">
         <f t="shared" si="29"/>
@@ -15259,7 +15204,7 @@
       <c r="D367" s="14"/>
       <c r="E367" s="31"/>
       <c r="F367" s="45" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="G367" s="20">
         <f t="shared" si="29"/>
@@ -15293,7 +15238,7 @@
       </c>
       <c r="E368" s="31"/>
       <c r="F368" s="45" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="G368" s="20">
         <f t="shared" si="29"/>
@@ -15325,7 +15270,7 @@
       <c r="D369" s="14"/>
       <c r="E369" s="31"/>
       <c r="F369" s="45" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="G369" s="20">
         <f t="shared" si="29"/>
@@ -15493,7 +15438,7 @@
       <c r="D374" s="14"/>
       <c r="E374" s="31"/>
       <c r="F374" s="45" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="G374" s="20">
         <f t="shared" si="29"/>
@@ -15557,7 +15502,7 @@
       <c r="D376" s="14"/>
       <c r="E376" s="31"/>
       <c r="F376" s="45" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="G376" s="20">
         <f t="shared" si="29"/>
@@ -15625,7 +15570,7 @@
       <c r="D378" s="14"/>
       <c r="E378" s="31"/>
       <c r="F378" s="45" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="G378" s="20">
         <f t="shared" si="29"/>
@@ -15655,11 +15600,11 @@
       <c r="B379" s="21"/>
       <c r="C379" s="3"/>
       <c r="D379" s="14" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="E379" s="31"/>
       <c r="F379" s="45" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="G379" s="20">
         <f t="shared" si="29"/>
@@ -15691,7 +15636,7 @@
       <c r="D380" s="14"/>
       <c r="E380" s="31"/>
       <c r="F380" s="45" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="G380" s="20">
         <f t="shared" si="29"/>
@@ -15716,16 +15661,16 @@
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="B381" s="21"/>
       <c r="C381" s="3"/>
       <c r="D381" s="14" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="E381" s="31"/>
       <c r="F381" s="45" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="G381" s="20">
         <f t="shared" si="29"/>
@@ -15761,7 +15706,7 @@
         <v>15</v>
       </c>
       <c r="F382" s="45" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="G382" s="20">
         <f t="shared" si="29"/>
@@ -15793,7 +15738,7 @@
       <c r="D383" s="14"/>
       <c r="E383" s="31"/>
       <c r="F383" s="45" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="G383" s="20">
         <f t="shared" si="29"/>
@@ -15995,7 +15940,7 @@
       <c r="D389" s="14"/>
       <c r="E389" s="31"/>
       <c r="F389" s="45" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="G389" s="20">
         <f t="shared" si="29"/>
@@ -16027,7 +15972,7 @@
       <c r="D390" s="14"/>
       <c r="E390" s="31"/>
       <c r="F390" s="45" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="G390" s="20">
         <f t="shared" si="29"/>
@@ -16091,7 +16036,7 @@
       <c r="D392" s="14"/>
       <c r="E392" s="31"/>
       <c r="F392" s="45" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="G392" s="20">
         <f t="shared" ref="G392:G455" si="33">COUNTA(A392)</f>
@@ -16223,7 +16168,7 @@
       <c r="D396" s="14"/>
       <c r="E396" s="31"/>
       <c r="F396" s="45" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="G396" s="20">
         <f t="shared" si="33"/>
@@ -16255,7 +16200,7 @@
       <c r="D397" s="14"/>
       <c r="E397" s="31"/>
       <c r="F397" s="45" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="G397" s="20">
         <f t="shared" si="33"/>
@@ -16287,7 +16232,7 @@
       <c r="D398" s="14"/>
       <c r="E398" s="31"/>
       <c r="F398" s="45" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="G398" s="20">
         <f t="shared" si="33"/>
@@ -16415,7 +16360,7 @@
         <v>19</v>
       </c>
       <c r="F402" s="45" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="G402" s="20">
         <f t="shared" si="33"/>
@@ -16447,7 +16392,7 @@
       <c r="D403" s="14"/>
       <c r="E403" s="31"/>
       <c r="F403" s="45" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="G403" s="20">
         <f t="shared" si="33"/>
@@ -16479,7 +16424,7 @@
       <c r="D404" s="14"/>
       <c r="E404" s="31"/>
       <c r="F404" s="45" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="G404" s="20">
         <f t="shared" si="33"/>
@@ -16517,7 +16462,7 @@
         <v>24</v>
       </c>
       <c r="F405" s="71" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="G405" s="20">
         <f t="shared" si="33"/>
@@ -16549,7 +16494,7 @@
       <c r="D406" s="14"/>
       <c r="E406" s="31"/>
       <c r="F406" s="45" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="G406" s="20">
         <f t="shared" si="33"/>
@@ -16581,7 +16526,7 @@
       <c r="D407" s="14"/>
       <c r="E407" s="31"/>
       <c r="F407" s="45" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="G407" s="20">
         <f t="shared" si="33"/>
@@ -16681,7 +16626,7 @@
       <c r="D410" s="14"/>
       <c r="E410" s="31"/>
       <c r="F410" s="45" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="G410" s="20">
         <f t="shared" si="33"/>
@@ -16849,7 +16794,7 @@
       </c>
       <c r="E415" s="31"/>
       <c r="F415" s="45" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="G415" s="20">
         <f t="shared" si="33"/>
@@ -16873,7 +16818,7 @@
       <c r="D416" s="14"/>
       <c r="E416" s="31"/>
       <c r="F416" s="45" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="G416" s="20">
         <f t="shared" si="33"/>
@@ -17073,7 +17018,7 @@
       <c r="D422" s="14"/>
       <c r="E422" s="31"/>
       <c r="F422" s="45" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="G422" s="20">
         <f t="shared" si="33"/>
@@ -17105,7 +17050,7 @@
       <c r="D423" s="14"/>
       <c r="E423" s="31"/>
       <c r="F423" s="45" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="G423" s="20">
         <f t="shared" si="33"/>
@@ -17271,11 +17216,11 @@
       <c r="B428" s="21"/>
       <c r="C428" s="3"/>
       <c r="D428" s="14" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="E428" s="31"/>
       <c r="F428" s="45" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="G428" s="20">
         <f t="shared" si="33"/>
@@ -17329,11 +17274,11 @@
       <c r="B430" s="21"/>
       <c r="C430" s="3"/>
       <c r="D430" s="14" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="E430" s="31"/>
       <c r="F430" s="45" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="G430" s="20">
         <f t="shared" si="33"/>
@@ -17365,7 +17310,7 @@
       <c r="D431" s="14"/>
       <c r="E431" s="31"/>
       <c r="F431" s="45" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="G431" s="20">
         <f t="shared" si="33"/>
@@ -17493,7 +17438,7 @@
       <c r="D435" s="14"/>
       <c r="E435" s="31"/>
       <c r="F435" s="45" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="G435" s="20">
         <f t="shared" si="33"/>
@@ -17584,14 +17529,14 @@
     </row>
     <row r="438" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="B438" s="21"/>
       <c r="C438" s="3"/>
       <c r="D438" s="14"/>
       <c r="E438" s="31"/>
       <c r="F438" s="45" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="G438" s="20">
         <f t="shared" si="33"/>
@@ -17681,11 +17626,11 @@
       <c r="B441" s="21"/>
       <c r="C441" s="3"/>
       <c r="D441" s="14" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="E441" s="31"/>
       <c r="F441" s="45" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="G441" s="20">
         <f t="shared" si="33"/>
@@ -17923,7 +17868,7 @@
       </c>
       <c r="E448" s="31"/>
       <c r="F448" s="45" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="G448" s="20">
         <f t="shared" si="33"/>
@@ -17987,14 +17932,12 @@
         <v>5</v>
       </c>
       <c r="D450" s="13" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
       <c r="E450" s="30">
         <v>9</v>
       </c>
-      <c r="F450" s="46" t="s">
-        <v>794</v>
-      </c>
+      <c r="F450" s="46"/>
       <c r="G450" s="20">
         <f t="shared" si="33"/>
         <v>1</v>
@@ -18165,7 +18108,7 @@
       <c r="D455" s="14"/>
       <c r="E455" s="31"/>
       <c r="F455" s="45" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="G455" s="20">
         <f t="shared" si="33"/>
@@ -18301,7 +18244,7 @@
       <c r="D459" s="41"/>
       <c r="E459" s="42"/>
       <c r="F459" s="72" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="G459" s="20">
         <f t="shared" si="37"/>
@@ -18397,7 +18340,7 @@
       <c r="D462" s="14"/>
       <c r="E462" s="31"/>
       <c r="F462" s="45" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="G462" s="20">
         <f t="shared" si="37"/>
@@ -18429,7 +18372,7 @@
       <c r="D463" s="14"/>
       <c r="E463" s="31"/>
       <c r="F463" s="45" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="G463" s="20">
         <f t="shared" si="37"/>
@@ -18459,11 +18402,11 @@
       <c r="B464" s="21"/>
       <c r="C464" s="3"/>
       <c r="D464" s="14" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="E464" s="31"/>
       <c r="F464" s="45" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="G464" s="20">
         <f t="shared" si="37"/>
@@ -18551,7 +18494,7 @@
       <c r="D467" s="14"/>
       <c r="E467" s="31"/>
       <c r="F467" s="45" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="G467" s="20">
         <f t="shared" si="37"/>
@@ -18647,11 +18590,11 @@
       <c r="B470" s="21"/>
       <c r="C470" s="3"/>
       <c r="D470" s="14" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="E470" s="31"/>
       <c r="F470" s="45" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="G470" s="20">
         <f t="shared" si="37"/>
@@ -18711,16 +18654,16 @@
       </c>
     </row>
     <row r="472" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A472" s="2" t="s">
+      <c r="A472" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="B472" s="21"/>
-      <c r="C472" s="3"/>
-      <c r="D472" s="14"/>
-      <c r="E472" s="31"/>
-      <c r="F472" s="45" t="s">
-        <v>778</v>
-      </c>
+      <c r="B472" s="1"/>
+      <c r="C472" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D472" s="13"/>
+      <c r="E472" s="30"/>
+      <c r="F472" s="46"/>
       <c r="G472" s="20">
         <f t="shared" si="37"/>
         <v>1</v>
@@ -18728,7 +18671,7 @@
       <c r="H472" s="18"/>
       <c r="I472" s="19">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J472" s="19"/>
       <c r="K472" s="20"/>
@@ -18785,7 +18728,7 @@
       <c r="D474" s="14"/>
       <c r="E474" s="31"/>
       <c r="F474" s="45" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="G474" s="20">
         <f t="shared" si="37"/>
@@ -18810,14 +18753,14 @@
     </row>
     <row r="475" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="B475" s="21"/>
       <c r="C475" s="3"/>
       <c r="D475" s="14"/>
       <c r="E475" s="31"/>
       <c r="F475" s="45" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="G475" s="20">
         <f t="shared" si="37"/>
@@ -18981,7 +18924,7 @@
       <c r="D480" s="14"/>
       <c r="E480" s="31"/>
       <c r="F480" s="45" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="G480" s="20">
         <f t="shared" si="37"/>
@@ -19041,7 +18984,7 @@
         <v>5</v>
       </c>
       <c r="D482" s="13" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="E482" s="30"/>
       <c r="F482" s="43"/>
@@ -19111,11 +19054,11 @@
       <c r="B484" s="21"/>
       <c r="C484" s="3"/>
       <c r="D484" s="14" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="E484" s="31"/>
       <c r="F484" s="45" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="G484" s="20">
         <f t="shared" si="37"/>
@@ -19147,7 +19090,7 @@
       <c r="D485" s="14"/>
       <c r="E485" s="31"/>
       <c r="F485" s="45" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="G485" s="20">
         <f t="shared" si="37"/>
@@ -19335,7 +19278,7 @@
       <c r="D491" s="14"/>
       <c r="E491" s="31"/>
       <c r="F491" s="45" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="G491" s="20">
         <f t="shared" si="37"/>
@@ -19597,7 +19540,7 @@
       <c r="D499" s="14"/>
       <c r="E499" s="31"/>
       <c r="F499" s="45" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="G499" s="20">
         <f t="shared" si="37"/>
@@ -19697,7 +19640,7 @@
       <c r="D502" s="14"/>
       <c r="E502" s="31"/>
       <c r="F502" s="45" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="G502" s="20">
         <f t="shared" si="37"/>
@@ -19827,7 +19770,7 @@
       <c r="D506" s="14"/>
       <c r="E506" s="31"/>
       <c r="F506" s="45" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="G506" s="20">
         <f t="shared" si="37"/>
@@ -19859,7 +19802,7 @@
       <c r="D507" s="14"/>
       <c r="E507" s="31"/>
       <c r="F507" s="45" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="G507" s="20">
         <f t="shared" si="37"/>
@@ -19889,11 +19832,11 @@
       <c r="B508" s="21"/>
       <c r="C508" s="3"/>
       <c r="D508" s="14" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="E508" s="31"/>
       <c r="F508" s="45" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="G508" s="20">
         <f t="shared" si="37"/>
@@ -22050,223 +21993,209 @@
   <hyperlinks>
     <hyperlink ref="F6" r:id="rId1" xr:uid="{D7A0FF52-BDB0-45AF-A78C-0F14D45ADEB9}"/>
     <hyperlink ref="F10" r:id="rId2" xr:uid="{0A6C05BF-E5BA-4453-B5C4-1C6AC207FD7D}"/>
-    <hyperlink ref="F40" r:id="rId3" xr:uid="{24D0F02B-A875-4B2E-8A54-E7A443A1CDDE}"/>
-    <hyperlink ref="F48" r:id="rId4" xr:uid="{23CC66FC-BFF9-4E4E-BEE3-4905CD2701CF}"/>
-    <hyperlink ref="F49" r:id="rId5" xr:uid="{E97B6BF9-A780-4125-8A1C-3BFA145F2315}"/>
-    <hyperlink ref="F101" r:id="rId6" xr:uid="{7C397FB8-454F-4E6D-A0A9-8DBA8C35E3FD}"/>
-    <hyperlink ref="F134" r:id="rId7" xr:uid="{98187E28-91D7-4586-8A16-54DB14B71454}"/>
-    <hyperlink ref="F243" r:id="rId8" xr:uid="{E1906014-F24D-42F6-B5BD-5BF6567777B0}"/>
-    <hyperlink ref="F251" r:id="rId9" xr:uid="{092D0A70-B180-47D2-95E0-512F7DE851A2}"/>
-    <hyperlink ref="F3" r:id="rId10" xr:uid="{240B9773-2FA8-4A2D-9F8A-A7C690CE9B8C}"/>
-    <hyperlink ref="F11" r:id="rId11" xr:uid="{A0669F74-6AD4-4EBA-B30F-60C5690001BA}"/>
-    <hyperlink ref="F12" r:id="rId12" xr:uid="{D0186569-EAC3-4781-BAF9-34DAA466A8A6}"/>
-    <hyperlink ref="F13" r:id="rId13" xr:uid="{58A70D98-8E51-4AF6-8410-1023CB6D5FF9}"/>
-    <hyperlink ref="F15" r:id="rId14" xr:uid="{660B7F43-71A6-422B-88C3-4E2A530DA30E}"/>
-    <hyperlink ref="F14" r:id="rId15" xr:uid="{8ED461B0-4914-45B9-B6D9-0C72B4A333B1}"/>
-    <hyperlink ref="F16" r:id="rId16" xr:uid="{A502C1D7-1C5F-4B31-966B-90ED2032AB64}"/>
-    <hyperlink ref="F23" r:id="rId17" xr:uid="{8C45DCAB-1B50-49D9-8E4E-4205BCE068F4}"/>
-    <hyperlink ref="F25" r:id="rId18" xr:uid="{D2F0628C-7C10-43C5-8E81-FACE00308BDE}"/>
-    <hyperlink ref="F26" r:id="rId19" xr:uid="{3085D5D3-D3BD-4927-AB10-DB2FB617498C}"/>
-    <hyperlink ref="F28" r:id="rId20" xr:uid="{B3FF4F50-5CF4-489D-A988-F6D76906A632}"/>
-    <hyperlink ref="F31" r:id="rId21" xr:uid="{5B72F267-F06C-4C53-B81F-2F557BFDBBC9}"/>
-    <hyperlink ref="F35" r:id="rId22" xr:uid="{D51EBF97-EE65-4B38-9B68-103331F59DEB}"/>
-    <hyperlink ref="F38" r:id="rId23" xr:uid="{FB271DF3-47BC-40A3-8984-35BCE98A410F}"/>
-    <hyperlink ref="F42" r:id="rId24" xr:uid="{6FC9FC74-9E96-4309-8D41-24ABF40E101E}"/>
-    <hyperlink ref="F43" r:id="rId25" xr:uid="{D097568F-D244-43FC-8958-E706DCD62DB2}"/>
-    <hyperlink ref="F47" r:id="rId26" xr:uid="{82D443A2-228E-4042-BEE1-4D9A3DA9E746}"/>
-    <hyperlink ref="F53" r:id="rId27" xr:uid="{F44C4005-1777-42B4-86B1-8FDEF3BDB880}"/>
-    <hyperlink ref="F54" r:id="rId28" xr:uid="{D1350595-116B-4760-817C-F7752ED9F422}"/>
-    <hyperlink ref="F60" r:id="rId29" xr:uid="{002C9AF2-AF85-4E93-B637-66FBFAF13744}"/>
-    <hyperlink ref="F66" r:id="rId30" xr:uid="{3C0E607A-375F-462F-8109-9919470DA86A}"/>
-    <hyperlink ref="F67" r:id="rId31" xr:uid="{7ADA1535-124B-4AFF-AAB8-65C941CFB589}"/>
-    <hyperlink ref="F72" r:id="rId32" xr:uid="{1906D5D8-378E-46AB-B9D6-464CC4551E85}"/>
-    <hyperlink ref="F73" r:id="rId33" xr:uid="{04C557CB-5EF4-4CDB-B043-7DDDD782D5F4}"/>
-    <hyperlink ref="F74" r:id="rId34" xr:uid="{6830BC1E-7836-4AAF-9897-30FB8F5087A0}"/>
-    <hyperlink ref="F75" r:id="rId35" xr:uid="{A712D65D-C980-47C8-8295-0D729C30C8A1}"/>
-    <hyperlink ref="F79" r:id="rId36" xr:uid="{BCEE97FE-6B24-4FA0-BBCB-157356D1570A}"/>
-    <hyperlink ref="F82" r:id="rId37" xr:uid="{AF937CE0-C7E1-48F9-B470-E088BCAEB95E}"/>
-    <hyperlink ref="F83" r:id="rId38" xr:uid="{E5AD684B-9F41-4E7D-B48A-80197724B9C8}"/>
-    <hyperlink ref="F87" r:id="rId39" xr:uid="{B2970190-3FBE-4ECB-8BF5-BCE982416D1C}"/>
-    <hyperlink ref="F88" r:id="rId40" xr:uid="{4EB19BDD-9285-4736-A063-81B5A0C630ED}"/>
-    <hyperlink ref="F89" r:id="rId41" xr:uid="{4FB57C28-06DC-45F3-8AD0-D0A8A023AC2A}"/>
-    <hyperlink ref="F90" r:id="rId42" xr:uid="{7006595E-4235-410C-9C3B-7945CAD12F99}"/>
-    <hyperlink ref="F91" r:id="rId43" xr:uid="{4B6D1832-6A46-449A-83F8-CEC7DD98A533}"/>
-    <hyperlink ref="F102" r:id="rId44" xr:uid="{4C5BAADE-3A41-4971-A969-80819EE5AD49}"/>
-    <hyperlink ref="F103" r:id="rId45" xr:uid="{1B04D965-8D13-4DB0-A915-88E3476B65D9}"/>
-    <hyperlink ref="F105" r:id="rId46" xr:uid="{3C6D9EE6-6EA5-4D87-8E20-86D8EB653402}"/>
-    <hyperlink ref="F106" r:id="rId47" xr:uid="{0957FCED-C729-454E-809A-E08E998077EA}"/>
-    <hyperlink ref="F107" r:id="rId48" xr:uid="{5F6A54C0-CDEE-4958-905A-F9437867ABBE}"/>
-    <hyperlink ref="F109" r:id="rId49" xr:uid="{AE80F88A-60D9-4D85-A993-6BC9C54E8E43}"/>
-    <hyperlink ref="F111" r:id="rId50" xr:uid="{1CBBDB71-1D3A-414E-92E6-74CC608E54CF}"/>
-    <hyperlink ref="F112" r:id="rId51" xr:uid="{54AF6E87-6508-4ABA-BF6C-42FE3F23388E}"/>
-    <hyperlink ref="F120" r:id="rId52" xr:uid="{DEE14EDA-3A86-48BF-A90C-C9F877CD35FE}"/>
-    <hyperlink ref="F116" r:id="rId53" xr:uid="{68185A60-F5D0-49B3-A5EC-423D21AC2007}"/>
-    <hyperlink ref="F122" r:id="rId54" xr:uid="{24E4A1F1-F5EE-4142-A628-552DF253559E}"/>
-    <hyperlink ref="F125" r:id="rId55" xr:uid="{419B072F-2A71-427A-8511-E911DAF28DD7}"/>
-    <hyperlink ref="F124" r:id="rId56" xr:uid="{B93D5E91-2959-4BDF-B626-9B3C6F9042E3}"/>
-    <hyperlink ref="F126" r:id="rId57" xr:uid="{3AA089E2-3E0E-4693-9903-60A5A001B103}"/>
-    <hyperlink ref="F137" r:id="rId58" xr:uid="{87732D99-B749-43F8-BDE7-FC106CA07CF8}"/>
-    <hyperlink ref="F138" r:id="rId59" xr:uid="{FC689C5A-BDEA-4808-8A97-F7B0B28C31EB}"/>
-    <hyperlink ref="F139" r:id="rId60" xr:uid="{D05C6D5C-00B8-4D80-B8FB-A900146D93E1}"/>
-    <hyperlink ref="F140" r:id="rId61" xr:uid="{551B4426-E1E0-43C4-8DAC-5948E2888EB1}"/>
-    <hyperlink ref="F141" r:id="rId62" xr:uid="{92C14F4A-A5B1-4338-9801-23C126FA3E9C}"/>
-    <hyperlink ref="F142" r:id="rId63" xr:uid="{0E574DDD-345A-44D0-865B-0D5104620825}"/>
-    <hyperlink ref="F146" r:id="rId64" xr:uid="{73F6255A-A93E-4595-AA53-5A87E3C27E02}"/>
-    <hyperlink ref="F148" r:id="rId65" xr:uid="{555BB1F1-6921-4BBF-A3C1-DF3A69819E1F}"/>
-    <hyperlink ref="F151" r:id="rId66" xr:uid="{29590BA1-3CB5-4D8F-A9C1-C0F8B88E6C20}"/>
-    <hyperlink ref="F152" r:id="rId67" xr:uid="{AF5738C0-2C53-4D5E-BDCF-38B5DF4F7134}"/>
-    <hyperlink ref="F157" r:id="rId68" xr:uid="{4BA46DF7-AE35-4E62-B41F-8E633F057A9A}"/>
-    <hyperlink ref="F162" r:id="rId69" xr:uid="{DF630741-5347-4C4B-9C1A-34AB0B55FAB0}"/>
-    <hyperlink ref="F163" r:id="rId70" xr:uid="{52017FD8-4913-4C76-84FB-21BAFCD9288A}"/>
-    <hyperlink ref="F164" r:id="rId71" xr:uid="{DBEE5566-25B3-4F5D-90DB-BA92C820C8E9}"/>
-    <hyperlink ref="F168" r:id="rId72" xr:uid="{43D957EA-1220-4546-81AA-6EA0068891D1}"/>
-    <hyperlink ref="F169" r:id="rId73" xr:uid="{7D1F69E7-F80A-4033-A995-CFFAB7E6F3AA}"/>
-    <hyperlink ref="F170" r:id="rId74" xr:uid="{1B49C331-115C-46C8-96EA-88842B37909B}"/>
-    <hyperlink ref="F174" r:id="rId75" xr:uid="{8D1656FB-2390-452F-9A98-C57CD66A9527}"/>
-    <hyperlink ref="F175" r:id="rId76" xr:uid="{87F70932-053A-4078-A2BB-0C916D89F0B6}"/>
-    <hyperlink ref="F176" r:id="rId77" xr:uid="{2E536698-8412-4A34-B6BE-0E9D942DE08A}"/>
-    <hyperlink ref="F177" r:id="rId78" xr:uid="{C7A97165-6B18-4AAE-8880-54BA736B7FBB}"/>
-    <hyperlink ref="F179" r:id="rId79" xr:uid="{0ADDB00F-0E69-42F1-A4C3-523460E97CF9}"/>
-    <hyperlink ref="F181" r:id="rId80" xr:uid="{04A97764-C901-4BFF-B0C0-CA7A4FB23F12}"/>
-    <hyperlink ref="F182" r:id="rId81" xr:uid="{EEAD67A7-F127-4695-AC27-5E64955952C4}"/>
-    <hyperlink ref="F185" r:id="rId82" xr:uid="{604C72FF-CA76-4346-BBD2-8B254124A21A}"/>
-    <hyperlink ref="F187" r:id="rId83" xr:uid="{769F7894-B4C7-495E-91B8-D1C7B99BB9E8}"/>
-    <hyperlink ref="F193" r:id="rId84" xr:uid="{CBBB0CE0-21E7-450D-A780-B3B522F44A28}"/>
-    <hyperlink ref="F205" r:id="rId85" xr:uid="{062006D4-AE93-4260-BFBC-B0AE1882E9E4}"/>
-    <hyperlink ref="F213" r:id="rId86" xr:uid="{D3B8250E-417A-4C93-8528-85C67429E67D}"/>
-    <hyperlink ref="F215" r:id="rId87" xr:uid="{0E509337-19B5-4302-AD5A-45F3F9A8A099}"/>
-    <hyperlink ref="F216" r:id="rId88" xr:uid="{9E60156C-8968-48E1-8B49-70AC3760A6C0}"/>
-    <hyperlink ref="F218" r:id="rId89" xr:uid="{A17419D8-CCBC-45AC-B8F0-7E4BF649C88A}"/>
-    <hyperlink ref="F223" r:id="rId90" xr:uid="{0DA1AC25-F430-4455-A205-6DE7A95F8B36}"/>
-    <hyperlink ref="F222" r:id="rId91" xr:uid="{899E51D5-08F2-4951-8381-783E45598A7C}"/>
-    <hyperlink ref="F226" r:id="rId92" xr:uid="{ABAFAB82-84B1-4E42-81FC-C18D41781682}"/>
-    <hyperlink ref="F227" r:id="rId93" xr:uid="{B6A85E32-F71B-47DF-931E-B36AAC6DDC3C}"/>
-    <hyperlink ref="F229" r:id="rId94" xr:uid="{683025DB-DF40-44F8-8FC6-631B454B394C}"/>
-    <hyperlink ref="F233" r:id="rId95" xr:uid="{35BC5032-5A6C-457E-B395-CC22883B245B}"/>
-    <hyperlink ref="F240" r:id="rId96" xr:uid="{965DC3FC-7483-43A0-8519-B6B1CFE9540A}"/>
-    <hyperlink ref="F241" r:id="rId97" xr:uid="{A37E6543-1D3E-4781-AB91-22511575D05B}"/>
-    <hyperlink ref="F242" r:id="rId98" xr:uid="{5FFC4DAB-F374-41E9-8B47-2EF464C2C536}"/>
-    <hyperlink ref="F244" r:id="rId99" xr:uid="{21768D99-C089-4DC1-A53E-266E758687C5}"/>
-    <hyperlink ref="F245" r:id="rId100" xr:uid="{12D9319F-5A87-4ACB-8631-89B7EB5B7871}"/>
-    <hyperlink ref="F247" r:id="rId101" xr:uid="{3D734675-475D-49CB-AC3A-1AA184658D00}"/>
-    <hyperlink ref="F248" r:id="rId102" xr:uid="{601F76B0-2BDD-4217-83A4-E1D708C84C54}"/>
-    <hyperlink ref="F249" r:id="rId103" xr:uid="{0A1BA194-5A1D-4A17-AE7B-F1DBD179498A}"/>
-    <hyperlink ref="F252" r:id="rId104" xr:uid="{8A58FF55-8B70-4BE0-A7D2-84512CFF69EB}"/>
-    <hyperlink ref="F257" r:id="rId105" xr:uid="{565102C8-B4B3-4CA9-A13D-AA08F0B1F501}"/>
-    <hyperlink ref="F260" r:id="rId106" xr:uid="{888081FC-B79F-4537-A612-589B4AA24A5F}"/>
-    <hyperlink ref="F264" r:id="rId107" xr:uid="{B89A7894-A653-457E-B297-66EEF7E78CCD}"/>
-    <hyperlink ref="F265" r:id="rId108" xr:uid="{C1F38060-8982-4B83-89B9-3ACB71AAE7E9}"/>
-    <hyperlink ref="F266" r:id="rId109" xr:uid="{90A2D3D4-11E9-4E70-9F26-57374F26E828}"/>
-    <hyperlink ref="F267" r:id="rId110" xr:uid="{CE2AC91D-F72D-498F-8D0D-E22DF8700BFD}"/>
-    <hyperlink ref="F268" r:id="rId111" xr:uid="{E35AF51A-834D-4EFC-823F-4026E999DF7A}"/>
-    <hyperlink ref="F269" r:id="rId112" xr:uid="{558DB0B2-17D5-4A39-AAB8-814B18D28642}"/>
-    <hyperlink ref="F273" r:id="rId113" xr:uid="{A613562F-CFC5-4214-AF12-2CFDD342953A}"/>
-    <hyperlink ref="F274" r:id="rId114" xr:uid="{CBD79827-526D-4DFF-97E6-5306C293752C}"/>
-    <hyperlink ref="F277" r:id="rId115" xr:uid="{09E53517-D130-471F-B71B-653DFA8A8955}"/>
-    <hyperlink ref="F276" r:id="rId116" xr:uid="{30A1C381-1EDC-4BFC-804E-FBB45AC51FEF}"/>
-    <hyperlink ref="F278" r:id="rId117" xr:uid="{A26AA755-950A-4B52-9312-83FA946F9EA2}"/>
-    <hyperlink ref="F280" r:id="rId118" xr:uid="{05C39E49-F52C-40AB-B184-32A8BEA8FA7A}"/>
-    <hyperlink ref="F286" r:id="rId119" xr:uid="{6FCC01F3-1F01-4694-8770-C3C00E5E496C}"/>
-    <hyperlink ref="F288" r:id="rId120" xr:uid="{ACDA379B-D785-41F9-A567-FACF7027F155}"/>
-    <hyperlink ref="F289" r:id="rId121" xr:uid="{55184FCA-C9E5-4C87-B518-47BB97CC674F}"/>
-    <hyperlink ref="F292" r:id="rId122" xr:uid="{183A293E-7539-47D2-9CDE-B3563DB11191}"/>
-    <hyperlink ref="F293" r:id="rId123" xr:uid="{A37CFD74-5F70-453B-9C1A-31C32E66D91A}"/>
-    <hyperlink ref="F294" r:id="rId124" xr:uid="{1A424E49-407B-4819-9BAE-BD7020E136C8}"/>
-    <hyperlink ref="F295" r:id="rId125" xr:uid="{16772841-91B4-4063-B41A-59B960FDEFC4}"/>
-    <hyperlink ref="F296" r:id="rId126" xr:uid="{F8E811E4-C56E-4020-8515-CA14E5BC6E3C}"/>
-    <hyperlink ref="F299" r:id="rId127" xr:uid="{8169F733-8E2D-4AC1-9A4F-A49A54D41A52}"/>
-    <hyperlink ref="F302" r:id="rId128" xr:uid="{0CE762D6-744B-40A7-8F98-8AF1053C4C20}"/>
-    <hyperlink ref="F306" r:id="rId129" xr:uid="{091067F1-8D60-40C3-B79B-EDA05B5A7DA4}"/>
-    <hyperlink ref="F307" r:id="rId130" xr:uid="{AC3C0A2F-C850-4DC8-B816-62B521573541}"/>
-    <hyperlink ref="F308" r:id="rId131" xr:uid="{BD4C4423-9801-48B9-BE4A-6FA8B9B411A4}"/>
-    <hyperlink ref="F309" r:id="rId132" xr:uid="{03558391-13D5-417E-8518-5A118844CD95}"/>
-    <hyperlink ref="F312" r:id="rId133" xr:uid="{2005E731-59D7-4620-B28C-434266F6022D}"/>
-    <hyperlink ref="F313" r:id="rId134" xr:uid="{2FD5242C-CF0A-4A63-816A-EA2A83984E64}"/>
-    <hyperlink ref="F314" r:id="rId135" xr:uid="{3123CD08-C684-4CC9-AB12-F9105EA97288}"/>
-    <hyperlink ref="F315" r:id="rId136" xr:uid="{2213C59C-4A61-40A9-A06B-1FEF17A027B0}"/>
-    <hyperlink ref="F316" r:id="rId137" xr:uid="{68B28FC2-AA1F-41B6-9A23-516E9B83B6E0}"/>
-    <hyperlink ref="F318" r:id="rId138" xr:uid="{B5599032-4454-4E2C-A68F-8CFFE50F4FDA}"/>
-    <hyperlink ref="F319" r:id="rId139" xr:uid="{A0B5737A-A70A-4218-B2E1-A76C8720DB56}"/>
-    <hyperlink ref="F320" r:id="rId140" xr:uid="{D4B5840E-77B4-47E2-8436-CD2E572AF2B8}"/>
-    <hyperlink ref="F321" r:id="rId141" xr:uid="{BD67BD55-40E9-45BF-A3F6-8F5115DDB229}"/>
-    <hyperlink ref="F322" r:id="rId142" xr:uid="{006FB328-F8E9-4758-AE01-3843E2E75398}"/>
-    <hyperlink ref="F324" r:id="rId143" xr:uid="{D8274070-5E6A-448F-BE2B-E62287C27B7F}"/>
-    <hyperlink ref="F325" r:id="rId144" xr:uid="{3107A474-1B13-410C-98D5-4BDFF1B318A0}"/>
-    <hyperlink ref="F329" r:id="rId145" xr:uid="{AEE59407-C7BF-4741-8788-B6DE8B5B56F0}"/>
-    <hyperlink ref="F331" r:id="rId146" xr:uid="{9E43F2AF-CA8D-45AD-8AF2-43E79516D8C4}"/>
-    <hyperlink ref="F334" r:id="rId147" xr:uid="{527DB674-2191-4390-A5E3-AF104DB8B4DD}"/>
-    <hyperlink ref="F339" r:id="rId148" xr:uid="{6CBC3A1F-EFB9-4C79-8568-CA7B9F4AE2C5}"/>
-    <hyperlink ref="F349" r:id="rId149" xr:uid="{15A14E1E-9440-4524-8E71-E2F0B928B953}"/>
-    <hyperlink ref="F351" r:id="rId150" xr:uid="{C92EA61B-8F06-42A1-A7F9-7F45453FF60F}"/>
-    <hyperlink ref="F355" r:id="rId151" xr:uid="{8A245E57-176A-4426-987A-230A824E21F5}"/>
-    <hyperlink ref="F362" r:id="rId152" xr:uid="{E66A3719-554E-4E28-86A4-324883D73CAE}"/>
-    <hyperlink ref="F366" r:id="rId153" xr:uid="{7BDE2C38-EC1A-4C17-B1C6-1E4D17FC0EE5}"/>
-    <hyperlink ref="F367" r:id="rId154" xr:uid="{00F24AF7-BECF-42F0-AB31-2C0DED0C37A2}"/>
-    <hyperlink ref="F368" r:id="rId155" xr:uid="{5852A063-4D20-4FBB-B346-BF786AFC86EC}"/>
-    <hyperlink ref="F369" r:id="rId156" xr:uid="{B67214DC-0A47-4AD1-BF86-5DC069815DE1}"/>
-    <hyperlink ref="F374" r:id="rId157" xr:uid="{8299AD99-FFD7-4B97-A788-030B31407DDD}"/>
-    <hyperlink ref="F376" r:id="rId158" xr:uid="{78971510-8CDC-4BF5-AE19-0D07D647D047}"/>
-    <hyperlink ref="F378" r:id="rId159" xr:uid="{A0C94A52-B22E-4392-9DAE-3EA37FFA5A46}"/>
-    <hyperlink ref="F379" r:id="rId160" xr:uid="{3B87B23F-40F6-462E-9110-A5A9A19D2232}"/>
-    <hyperlink ref="F380" r:id="rId161" xr:uid="{292120C3-4914-44B9-9098-59807C6E7C6C}"/>
-    <hyperlink ref="F381" r:id="rId162" xr:uid="{5B5091B4-FEAA-4CAD-8FAF-43B120B259B8}"/>
-    <hyperlink ref="F382" r:id="rId163" xr:uid="{B4A8D738-F438-4B79-8C25-2D43D085BC71}"/>
-    <hyperlink ref="F383" r:id="rId164" xr:uid="{9C2371F9-4C06-48FC-AD5B-9E5916618520}"/>
-    <hyperlink ref="F389" r:id="rId165" xr:uid="{2C42E22B-0DD1-40FA-8493-10406BA7A1D9}"/>
-    <hyperlink ref="F390" r:id="rId166" xr:uid="{70286227-A588-43E1-91FC-1EB348F42574}"/>
-    <hyperlink ref="F392" r:id="rId167" xr:uid="{D1A39FB3-D165-4B56-88B9-CFB02C80378B}"/>
-    <hyperlink ref="F396" r:id="rId168" xr:uid="{86B3426F-8CFE-45AB-9DE6-873C49E7DB80}"/>
-    <hyperlink ref="F397" r:id="rId169" xr:uid="{6F07A94A-75BF-4D0C-A155-1F147D55686D}"/>
-    <hyperlink ref="F398" r:id="rId170" xr:uid="{925770DF-4D55-4F2C-B57F-546C6CF49F83}"/>
-    <hyperlink ref="F402" r:id="rId171" xr:uid="{86833F34-D3B8-49A2-B048-9143D1D268E1}"/>
-    <hyperlink ref="F403" r:id="rId172" xr:uid="{DC475E94-CED6-4041-A19D-421EDEC91083}"/>
-    <hyperlink ref="F404" r:id="rId173" xr:uid="{8CE58332-34FE-45F0-B53E-D28E50ECC3F5}"/>
-    <hyperlink ref="F405" r:id="rId174" xr:uid="{DD0386C7-D589-4779-A82D-1F72C4B6FBDD}"/>
-    <hyperlink ref="F406" r:id="rId175" xr:uid="{BC460B10-00B8-4916-B3EF-7D1ED959A78B}"/>
-    <hyperlink ref="F407" r:id="rId176" xr:uid="{40729791-C768-4D88-821E-9253252FB0F3}"/>
-    <hyperlink ref="F410" r:id="rId177" xr:uid="{BCA7C023-C424-401D-88B3-107FB2ACBF81}"/>
-    <hyperlink ref="F415" r:id="rId178" xr:uid="{43A41B2A-DEFE-495E-997D-ED085CF2FC91}"/>
-    <hyperlink ref="F416" r:id="rId179" xr:uid="{B12F044C-CB46-4CCB-89F1-EB0C8F7EB892}"/>
-    <hyperlink ref="F422" r:id="rId180" xr:uid="{28D016CB-3B77-415C-8166-D13FE68341D1}"/>
-    <hyperlink ref="F423" r:id="rId181" xr:uid="{CD429C9A-749F-491E-9E58-B9CB7A90A2FB}"/>
-    <hyperlink ref="F428" r:id="rId182" xr:uid="{5CC5C5A2-EE60-4284-8128-2E87C488D632}"/>
-    <hyperlink ref="F431" r:id="rId183" xr:uid="{C2BD70BB-F593-4AF0-B6A4-B32D5304C625}"/>
-    <hyperlink ref="F435" r:id="rId184" xr:uid="{F6E6F0EA-9817-4AA3-BC4A-B1ED8E6931ED}"/>
-    <hyperlink ref="F438" r:id="rId185" xr:uid="{5EB5671F-FF63-475A-9238-21AD45B4C5EE}"/>
-    <hyperlink ref="F441" r:id="rId186" xr:uid="{B97349D3-8379-49CF-AB1C-503D2A28FCDC}"/>
-    <hyperlink ref="F448" r:id="rId187" xr:uid="{DCBAF156-741D-4CDD-A1BB-BEE3DCAFC7E4}"/>
-    <hyperlink ref="F455" r:id="rId188" xr:uid="{8B8F94DD-ABB2-4320-920C-216E8ECE661F}"/>
-    <hyperlink ref="F340" r:id="rId189" xr:uid="{A1876CDA-D2D9-4ACE-9E52-75F2A87E4D4F}"/>
-    <hyperlink ref="F459" r:id="rId190" xr:uid="{21AFB719-500D-49EA-9A94-E1F0F8DEAF1D}"/>
-    <hyperlink ref="F462" r:id="rId191" xr:uid="{9FB30793-74F5-4EE1-997B-A29276854B0F}"/>
-    <hyperlink ref="F463" r:id="rId192" xr:uid="{F7D721C1-6EE7-431C-825B-C14B050040BE}"/>
-    <hyperlink ref="F464" r:id="rId193" xr:uid="{E82C3262-E183-4FD0-A624-6B9CBBA13E22}"/>
-    <hyperlink ref="F467" r:id="rId194" xr:uid="{2F3A224E-996D-44F2-BB99-EC5746F0E81D}"/>
-    <hyperlink ref="F470" r:id="rId195" xr:uid="{66281EB3-1C84-4327-8A41-AC8CB05AAABD}"/>
-    <hyperlink ref="F472" r:id="rId196" xr:uid="{E3C74E77-C496-4510-8806-2D2606716F78}"/>
-    <hyperlink ref="F474" r:id="rId197" xr:uid="{9BE712DE-053D-4691-8A07-B0D3C3304A32}"/>
-    <hyperlink ref="F475" r:id="rId198" xr:uid="{97572BBD-E6D2-4CFC-B983-6629083AAA30}"/>
-    <hyperlink ref="F480" r:id="rId199" xr:uid="{F9FBA57F-7D2B-4679-A566-A492ECEF9035}"/>
-    <hyperlink ref="F484" r:id="rId200" xr:uid="{5942006B-880C-4C23-9ED8-EE6DF160CAFC}"/>
-    <hyperlink ref="F485" r:id="rId201" xr:uid="{93B54EDE-1866-4706-A5FE-E39688316329}"/>
-    <hyperlink ref="F491" r:id="rId202" xr:uid="{D1F916D6-B062-4FD4-9C02-9546DAF97B5D}"/>
-    <hyperlink ref="F499" r:id="rId203" xr:uid="{82BB8238-8B3C-44CF-B8DB-8B220659D0F1}"/>
-    <hyperlink ref="F502" r:id="rId204" xr:uid="{BC41CEBA-AAE5-49A0-8216-3B4403811C0B}"/>
-    <hyperlink ref="F506" r:id="rId205" xr:uid="{3ED9D9C9-88BD-4D38-8C17-2147C43DCA41}"/>
-    <hyperlink ref="F507" r:id="rId206" xr:uid="{8EE4BBCE-100C-422D-A8AE-E1855B7531DD}"/>
-    <hyperlink ref="F508" r:id="rId207" xr:uid="{7393F241-1EE0-4975-B705-3BB32A866045}"/>
-    <hyperlink ref="F450" r:id="rId208" xr:uid="{80AE22F1-0F21-450E-BE5A-444AA127014C}"/>
-    <hyperlink ref="F45" r:id="rId209" xr:uid="{9166A086-6452-4A3C-AEE1-EA61B6F0040C}"/>
-    <hyperlink ref="F63" r:id="rId210" xr:uid="{C3D2727A-54A4-4ABC-BE29-C663282CB00F}"/>
-    <hyperlink ref="F65" r:id="rId211" xr:uid="{290EDB11-A937-4642-B4C4-762CABC87A86}"/>
-    <hyperlink ref="F92" r:id="rId212" xr:uid="{7BD3346D-C133-4F85-BA8B-06E893A5AA15}"/>
-    <hyperlink ref="F236" r:id="rId213" xr:uid="{A89FDFBB-71B2-4738-9E20-379D288195B3}"/>
-    <hyperlink ref="F237" r:id="rId214" xr:uid="{71BBAFA0-9838-4AE0-B1A3-8148C5047B22}"/>
-    <hyperlink ref="F430" r:id="rId215" xr:uid="{CE9B73F7-6206-43BE-A0D7-238A375EF8C2}"/>
-    <hyperlink ref="F303" r:id="rId216" xr:uid="{95974537-849E-47AD-A8B3-2D3E2FBBC6C7}"/>
+    <hyperlink ref="F101" r:id="rId3" xr:uid="{7C397FB8-454F-4E6D-A0A9-8DBA8C35E3FD}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{240B9773-2FA8-4A2D-9F8A-A7C690CE9B8C}"/>
+    <hyperlink ref="F11" r:id="rId5" xr:uid="{A0669F74-6AD4-4EBA-B30F-60C5690001BA}"/>
+    <hyperlink ref="F12" r:id="rId6" xr:uid="{D0186569-EAC3-4781-BAF9-34DAA466A8A6}"/>
+    <hyperlink ref="F13" r:id="rId7" xr:uid="{58A70D98-8E51-4AF6-8410-1023CB6D5FF9}"/>
+    <hyperlink ref="F15" r:id="rId8" xr:uid="{660B7F43-71A6-422B-88C3-4E2A530DA30E}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{8ED461B0-4914-45B9-B6D9-0C72B4A333B1}"/>
+    <hyperlink ref="F16" r:id="rId10" xr:uid="{A502C1D7-1C5F-4B31-966B-90ED2032AB64}"/>
+    <hyperlink ref="F23" r:id="rId11" xr:uid="{8C45DCAB-1B50-49D9-8E4E-4205BCE068F4}"/>
+    <hyperlink ref="F26" r:id="rId12" xr:uid="{3085D5D3-D3BD-4927-AB10-DB2FB617498C}"/>
+    <hyperlink ref="F28" r:id="rId13" xr:uid="{B3FF4F50-5CF4-489D-A988-F6D76906A632}"/>
+    <hyperlink ref="F31" r:id="rId14" xr:uid="{5B72F267-F06C-4C53-B81F-2F557BFDBBC9}"/>
+    <hyperlink ref="F35" r:id="rId15" xr:uid="{D51EBF97-EE65-4B38-9B68-103331F59DEB}"/>
+    <hyperlink ref="F38" r:id="rId16" xr:uid="{FB271DF3-47BC-40A3-8984-35BCE98A410F}"/>
+    <hyperlink ref="F42" r:id="rId17" xr:uid="{6FC9FC74-9E96-4309-8D41-24ABF40E101E}"/>
+    <hyperlink ref="F43" r:id="rId18" xr:uid="{D097568F-D244-43FC-8958-E706DCD62DB2}"/>
+    <hyperlink ref="F47" r:id="rId19" xr:uid="{82D443A2-228E-4042-BEE1-4D9A3DA9E746}"/>
+    <hyperlink ref="F53" r:id="rId20" xr:uid="{F44C4005-1777-42B4-86B1-8FDEF3BDB880}"/>
+    <hyperlink ref="F54" r:id="rId21" xr:uid="{D1350595-116B-4760-817C-F7752ED9F422}"/>
+    <hyperlink ref="F60" r:id="rId22" xr:uid="{002C9AF2-AF85-4E93-B637-66FBFAF13744}"/>
+    <hyperlink ref="F66" r:id="rId23" xr:uid="{3C0E607A-375F-462F-8109-9919470DA86A}"/>
+    <hyperlink ref="F67" r:id="rId24" xr:uid="{7ADA1535-124B-4AFF-AAB8-65C941CFB589}"/>
+    <hyperlink ref="F72" r:id="rId25" xr:uid="{1906D5D8-378E-46AB-B9D6-464CC4551E85}"/>
+    <hyperlink ref="F73" r:id="rId26" xr:uid="{04C557CB-5EF4-4CDB-B043-7DDDD782D5F4}"/>
+    <hyperlink ref="F74" r:id="rId27" xr:uid="{6830BC1E-7836-4AAF-9897-30FB8F5087A0}"/>
+    <hyperlink ref="F75" r:id="rId28" xr:uid="{A712D65D-C980-47C8-8295-0D729C30C8A1}"/>
+    <hyperlink ref="F79" r:id="rId29" xr:uid="{BCEE97FE-6B24-4FA0-BBCB-157356D1570A}"/>
+    <hyperlink ref="F82" r:id="rId30" xr:uid="{AF937CE0-C7E1-48F9-B470-E088BCAEB95E}"/>
+    <hyperlink ref="F83" r:id="rId31" xr:uid="{E5AD684B-9F41-4E7D-B48A-80197724B9C8}"/>
+    <hyperlink ref="F87" r:id="rId32" xr:uid="{B2970190-3FBE-4ECB-8BF5-BCE982416D1C}"/>
+    <hyperlink ref="F88" r:id="rId33" xr:uid="{4EB19BDD-9285-4736-A063-81B5A0C630ED}"/>
+    <hyperlink ref="F89" r:id="rId34" xr:uid="{4FB57C28-06DC-45F3-8AD0-D0A8A023AC2A}"/>
+    <hyperlink ref="F90" r:id="rId35" xr:uid="{7006595E-4235-410C-9C3B-7945CAD12F99}"/>
+    <hyperlink ref="F91" r:id="rId36" xr:uid="{4B6D1832-6A46-449A-83F8-CEC7DD98A533}"/>
+    <hyperlink ref="F102" r:id="rId37" xr:uid="{4C5BAADE-3A41-4971-A969-80819EE5AD49}"/>
+    <hyperlink ref="F103" r:id="rId38" xr:uid="{1B04D965-8D13-4DB0-A915-88E3476B65D9}"/>
+    <hyperlink ref="F105" r:id="rId39" xr:uid="{3C6D9EE6-6EA5-4D87-8E20-86D8EB653402}"/>
+    <hyperlink ref="F106" r:id="rId40" xr:uid="{0957FCED-C729-454E-809A-E08E998077EA}"/>
+    <hyperlink ref="F107" r:id="rId41" xr:uid="{5F6A54C0-CDEE-4958-905A-F9437867ABBE}"/>
+    <hyperlink ref="F109" r:id="rId42" xr:uid="{AE80F88A-60D9-4D85-A993-6BC9C54E8E43}"/>
+    <hyperlink ref="F111" r:id="rId43" xr:uid="{1CBBDB71-1D3A-414E-92E6-74CC608E54CF}"/>
+    <hyperlink ref="F112" r:id="rId44" xr:uid="{54AF6E87-6508-4ABA-BF6C-42FE3F23388E}"/>
+    <hyperlink ref="F120" r:id="rId45" xr:uid="{DEE14EDA-3A86-48BF-A90C-C9F877CD35FE}"/>
+    <hyperlink ref="F116" r:id="rId46" xr:uid="{68185A60-F5D0-49B3-A5EC-423D21AC2007}"/>
+    <hyperlink ref="F122" r:id="rId47" xr:uid="{24E4A1F1-F5EE-4142-A628-552DF253559E}"/>
+    <hyperlink ref="F125" r:id="rId48" xr:uid="{419B072F-2A71-427A-8511-E911DAF28DD7}"/>
+    <hyperlink ref="F124" r:id="rId49" xr:uid="{B93D5E91-2959-4BDF-B626-9B3C6F9042E3}"/>
+    <hyperlink ref="F126" r:id="rId50" xr:uid="{3AA089E2-3E0E-4693-9903-60A5A001B103}"/>
+    <hyperlink ref="F137" r:id="rId51" xr:uid="{87732D99-B749-43F8-BDE7-FC106CA07CF8}"/>
+    <hyperlink ref="F138" r:id="rId52" xr:uid="{FC689C5A-BDEA-4808-8A97-F7B0B28C31EB}"/>
+    <hyperlink ref="F139" r:id="rId53" xr:uid="{D05C6D5C-00B8-4D80-B8FB-A900146D93E1}"/>
+    <hyperlink ref="F140" r:id="rId54" xr:uid="{551B4426-E1E0-43C4-8DAC-5948E2888EB1}"/>
+    <hyperlink ref="F141" r:id="rId55" xr:uid="{92C14F4A-A5B1-4338-9801-23C126FA3E9C}"/>
+    <hyperlink ref="F142" r:id="rId56" xr:uid="{0E574DDD-345A-44D0-865B-0D5104620825}"/>
+    <hyperlink ref="F148" r:id="rId57" xr:uid="{555BB1F1-6921-4BBF-A3C1-DF3A69819E1F}"/>
+    <hyperlink ref="F151" r:id="rId58" xr:uid="{29590BA1-3CB5-4D8F-A9C1-C0F8B88E6C20}"/>
+    <hyperlink ref="F152" r:id="rId59" xr:uid="{AF5738C0-2C53-4D5E-BDCF-38B5DF4F7134}"/>
+    <hyperlink ref="F157" r:id="rId60" xr:uid="{4BA46DF7-AE35-4E62-B41F-8E633F057A9A}"/>
+    <hyperlink ref="F162" r:id="rId61" xr:uid="{DF630741-5347-4C4B-9C1A-34AB0B55FAB0}"/>
+    <hyperlink ref="F163" r:id="rId62" xr:uid="{52017FD8-4913-4C76-84FB-21BAFCD9288A}"/>
+    <hyperlink ref="F164" r:id="rId63" xr:uid="{DBEE5566-25B3-4F5D-90DB-BA92C820C8E9}"/>
+    <hyperlink ref="F168" r:id="rId64" xr:uid="{43D957EA-1220-4546-81AA-6EA0068891D1}"/>
+    <hyperlink ref="F169" r:id="rId65" xr:uid="{7D1F69E7-F80A-4033-A995-CFFAB7E6F3AA}"/>
+    <hyperlink ref="F170" r:id="rId66" xr:uid="{1B49C331-115C-46C8-96EA-88842B37909B}"/>
+    <hyperlink ref="F174" r:id="rId67" xr:uid="{8D1656FB-2390-452F-9A98-C57CD66A9527}"/>
+    <hyperlink ref="F175" r:id="rId68" xr:uid="{87F70932-053A-4078-A2BB-0C916D89F0B6}"/>
+    <hyperlink ref="F176" r:id="rId69" xr:uid="{2E536698-8412-4A34-B6BE-0E9D942DE08A}"/>
+    <hyperlink ref="F177" r:id="rId70" xr:uid="{C7A97165-6B18-4AAE-8880-54BA736B7FBB}"/>
+    <hyperlink ref="F179" r:id="rId71" xr:uid="{0ADDB00F-0E69-42F1-A4C3-523460E97CF9}"/>
+    <hyperlink ref="F181" r:id="rId72" xr:uid="{04A97764-C901-4BFF-B0C0-CA7A4FB23F12}"/>
+    <hyperlink ref="F182" r:id="rId73" xr:uid="{EEAD67A7-F127-4695-AC27-5E64955952C4}"/>
+    <hyperlink ref="F185" r:id="rId74" xr:uid="{604C72FF-CA76-4346-BBD2-8B254124A21A}"/>
+    <hyperlink ref="F187" r:id="rId75" xr:uid="{769F7894-B4C7-495E-91B8-D1C7B99BB9E8}"/>
+    <hyperlink ref="F193" r:id="rId76" xr:uid="{CBBB0CE0-21E7-450D-A780-B3B522F44A28}"/>
+    <hyperlink ref="F205" r:id="rId77" xr:uid="{062006D4-AE93-4260-BFBC-B0AE1882E9E4}"/>
+    <hyperlink ref="F213" r:id="rId78" xr:uid="{D3B8250E-417A-4C93-8528-85C67429E67D}"/>
+    <hyperlink ref="F223" r:id="rId79" xr:uid="{0DA1AC25-F430-4455-A205-6DE7A95F8B36}"/>
+    <hyperlink ref="F222" r:id="rId80" xr:uid="{899E51D5-08F2-4951-8381-783E45598A7C}"/>
+    <hyperlink ref="F226" r:id="rId81" xr:uid="{ABAFAB82-84B1-4E42-81FC-C18D41781682}"/>
+    <hyperlink ref="F227" r:id="rId82" xr:uid="{B6A85E32-F71B-47DF-931E-B36AAC6DDC3C}"/>
+    <hyperlink ref="F229" r:id="rId83" xr:uid="{683025DB-DF40-44F8-8FC6-631B454B394C}"/>
+    <hyperlink ref="F233" r:id="rId84" xr:uid="{35BC5032-5A6C-457E-B395-CC22883B245B}"/>
+    <hyperlink ref="F240" r:id="rId85" xr:uid="{965DC3FC-7483-43A0-8519-B6B1CFE9540A}"/>
+    <hyperlink ref="F241" r:id="rId86" xr:uid="{A37E6543-1D3E-4781-AB91-22511575D05B}"/>
+    <hyperlink ref="F242" r:id="rId87" xr:uid="{5FFC4DAB-F374-41E9-8B47-2EF464C2C536}"/>
+    <hyperlink ref="F244" r:id="rId88" xr:uid="{21768D99-C089-4DC1-A53E-266E758687C5}"/>
+    <hyperlink ref="F245" r:id="rId89" xr:uid="{12D9319F-5A87-4ACB-8631-89B7EB5B7871}"/>
+    <hyperlink ref="F247" r:id="rId90" xr:uid="{3D734675-475D-49CB-AC3A-1AA184658D00}"/>
+    <hyperlink ref="F248" r:id="rId91" xr:uid="{601F76B0-2BDD-4217-83A4-E1D708C84C54}"/>
+    <hyperlink ref="F249" r:id="rId92" xr:uid="{0A1BA194-5A1D-4A17-AE7B-F1DBD179498A}"/>
+    <hyperlink ref="F252" r:id="rId93" xr:uid="{8A58FF55-8B70-4BE0-A7D2-84512CFF69EB}"/>
+    <hyperlink ref="F257" r:id="rId94" xr:uid="{565102C8-B4B3-4CA9-A13D-AA08F0B1F501}"/>
+    <hyperlink ref="F260" r:id="rId95" xr:uid="{888081FC-B79F-4537-A612-589B4AA24A5F}"/>
+    <hyperlink ref="F264" r:id="rId96" xr:uid="{B89A7894-A653-457E-B297-66EEF7E78CCD}"/>
+    <hyperlink ref="F265" r:id="rId97" xr:uid="{C1F38060-8982-4B83-89B9-3ACB71AAE7E9}"/>
+    <hyperlink ref="F266" r:id="rId98" xr:uid="{90A2D3D4-11E9-4E70-9F26-57374F26E828}"/>
+    <hyperlink ref="F267" r:id="rId99" xr:uid="{CE2AC91D-F72D-498F-8D0D-E22DF8700BFD}"/>
+    <hyperlink ref="F268" r:id="rId100" xr:uid="{E35AF51A-834D-4EFC-823F-4026E999DF7A}"/>
+    <hyperlink ref="F269" r:id="rId101" xr:uid="{558DB0B2-17D5-4A39-AAB8-814B18D28642}"/>
+    <hyperlink ref="F273" r:id="rId102" xr:uid="{A613562F-CFC5-4214-AF12-2CFDD342953A}"/>
+    <hyperlink ref="F274" r:id="rId103" xr:uid="{CBD79827-526D-4DFF-97E6-5306C293752C}"/>
+    <hyperlink ref="F277" r:id="rId104" xr:uid="{09E53517-D130-471F-B71B-653DFA8A8955}"/>
+    <hyperlink ref="F276" r:id="rId105" xr:uid="{30A1C381-1EDC-4BFC-804E-FBB45AC51FEF}"/>
+    <hyperlink ref="F278" r:id="rId106" xr:uid="{A26AA755-950A-4B52-9312-83FA946F9EA2}"/>
+    <hyperlink ref="F280" r:id="rId107" xr:uid="{05C39E49-F52C-40AB-B184-32A8BEA8FA7A}"/>
+    <hyperlink ref="F286" r:id="rId108" xr:uid="{6FCC01F3-1F01-4694-8770-C3C00E5E496C}"/>
+    <hyperlink ref="F288" r:id="rId109" xr:uid="{ACDA379B-D785-41F9-A567-FACF7027F155}"/>
+    <hyperlink ref="F289" r:id="rId110" xr:uid="{55184FCA-C9E5-4C87-B518-47BB97CC674F}"/>
+    <hyperlink ref="F292" r:id="rId111" xr:uid="{183A293E-7539-47D2-9CDE-B3563DB11191}"/>
+    <hyperlink ref="F293" r:id="rId112" xr:uid="{A37CFD74-5F70-453B-9C1A-31C32E66D91A}"/>
+    <hyperlink ref="F294" r:id="rId113" xr:uid="{1A424E49-407B-4819-9BAE-BD7020E136C8}"/>
+    <hyperlink ref="F295" r:id="rId114" xr:uid="{16772841-91B4-4063-B41A-59B960FDEFC4}"/>
+    <hyperlink ref="F296" r:id="rId115" xr:uid="{F8E811E4-C56E-4020-8515-CA14E5BC6E3C}"/>
+    <hyperlink ref="F299" r:id="rId116" xr:uid="{8169F733-8E2D-4AC1-9A4F-A49A54D41A52}"/>
+    <hyperlink ref="F302" r:id="rId117" xr:uid="{0CE762D6-744B-40A7-8F98-8AF1053C4C20}"/>
+    <hyperlink ref="F306" r:id="rId118" xr:uid="{091067F1-8D60-40C3-B79B-EDA05B5A7DA4}"/>
+    <hyperlink ref="F307" r:id="rId119" xr:uid="{AC3C0A2F-C850-4DC8-B816-62B521573541}"/>
+    <hyperlink ref="F308" r:id="rId120" xr:uid="{BD4C4423-9801-48B9-BE4A-6FA8B9B411A4}"/>
+    <hyperlink ref="F309" r:id="rId121" xr:uid="{03558391-13D5-417E-8518-5A118844CD95}"/>
+    <hyperlink ref="F312" r:id="rId122" xr:uid="{2005E731-59D7-4620-B28C-434266F6022D}"/>
+    <hyperlink ref="F313" r:id="rId123" xr:uid="{2FD5242C-CF0A-4A63-816A-EA2A83984E64}"/>
+    <hyperlink ref="F314" r:id="rId124" xr:uid="{3123CD08-C684-4CC9-AB12-F9105EA97288}"/>
+    <hyperlink ref="F315" r:id="rId125" xr:uid="{2213C59C-4A61-40A9-A06B-1FEF17A027B0}"/>
+    <hyperlink ref="F316" r:id="rId126" xr:uid="{68B28FC2-AA1F-41B6-9A23-516E9B83B6E0}"/>
+    <hyperlink ref="F318" r:id="rId127" xr:uid="{B5599032-4454-4E2C-A68F-8CFFE50F4FDA}"/>
+    <hyperlink ref="F319" r:id="rId128" xr:uid="{A0B5737A-A70A-4218-B2E1-A76C8720DB56}"/>
+    <hyperlink ref="F320" r:id="rId129" xr:uid="{D4B5840E-77B4-47E2-8436-CD2E572AF2B8}"/>
+    <hyperlink ref="F321" r:id="rId130" xr:uid="{BD67BD55-40E9-45BF-A3F6-8F5115DDB229}"/>
+    <hyperlink ref="F322" r:id="rId131" xr:uid="{006FB328-F8E9-4758-AE01-3843E2E75398}"/>
+    <hyperlink ref="F324" r:id="rId132" xr:uid="{D8274070-5E6A-448F-BE2B-E62287C27B7F}"/>
+    <hyperlink ref="F325" r:id="rId133" xr:uid="{3107A474-1B13-410C-98D5-4BDFF1B318A0}"/>
+    <hyperlink ref="F329" r:id="rId134" xr:uid="{AEE59407-C7BF-4741-8788-B6DE8B5B56F0}"/>
+    <hyperlink ref="F331" r:id="rId135" xr:uid="{9E43F2AF-CA8D-45AD-8AF2-43E79516D8C4}"/>
+    <hyperlink ref="F334" r:id="rId136" xr:uid="{527DB674-2191-4390-A5E3-AF104DB8B4DD}"/>
+    <hyperlink ref="F339" r:id="rId137" xr:uid="{6CBC3A1F-EFB9-4C79-8568-CA7B9F4AE2C5}"/>
+    <hyperlink ref="F349" r:id="rId138" xr:uid="{15A14E1E-9440-4524-8E71-E2F0B928B953}"/>
+    <hyperlink ref="F351" r:id="rId139" xr:uid="{C92EA61B-8F06-42A1-A7F9-7F45453FF60F}"/>
+    <hyperlink ref="F355" r:id="rId140" xr:uid="{8A245E57-176A-4426-987A-230A824E21F5}"/>
+    <hyperlink ref="F362" r:id="rId141" xr:uid="{E66A3719-554E-4E28-86A4-324883D73CAE}"/>
+    <hyperlink ref="F366" r:id="rId142" xr:uid="{7BDE2C38-EC1A-4C17-B1C6-1E4D17FC0EE5}"/>
+    <hyperlink ref="F367" r:id="rId143" xr:uid="{00F24AF7-BECF-42F0-AB31-2C0DED0C37A2}"/>
+    <hyperlink ref="F368" r:id="rId144" xr:uid="{5852A063-4D20-4FBB-B346-BF786AFC86EC}"/>
+    <hyperlink ref="F369" r:id="rId145" xr:uid="{B67214DC-0A47-4AD1-BF86-5DC069815DE1}"/>
+    <hyperlink ref="F374" r:id="rId146" xr:uid="{8299AD99-FFD7-4B97-A788-030B31407DDD}"/>
+    <hyperlink ref="F376" r:id="rId147" xr:uid="{78971510-8CDC-4BF5-AE19-0D07D647D047}"/>
+    <hyperlink ref="F378" r:id="rId148" xr:uid="{A0C94A52-B22E-4392-9DAE-3EA37FFA5A46}"/>
+    <hyperlink ref="F379" r:id="rId149" xr:uid="{3B87B23F-40F6-462E-9110-A5A9A19D2232}"/>
+    <hyperlink ref="F380" r:id="rId150" xr:uid="{292120C3-4914-44B9-9098-59807C6E7C6C}"/>
+    <hyperlink ref="F381" r:id="rId151" xr:uid="{5B5091B4-FEAA-4CAD-8FAF-43B120B259B8}"/>
+    <hyperlink ref="F382" r:id="rId152" xr:uid="{B4A8D738-F438-4B79-8C25-2D43D085BC71}"/>
+    <hyperlink ref="F383" r:id="rId153" xr:uid="{9C2371F9-4C06-48FC-AD5B-9E5916618520}"/>
+    <hyperlink ref="F389" r:id="rId154" xr:uid="{2C42E22B-0DD1-40FA-8493-10406BA7A1D9}"/>
+    <hyperlink ref="F390" r:id="rId155" xr:uid="{70286227-A588-43E1-91FC-1EB348F42574}"/>
+    <hyperlink ref="F392" r:id="rId156" xr:uid="{D1A39FB3-D165-4B56-88B9-CFB02C80378B}"/>
+    <hyperlink ref="F396" r:id="rId157" xr:uid="{86B3426F-8CFE-45AB-9DE6-873C49E7DB80}"/>
+    <hyperlink ref="F397" r:id="rId158" xr:uid="{6F07A94A-75BF-4D0C-A155-1F147D55686D}"/>
+    <hyperlink ref="F398" r:id="rId159" xr:uid="{925770DF-4D55-4F2C-B57F-546C6CF49F83}"/>
+    <hyperlink ref="F402" r:id="rId160" xr:uid="{86833F34-D3B8-49A2-B048-9143D1D268E1}"/>
+    <hyperlink ref="F403" r:id="rId161" xr:uid="{DC475E94-CED6-4041-A19D-421EDEC91083}"/>
+    <hyperlink ref="F404" r:id="rId162" xr:uid="{8CE58332-34FE-45F0-B53E-D28E50ECC3F5}"/>
+    <hyperlink ref="F405" r:id="rId163" xr:uid="{DD0386C7-D589-4779-A82D-1F72C4B6FBDD}"/>
+    <hyperlink ref="F406" r:id="rId164" xr:uid="{BC460B10-00B8-4916-B3EF-7D1ED959A78B}"/>
+    <hyperlink ref="F407" r:id="rId165" xr:uid="{40729791-C768-4D88-821E-9253252FB0F3}"/>
+    <hyperlink ref="F410" r:id="rId166" xr:uid="{BCA7C023-C424-401D-88B3-107FB2ACBF81}"/>
+    <hyperlink ref="F415" r:id="rId167" xr:uid="{43A41B2A-DEFE-495E-997D-ED085CF2FC91}"/>
+    <hyperlink ref="F416" r:id="rId168" xr:uid="{B12F044C-CB46-4CCB-89F1-EB0C8F7EB892}"/>
+    <hyperlink ref="F422" r:id="rId169" xr:uid="{28D016CB-3B77-415C-8166-D13FE68341D1}"/>
+    <hyperlink ref="F423" r:id="rId170" xr:uid="{CD429C9A-749F-491E-9E58-B9CB7A90A2FB}"/>
+    <hyperlink ref="F428" r:id="rId171" xr:uid="{5CC5C5A2-EE60-4284-8128-2E87C488D632}"/>
+    <hyperlink ref="F431" r:id="rId172" xr:uid="{C2BD70BB-F593-4AF0-B6A4-B32D5304C625}"/>
+    <hyperlink ref="F435" r:id="rId173" xr:uid="{F6E6F0EA-9817-4AA3-BC4A-B1ED8E6931ED}"/>
+    <hyperlink ref="F438" r:id="rId174" xr:uid="{5EB5671F-FF63-475A-9238-21AD45B4C5EE}"/>
+    <hyperlink ref="F441" r:id="rId175" xr:uid="{B97349D3-8379-49CF-AB1C-503D2A28FCDC}"/>
+    <hyperlink ref="F448" r:id="rId176" xr:uid="{DCBAF156-741D-4CDD-A1BB-BEE3DCAFC7E4}"/>
+    <hyperlink ref="F455" r:id="rId177" xr:uid="{8B8F94DD-ABB2-4320-920C-216E8ECE661F}"/>
+    <hyperlink ref="F340" r:id="rId178" xr:uid="{A1876CDA-D2D9-4ACE-9E52-75F2A87E4D4F}"/>
+    <hyperlink ref="F459" r:id="rId179" xr:uid="{21AFB719-500D-49EA-9A94-E1F0F8DEAF1D}"/>
+    <hyperlink ref="F462" r:id="rId180" xr:uid="{9FB30793-74F5-4EE1-997B-A29276854B0F}"/>
+    <hyperlink ref="F463" r:id="rId181" xr:uid="{F7D721C1-6EE7-431C-825B-C14B050040BE}"/>
+    <hyperlink ref="F464" r:id="rId182" xr:uid="{E82C3262-E183-4FD0-A624-6B9CBBA13E22}"/>
+    <hyperlink ref="F467" r:id="rId183" xr:uid="{2F3A224E-996D-44F2-BB99-EC5746F0E81D}"/>
+    <hyperlink ref="F470" r:id="rId184" xr:uid="{66281EB3-1C84-4327-8A41-AC8CB05AAABD}"/>
+    <hyperlink ref="F474" r:id="rId185" xr:uid="{9BE712DE-053D-4691-8A07-B0D3C3304A32}"/>
+    <hyperlink ref="F475" r:id="rId186" xr:uid="{97572BBD-E6D2-4CFC-B983-6629083AAA30}"/>
+    <hyperlink ref="F480" r:id="rId187" xr:uid="{F9FBA57F-7D2B-4679-A566-A492ECEF9035}"/>
+    <hyperlink ref="F484" r:id="rId188" xr:uid="{5942006B-880C-4C23-9ED8-EE6DF160CAFC}"/>
+    <hyperlink ref="F485" r:id="rId189" xr:uid="{93B54EDE-1866-4706-A5FE-E39688316329}"/>
+    <hyperlink ref="F491" r:id="rId190" xr:uid="{D1F916D6-B062-4FD4-9C02-9546DAF97B5D}"/>
+    <hyperlink ref="F499" r:id="rId191" xr:uid="{82BB8238-8B3C-44CF-B8DB-8B220659D0F1}"/>
+    <hyperlink ref="F502" r:id="rId192" xr:uid="{BC41CEBA-AAE5-49A0-8216-3B4403811C0B}"/>
+    <hyperlink ref="F506" r:id="rId193" xr:uid="{3ED9D9C9-88BD-4D38-8C17-2147C43DCA41}"/>
+    <hyperlink ref="F507" r:id="rId194" xr:uid="{8EE4BBCE-100C-422D-A8AE-E1855B7531DD}"/>
+    <hyperlink ref="F508" r:id="rId195" xr:uid="{7393F241-1EE0-4975-B705-3BB32A866045}"/>
+    <hyperlink ref="F63" r:id="rId196" xr:uid="{C3D2727A-54A4-4ABC-BE29-C663282CB00F}"/>
+    <hyperlink ref="F65" r:id="rId197" xr:uid="{290EDB11-A937-4642-B4C4-762CABC87A86}"/>
+    <hyperlink ref="F92" r:id="rId198" xr:uid="{7BD3346D-C133-4F85-BA8B-06E893A5AA15}"/>
+    <hyperlink ref="F236" r:id="rId199" xr:uid="{A89FDFBB-71B2-4738-9E20-379D288195B3}"/>
+    <hyperlink ref="F237" r:id="rId200" xr:uid="{71BBAFA0-9838-4AE0-B1A3-8148C5047B22}"/>
+    <hyperlink ref="F430" r:id="rId201" xr:uid="{CE9B73F7-6206-43BE-A0D7-238A375EF8C2}"/>
+    <hyperlink ref="F303" r:id="rId202" xr:uid="{95974537-849E-47AD-A8B3-2D3E2FBBC6C7}"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId217"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId203"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;C&amp;8EC_Not_technical&amp;8
 </oddHeader>
@@ -22286,11 +22215,11 @@
       <c r="B3" s="21"/>
       <c r="C3" s="3"/>
       <c r="D3" s="14" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="E3" s="31"/>
       <c r="F3" s="45" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
